--- a/artfynd/A 27938-2023 artfynd.xlsx
+++ b/artfynd/A 27938-2023 artfynd.xlsx
@@ -675,45 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>126889312</v>
+        <v>126879850</v>
       </c>
       <c r="B2" t="n">
-        <v>91210</v>
+        <v>88722</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5447</v>
+        <v>510</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Kravattensliden, Ång</t>
+          <t>Kravattensliden, Kravattensliden, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>672839</v>
+        <v>672873</v>
       </c>
       <c r="R2" t="n">
-        <v>7058142</v>
+        <v>7058228</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -760,12 +760,12 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Fredrik Wilde</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Fredrik Wilde, Alva Danielsson, Emil Lindgren, Mattias Dalkvist, Elke Blöhbaum, Miriam Schenk, Vilhelm Kroon</t>
+          <t>Fredrik Wilde</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -776,45 +776,45 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126879850</v>
+        <v>126889312</v>
       </c>
       <c r="B3" t="n">
-        <v>88654</v>
+        <v>91284</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>510</v>
+        <v>5447</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Kravattensliden, Kravattensliden, Ång</t>
+          <t>Kravattensliden, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>672873</v>
+        <v>672839</v>
       </c>
       <c r="R3" t="n">
-        <v>7058228</v>
+        <v>7058142</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -861,12 +861,12 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Fredrik Wilde</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Fredrik Wilde</t>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Fredrik Wilde, Alva Danielsson, Emil Lindgren, Mattias Dalkvist, Elke Blöhbaum, Miriam Schenk, Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
@@ -880,7 +880,7 @@
         <v>126889833</v>
       </c>
       <c r="B4" t="n">
-        <v>91210</v>
+        <v>91284</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -981,7 +981,7 @@
         <v>126889402</v>
       </c>
       <c r="B5" t="n">
-        <v>97239</v>
+        <v>97314</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1082,7 +1082,7 @@
         <v>126892811</v>
       </c>
       <c r="B6" t="n">
-        <v>79012</v>
+        <v>79043</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1190,10 +1190,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126892805</v>
+        <v>126889505</v>
       </c>
       <c r="B7" t="n">
-        <v>57657</v>
+        <v>79011</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1201,21 +1201,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,13 +1225,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>672877</v>
+        <v>672864</v>
       </c>
       <c r="R7" t="n">
-        <v>7058189</v>
+        <v>7058181</v>
       </c>
       <c r="S7" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1258,24 +1258,9 @@
           <t>2025-07-24</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>11:15</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-07-24</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>11:15</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Gamla ringhack</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1290,12 +1275,12 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist, Fredrik Wilde, Liam Sebestyén, Alva Danielsson, Elke Blöhbaum, Vilhelm Kroon, Miriam Schenk, Cajsa Björkén, Philipp Weiss, Emil Lindgren</t>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Fredrik Wilde, Alva Danielsson, Emil Lindgren, Mattias Dalkvist, Elke Blöhbaum, Miriam Schenk, Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
@@ -1306,10 +1291,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126889505</v>
+        <v>126892805</v>
       </c>
       <c r="B8" t="n">
-        <v>78980</v>
+        <v>57657</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1317,21 +1302,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1341,13 +1326,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>672864</v>
+        <v>672877</v>
       </c>
       <c r="R8" t="n">
-        <v>7058181</v>
+        <v>7058189</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1374,9 +1359,24 @@
           <t>2025-07-24</t>
         </is>
       </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>11:15</t>
+        </is>
+      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-07-24</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>11:15</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Gamla ringhack</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1391,12 +1391,12 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Fredrik Wilde, Alva Danielsson, Emil Lindgren, Mattias Dalkvist, Elke Blöhbaum, Miriam Schenk, Vilhelm Kroon</t>
+          <t>Mattias Dalkvist, Fredrik Wilde, Liam Sebestyén, Alva Danielsson, Elke Blöhbaum, Vilhelm Kroon, Miriam Schenk, Cajsa Björkén, Philipp Weiss, Emil Lindgren</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
@@ -1410,7 +1410,7 @@
         <v>126889513</v>
       </c>
       <c r="B9" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1511,7 +1511,7 @@
         <v>126891323</v>
       </c>
       <c r="B10" t="n">
-        <v>91263</v>
+        <v>91337</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Liam Sebestyén, Mattias Dalkvist, Miriam Schenk, Fredrik Wilde, Elke Blöhbaum, Emil Lindgren</t>
+          <t>Alva Danielsson, Emil Lindgren, Elke Blöhbaum, Fredrik Wilde, Miriam Schenk, Mattias Dalkvist, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
@@ -1609,10 +1609,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126889493</v>
+        <v>126893729</v>
       </c>
       <c r="B11" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1644,10 +1644,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>672651</v>
+        <v>672603</v>
       </c>
       <c r="R11" t="n">
-        <v>7057972</v>
+        <v>7057959</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1694,12 +1694,12 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Fredrik Wilde, Alva Danielsson, Emil Lindgren, Mattias Dalkvist, Elke Blöhbaum, Miriam Schenk, Vilhelm Kroon</t>
+          <t>Alva Danielsson, Fredrik Wilde, Liam Sebestyén, Elke Blöhbaum, Miriam Schenk, Mattias Dalkvist, Emil Lindgren</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
@@ -1710,10 +1710,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126893729</v>
+        <v>126889493</v>
       </c>
       <c r="B12" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1745,10 +1745,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>672603</v>
+        <v>672651</v>
       </c>
       <c r="R12" t="n">
-        <v>7057959</v>
+        <v>7057972</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1795,12 +1795,12 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Fredrik Wilde, Liam Sebestyén, Elke Blöhbaum, Miriam Schenk, Mattias Dalkvist, Emil Lindgren</t>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Fredrik Wilde, Alva Danielsson, Emil Lindgren, Mattias Dalkvist, Elke Blöhbaum, Miriam Schenk, Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
@@ -1814,7 +1814,7 @@
         <v>126892815</v>
       </c>
       <c r="B13" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2031,7 +2031,7 @@
         <v>126889492</v>
       </c>
       <c r="B15" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2132,7 +2132,7 @@
         <v>126889835</v>
       </c>
       <c r="B16" t="n">
-        <v>91210</v>
+        <v>91284</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2233,7 +2233,7 @@
         <v>126891315</v>
       </c>
       <c r="B17" t="n">
-        <v>98382</v>
+        <v>98457</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2320,7 +2320,7 @@
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Liam Sebestyén, Mattias Dalkvist, Miriam Schenk, Fredrik Wilde, Elke Blöhbaum, Emil Lindgren</t>
+          <t>Alva Danielsson, Emil Lindgren, Elke Blöhbaum, Fredrik Wilde, Miriam Schenk, Mattias Dalkvist, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
@@ -2334,7 +2334,7 @@
         <v>126892810</v>
       </c>
       <c r="B18" t="n">
-        <v>91210</v>
+        <v>91284</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2445,7 +2445,7 @@
         <v>126891131</v>
       </c>
       <c r="B19" t="n">
-        <v>79012</v>
+        <v>79043</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2547,7 +2547,7 @@
         <v>126892808</v>
       </c>
       <c r="B20" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2655,10 +2655,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>126891314</v>
+        <v>126889374</v>
       </c>
       <c r="B21" t="n">
-        <v>80112</v>
+        <v>98457</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2666,34 +2666,48 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6462</v>
+        <v>221952</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Kravattensliden, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>672999</v>
+        <v>672898</v>
       </c>
       <c r="R21" t="n">
-        <v>7058211</v>
+        <v>7058146</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2740,12 +2754,12 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Liam Sebestyén, Mattias Dalkvist, Miriam Schenk, Fredrik Wilde, Elke Blöhbaum, Emil Lindgren</t>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Fredrik Wilde, Alva Danielsson, Emil Lindgren, Mattias Dalkvist, Elke Blöhbaum, Miriam Schenk, Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
@@ -2756,10 +2770,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>126889311</v>
+        <v>126889869</v>
       </c>
       <c r="B22" t="n">
-        <v>91210</v>
+        <v>98353</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2767,21 +2781,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5447</v>
+        <v>219790</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2791,10 +2805,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>672799</v>
+        <v>672855</v>
       </c>
       <c r="R22" t="n">
-        <v>7058086</v>
+        <v>7058116</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2841,12 +2855,12 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Fredrik Wilde, Alva Danielsson, Emil Lindgren, Mattias Dalkvist, Elke Blöhbaum, Miriam Schenk, Vilhelm Kroon</t>
+          <t>Liam Sebestyén, Philipp Weiss, Miriam Schenk, Cajsa Björkén, Fredrik Wilde, Alva Danielsson, Elke Blöhbaum, Vilhelm Kroon, Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
@@ -2857,10 +2871,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>126889370</v>
+        <v>126889311</v>
       </c>
       <c r="B23" t="n">
-        <v>4772</v>
+        <v>91284</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2868,39 +2882,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100299</v>
+        <v>5447</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Kravattensliden, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>672839</v>
+        <v>672799</v>
       </c>
       <c r="R23" t="n">
-        <v>7058141</v>
+        <v>7058086</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2963,10 +2972,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>126889869</v>
+        <v>126891314</v>
       </c>
       <c r="B24" t="n">
-        <v>98278</v>
+        <v>80143</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2974,21 +2983,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>219790</v>
+        <v>6462</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2998,10 +3007,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>672855</v>
+        <v>672999</v>
       </c>
       <c r="R24" t="n">
-        <v>7058116</v>
+        <v>7058211</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3048,12 +3057,12 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Philipp Weiss, Miriam Schenk, Cajsa Björkén, Fredrik Wilde, Alva Danielsson, Elke Blöhbaum, Vilhelm Kroon, Mattias Dalkvist</t>
+          <t>Alva Danielsson, Emil Lindgren, Elke Blöhbaum, Fredrik Wilde, Miriam Schenk, Mattias Dalkvist, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr">
@@ -3064,10 +3073,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>126889374</v>
+        <v>126889370</v>
       </c>
       <c r="B25" t="n">
-        <v>98382</v>
+        <v>4772</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3075,36 +3084,27 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>221952</v>
+        <v>100299</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>överblommad</t>
+          <t>(Kraatz, 1881)</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
@@ -3113,10 +3113,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>672898</v>
+        <v>672839</v>
       </c>
       <c r="R25" t="n">
-        <v>7058146</v>
+        <v>7058141</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3168,7 +3168,7 @@
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Fredrik Wilde, Alva Danielsson, Emil Lindgren, Mattias Dalkvist, Elke Blöhbaum, Miriam Schenk, Vilhelm Kroon</t>
+          <t>Vilhelm Kroon, Miriam Schenk, Elke Blöhbaum, Mattias Dalkvist, Emil Lindgren, Alva Danielsson, Fredrik Wilde, Liam Sebestyén, Cajsa Björkén, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr">
@@ -3179,10 +3179,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>126892816</v>
+        <v>126889502</v>
       </c>
       <c r="B26" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3214,13 +3214,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>672627</v>
+        <v>672801</v>
       </c>
       <c r="R26" t="n">
-        <v>7058024</v>
+        <v>7058095</v>
       </c>
       <c r="S26" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3247,19 +3247,9 @@
           <t>2025-07-24</t>
         </is>
       </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>11:52</t>
-        </is>
-      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-07-24</t>
-        </is>
-      </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>11:52</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3274,12 +3264,12 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist, Fredrik Wilde, Liam Sebestyén, Alva Danielsson, Elke Blöhbaum, Vilhelm Kroon, Miriam Schenk, Cajsa Björkén, Philipp Weiss, Emil Lindgren</t>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Fredrik Wilde, Alva Danielsson, Emil Lindgren, Mattias Dalkvist, Elke Blöhbaum, Miriam Schenk, Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr">
@@ -3293,7 +3283,7 @@
         <v>126891313</v>
       </c>
       <c r="B27" t="n">
-        <v>80112</v>
+        <v>80143</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3380,7 +3370,7 @@
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Liam Sebestyén, Mattias Dalkvist, Miriam Schenk, Fredrik Wilde, Elke Blöhbaum, Emil Lindgren</t>
+          <t>Alva Danielsson, Emil Lindgren, Elke Blöhbaum, Fredrik Wilde, Miriam Schenk, Mattias Dalkvist, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr">
@@ -3500,10 +3490,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>126889502</v>
+        <v>126892816</v>
       </c>
       <c r="B29" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3535,13 +3525,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>672801</v>
+        <v>672627</v>
       </c>
       <c r="R29" t="n">
-        <v>7058095</v>
+        <v>7058024</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3568,9 +3558,19 @@
           <t>2025-07-24</t>
         </is>
       </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>11:52</t>
+        </is>
+      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-07-24</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3585,12 +3585,12 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Fredrik Wilde, Alva Danielsson, Emil Lindgren, Mattias Dalkvist, Elke Blöhbaum, Miriam Schenk, Vilhelm Kroon</t>
+          <t>Mattias Dalkvist, Fredrik Wilde, Liam Sebestyén, Alva Danielsson, Elke Blöhbaum, Vilhelm Kroon, Miriam Schenk, Cajsa Björkén, Philipp Weiss, Emil Lindgren</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr">
@@ -3604,7 +3604,7 @@
         <v>126893730</v>
       </c>
       <c r="B30" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3702,10 +3702,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>126889377</v>
+        <v>126889536</v>
       </c>
       <c r="B31" t="n">
-        <v>98382</v>
+        <v>5176</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3713,36 +3713,27 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>221952</v>
+        <v>100526</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>överblommad</t>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
@@ -3751,10 +3742,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>672810</v>
+        <v>672659</v>
       </c>
       <c r="R31" t="n">
-        <v>7058105</v>
+        <v>7057975</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3817,10 +3808,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>126889536</v>
+        <v>126889377</v>
       </c>
       <c r="B32" t="n">
-        <v>5176</v>
+        <v>98457</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3828,27 +3819,36 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100526</v>
+        <v>221952</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
@@ -3857,10 +3857,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>672659</v>
+        <v>672810</v>
       </c>
       <c r="R32" t="n">
-        <v>7057975</v>
+        <v>7058105</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3926,7 +3926,7 @@
         <v>126891328</v>
       </c>
       <c r="B33" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4013,7 +4013,7 @@
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Liam Sebestyén, Mattias Dalkvist, Miriam Schenk, Fredrik Wilde, Elke Blöhbaum, Emil Lindgren</t>
+          <t>Alva Danielsson, Emil Lindgren, Elke Blöhbaum, Fredrik Wilde, Miriam Schenk, Mattias Dalkvist, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr">
@@ -4027,7 +4027,7 @@
         <v>126893692</v>
       </c>
       <c r="B34" t="n">
-        <v>91245</v>
+        <v>91319</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4133,10 +4133,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>126891134</v>
+        <v>126889834</v>
       </c>
       <c r="B35" t="n">
-        <v>80112</v>
+        <v>91284</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4144,21 +4144,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6462</v>
+        <v>5447</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4168,13 +4168,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>673029</v>
+        <v>672819</v>
       </c>
       <c r="R35" t="n">
-        <v>7058247</v>
+        <v>7058089</v>
       </c>
       <c r="S35" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4218,12 +4218,12 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Miriam Schenk</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Miriam Schenk, Cajsa Björkén, Fredrik Wilde, Philipp Weiss, Mattias Dalkvist, Vilhelm Kroon, Liam Sebestyén, Emil Lindgren, Alva Danielsson</t>
+          <t>Liam Sebestyén, Philipp Weiss, Miriam Schenk, Cajsa Björkén, Fredrik Wilde, Alva Danielsson, Elke Blöhbaum, Vilhelm Kroon, Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr">
@@ -4234,10 +4234,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>126889834</v>
+        <v>126891134</v>
       </c>
       <c r="B36" t="n">
-        <v>91210</v>
+        <v>80143</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4245,21 +4245,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>5447</v>
+        <v>6462</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4269,13 +4269,13 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>672819</v>
+        <v>673029</v>
       </c>
       <c r="R36" t="n">
-        <v>7058089</v>
+        <v>7058247</v>
       </c>
       <c r="S36" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4319,12 +4319,12 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Miriam Schenk</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Philipp Weiss, Miriam Schenk, Cajsa Björkén, Fredrik Wilde, Alva Danielsson, Elke Blöhbaum, Vilhelm Kroon, Mattias Dalkvist</t>
+          <t>Miriam Schenk, Cajsa Björkén, Fredrik Wilde, Philipp Weiss, Mattias Dalkvist, Vilhelm Kroon, Liam Sebestyén, Emil Lindgren, Alva Danielsson</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr">
@@ -4335,10 +4335,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>126890308</v>
+        <v>126892814</v>
       </c>
       <c r="B37" t="n">
-        <v>78980</v>
+        <v>79043</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4346,21 +4346,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4370,13 +4370,13 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>672880</v>
+        <v>672659</v>
       </c>
       <c r="R37" t="n">
-        <v>7058209</v>
+        <v>7058027</v>
       </c>
       <c r="S37" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4403,9 +4403,19 @@
           <t>2025-07-24</t>
         </is>
       </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>11:51</t>
+        </is>
+      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-07-24</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4420,12 +4430,12 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon, Cajsa Björkén, Fredrik Wilde, Mattias Dalkvist, Philipp Weiss, Miriam Schenk, Liam Sebestyén, Alva Danielsson, Emil Lindgren</t>
+          <t>Mattias Dalkvist, Fredrik Wilde, Liam Sebestyén, Alva Danielsson, Elke Blöhbaum, Vilhelm Kroon, Miriam Schenk, Cajsa Björkén, Philipp Weiss, Emil Lindgren</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr">
@@ -4439,7 +4449,7 @@
         <v>126892813</v>
       </c>
       <c r="B38" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4547,10 +4557,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>126891320</v>
+        <v>126890308</v>
       </c>
       <c r="B39" t="n">
-        <v>80083</v>
+        <v>79011</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4558,21 +4568,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4582,13 +4592,13 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>672929</v>
+        <v>672880</v>
       </c>
       <c r="R39" t="n">
-        <v>7058203</v>
+        <v>7058209</v>
       </c>
       <c r="S39" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4632,12 +4642,12 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Liam Sebestyén, Mattias Dalkvist, Miriam Schenk, Fredrik Wilde, Elke Blöhbaum, Emil Lindgren</t>
+          <t>Liam Sebestyén, Miriam Schenk, Philipp Weiss, Mattias Dalkvist, Fredrik Wilde, Cajsa Björkén, Vilhelm Kroon, Alva Danielsson, Emil Lindgren</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr">
@@ -4648,10 +4658,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>126892814</v>
+        <v>126891320</v>
       </c>
       <c r="B40" t="n">
-        <v>79012</v>
+        <v>80114</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4659,21 +4669,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>185</v>
+        <v>6458</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4683,13 +4693,13 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>672659</v>
+        <v>672929</v>
       </c>
       <c r="R40" t="n">
-        <v>7058027</v>
+        <v>7058203</v>
       </c>
       <c r="S40" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4716,19 +4726,9 @@
           <t>2025-07-24</t>
         </is>
       </c>
-      <c r="Z40" t="inlineStr">
-        <is>
-          <t>11:51</t>
-        </is>
-      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-07-24</t>
-        </is>
-      </c>
-      <c r="AB40" t="inlineStr">
-        <is>
-          <t>11:51</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4743,12 +4743,12 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist, Fredrik Wilde, Liam Sebestyén, Alva Danielsson, Elke Blöhbaum, Vilhelm Kroon, Miriam Schenk, Cajsa Björkén, Philipp Weiss, Emil Lindgren</t>
+          <t>Alva Danielsson, Emil Lindgren, Elke Blöhbaum, Fredrik Wilde, Miriam Schenk, Mattias Dalkvist, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr">
@@ -4762,7 +4762,7 @@
         <v>126893847</v>
       </c>
       <c r="B41" t="n">
-        <v>80083</v>
+        <v>80114</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4867,7 +4867,7 @@
         <v>126880507</v>
       </c>
       <c r="B42" t="n">
-        <v>82792</v>
+        <v>82852</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4968,7 +4968,7 @@
         <v>126892804</v>
       </c>
       <c r="B43" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5076,52 +5076,45 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>126893671</v>
+        <v>126889506</v>
       </c>
       <c r="B44" t="n">
-        <v>91210</v>
+        <v>79011</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="J44" t="inlineStr"/>
-      <c r="K44" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Kravattensliden , Ång</t>
+          <t>Kravattensliden, Ång</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>672808</v>
+        <v>672889</v>
       </c>
       <c r="R44" t="n">
-        <v>7058090</v>
+        <v>7058145</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5162,19 +5155,18 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
-      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Emil Lindgren</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Emil Lindgren</t>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Fredrik Wilde, Alva Danielsson, Emil Lindgren, Mattias Dalkvist, Elke Blöhbaum, Miriam Schenk, Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr">
@@ -5185,45 +5177,52 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>126889506</v>
+        <v>126893671</v>
       </c>
       <c r="B45" t="n">
-        <v>78980</v>
+        <v>91284</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="J45" t="inlineStr"/>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Kravattensliden, Ång</t>
+          <t>Kravattensliden , Ång</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>672889</v>
+        <v>672808</v>
       </c>
       <c r="R45" t="n">
-        <v>7058145</v>
+        <v>7058090</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5264,18 +5263,19 @@
       <c r="AE45" t="b">
         <v>0</v>
       </c>
+      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Emil Lindgren</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Fredrik Wilde, Alva Danielsson, Emil Lindgren, Mattias Dalkvist, Elke Blöhbaum, Miriam Schenk, Vilhelm Kroon</t>
+          <t>Emil Lindgren</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr">
@@ -5289,7 +5289,7 @@
         <v>126891321</v>
       </c>
       <c r="B46" t="n">
-        <v>80083</v>
+        <v>80114</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5376,7 +5376,7 @@
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Liam Sebestyén, Mattias Dalkvist, Miriam Schenk, Fredrik Wilde, Elke Blöhbaum, Emil Lindgren</t>
+          <t>Alva Danielsson, Emil Lindgren, Elke Blöhbaum, Fredrik Wilde, Miriam Schenk, Mattias Dalkvist, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr">
@@ -5387,10 +5387,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>126890311</v>
+        <v>126890305</v>
       </c>
       <c r="B47" t="n">
-        <v>88654</v>
+        <v>79011</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5398,21 +5398,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>510</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5422,10 +5422,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>673023</v>
+        <v>672724</v>
       </c>
       <c r="R47" t="n">
-        <v>7058218</v>
+        <v>7058075</v>
       </c>
       <c r="S47" t="n">
         <v>15</v>
@@ -5477,7 +5477,7 @@
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon, Cajsa Björkén, Fredrik Wilde, Mattias Dalkvist, Philipp Weiss, Miriam Schenk, Liam Sebestyén, Alva Danielsson, Emil Lindgren</t>
+          <t>Liam Sebestyén, Miriam Schenk, Philipp Weiss, Mattias Dalkvist, Fredrik Wilde, Cajsa Björkén, Vilhelm Kroon, Alva Danielsson, Emil Lindgren</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr">
@@ -5488,10 +5488,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>126889494</v>
+        <v>126890311</v>
       </c>
       <c r="B48" t="n">
-        <v>78980</v>
+        <v>88722</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5499,21 +5499,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>510</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5523,13 +5523,13 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>672657</v>
+        <v>673023</v>
       </c>
       <c r="R48" t="n">
-        <v>7057974</v>
+        <v>7058218</v>
       </c>
       <c r="S48" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5573,12 +5573,12 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Fredrik Wilde, Alva Danielsson, Emil Lindgren, Mattias Dalkvist, Elke Blöhbaum, Miriam Schenk, Vilhelm Kroon</t>
+          <t>Liam Sebestyén, Miriam Schenk, Philipp Weiss, Mattias Dalkvist, Fredrik Wilde, Cajsa Björkén, Vilhelm Kroon, Alva Danielsson, Emil Lindgren</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr">
@@ -5589,10 +5589,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>126890305</v>
+        <v>126889494</v>
       </c>
       <c r="B49" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5624,13 +5624,13 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>672724</v>
+        <v>672657</v>
       </c>
       <c r="R49" t="n">
-        <v>7058075</v>
+        <v>7057974</v>
       </c>
       <c r="S49" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5674,12 +5674,12 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon, Cajsa Björkén, Fredrik Wilde, Mattias Dalkvist, Philipp Weiss, Miriam Schenk, Liam Sebestyén, Alva Danielsson, Emil Lindgren</t>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Fredrik Wilde, Alva Danielsson, Emil Lindgren, Mattias Dalkvist, Elke Blöhbaum, Miriam Schenk, Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr">
@@ -5693,7 +5693,7 @@
         <v>126889503</v>
       </c>
       <c r="B50" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5794,7 +5794,7 @@
         <v>126889856</v>
       </c>
       <c r="B51" t="n">
-        <v>80083</v>
+        <v>80114</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5895,7 +5895,7 @@
         <v>126889837</v>
       </c>
       <c r="B52" t="n">
-        <v>91210</v>
+        <v>91284</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5993,10 +5993,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>126879684</v>
+        <v>126889862</v>
       </c>
       <c r="B53" t="n">
-        <v>78980</v>
+        <v>91337</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6004,34 +6004,34 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Kravattensliden, Kravattensliden, Ång</t>
+          <t>Kravattensliden, Ång</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>672895</v>
+        <v>672981</v>
       </c>
       <c r="R53" t="n">
-        <v>7058223</v>
+        <v>7058264</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6078,12 +6078,12 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Fredrik Wilde</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Fredrik Wilde</t>
+          <t>Liam Sebestyén, Philipp Weiss, Miriam Schenk, Cajsa Björkén, Fredrik Wilde, Alva Danielsson, Elke Blöhbaum, Vilhelm Kroon, Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr">
@@ -6094,10 +6094,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>126889862</v>
+        <v>126879684</v>
       </c>
       <c r="B54" t="n">
-        <v>91263</v>
+        <v>79011</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6105,34 +6105,34 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Kravattensliden, Ång</t>
+          <t>Kravattensliden, Kravattensliden, Ång</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>672981</v>
+        <v>672895</v>
       </c>
       <c r="R54" t="n">
-        <v>7058264</v>
+        <v>7058223</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6179,12 +6179,12 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Fredrik Wilde</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Philipp Weiss, Miriam Schenk, Cajsa Björkén, Fredrik Wilde, Alva Danielsson, Elke Blöhbaum, Vilhelm Kroon, Mattias Dalkvist</t>
+          <t>Fredrik Wilde</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr">
@@ -6198,7 +6198,7 @@
         <v>126891325</v>
       </c>
       <c r="B55" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6285,7 +6285,7 @@
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Liam Sebestyén, Mattias Dalkvist, Miriam Schenk, Fredrik Wilde, Elke Blöhbaum, Emil Lindgren</t>
+          <t>Alva Danielsson, Emil Lindgren, Elke Blöhbaum, Fredrik Wilde, Miriam Schenk, Mattias Dalkvist, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr">
@@ -6299,7 +6299,7 @@
         <v>126893733</v>
       </c>
       <c r="B56" t="n">
-        <v>98278</v>
+        <v>98353</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6397,10 +6397,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>126889504</v>
+        <v>126879133</v>
       </c>
       <c r="B57" t="n">
-        <v>78980</v>
+        <v>79043</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6408,34 +6408,34 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Kravattensliden, Ång</t>
+          <t>Kravattensliden, Kravattensliden, Ång</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>672853</v>
+        <v>673041</v>
       </c>
       <c r="R57" t="n">
-        <v>7058173</v>
+        <v>7058262</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6482,12 +6482,12 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Fredrik Wilde</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Fredrik Wilde, Alva Danielsson, Emil Lindgren, Mattias Dalkvist, Elke Blöhbaum, Miriam Schenk, Vilhelm Kroon</t>
+          <t>Fredrik Wilde</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr">
@@ -6498,10 +6498,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>126879133</v>
+        <v>126892806</v>
       </c>
       <c r="B58" t="n">
-        <v>79012</v>
+        <v>79011</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6509,34 +6509,34 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Kravattensliden, Kravattensliden, Ång</t>
+          <t>Kravattensliden, Ång</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>673041</v>
+        <v>672883</v>
       </c>
       <c r="R58" t="n">
-        <v>7058262</v>
+        <v>7058166</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6566,9 +6566,19 @@
           <t>2025-07-24</t>
         </is>
       </c>
+      <c r="Z58" t="inlineStr">
+        <is>
+          <t>11:18</t>
+        </is>
+      </c>
       <c r="AA58" t="inlineStr">
         <is>
           <t>2025-07-24</t>
+        </is>
+      </c>
+      <c r="AB58" t="inlineStr">
+        <is>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6583,12 +6593,12 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Fredrik Wilde</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Fredrik Wilde</t>
+          <t>Mattias Dalkvist, Fredrik Wilde, Liam Sebestyén, Alva Danielsson, Elke Blöhbaum, Vilhelm Kroon, Miriam Schenk, Cajsa Björkén, Philipp Weiss, Emil Lindgren</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr">
@@ -6599,10 +6609,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>126892806</v>
+        <v>126889504</v>
       </c>
       <c r="B59" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6634,10 +6644,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>672883</v>
+        <v>672853</v>
       </c>
       <c r="R59" t="n">
-        <v>7058166</v>
+        <v>7058173</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6667,19 +6677,9 @@
           <t>2025-07-24</t>
         </is>
       </c>
-      <c r="Z59" t="inlineStr">
-        <is>
-          <t>11:18</t>
-        </is>
-      </c>
       <c r="AA59" t="inlineStr">
         <is>
           <t>2025-07-24</t>
-        </is>
-      </c>
-      <c r="AB59" t="inlineStr">
-        <is>
-          <t>11:18</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6694,12 +6694,12 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist, Fredrik Wilde, Liam Sebestyén, Alva Danielsson, Elke Blöhbaum, Vilhelm Kroon, Miriam Schenk, Cajsa Björkén, Philipp Weiss, Emil Lindgren</t>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Fredrik Wilde, Alva Danielsson, Emil Lindgren, Mattias Dalkvist, Elke Blöhbaum, Miriam Schenk, Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr">
@@ -6710,10 +6710,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>126880199</v>
+        <v>126892812</v>
       </c>
       <c r="B60" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6739,24 +6739,19 @@
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
-      <c r="K60" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Kravattensliden, Kravattensliden, Ång</t>
+          <t>Kravattensliden, Ång</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>672894</v>
+        <v>672685</v>
       </c>
       <c r="R60" t="n">
-        <v>7058198</v>
+        <v>7058010</v>
       </c>
       <c r="S60" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -6783,9 +6778,19 @@
           <t>2025-07-24</t>
         </is>
       </c>
+      <c r="Z60" t="inlineStr">
+        <is>
+          <t>11:41</t>
+        </is>
+      </c>
       <c r="AA60" t="inlineStr">
         <is>
           <t>2025-07-24</t>
+        </is>
+      </c>
+      <c r="AB60" t="inlineStr">
+        <is>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6800,12 +6805,12 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Fredrik Wilde</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Fredrik Wilde</t>
+          <t>Mattias Dalkvist, Fredrik Wilde, Liam Sebestyén, Alva Danielsson, Elke Blöhbaum, Vilhelm Kroon, Miriam Schenk, Cajsa Björkén, Philipp Weiss, Emil Lindgren</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr">
@@ -6816,32 +6821,32 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>126890296</v>
+        <v>126892809</v>
       </c>
       <c r="B61" t="n">
-        <v>80112</v>
+        <v>79011</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6851,13 +6856,13 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>673025</v>
+        <v>672831</v>
       </c>
       <c r="R61" t="n">
-        <v>7058244</v>
+        <v>7058091</v>
       </c>
       <c r="S61" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -6884,9 +6889,19 @@
           <t>2025-07-24</t>
         </is>
       </c>
+      <c r="Z61" t="inlineStr">
+        <is>
+          <t>11:32</t>
+        </is>
+      </c>
       <c r="AA61" t="inlineStr">
         <is>
           <t>2025-07-24</t>
+        </is>
+      </c>
+      <c r="AB61" t="inlineStr">
+        <is>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -6901,12 +6916,12 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon, Cajsa Björkén, Fredrik Wilde, Mattias Dalkvist, Philipp Weiss, Miriam Schenk, Liam Sebestyén, Alva Danielsson, Emil Lindgren</t>
+          <t>Mattias Dalkvist, Fredrik Wilde, Liam Sebestyén, Alva Danielsson, Elke Blöhbaum, Vilhelm Kroon, Miriam Schenk, Cajsa Björkén, Philipp Weiss, Emil Lindgren</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr">
@@ -6917,32 +6932,32 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>126892812</v>
+        <v>126890296</v>
       </c>
       <c r="B62" t="n">
-        <v>78980</v>
+        <v>80143</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6952,13 +6967,13 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>672685</v>
+        <v>673025</v>
       </c>
       <c r="R62" t="n">
-        <v>7058010</v>
+        <v>7058244</v>
       </c>
       <c r="S62" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -6985,19 +7000,9 @@
           <t>2025-07-24</t>
         </is>
       </c>
-      <c r="Z62" t="inlineStr">
-        <is>
-          <t>11:41</t>
-        </is>
-      </c>
       <c r="AA62" t="inlineStr">
         <is>
           <t>2025-07-24</t>
-        </is>
-      </c>
-      <c r="AB62" t="inlineStr">
-        <is>
-          <t>11:41</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7012,12 +7017,12 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist, Fredrik Wilde, Liam Sebestyén, Alva Danielsson, Elke Blöhbaum, Vilhelm Kroon, Miriam Schenk, Cajsa Björkén, Philipp Weiss, Emil Lindgren</t>
+          <t>Vilhelm Kroon, Cajsa Björkén, Fredrik Wilde, Mattias Dalkvist, Philipp Weiss, Miriam Schenk, Liam Sebestyén, Alva Danielsson, Emil Lindgren</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr">
@@ -7028,10 +7033,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>126892809</v>
+        <v>126880199</v>
       </c>
       <c r="B63" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7057,19 +7062,24 @@
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Kravattensliden, Ång</t>
+          <t>Kravattensliden, Kravattensliden, Ång</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>672831</v>
+        <v>672894</v>
       </c>
       <c r="R63" t="n">
-        <v>7058091</v>
+        <v>7058198</v>
       </c>
       <c r="S63" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7096,19 +7106,9 @@
           <t>2025-07-24</t>
         </is>
       </c>
-      <c r="Z63" t="inlineStr">
-        <is>
-          <t>11:32</t>
-        </is>
-      </c>
       <c r="AA63" t="inlineStr">
         <is>
           <t>2025-07-24</t>
-        </is>
-      </c>
-      <c r="AB63" t="inlineStr">
-        <is>
-          <t>11:32</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7123,12 +7123,12 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Fredrik Wilde</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist, Fredrik Wilde, Liam Sebestyén, Alva Danielsson, Elke Blöhbaum, Vilhelm Kroon, Miriam Schenk, Cajsa Björkén, Philipp Weiss, Emil Lindgren</t>
+          <t>Fredrik Wilde</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr">
@@ -7139,45 +7139,54 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>126880532</v>
+        <v>126879033</v>
       </c>
       <c r="B64" t="n">
-        <v>80112</v>
+        <v>79043</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6462</v>
+        <v>185</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr"/>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P64" t="inlineStr">
         <is>
           <t>Kravattensliden, Kravattensliden, Ång</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>672863</v>
+        <v>673046</v>
       </c>
       <c r="R64" t="n">
-        <v>7058124</v>
+        <v>7058286</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7240,54 +7249,45 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>126879033</v>
+        <v>126891312</v>
       </c>
       <c r="B65" t="n">
-        <v>79012</v>
+        <v>91284</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>185</v>
+        <v>5447</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J65" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Kravattensliden, Kravattensliden, Ång</t>
+          <t>Kravattensliden, Ång</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>673046</v>
+        <v>673027</v>
       </c>
       <c r="R65" t="n">
-        <v>7058286</v>
+        <v>7058282</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7334,12 +7334,12 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Fredrik Wilde</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Fredrik Wilde</t>
+          <t>Alva Danielsson, Emil Lindgren, Elke Blöhbaum, Fredrik Wilde, Miriam Schenk, Mattias Dalkvist, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr">
@@ -7353,7 +7353,7 @@
         <v>126879425</v>
       </c>
       <c r="B66" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7451,50 +7451,45 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>126889382</v>
+        <v>126880532</v>
       </c>
       <c r="B67" t="n">
-        <v>57654</v>
+        <v>80143</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>100049</v>
+        <v>6462</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
-      <c r="M67" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Kravattensliden, Ång</t>
+          <t>Kravattensliden, Kravattensliden, Ång</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>672838</v>
+        <v>672863</v>
       </c>
       <c r="R67" t="n">
-        <v>7058134</v>
+        <v>7058124</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7541,12 +7536,12 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Fredrik Wilde</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Fredrik Wilde, Alva Danielsson, Emil Lindgren, Mattias Dalkvist, Elke Blöhbaum, Miriam Schenk, Vilhelm Kroon</t>
+          <t>Fredrik Wilde</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr">
@@ -7557,45 +7552,50 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>126891312</v>
+        <v>126889382</v>
       </c>
       <c r="B68" t="n">
-        <v>91210</v>
+        <v>57654</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>5447</v>
+        <v>100049</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P68" t="inlineStr">
         <is>
           <t>Kravattensliden, Ång</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>673027</v>
+        <v>672838</v>
       </c>
       <c r="R68" t="n">
-        <v>7058282</v>
+        <v>7058134</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7642,12 +7642,12 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Liam Sebestyén, Mattias Dalkvist, Miriam Schenk, Fredrik Wilde, Elke Blöhbaum, Emil Lindgren</t>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Fredrik Wilde, Alva Danielsson, Emil Lindgren, Mattias Dalkvist, Elke Blöhbaum, Miriam Schenk, Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr">
@@ -7658,32 +7658,32 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>126890370</v>
+        <v>126890401</v>
       </c>
       <c r="B69" t="n">
-        <v>80112</v>
+        <v>79011</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7693,10 +7693,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>672554</v>
+        <v>672705</v>
       </c>
       <c r="R69" t="n">
-        <v>7058145</v>
+        <v>7058080</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7759,10 +7759,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>126890401</v>
+        <v>126890408</v>
       </c>
       <c r="B70" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7794,10 +7794,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>672705</v>
+        <v>672874</v>
       </c>
       <c r="R70" t="n">
-        <v>7058080</v>
+        <v>7058313</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7860,32 +7860,32 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>126890408</v>
+        <v>126890370</v>
       </c>
       <c r="B71" t="n">
-        <v>78980</v>
+        <v>80143</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7895,10 +7895,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>672874</v>
+        <v>672554</v>
       </c>
       <c r="R71" t="n">
-        <v>7058313</v>
+        <v>7058145</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7964,7 +7964,7 @@
         <v>126890405</v>
       </c>
       <c r="B72" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8065,7 +8065,7 @@
         <v>126890409</v>
       </c>
       <c r="B73" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8163,10 +8163,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>126890387</v>
+        <v>126890407</v>
       </c>
       <c r="B74" t="n">
-        <v>80083</v>
+        <v>79011</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8174,21 +8174,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8198,10 +8198,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>672556</v>
+        <v>672859</v>
       </c>
       <c r="R74" t="n">
-        <v>7058143</v>
+        <v>7058290</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8264,10 +8264,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>126890407</v>
+        <v>126890387</v>
       </c>
       <c r="B75" t="n">
-        <v>78980</v>
+        <v>80114</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8275,21 +8275,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8299,10 +8299,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>672859</v>
+        <v>672556</v>
       </c>
       <c r="R75" t="n">
-        <v>7058290</v>
+        <v>7058143</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8368,7 +8368,7 @@
         <v>126890404</v>
       </c>
       <c r="B76" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8469,7 +8469,7 @@
         <v>126890354</v>
       </c>
       <c r="B77" t="n">
-        <v>79012</v>
+        <v>79043</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8570,7 +8570,7 @@
         <v>126890353</v>
       </c>
       <c r="B78" t="n">
-        <v>79012</v>
+        <v>79043</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8671,7 +8671,7 @@
         <v>126890349</v>
       </c>
       <c r="B79" t="n">
-        <v>79012</v>
+        <v>79043</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8772,7 +8772,7 @@
         <v>126890348</v>
       </c>
       <c r="B80" t="n">
-        <v>79012</v>
+        <v>79043</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8873,7 +8873,7 @@
         <v>126890351</v>
       </c>
       <c r="B81" t="n">
-        <v>79012</v>
+        <v>79043</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8974,7 +8974,7 @@
         <v>126890350</v>
       </c>
       <c r="B82" t="n">
-        <v>79012</v>
+        <v>79043</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9075,7 +9075,7 @@
         <v>126890416</v>
       </c>
       <c r="B83" t="n">
-        <v>80118</v>
+        <v>80149</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9176,7 +9176,7 @@
         <v>126890403</v>
       </c>
       <c r="B84" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9277,7 +9277,7 @@
         <v>126890352</v>
       </c>
       <c r="B85" t="n">
-        <v>79012</v>
+        <v>79043</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>

--- a/artfynd/A 27938-2023 artfynd.xlsx
+++ b/artfynd/A 27938-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126879850</v>
       </c>
       <c r="B2" t="n">
-        <v>88722</v>
+        <v>88728</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>126889312</v>
       </c>
       <c r="B3" t="n">
-        <v>91284</v>
+        <v>91290</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -880,7 +880,7 @@
         <v>126889833</v>
       </c>
       <c r="B4" t="n">
-        <v>91284</v>
+        <v>91290</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -981,7 +981,7 @@
         <v>126889402</v>
       </c>
       <c r="B5" t="n">
-        <v>97314</v>
+        <v>97320</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1082,7 +1082,7 @@
         <v>126892811</v>
       </c>
       <c r="B6" t="n">
-        <v>79043</v>
+        <v>79046</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1179,7 +1179,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist, Fredrik Wilde, Liam Sebestyén, Alva Danielsson, Elke Blöhbaum, Vilhelm Kroon, Miriam Schenk, Cajsa Björkén, Philipp Weiss, Emil Lindgren</t>
+          <t>Mattias Dalkvist, Fredrik Wilde, Emil Lindgren, Philipp Weiss, Cajsa Björkén, Miriam Schenk, Vilhelm Kroon, Elke Blöhbaum, Alva Danielsson, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
@@ -1190,10 +1190,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126889505</v>
+        <v>126892805</v>
       </c>
       <c r="B7" t="n">
-        <v>79011</v>
+        <v>57657</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1201,21 +1201,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,13 +1225,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>672864</v>
+        <v>672877</v>
       </c>
       <c r="R7" t="n">
-        <v>7058181</v>
+        <v>7058189</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1258,9 +1258,24 @@
           <t>2025-07-24</t>
         </is>
       </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>11:15</t>
+        </is>
+      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-07-24</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>11:15</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Gamla ringhack</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1275,12 +1290,12 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Fredrik Wilde, Alva Danielsson, Emil Lindgren, Mattias Dalkvist, Elke Blöhbaum, Miriam Schenk, Vilhelm Kroon</t>
+          <t>Mattias Dalkvist, Fredrik Wilde, Emil Lindgren, Philipp Weiss, Cajsa Björkén, Miriam Schenk, Vilhelm Kroon, Elke Blöhbaum, Alva Danielsson, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
@@ -1291,10 +1306,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126892805</v>
+        <v>126889505</v>
       </c>
       <c r="B8" t="n">
-        <v>57657</v>
+        <v>79014</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1302,21 +1317,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1326,13 +1341,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>672877</v>
+        <v>672864</v>
       </c>
       <c r="R8" t="n">
-        <v>7058189</v>
+        <v>7058181</v>
       </c>
       <c r="S8" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1359,24 +1374,9 @@
           <t>2025-07-24</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>11:15</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-07-24</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>11:15</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Gamla ringhack</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1391,12 +1391,12 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist, Fredrik Wilde, Liam Sebestyén, Alva Danielsson, Elke Blöhbaum, Vilhelm Kroon, Miriam Schenk, Cajsa Björkén, Philipp Weiss, Emil Lindgren</t>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Fredrik Wilde, Alva Danielsson, Emil Lindgren, Mattias Dalkvist, Elke Blöhbaum, Miriam Schenk, Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
@@ -1407,10 +1407,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126889513</v>
+        <v>126891323</v>
       </c>
       <c r="B9" t="n">
-        <v>79011</v>
+        <v>91343</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1418,21 +1418,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1442,10 +1442,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>673038</v>
+        <v>672897</v>
       </c>
       <c r="R9" t="n">
-        <v>7058279</v>
+        <v>7058210</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1492,12 +1492,12 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Fredrik Wilde, Alva Danielsson, Emil Lindgren, Mattias Dalkvist, Elke Blöhbaum, Miriam Schenk, Vilhelm Kroon</t>
+          <t>Alva Danielsson, Liam Sebestyén, Mattias Dalkvist, Miriam Schenk, Fredrik Wilde, Elke Blöhbaum, Emil Lindgren</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
@@ -1508,10 +1508,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126891323</v>
+        <v>126889513</v>
       </c>
       <c r="B10" t="n">
-        <v>91337</v>
+        <v>79014</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1519,21 +1519,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1543,10 +1543,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>672897</v>
+        <v>673038</v>
       </c>
       <c r="R10" t="n">
-        <v>7058210</v>
+        <v>7058279</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1593,12 +1593,12 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Emil Lindgren, Elke Blöhbaum, Fredrik Wilde, Miriam Schenk, Mattias Dalkvist, Liam Sebestyén</t>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Fredrik Wilde, Alva Danielsson, Emil Lindgren, Mattias Dalkvist, Elke Blöhbaum, Miriam Schenk, Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
@@ -1612,7 +1612,7 @@
         <v>126893729</v>
       </c>
       <c r="B11" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1713,7 +1713,7 @@
         <v>126889493</v>
       </c>
       <c r="B12" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1814,7 +1814,7 @@
         <v>126892815</v>
       </c>
       <c r="B13" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1911,7 +1911,7 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist, Fredrik Wilde, Liam Sebestyén, Alva Danielsson, Elke Blöhbaum, Vilhelm Kroon, Miriam Schenk, Cajsa Björkén, Philipp Weiss, Emil Lindgren</t>
+          <t>Mattias Dalkvist, Fredrik Wilde, Emil Lindgren, Philipp Weiss, Cajsa Björkén, Miriam Schenk, Vilhelm Kroon, Elke Blöhbaum, Alva Danielsson, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
@@ -2028,32 +2028,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126889492</v>
+        <v>126889835</v>
       </c>
       <c r="B15" t="n">
-        <v>79011</v>
+        <v>91290</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2063,10 +2063,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>672638</v>
+        <v>672843</v>
       </c>
       <c r="R15" t="n">
-        <v>7057953</v>
+        <v>7058124</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2113,12 +2113,12 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Fredrik Wilde, Alva Danielsson, Emil Lindgren, Mattias Dalkvist, Elke Blöhbaum, Miriam Schenk, Vilhelm Kroon</t>
+          <t>Liam Sebestyén, Philipp Weiss, Miriam Schenk, Cajsa Björkén, Fredrik Wilde, Alva Danielsson, Elke Blöhbaum, Vilhelm Kroon, Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
@@ -2129,32 +2129,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>126889835</v>
+        <v>126889492</v>
       </c>
       <c r="B16" t="n">
-        <v>91284</v>
+        <v>79014</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2164,10 +2164,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>672843</v>
+        <v>672638</v>
       </c>
       <c r="R16" t="n">
-        <v>7058124</v>
+        <v>7057953</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2214,12 +2214,12 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Philipp Weiss, Miriam Schenk, Cajsa Björkén, Fredrik Wilde, Alva Danielsson, Elke Blöhbaum, Vilhelm Kroon, Mattias Dalkvist</t>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Fredrik Wilde, Alva Danielsson, Emil Lindgren, Mattias Dalkvist, Elke Blöhbaum, Miriam Schenk, Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
@@ -2233,7 +2233,7 @@
         <v>126891315</v>
       </c>
       <c r="B17" t="n">
-        <v>98457</v>
+        <v>98463</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2320,7 +2320,7 @@
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Emil Lindgren, Elke Blöhbaum, Fredrik Wilde, Miriam Schenk, Mattias Dalkvist, Liam Sebestyén</t>
+          <t>Alva Danielsson, Liam Sebestyén, Mattias Dalkvist, Miriam Schenk, Fredrik Wilde, Elke Blöhbaum, Emil Lindgren</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
@@ -2334,7 +2334,7 @@
         <v>126892810</v>
       </c>
       <c r="B18" t="n">
-        <v>91284</v>
+        <v>91290</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2431,7 +2431,7 @@
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist, Fredrik Wilde, Liam Sebestyén, Alva Danielsson, Elke Blöhbaum, Vilhelm Kroon, Miriam Schenk, Cajsa Björkén, Philipp Weiss, Emil Lindgren</t>
+          <t>Mattias Dalkvist, Fredrik Wilde, Emil Lindgren, Philipp Weiss, Cajsa Björkén, Miriam Schenk, Vilhelm Kroon, Elke Blöhbaum, Alva Danielsson, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
@@ -2445,7 +2445,7 @@
         <v>126891131</v>
       </c>
       <c r="B19" t="n">
-        <v>79043</v>
+        <v>79046</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2547,7 +2547,7 @@
         <v>126892808</v>
       </c>
       <c r="B20" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2644,7 +2644,7 @@
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist, Fredrik Wilde, Liam Sebestyén, Alva Danielsson, Elke Blöhbaum, Vilhelm Kroon, Miriam Schenk, Cajsa Björkén, Philipp Weiss, Emil Lindgren</t>
+          <t>Mattias Dalkvist, Fredrik Wilde, Emil Lindgren, Philipp Weiss, Cajsa Björkén, Miriam Schenk, Vilhelm Kroon, Elke Blöhbaum, Alva Danielsson, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
@@ -2655,10 +2655,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>126889374</v>
+        <v>126889370</v>
       </c>
       <c r="B21" t="n">
-        <v>98457</v>
+        <v>4772</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2666,36 +2666,27 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>221952</v>
+        <v>100299</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>överblommad</t>
+          <t>(Kraatz, 1881)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -2704,10 +2695,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>672898</v>
+        <v>672839</v>
       </c>
       <c r="R21" t="n">
-        <v>7058146</v>
+        <v>7058141</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2770,10 +2761,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>126889869</v>
+        <v>126889374</v>
       </c>
       <c r="B22" t="n">
-        <v>98353</v>
+        <v>98463</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2781,34 +2772,48 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>219790</v>
+        <v>221952</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Kravattensliden, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>672855</v>
+        <v>672898</v>
       </c>
       <c r="R22" t="n">
-        <v>7058116</v>
+        <v>7058146</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2855,12 +2860,12 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Philipp Weiss, Miriam Schenk, Cajsa Björkén, Fredrik Wilde, Alva Danielsson, Elke Blöhbaum, Vilhelm Kroon, Mattias Dalkvist</t>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Fredrik Wilde, Alva Danielsson, Emil Lindgren, Mattias Dalkvist, Elke Blöhbaum, Miriam Schenk, Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
@@ -2871,10 +2876,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>126889311</v>
+        <v>126891314</v>
       </c>
       <c r="B23" t="n">
-        <v>91284</v>
+        <v>80146</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2882,21 +2887,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5447</v>
+        <v>6462</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2906,10 +2911,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>672799</v>
+        <v>672999</v>
       </c>
       <c r="R23" t="n">
-        <v>7058086</v>
+        <v>7058211</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2956,12 +2961,12 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Fredrik Wilde, Alva Danielsson, Emil Lindgren, Mattias Dalkvist, Elke Blöhbaum, Miriam Schenk, Vilhelm Kroon</t>
+          <t>Alva Danielsson, Liam Sebestyén, Mattias Dalkvist, Miriam Schenk, Fredrik Wilde, Elke Blöhbaum, Emil Lindgren</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">
@@ -2972,10 +2977,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>126891314</v>
+        <v>126889311</v>
       </c>
       <c r="B24" t="n">
-        <v>80143</v>
+        <v>91290</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2983,21 +2988,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6462</v>
+        <v>5447</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3007,10 +3012,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>672999</v>
+        <v>672799</v>
       </c>
       <c r="R24" t="n">
-        <v>7058211</v>
+        <v>7058086</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3057,12 +3062,12 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Emil Lindgren, Elke Blöhbaum, Fredrik Wilde, Miriam Schenk, Mattias Dalkvist, Liam Sebestyén</t>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Fredrik Wilde, Alva Danielsson, Emil Lindgren, Mattias Dalkvist, Elke Blöhbaum, Miriam Schenk, Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr">
@@ -3073,10 +3078,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>126889370</v>
+        <v>126889869</v>
       </c>
       <c r="B25" t="n">
-        <v>4772</v>
+        <v>98359</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3084,39 +3089,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100299</v>
+        <v>219790</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Kravattensliden, Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>672839</v>
+        <v>672855</v>
       </c>
       <c r="R25" t="n">
-        <v>7058141</v>
+        <v>7058116</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3163,12 +3163,12 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon, Miriam Schenk, Elke Blöhbaum, Mattias Dalkvist, Emil Lindgren, Alva Danielsson, Fredrik Wilde, Liam Sebestyén, Cajsa Björkén, Philipp Weiss</t>
+          <t>Liam Sebestyén, Philipp Weiss, Miriam Schenk, Cajsa Björkén, Fredrik Wilde, Alva Danielsson, Elke Blöhbaum, Vilhelm Kroon, Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr">
@@ -3179,32 +3179,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>126889502</v>
+        <v>126891313</v>
       </c>
       <c r="B26" t="n">
-        <v>79011</v>
+        <v>80146</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3214,10 +3214,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>672801</v>
+        <v>672933</v>
       </c>
       <c r="R26" t="n">
-        <v>7058095</v>
+        <v>7058201</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3264,12 +3264,12 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Fredrik Wilde, Alva Danielsson, Emil Lindgren, Mattias Dalkvist, Elke Blöhbaum, Miriam Schenk, Vilhelm Kroon</t>
+          <t>Alva Danielsson, Liam Sebestyén, Mattias Dalkvist, Miriam Schenk, Fredrik Wilde, Elke Blöhbaum, Emil Lindgren</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr">
@@ -3280,32 +3280,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>126891313</v>
+        <v>126892816</v>
       </c>
       <c r="B27" t="n">
-        <v>80143</v>
+        <v>79014</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3315,13 +3315,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>672933</v>
+        <v>672627</v>
       </c>
       <c r="R27" t="n">
-        <v>7058201</v>
+        <v>7058024</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3348,9 +3348,19 @@
           <t>2025-07-24</t>
         </is>
       </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>11:52</t>
+        </is>
+      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-07-24</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3365,12 +3375,12 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Emil Lindgren, Elke Blöhbaum, Fredrik Wilde, Miriam Schenk, Mattias Dalkvist, Liam Sebestyén</t>
+          <t>Mattias Dalkvist, Fredrik Wilde, Emil Lindgren, Philipp Weiss, Cajsa Björkén, Miriam Schenk, Vilhelm Kroon, Elke Blöhbaum, Alva Danielsson, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr">
@@ -3490,10 +3500,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>126892816</v>
+        <v>126893730</v>
       </c>
       <c r="B29" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3525,13 +3535,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>672627</v>
+        <v>672929</v>
       </c>
       <c r="R29" t="n">
-        <v>7058024</v>
+        <v>7058213</v>
       </c>
       <c r="S29" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3558,19 +3568,9 @@
           <t>2025-07-24</t>
         </is>
       </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>11:52</t>
-        </is>
-      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-07-24</t>
-        </is>
-      </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>11:52</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3585,12 +3585,12 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist, Fredrik Wilde, Liam Sebestyén, Alva Danielsson, Elke Blöhbaum, Vilhelm Kroon, Miriam Schenk, Cajsa Björkén, Philipp Weiss, Emil Lindgren</t>
+          <t>Alva Danielsson, Fredrik Wilde, Liam Sebestyén, Elke Blöhbaum, Miriam Schenk, Mattias Dalkvist, Emil Lindgren</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr">
@@ -3601,10 +3601,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>126893730</v>
+        <v>126889502</v>
       </c>
       <c r="B30" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3636,10 +3636,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>672929</v>
+        <v>672801</v>
       </c>
       <c r="R30" t="n">
-        <v>7058213</v>
+        <v>7058095</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3686,12 +3686,12 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Fredrik Wilde, Liam Sebestyén, Elke Blöhbaum, Miriam Schenk, Mattias Dalkvist, Emil Lindgren</t>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Fredrik Wilde, Alva Danielsson, Emil Lindgren, Mattias Dalkvist, Elke Blöhbaum, Miriam Schenk, Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr">
@@ -3702,50 +3702,45 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>126889536</v>
+        <v>126891328</v>
       </c>
       <c r="B31" t="n">
-        <v>5176</v>
+        <v>79014</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100526</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Kravattensliden, Ång</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>672659</v>
+        <v>672972</v>
       </c>
       <c r="R31" t="n">
-        <v>7057975</v>
+        <v>7058246</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3792,12 +3787,12 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Fredrik Wilde, Alva Danielsson, Emil Lindgren, Mattias Dalkvist, Elke Blöhbaum, Miriam Schenk, Vilhelm Kroon</t>
+          <t>Alva Danielsson, Liam Sebestyén, Mattias Dalkvist, Miriam Schenk, Fredrik Wilde, Elke Blöhbaum, Emil Lindgren</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr">
@@ -3808,10 +3803,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>126889377</v>
+        <v>126889536</v>
       </c>
       <c r="B32" t="n">
-        <v>98457</v>
+        <v>5176</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3819,36 +3814,27 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>221952</v>
+        <v>100526</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K32" t="inlineStr">
-        <is>
-          <t>överblommad</t>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
@@ -3857,10 +3843,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>672810</v>
+        <v>672659</v>
       </c>
       <c r="R32" t="n">
-        <v>7058105</v>
+        <v>7057975</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3923,45 +3909,59 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>126891328</v>
+        <v>126889377</v>
       </c>
       <c r="B33" t="n">
-        <v>79011</v>
+        <v>98463</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>221952</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Kravattensliden, Ång</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>672972</v>
+        <v>672810</v>
       </c>
       <c r="R33" t="n">
-        <v>7058246</v>
+        <v>7058105</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4008,12 +4008,12 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Emil Lindgren, Elke Blöhbaum, Fredrik Wilde, Miriam Schenk, Mattias Dalkvist, Liam Sebestyén</t>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Fredrik Wilde, Alva Danielsson, Emil Lindgren, Mattias Dalkvist, Elke Blöhbaum, Miriam Schenk, Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr">
@@ -4027,7 +4027,7 @@
         <v>126893692</v>
       </c>
       <c r="B34" t="n">
-        <v>91319</v>
+        <v>91325</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4133,10 +4133,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>126889834</v>
+        <v>126891134</v>
       </c>
       <c r="B35" t="n">
-        <v>91284</v>
+        <v>80146</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4144,21 +4144,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>5447</v>
+        <v>6462</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4168,13 +4168,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>672819</v>
+        <v>673029</v>
       </c>
       <c r="R35" t="n">
-        <v>7058089</v>
+        <v>7058247</v>
       </c>
       <c r="S35" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4218,12 +4218,12 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Miriam Schenk</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Philipp Weiss, Miriam Schenk, Cajsa Björkén, Fredrik Wilde, Alva Danielsson, Elke Blöhbaum, Vilhelm Kroon, Mattias Dalkvist</t>
+          <t>Miriam Schenk, Cajsa Björkén, Fredrik Wilde, Philipp Weiss, Mattias Dalkvist, Vilhelm Kroon, Liam Sebestyén, Emil Lindgren, Alva Danielsson</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr">
@@ -4234,10 +4234,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>126891134</v>
+        <v>126889834</v>
       </c>
       <c r="B36" t="n">
-        <v>80143</v>
+        <v>91290</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4245,21 +4245,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6462</v>
+        <v>5447</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4269,13 +4269,13 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>673029</v>
+        <v>672819</v>
       </c>
       <c r="R36" t="n">
-        <v>7058247</v>
+        <v>7058089</v>
       </c>
       <c r="S36" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4319,12 +4319,12 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Miriam Schenk</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Miriam Schenk, Cajsa Björkén, Fredrik Wilde, Philipp Weiss, Mattias Dalkvist, Vilhelm Kroon, Liam Sebestyén, Emil Lindgren, Alva Danielsson</t>
+          <t>Liam Sebestyén, Philipp Weiss, Miriam Schenk, Cajsa Björkén, Fredrik Wilde, Alva Danielsson, Elke Blöhbaum, Vilhelm Kroon, Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr">
@@ -4338,7 +4338,7 @@
         <v>126892814</v>
       </c>
       <c r="B37" t="n">
-        <v>79043</v>
+        <v>79046</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4435,7 +4435,7 @@
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist, Fredrik Wilde, Liam Sebestyén, Alva Danielsson, Elke Blöhbaum, Vilhelm Kroon, Miriam Schenk, Cajsa Björkén, Philipp Weiss, Emil Lindgren</t>
+          <t>Mattias Dalkvist, Fredrik Wilde, Emil Lindgren, Philipp Weiss, Cajsa Björkén, Miriam Schenk, Vilhelm Kroon, Elke Blöhbaum, Alva Danielsson, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr">
@@ -4446,10 +4446,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>126892813</v>
+        <v>126890308</v>
       </c>
       <c r="B38" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4481,13 +4481,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>672661</v>
+        <v>672880</v>
       </c>
       <c r="R38" t="n">
-        <v>7058026</v>
+        <v>7058209</v>
       </c>
       <c r="S38" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4514,19 +4514,9 @@
           <t>2025-07-24</t>
         </is>
       </c>
-      <c r="Z38" t="inlineStr">
-        <is>
-          <t>11:51</t>
-        </is>
-      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-07-24</t>
-        </is>
-      </c>
-      <c r="AB38" t="inlineStr">
-        <is>
-          <t>11:51</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4541,12 +4531,12 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist, Fredrik Wilde, Liam Sebestyén, Alva Danielsson, Elke Blöhbaum, Vilhelm Kroon, Miriam Schenk, Cajsa Björkén, Philipp Weiss, Emil Lindgren</t>
+          <t>Vilhelm Kroon, Cajsa Björkén, Fredrik Wilde, Mattias Dalkvist, Philipp Weiss, Miriam Schenk, Liam Sebestyén, Alva Danielsson, Emil Lindgren</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr">
@@ -4557,10 +4547,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>126890308</v>
+        <v>126892813</v>
       </c>
       <c r="B39" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4592,13 +4582,13 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>672880</v>
+        <v>672661</v>
       </c>
       <c r="R39" t="n">
-        <v>7058209</v>
+        <v>7058026</v>
       </c>
       <c r="S39" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4625,9 +4615,19 @@
           <t>2025-07-24</t>
         </is>
       </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>11:51</t>
+        </is>
+      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-07-24</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4642,12 +4642,12 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Miriam Schenk, Philipp Weiss, Mattias Dalkvist, Fredrik Wilde, Cajsa Björkén, Vilhelm Kroon, Alva Danielsson, Emil Lindgren</t>
+          <t>Mattias Dalkvist, Fredrik Wilde, Emil Lindgren, Philipp Weiss, Cajsa Björkén, Miriam Schenk, Vilhelm Kroon, Elke Blöhbaum, Alva Danielsson, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr">
@@ -4661,7 +4661,7 @@
         <v>126891320</v>
       </c>
       <c r="B40" t="n">
-        <v>80114</v>
+        <v>80117</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4748,7 +4748,7 @@
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Emil Lindgren, Elke Blöhbaum, Fredrik Wilde, Miriam Schenk, Mattias Dalkvist, Liam Sebestyén</t>
+          <t>Alva Danielsson, Liam Sebestyén, Mattias Dalkvist, Miriam Schenk, Fredrik Wilde, Elke Blöhbaum, Emil Lindgren</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr">
@@ -4762,7 +4762,7 @@
         <v>126893847</v>
       </c>
       <c r="B41" t="n">
-        <v>80114</v>
+        <v>80117</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4864,10 +4864,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>126880507</v>
+        <v>126891321</v>
       </c>
       <c r="B42" t="n">
-        <v>82852</v>
+        <v>80117</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4875,34 +4875,34 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1312</v>
+        <v>6458</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Kravattensliden, Kravattensliden, Ång</t>
+          <t>Kravattensliden, Ång</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>672859</v>
+        <v>673004</v>
       </c>
       <c r="R42" t="n">
-        <v>7058136</v>
+        <v>7058209</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4949,12 +4949,12 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Fredrik Wilde</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Fredrik Wilde</t>
+          <t>Alva Danielsson, Liam Sebestyén, Mattias Dalkvist, Miriam Schenk, Fredrik Wilde, Elke Blöhbaum, Emil Lindgren</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr">
@@ -4965,10 +4965,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>126892804</v>
+        <v>126880507</v>
       </c>
       <c r="B43" t="n">
-        <v>79011</v>
+        <v>82855</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4976,37 +4976,37 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Kravattensliden, Ång</t>
+          <t>Kravattensliden, Kravattensliden, Ång</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>673003</v>
+        <v>672859</v>
       </c>
       <c r="R43" t="n">
-        <v>7058280</v>
+        <v>7058136</v>
       </c>
       <c r="S43" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5033,19 +5033,9 @@
           <t>2025-07-24</t>
         </is>
       </c>
-      <c r="Z43" t="inlineStr">
-        <is>
-          <t>10:49</t>
-        </is>
-      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-07-24</t>
-        </is>
-      </c>
-      <c r="AB43" t="inlineStr">
-        <is>
-          <t>10:49</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5060,12 +5050,12 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Fredrik Wilde</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist, Fredrik Wilde, Liam Sebestyén, Alva Danielsson, Elke Blöhbaum, Vilhelm Kroon, Miriam Schenk, Cajsa Björkén, Philipp Weiss, Emil Lindgren</t>
+          <t>Fredrik Wilde</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr">
@@ -5076,45 +5066,52 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>126889506</v>
+        <v>126893671</v>
       </c>
       <c r="B44" t="n">
-        <v>79011</v>
+        <v>91290</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="J44" t="inlineStr"/>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Kravattensliden, Ång</t>
+          <t>Kravattensliden , Ång</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>672889</v>
+        <v>672808</v>
       </c>
       <c r="R44" t="n">
-        <v>7058145</v>
+        <v>7058090</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5155,18 +5152,19 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
+      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Emil Lindgren</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Fredrik Wilde, Alva Danielsson, Emil Lindgren, Mattias Dalkvist, Elke Blöhbaum, Miriam Schenk, Vilhelm Kroon</t>
+          <t>Emil Lindgren</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr">
@@ -5177,55 +5175,48 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>126893671</v>
+        <v>126892804</v>
       </c>
       <c r="B45" t="n">
-        <v>91284</v>
+        <v>79014</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="J45" t="inlineStr"/>
-      <c r="K45" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Kravattensliden , Ång</t>
+          <t>Kravattensliden, Ång</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>672808</v>
+        <v>673003</v>
       </c>
       <c r="R45" t="n">
-        <v>7058090</v>
+        <v>7058280</v>
       </c>
       <c r="S45" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5252,30 +5243,39 @@
           <t>2025-07-24</t>
         </is>
       </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>10:49</t>
+        </is>
+      </c>
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-07-24</t>
         </is>
       </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>10:49</t>
+        </is>
+      </c>
       <c r="AD45" t="b">
         <v>0</v>
       </c>
       <c r="AE45" t="b">
         <v>0</v>
       </c>
-      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Emil Lindgren</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Emil Lindgren</t>
+          <t>Mattias Dalkvist, Fredrik Wilde, Emil Lindgren, Philipp Weiss, Cajsa Björkén, Miriam Schenk, Vilhelm Kroon, Elke Blöhbaum, Alva Danielsson, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr">
@@ -5286,10 +5286,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>126891321</v>
+        <v>126889506</v>
       </c>
       <c r="B46" t="n">
-        <v>80114</v>
+        <v>79014</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5297,21 +5297,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5321,10 +5321,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>673004</v>
+        <v>672889</v>
       </c>
       <c r="R46" t="n">
-        <v>7058209</v>
+        <v>7058145</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5371,12 +5371,12 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Emil Lindgren, Elke Blöhbaum, Fredrik Wilde, Miriam Schenk, Mattias Dalkvist, Liam Sebestyén</t>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Fredrik Wilde, Alva Danielsson, Emil Lindgren, Mattias Dalkvist, Elke Blöhbaum, Miriam Schenk, Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr">
@@ -5387,10 +5387,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>126890305</v>
+        <v>126890311</v>
       </c>
       <c r="B47" t="n">
-        <v>79011</v>
+        <v>88728</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5398,21 +5398,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>510</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5422,10 +5422,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>672724</v>
+        <v>673023</v>
       </c>
       <c r="R47" t="n">
-        <v>7058075</v>
+        <v>7058218</v>
       </c>
       <c r="S47" t="n">
         <v>15</v>
@@ -5477,7 +5477,7 @@
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Miriam Schenk, Philipp Weiss, Mattias Dalkvist, Fredrik Wilde, Cajsa Björkén, Vilhelm Kroon, Alva Danielsson, Emil Lindgren</t>
+          <t>Vilhelm Kroon, Cajsa Björkén, Fredrik Wilde, Mattias Dalkvist, Philipp Weiss, Miriam Schenk, Liam Sebestyén, Alva Danielsson, Emil Lindgren</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr">
@@ -5488,10 +5488,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>126890311</v>
+        <v>126890305</v>
       </c>
       <c r="B48" t="n">
-        <v>88722</v>
+        <v>79014</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5499,21 +5499,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>510</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5523,10 +5523,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>673023</v>
+        <v>672724</v>
       </c>
       <c r="R48" t="n">
-        <v>7058218</v>
+        <v>7058075</v>
       </c>
       <c r="S48" t="n">
         <v>15</v>
@@ -5578,7 +5578,7 @@
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Miriam Schenk, Philipp Weiss, Mattias Dalkvist, Fredrik Wilde, Cajsa Björkén, Vilhelm Kroon, Alva Danielsson, Emil Lindgren</t>
+          <t>Vilhelm Kroon, Cajsa Björkén, Fredrik Wilde, Mattias Dalkvist, Philipp Weiss, Miriam Schenk, Liam Sebestyén, Alva Danielsson, Emil Lindgren</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr">
@@ -5592,7 +5592,7 @@
         <v>126889494</v>
       </c>
       <c r="B49" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5693,7 +5693,7 @@
         <v>126889503</v>
       </c>
       <c r="B50" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5794,7 +5794,7 @@
         <v>126889856</v>
       </c>
       <c r="B51" t="n">
-        <v>80114</v>
+        <v>80117</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5892,45 +5892,45 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>126889837</v>
+        <v>126879684</v>
       </c>
       <c r="B52" t="n">
-        <v>91284</v>
+        <v>79014</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Kravattensliden, Ång</t>
+          <t>Kravattensliden, Kravattensliden, Ång</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>672912</v>
+        <v>672895</v>
       </c>
       <c r="R52" t="n">
-        <v>7058191</v>
+        <v>7058223</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5977,12 +5977,12 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Fredrik Wilde</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Philipp Weiss, Miriam Schenk, Cajsa Björkén, Fredrik Wilde, Alva Danielsson, Elke Blöhbaum, Vilhelm Kroon, Mattias Dalkvist</t>
+          <t>Fredrik Wilde</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr">
@@ -5993,32 +5993,32 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>126889862</v>
+        <v>126889837</v>
       </c>
       <c r="B53" t="n">
-        <v>91337</v>
+        <v>91290</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>5432</v>
+        <v>5447</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6028,10 +6028,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>672981</v>
+        <v>672912</v>
       </c>
       <c r="R53" t="n">
-        <v>7058264</v>
+        <v>7058191</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6094,10 +6094,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>126879684</v>
+        <v>126891325</v>
       </c>
       <c r="B54" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6125,14 +6125,14 @@
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Kravattensliden, Kravattensliden, Ång</t>
+          <t>Kravattensliden, Ång</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>672895</v>
+        <v>672660</v>
       </c>
       <c r="R54" t="n">
-        <v>7058223</v>
+        <v>7057985</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6179,12 +6179,12 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Fredrik Wilde</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Fredrik Wilde</t>
+          <t>Alva Danielsson, Liam Sebestyén, Mattias Dalkvist, Miriam Schenk, Fredrik Wilde, Elke Blöhbaum, Emil Lindgren</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr">
@@ -6195,10 +6195,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>126891325</v>
+        <v>126889862</v>
       </c>
       <c r="B55" t="n">
-        <v>79011</v>
+        <v>91343</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6206,21 +6206,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6230,10 +6230,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>672660</v>
+        <v>672981</v>
       </c>
       <c r="R55" t="n">
-        <v>7057985</v>
+        <v>7058264</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6280,12 +6280,12 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Emil Lindgren, Elke Blöhbaum, Fredrik Wilde, Miriam Schenk, Mattias Dalkvist, Liam Sebestyén</t>
+          <t>Liam Sebestyén, Philipp Weiss, Miriam Schenk, Cajsa Björkén, Fredrik Wilde, Alva Danielsson, Elke Blöhbaum, Vilhelm Kroon, Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr">
@@ -6299,7 +6299,7 @@
         <v>126893733</v>
       </c>
       <c r="B56" t="n">
-        <v>98353</v>
+        <v>98359</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6400,7 +6400,7 @@
         <v>126879133</v>
       </c>
       <c r="B57" t="n">
-        <v>79043</v>
+        <v>79046</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6501,7 +6501,7 @@
         <v>126892806</v>
       </c>
       <c r="B58" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6598,7 +6598,7 @@
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist, Fredrik Wilde, Liam Sebestyén, Alva Danielsson, Elke Blöhbaum, Vilhelm Kroon, Miriam Schenk, Cajsa Björkén, Philipp Weiss, Emil Lindgren</t>
+          <t>Mattias Dalkvist, Fredrik Wilde, Emil Lindgren, Philipp Weiss, Cajsa Björkén, Miriam Schenk, Vilhelm Kroon, Elke Blöhbaum, Alva Danielsson, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr">
@@ -6612,7 +6612,7 @@
         <v>126889504</v>
       </c>
       <c r="B59" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6710,32 +6710,32 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>126892812</v>
+        <v>126890296</v>
       </c>
       <c r="B60" t="n">
-        <v>79011</v>
+        <v>80146</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6745,13 +6745,13 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>672685</v>
+        <v>673025</v>
       </c>
       <c r="R60" t="n">
-        <v>7058010</v>
+        <v>7058244</v>
       </c>
       <c r="S60" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -6778,19 +6778,9 @@
           <t>2025-07-24</t>
         </is>
       </c>
-      <c r="Z60" t="inlineStr">
-        <is>
-          <t>11:41</t>
-        </is>
-      </c>
       <c r="AA60" t="inlineStr">
         <is>
           <t>2025-07-24</t>
-        </is>
-      </c>
-      <c r="AB60" t="inlineStr">
-        <is>
-          <t>11:41</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6805,12 +6795,12 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist, Fredrik Wilde, Liam Sebestyén, Alva Danielsson, Elke Blöhbaum, Vilhelm Kroon, Miriam Schenk, Cajsa Björkén, Philipp Weiss, Emil Lindgren</t>
+          <t>Vilhelm Kroon, Cajsa Björkén, Fredrik Wilde, Mattias Dalkvist, Philipp Weiss, Miriam Schenk, Liam Sebestyén, Alva Danielsson, Emil Lindgren</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr">
@@ -6821,10 +6811,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>126892809</v>
+        <v>126892812</v>
       </c>
       <c r="B61" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6856,13 +6846,13 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>672831</v>
+        <v>672685</v>
       </c>
       <c r="R61" t="n">
-        <v>7058091</v>
+        <v>7058010</v>
       </c>
       <c r="S61" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -6891,7 +6881,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -6901,7 +6891,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -6921,7 +6911,7 @@
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist, Fredrik Wilde, Liam Sebestyén, Alva Danielsson, Elke Blöhbaum, Vilhelm Kroon, Miriam Schenk, Cajsa Björkén, Philipp Weiss, Emil Lindgren</t>
+          <t>Mattias Dalkvist, Fredrik Wilde, Emil Lindgren, Philipp Weiss, Cajsa Björkén, Miriam Schenk, Vilhelm Kroon, Elke Blöhbaum, Alva Danielsson, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr">
@@ -6932,48 +6922,53 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>126890296</v>
+        <v>126880199</v>
       </c>
       <c r="B62" t="n">
-        <v>80143</v>
+        <v>79014</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Kravattensliden, Ång</t>
+          <t>Kravattensliden, Kravattensliden, Ång</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>673025</v>
+        <v>672894</v>
       </c>
       <c r="R62" t="n">
-        <v>7058244</v>
+        <v>7058198</v>
       </c>
       <c r="S62" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7017,12 +7012,12 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Fredrik Wilde</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon, Cajsa Björkén, Fredrik Wilde, Mattias Dalkvist, Philipp Weiss, Miriam Schenk, Liam Sebestyén, Alva Danielsson, Emil Lindgren</t>
+          <t>Fredrik Wilde</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr">
@@ -7033,10 +7028,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>126880199</v>
+        <v>126892809</v>
       </c>
       <c r="B63" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7062,24 +7057,19 @@
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
-      <c r="K63" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Kravattensliden, Kravattensliden, Ång</t>
+          <t>Kravattensliden, Ång</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>672894</v>
+        <v>672831</v>
       </c>
       <c r="R63" t="n">
-        <v>7058198</v>
+        <v>7058091</v>
       </c>
       <c r="S63" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7106,9 +7096,19 @@
           <t>2025-07-24</t>
         </is>
       </c>
+      <c r="Z63" t="inlineStr">
+        <is>
+          <t>11:32</t>
+        </is>
+      </c>
       <c r="AA63" t="inlineStr">
         <is>
           <t>2025-07-24</t>
+        </is>
+      </c>
+      <c r="AB63" t="inlineStr">
+        <is>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7123,12 +7123,12 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Fredrik Wilde</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Fredrik Wilde</t>
+          <t>Mattias Dalkvist, Fredrik Wilde, Emil Lindgren, Philipp Weiss, Cajsa Björkén, Miriam Schenk, Vilhelm Kroon, Elke Blöhbaum, Alva Danielsson, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr">
@@ -7139,10 +7139,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>126879033</v>
+        <v>126889382</v>
       </c>
       <c r="B64" t="n">
-        <v>79043</v>
+        <v>57654</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7150,43 +7150,39 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>185</v>
+        <v>100049</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J64" t="inlineStr">
-        <is>
-          <t>bålar</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Kravattensliden, Kravattensliden, Ång</t>
+          <t>Kravattensliden, Ång</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>673046</v>
+        <v>672838</v>
       </c>
       <c r="R64" t="n">
-        <v>7058286</v>
+        <v>7058134</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7233,12 +7229,12 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Fredrik Wilde</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Fredrik Wilde</t>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Fredrik Wilde, Alva Danielsson, Emil Lindgren, Mattias Dalkvist, Elke Blöhbaum, Miriam Schenk, Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr">
@@ -7249,10 +7245,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>126891312</v>
+        <v>126880532</v>
       </c>
       <c r="B65" t="n">
-        <v>91284</v>
+        <v>80146</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7260,34 +7256,34 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>5447</v>
+        <v>6462</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Kravattensliden, Ång</t>
+          <t>Kravattensliden, Kravattensliden, Ång</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>673027</v>
+        <v>672863</v>
       </c>
       <c r="R65" t="n">
-        <v>7058282</v>
+        <v>7058124</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7334,12 +7330,12 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Fredrik Wilde</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Emil Lindgren, Elke Blöhbaum, Fredrik Wilde, Miriam Schenk, Mattias Dalkvist, Liam Sebestyén</t>
+          <t>Fredrik Wilde</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr">
@@ -7350,45 +7346,45 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>126879425</v>
+        <v>126891312</v>
       </c>
       <c r="B66" t="n">
-        <v>79011</v>
+        <v>91290</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Kravattensliden, Kravattensliden, Ång</t>
+          <t>Kravattensliden, Ång</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>672947</v>
+        <v>673027</v>
       </c>
       <c r="R66" t="n">
-        <v>7058198</v>
+        <v>7058282</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7435,12 +7431,12 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Fredrik Wilde</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Fredrik Wilde</t>
+          <t>Alva Danielsson, Liam Sebestyén, Mattias Dalkvist, Miriam Schenk, Fredrik Wilde, Elke Blöhbaum, Emil Lindgren</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr">
@@ -7451,32 +7447,32 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>126880532</v>
+        <v>126879425</v>
       </c>
       <c r="B67" t="n">
-        <v>80143</v>
+        <v>79014</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7486,10 +7482,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>672863</v>
+        <v>672947</v>
       </c>
       <c r="R67" t="n">
-        <v>7058124</v>
+        <v>7058198</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7552,10 +7548,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>126889382</v>
+        <v>126879033</v>
       </c>
       <c r="B68" t="n">
-        <v>57654</v>
+        <v>79046</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7563,39 +7559,43 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>100049</v>
+        <v>185</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr"/>
-      <c r="M68" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Kravattensliden, Ång</t>
+          <t>Kravattensliden, Kravattensliden, Ång</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>672838</v>
+        <v>673046</v>
       </c>
       <c r="R68" t="n">
-        <v>7058134</v>
+        <v>7058286</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7642,12 +7642,12 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Fredrik Wilde</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Fredrik Wilde, Alva Danielsson, Emil Lindgren, Mattias Dalkvist, Elke Blöhbaum, Miriam Schenk, Vilhelm Kroon</t>
+          <t>Fredrik Wilde</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr">
@@ -7658,32 +7658,32 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>126890401</v>
+        <v>126890370</v>
       </c>
       <c r="B69" t="n">
-        <v>79011</v>
+        <v>80146</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7693,10 +7693,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>672705</v>
+        <v>672554</v>
       </c>
       <c r="R69" t="n">
-        <v>7058080</v>
+        <v>7058145</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7759,10 +7759,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>126890408</v>
+        <v>126890401</v>
       </c>
       <c r="B70" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7794,10 +7794,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>672874</v>
+        <v>672705</v>
       </c>
       <c r="R70" t="n">
-        <v>7058313</v>
+        <v>7058080</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7860,32 +7860,32 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>126890370</v>
+        <v>126890408</v>
       </c>
       <c r="B71" t="n">
-        <v>80143</v>
+        <v>79014</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7895,10 +7895,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>672554</v>
+        <v>672874</v>
       </c>
       <c r="R71" t="n">
-        <v>7058145</v>
+        <v>7058313</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7964,7 +7964,7 @@
         <v>126890405</v>
       </c>
       <c r="B72" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8065,7 +8065,7 @@
         <v>126890409</v>
       </c>
       <c r="B73" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8166,7 +8166,7 @@
         <v>126890407</v>
       </c>
       <c r="B74" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8267,7 +8267,7 @@
         <v>126890387</v>
       </c>
       <c r="B75" t="n">
-        <v>80114</v>
+        <v>80117</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8365,10 +8365,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>126890404</v>
+        <v>126890354</v>
       </c>
       <c r="B76" t="n">
-        <v>79011</v>
+        <v>79046</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8376,21 +8376,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8400,10 +8400,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>672805</v>
+        <v>672891</v>
       </c>
       <c r="R76" t="n">
-        <v>7058312</v>
+        <v>7058285</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8466,10 +8466,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>126890354</v>
+        <v>126890404</v>
       </c>
       <c r="B77" t="n">
-        <v>79043</v>
+        <v>79014</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8477,21 +8477,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8501,10 +8501,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>672891</v>
+        <v>672805</v>
       </c>
       <c r="R77" t="n">
-        <v>7058285</v>
+        <v>7058312</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8570,7 +8570,7 @@
         <v>126890353</v>
       </c>
       <c r="B78" t="n">
-        <v>79043</v>
+        <v>79046</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8671,7 +8671,7 @@
         <v>126890349</v>
       </c>
       <c r="B79" t="n">
-        <v>79043</v>
+        <v>79046</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8772,7 +8772,7 @@
         <v>126890348</v>
       </c>
       <c r="B80" t="n">
-        <v>79043</v>
+        <v>79046</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8873,7 +8873,7 @@
         <v>126890351</v>
       </c>
       <c r="B81" t="n">
-        <v>79043</v>
+        <v>79046</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8974,7 +8974,7 @@
         <v>126890350</v>
       </c>
       <c r="B82" t="n">
-        <v>79043</v>
+        <v>79046</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9075,7 +9075,7 @@
         <v>126890416</v>
       </c>
       <c r="B83" t="n">
-        <v>80149</v>
+        <v>80152</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9173,10 +9173,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>126890403</v>
+        <v>126890352</v>
       </c>
       <c r="B84" t="n">
-        <v>79011</v>
+        <v>79046</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9184,21 +9184,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9208,10 +9208,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>672796</v>
+        <v>672847</v>
       </c>
       <c r="R84" t="n">
-        <v>7058317</v>
+        <v>7058276</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9274,10 +9274,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>126890352</v>
+        <v>126890403</v>
       </c>
       <c r="B85" t="n">
-        <v>79043</v>
+        <v>79014</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9285,21 +9285,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9309,10 +9309,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>672847</v>
+        <v>672796</v>
       </c>
       <c r="R85" t="n">
-        <v>7058276</v>
+        <v>7058317</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>

--- a/artfynd/A 27938-2023 artfynd.xlsx
+++ b/artfynd/A 27938-2023 artfynd.xlsx
@@ -1179,7 +1179,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist, Fredrik Wilde, Emil Lindgren, Philipp Weiss, Cajsa Björkén, Miriam Schenk, Vilhelm Kroon, Elke Blöhbaum, Alva Danielsson, Liam Sebestyén</t>
+          <t>Mattias Dalkvist, Fredrik Wilde, Liam Sebestyén, Alva Danielsson, Elke Blöhbaum, Vilhelm Kroon, Miriam Schenk, Cajsa Björkén, Philipp Weiss, Emil Lindgren</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
@@ -1190,10 +1190,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126892805</v>
+        <v>126889505</v>
       </c>
       <c r="B7" t="n">
-        <v>57657</v>
+        <v>79014</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1201,21 +1201,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,13 +1225,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>672877</v>
+        <v>672864</v>
       </c>
       <c r="R7" t="n">
-        <v>7058189</v>
+        <v>7058181</v>
       </c>
       <c r="S7" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1258,24 +1258,9 @@
           <t>2025-07-24</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>11:15</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-07-24</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>11:15</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Gamla ringhack</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1290,12 +1275,12 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist, Fredrik Wilde, Emil Lindgren, Philipp Weiss, Cajsa Björkén, Miriam Schenk, Vilhelm Kroon, Elke Blöhbaum, Alva Danielsson, Liam Sebestyén</t>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Fredrik Wilde, Alva Danielsson, Emil Lindgren, Mattias Dalkvist, Elke Blöhbaum, Miriam Schenk, Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
@@ -1306,10 +1291,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126889505</v>
+        <v>126892805</v>
       </c>
       <c r="B8" t="n">
-        <v>79014</v>
+        <v>57657</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1317,21 +1302,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1341,13 +1326,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>672864</v>
+        <v>672877</v>
       </c>
       <c r="R8" t="n">
-        <v>7058181</v>
+        <v>7058189</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1374,9 +1359,24 @@
           <t>2025-07-24</t>
         </is>
       </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>11:15</t>
+        </is>
+      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-07-24</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>11:15</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Gamla ringhack</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1391,12 +1391,12 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Fredrik Wilde, Alva Danielsson, Emil Lindgren, Mattias Dalkvist, Elke Blöhbaum, Miriam Schenk, Vilhelm Kroon</t>
+          <t>Mattias Dalkvist, Fredrik Wilde, Liam Sebestyén, Alva Danielsson, Elke Blöhbaum, Vilhelm Kroon, Miriam Schenk, Cajsa Björkén, Philipp Weiss, Emil Lindgren</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
@@ -1911,7 +1911,7 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist, Fredrik Wilde, Emil Lindgren, Philipp Weiss, Cajsa Björkén, Miriam Schenk, Vilhelm Kroon, Elke Blöhbaum, Alva Danielsson, Liam Sebestyén</t>
+          <t>Mattias Dalkvist, Fredrik Wilde, Liam Sebestyén, Alva Danielsson, Elke Blöhbaum, Vilhelm Kroon, Miriam Schenk, Cajsa Björkén, Philipp Weiss, Emil Lindgren</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
@@ -2331,32 +2331,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>126892810</v>
+        <v>126891131</v>
       </c>
       <c r="B18" t="n">
-        <v>91290</v>
+        <v>79046</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5447</v>
+        <v>185</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2366,13 +2366,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>672801</v>
+        <v>672898</v>
       </c>
       <c r="R18" t="n">
-        <v>7058081</v>
+        <v>7058209</v>
       </c>
       <c r="S18" t="n">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2399,39 +2399,30 @@
           <t>2025-07-24</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>11:35</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-07-24</t>
         </is>
       </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>11:35</t>
-        </is>
-      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Miriam Schenk</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist, Fredrik Wilde, Emil Lindgren, Philipp Weiss, Cajsa Björkén, Miriam Schenk, Vilhelm Kroon, Elke Blöhbaum, Alva Danielsson, Liam Sebestyén</t>
+          <t>Miriam Schenk, Cajsa Björkén, Fredrik Wilde, Philipp Weiss, Mattias Dalkvist, Vilhelm Kroon, Liam Sebestyén, Emil Lindgren, Alva Danielsson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
@@ -2442,32 +2433,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>126891131</v>
+        <v>126892810</v>
       </c>
       <c r="B19" t="n">
-        <v>79046</v>
+        <v>91290</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>185</v>
+        <v>5447</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2477,13 +2468,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>672898</v>
+        <v>672801</v>
       </c>
       <c r="R19" t="n">
-        <v>7058209</v>
+        <v>7058081</v>
       </c>
       <c r="S19" t="n">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2510,30 +2501,39 @@
           <t>2025-07-24</t>
         </is>
       </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>11:35</t>
+        </is>
+      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-07-24</t>
         </is>
       </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>11:35</t>
+        </is>
+      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Miriam Schenk</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Miriam Schenk, Cajsa Björkén, Fredrik Wilde, Philipp Weiss, Mattias Dalkvist, Vilhelm Kroon, Liam Sebestyén, Emil Lindgren, Alva Danielsson</t>
+          <t>Mattias Dalkvist, Fredrik Wilde, Liam Sebestyén, Alva Danielsson, Elke Blöhbaum, Vilhelm Kroon, Miriam Schenk, Cajsa Björkén, Philipp Weiss, Emil Lindgren</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
@@ -2644,7 +2644,7 @@
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist, Fredrik Wilde, Emil Lindgren, Philipp Weiss, Cajsa Björkén, Miriam Schenk, Vilhelm Kroon, Elke Blöhbaum, Alva Danielsson, Liam Sebestyén</t>
+          <t>Mattias Dalkvist, Fredrik Wilde, Liam Sebestyén, Alva Danielsson, Elke Blöhbaum, Vilhelm Kroon, Miriam Schenk, Cajsa Björkén, Philipp Weiss, Emil Lindgren</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
@@ -2761,10 +2761,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>126889374</v>
+        <v>126889311</v>
       </c>
       <c r="B22" t="n">
-        <v>98463</v>
+        <v>91290</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2772,48 +2772,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>221952</v>
+        <v>5447</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Kravattensliden, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>672898</v>
+        <v>672799</v>
       </c>
       <c r="R22" t="n">
-        <v>7058146</v>
+        <v>7058086</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2977,10 +2963,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>126889311</v>
+        <v>126889869</v>
       </c>
       <c r="B24" t="n">
-        <v>91290</v>
+        <v>98359</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2988,21 +2974,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5447</v>
+        <v>219790</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3012,10 +2998,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>672799</v>
+        <v>672855</v>
       </c>
       <c r="R24" t="n">
-        <v>7058086</v>
+        <v>7058116</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3062,12 +3048,12 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Fredrik Wilde, Alva Danielsson, Emil Lindgren, Mattias Dalkvist, Elke Blöhbaum, Miriam Schenk, Vilhelm Kroon</t>
+          <t>Liam Sebestyén, Philipp Weiss, Miriam Schenk, Cajsa Björkén, Fredrik Wilde, Alva Danielsson, Elke Blöhbaum, Vilhelm Kroon, Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr">
@@ -3078,10 +3064,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>126889869</v>
+        <v>126889374</v>
       </c>
       <c r="B25" t="n">
-        <v>98359</v>
+        <v>98463</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3089,34 +3075,48 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>219790</v>
+        <v>221952</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Kravattensliden, Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>672855</v>
+        <v>672898</v>
       </c>
       <c r="R25" t="n">
-        <v>7058116</v>
+        <v>7058146</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3163,12 +3163,12 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Philipp Weiss, Miriam Schenk, Cajsa Björkén, Fredrik Wilde, Alva Danielsson, Elke Blöhbaum, Vilhelm Kroon, Mattias Dalkvist</t>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Fredrik Wilde, Alva Danielsson, Emil Lindgren, Mattias Dalkvist, Elke Blöhbaum, Miriam Schenk, Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr">
@@ -3380,7 +3380,7 @@
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist, Fredrik Wilde, Emil Lindgren, Philipp Weiss, Cajsa Björkén, Miriam Schenk, Vilhelm Kroon, Elke Blöhbaum, Alva Danielsson, Liam Sebestyén</t>
+          <t>Mattias Dalkvist, Fredrik Wilde, Liam Sebestyén, Alva Danielsson, Elke Blöhbaum, Vilhelm Kroon, Miriam Schenk, Cajsa Björkén, Philipp Weiss, Emil Lindgren</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr">
@@ -3391,10 +3391,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>126889847</v>
+        <v>126893730</v>
       </c>
       <c r="B28" t="n">
-        <v>57654</v>
+        <v>79014</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3402,42 +3402,34 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Kravattensliden, Ång</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>672981</v>
+        <v>672929</v>
       </c>
       <c r="R28" t="n">
-        <v>7058264</v>
+        <v>7058213</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3484,12 +3476,12 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Philipp Weiss, Miriam Schenk, Cajsa Björkén, Fredrik Wilde, Alva Danielsson, Elke Blöhbaum, Vilhelm Kroon, Mattias Dalkvist</t>
+          <t>Alva Danielsson, Fredrik Wilde, Liam Sebestyén, Elke Blöhbaum, Miriam Schenk, Mattias Dalkvist, Emil Lindgren</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr">
@@ -3500,7 +3492,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>126893730</v>
+        <v>126889502</v>
       </c>
       <c r="B29" t="n">
         <v>79014</v>
@@ -3535,10 +3527,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>672929</v>
+        <v>672801</v>
       </c>
       <c r="R29" t="n">
-        <v>7058213</v>
+        <v>7058095</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3585,12 +3577,12 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Fredrik Wilde, Liam Sebestyén, Elke Blöhbaum, Miriam Schenk, Mattias Dalkvist, Emil Lindgren</t>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Fredrik Wilde, Alva Danielsson, Emil Lindgren, Mattias Dalkvist, Elke Blöhbaum, Miriam Schenk, Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr">
@@ -3601,10 +3593,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>126889502</v>
+        <v>126889847</v>
       </c>
       <c r="B30" t="n">
-        <v>79014</v>
+        <v>57654</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3612,34 +3604,42 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Kravattensliden, Ång</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>672801</v>
+        <v>672981</v>
       </c>
       <c r="R30" t="n">
-        <v>7058095</v>
+        <v>7058264</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3686,12 +3686,12 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Fredrik Wilde, Alva Danielsson, Emil Lindgren, Mattias Dalkvist, Elke Blöhbaum, Miriam Schenk, Vilhelm Kroon</t>
+          <t>Liam Sebestyén, Philipp Weiss, Miriam Schenk, Cajsa Björkén, Fredrik Wilde, Alva Danielsson, Elke Blöhbaum, Vilhelm Kroon, Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr">
@@ -4024,52 +4024,45 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>126893692</v>
+        <v>126889834</v>
       </c>
       <c r="B34" t="n">
-        <v>91325</v>
+        <v>91290</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Kravattensliden , Ång</t>
+          <t>Kravattensliden, Ång</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>672811</v>
+        <v>672819</v>
       </c>
       <c r="R34" t="n">
-        <v>7058091</v>
+        <v>7058089</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4110,19 +4103,18 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
-      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Emil Lindgren</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Emil Lindgren</t>
+          <t>Liam Sebestyén, Philipp Weiss, Miriam Schenk, Cajsa Björkén, Fredrik Wilde, Alva Danielsson, Elke Blöhbaum, Vilhelm Kroon, Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr">
@@ -4234,45 +4226,52 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>126889834</v>
+        <v>126893692</v>
       </c>
       <c r="B36" t="n">
-        <v>91290</v>
+        <v>91325</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Kravattensliden, Ång</t>
+          <t>Kravattensliden , Ång</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>672819</v>
+        <v>672811</v>
       </c>
       <c r="R36" t="n">
-        <v>7058089</v>
+        <v>7058091</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4313,18 +4312,19 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
+      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Emil Lindgren</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Philipp Weiss, Miriam Schenk, Cajsa Björkén, Fredrik Wilde, Alva Danielsson, Elke Blöhbaum, Vilhelm Kroon, Mattias Dalkvist</t>
+          <t>Emil Lindgren</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr">
@@ -4335,10 +4335,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>126892814</v>
+        <v>126890308</v>
       </c>
       <c r="B37" t="n">
-        <v>79046</v>
+        <v>79014</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4346,21 +4346,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4370,13 +4370,13 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>672659</v>
+        <v>672880</v>
       </c>
       <c r="R37" t="n">
-        <v>7058027</v>
+        <v>7058209</v>
       </c>
       <c r="S37" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4403,19 +4403,9 @@
           <t>2025-07-24</t>
         </is>
       </c>
-      <c r="Z37" t="inlineStr">
-        <is>
-          <t>11:51</t>
-        </is>
-      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-07-24</t>
-        </is>
-      </c>
-      <c r="AB37" t="inlineStr">
-        <is>
-          <t>11:51</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4430,12 +4420,12 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist, Fredrik Wilde, Emil Lindgren, Philipp Weiss, Cajsa Björkén, Miriam Schenk, Vilhelm Kroon, Elke Blöhbaum, Alva Danielsson, Liam Sebestyén</t>
+          <t>Vilhelm Kroon, Cajsa Björkén, Fredrik Wilde, Mattias Dalkvist, Philipp Weiss, Miriam Schenk, Liam Sebestyén, Alva Danielsson, Emil Lindgren</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr">
@@ -4446,10 +4436,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>126890308</v>
+        <v>126891320</v>
       </c>
       <c r="B38" t="n">
-        <v>79014</v>
+        <v>80117</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4457,21 +4447,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4481,13 +4471,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>672880</v>
+        <v>672929</v>
       </c>
       <c r="R38" t="n">
-        <v>7058209</v>
+        <v>7058203</v>
       </c>
       <c r="S38" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4531,12 +4521,12 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon, Cajsa Björkén, Fredrik Wilde, Mattias Dalkvist, Philipp Weiss, Miriam Schenk, Liam Sebestyén, Alva Danielsson, Emil Lindgren</t>
+          <t>Alva Danielsson, Liam Sebestyén, Mattias Dalkvist, Miriam Schenk, Fredrik Wilde, Elke Blöhbaum, Emil Lindgren</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr">
@@ -4547,10 +4537,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>126892813</v>
+        <v>126892814</v>
       </c>
       <c r="B39" t="n">
-        <v>79014</v>
+        <v>79046</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4558,21 +4548,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4582,13 +4572,13 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>672661</v>
+        <v>672659</v>
       </c>
       <c r="R39" t="n">
-        <v>7058026</v>
+        <v>7058027</v>
       </c>
       <c r="S39" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4647,7 +4637,7 @@
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist, Fredrik Wilde, Emil Lindgren, Philipp Weiss, Cajsa Björkén, Miriam Schenk, Vilhelm Kroon, Elke Blöhbaum, Alva Danielsson, Liam Sebestyén</t>
+          <t>Mattias Dalkvist, Fredrik Wilde, Liam Sebestyén, Alva Danielsson, Elke Blöhbaum, Vilhelm Kroon, Miriam Schenk, Cajsa Björkén, Philipp Weiss, Emil Lindgren</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr">
@@ -4658,10 +4648,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>126891320</v>
+        <v>126892813</v>
       </c>
       <c r="B40" t="n">
-        <v>80117</v>
+        <v>79014</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4669,21 +4659,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4693,13 +4683,13 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>672929</v>
+        <v>672661</v>
       </c>
       <c r="R40" t="n">
-        <v>7058203</v>
+        <v>7058026</v>
       </c>
       <c r="S40" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4726,9 +4716,19 @@
           <t>2025-07-24</t>
         </is>
       </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>11:51</t>
+        </is>
+      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-07-24</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4743,12 +4743,12 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Liam Sebestyén, Mattias Dalkvist, Miriam Schenk, Fredrik Wilde, Elke Blöhbaum, Emil Lindgren</t>
+          <t>Mattias Dalkvist, Fredrik Wilde, Liam Sebestyén, Alva Danielsson, Elke Blöhbaum, Vilhelm Kroon, Miriam Schenk, Cajsa Björkén, Philipp Weiss, Emil Lindgren</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr">
@@ -4864,10 +4864,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>126891321</v>
+        <v>126889506</v>
       </c>
       <c r="B42" t="n">
-        <v>80117</v>
+        <v>79014</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4875,21 +4875,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4899,10 +4899,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>673004</v>
+        <v>672889</v>
       </c>
       <c r="R42" t="n">
-        <v>7058209</v>
+        <v>7058145</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4949,12 +4949,12 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Liam Sebestyén, Mattias Dalkvist, Miriam Schenk, Fredrik Wilde, Elke Blöhbaum, Emil Lindgren</t>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Fredrik Wilde, Alva Danielsson, Emil Lindgren, Mattias Dalkvist, Elke Blöhbaum, Miriam Schenk, Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr">
@@ -4965,10 +4965,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>126880507</v>
+        <v>126891321</v>
       </c>
       <c r="B43" t="n">
-        <v>82855</v>
+        <v>80117</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4976,34 +4976,34 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1312</v>
+        <v>6458</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Kravattensliden, Kravattensliden, Ång</t>
+          <t>Kravattensliden, Ång</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>672859</v>
+        <v>673004</v>
       </c>
       <c r="R43" t="n">
-        <v>7058136</v>
+        <v>7058209</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5050,12 +5050,12 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Fredrik Wilde</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Fredrik Wilde</t>
+          <t>Alva Danielsson, Liam Sebestyén, Mattias Dalkvist, Miriam Schenk, Fredrik Wilde, Elke Blöhbaum, Emil Lindgren</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr">
@@ -5066,52 +5066,45 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>126893671</v>
+        <v>126880507</v>
       </c>
       <c r="B44" t="n">
-        <v>91290</v>
+        <v>82855</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>5447</v>
+        <v>1312</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="J44" t="inlineStr"/>
-      <c r="K44" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Kravattensliden , Ång</t>
+          <t>Kravattensliden, Kravattensliden, Ång</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>672808</v>
+        <v>672859</v>
       </c>
       <c r="R44" t="n">
-        <v>7058090</v>
+        <v>7058136</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5152,19 +5145,18 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
-      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Emil Lindgren</t>
+          <t>Fredrik Wilde</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Emil Lindgren</t>
+          <t>Fredrik Wilde</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr">
@@ -5175,48 +5167,55 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>126892804</v>
+        <v>126893671</v>
       </c>
       <c r="B45" t="n">
-        <v>79014</v>
+        <v>91290</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="J45" t="inlineStr"/>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Kravattensliden, Ång</t>
+          <t>Kravattensliden , Ång</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>673003</v>
+        <v>672808</v>
       </c>
       <c r="R45" t="n">
-        <v>7058280</v>
+        <v>7058090</v>
       </c>
       <c r="S45" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5243,39 +5242,30 @@
           <t>2025-07-24</t>
         </is>
       </c>
-      <c r="Z45" t="inlineStr">
-        <is>
-          <t>10:49</t>
-        </is>
-      </c>
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-07-24</t>
         </is>
       </c>
-      <c r="AB45" t="inlineStr">
-        <is>
-          <t>10:49</t>
-        </is>
-      </c>
       <c r="AD45" t="b">
         <v>0</v>
       </c>
       <c r="AE45" t="b">
         <v>0</v>
       </c>
+      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Emil Lindgren</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist, Fredrik Wilde, Emil Lindgren, Philipp Weiss, Cajsa Björkén, Miriam Schenk, Vilhelm Kroon, Elke Blöhbaum, Alva Danielsson, Liam Sebestyén</t>
+          <t>Emil Lindgren</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr">
@@ -5286,7 +5276,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>126889506</v>
+        <v>126892804</v>
       </c>
       <c r="B46" t="n">
         <v>79014</v>
@@ -5321,13 +5311,13 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>672889</v>
+        <v>673003</v>
       </c>
       <c r="R46" t="n">
-        <v>7058145</v>
+        <v>7058280</v>
       </c>
       <c r="S46" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5354,9 +5344,19 @@
           <t>2025-07-24</t>
         </is>
       </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>10:49</t>
+        </is>
+      </c>
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-07-24</t>
+        </is>
+      </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5371,12 +5371,12 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Fredrik Wilde, Alva Danielsson, Emil Lindgren, Mattias Dalkvist, Elke Blöhbaum, Miriam Schenk, Vilhelm Kroon</t>
+          <t>Mattias Dalkvist, Fredrik Wilde, Liam Sebestyén, Alva Danielsson, Elke Blöhbaum, Vilhelm Kroon, Miriam Schenk, Cajsa Björkén, Philipp Weiss, Emil Lindgren</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr">
@@ -5791,10 +5791,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>126889856</v>
+        <v>126889862</v>
       </c>
       <c r="B51" t="n">
-        <v>80117</v>
+        <v>91343</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5802,21 +5802,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5826,10 +5826,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>672929</v>
+        <v>672981</v>
       </c>
       <c r="R51" t="n">
-        <v>7058201</v>
+        <v>7058264</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5892,7 +5892,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>126879684</v>
+        <v>126891325</v>
       </c>
       <c r="B52" t="n">
         <v>79014</v>
@@ -5923,14 +5923,14 @@
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Kravattensliden, Kravattensliden, Ång</t>
+          <t>Kravattensliden, Ång</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>672895</v>
+        <v>672660</v>
       </c>
       <c r="R52" t="n">
-        <v>7058223</v>
+        <v>7057985</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5977,12 +5977,12 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Fredrik Wilde</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Fredrik Wilde</t>
+          <t>Alva Danielsson, Liam Sebestyén, Mattias Dalkvist, Miriam Schenk, Fredrik Wilde, Elke Blöhbaum, Emil Lindgren</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr">
@@ -5993,32 +5993,32 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>126889837</v>
+        <v>126889856</v>
       </c>
       <c r="B53" t="n">
-        <v>91290</v>
+        <v>80117</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>5447</v>
+        <v>6458</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6028,10 +6028,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>672912</v>
+        <v>672929</v>
       </c>
       <c r="R53" t="n">
-        <v>7058191</v>
+        <v>7058201</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6094,32 +6094,32 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>126891325</v>
+        <v>126893733</v>
       </c>
       <c r="B54" t="n">
-        <v>79014</v>
+        <v>98359</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>219790</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6129,10 +6129,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>672660</v>
+        <v>672989</v>
       </c>
       <c r="R54" t="n">
-        <v>7057985</v>
+        <v>7058233</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6184,7 +6184,7 @@
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Liam Sebestyén, Mattias Dalkvist, Miriam Schenk, Fredrik Wilde, Elke Blöhbaum, Emil Lindgren</t>
+          <t>Alva Danielsson, Fredrik Wilde, Emil Lindgren, Mattias Dalkvist, Miriam Schenk, Elke Blöhbaum, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr">
@@ -6195,32 +6195,32 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>126889862</v>
+        <v>126889837</v>
       </c>
       <c r="B55" t="n">
-        <v>91343</v>
+        <v>91290</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>5432</v>
+        <v>5447</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6230,10 +6230,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>672981</v>
+        <v>672912</v>
       </c>
       <c r="R55" t="n">
-        <v>7058264</v>
+        <v>7058191</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6296,45 +6296,45 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>126893733</v>
+        <v>126879684</v>
       </c>
       <c r="B56" t="n">
-        <v>98359</v>
+        <v>79014</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>219790</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Kravattensliden, Ång</t>
+          <t>Kravattensliden, Kravattensliden, Ång</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>672989</v>
+        <v>672895</v>
       </c>
       <c r="R56" t="n">
-        <v>7058233</v>
+        <v>7058223</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6381,12 +6381,12 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Fredrik Wilde</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Fredrik Wilde, Liam Sebestyén, Elke Blöhbaum, Miriam Schenk, Mattias Dalkvist, Emil Lindgren</t>
+          <t>Fredrik Wilde</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr">
@@ -6397,10 +6397,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>126879133</v>
+        <v>126892806</v>
       </c>
       <c r="B57" t="n">
-        <v>79046</v>
+        <v>79014</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6408,34 +6408,34 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Kravattensliden, Kravattensliden, Ång</t>
+          <t>Kravattensliden, Ång</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>673041</v>
+        <v>672883</v>
       </c>
       <c r="R57" t="n">
-        <v>7058262</v>
+        <v>7058166</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6465,9 +6465,19 @@
           <t>2025-07-24</t>
         </is>
       </c>
+      <c r="Z57" t="inlineStr">
+        <is>
+          <t>11:18</t>
+        </is>
+      </c>
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-07-24</t>
+        </is>
+      </c>
+      <c r="AB57" t="inlineStr">
+        <is>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6482,12 +6492,12 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Fredrik Wilde</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Fredrik Wilde</t>
+          <t>Mattias Dalkvist, Fredrik Wilde, Liam Sebestyén, Alva Danielsson, Elke Blöhbaum, Vilhelm Kroon, Miriam Schenk, Cajsa Björkén, Philipp Weiss, Emil Lindgren</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr">
@@ -6498,10 +6508,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>126892806</v>
+        <v>126879133</v>
       </c>
       <c r="B58" t="n">
-        <v>79014</v>
+        <v>79046</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6509,34 +6519,34 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Kravattensliden, Ång</t>
+          <t>Kravattensliden, Kravattensliden, Ång</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>672883</v>
+        <v>673041</v>
       </c>
       <c r="R58" t="n">
-        <v>7058166</v>
+        <v>7058262</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6566,19 +6576,9 @@
           <t>2025-07-24</t>
         </is>
       </c>
-      <c r="Z58" t="inlineStr">
-        <is>
-          <t>11:18</t>
-        </is>
-      </c>
       <c r="AA58" t="inlineStr">
         <is>
           <t>2025-07-24</t>
-        </is>
-      </c>
-      <c r="AB58" t="inlineStr">
-        <is>
-          <t>11:18</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6593,12 +6593,12 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Fredrik Wilde</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist, Fredrik Wilde, Emil Lindgren, Philipp Weiss, Cajsa Björkén, Miriam Schenk, Vilhelm Kroon, Elke Blöhbaum, Alva Danielsson, Liam Sebestyén</t>
+          <t>Fredrik Wilde</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr">
@@ -6710,32 +6710,32 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>126890296</v>
+        <v>126892812</v>
       </c>
       <c r="B60" t="n">
-        <v>80146</v>
+        <v>79014</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6745,13 +6745,13 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>673025</v>
+        <v>672685</v>
       </c>
       <c r="R60" t="n">
-        <v>7058244</v>
+        <v>7058010</v>
       </c>
       <c r="S60" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -6778,9 +6778,19 @@
           <t>2025-07-24</t>
         </is>
       </c>
+      <c r="Z60" t="inlineStr">
+        <is>
+          <t>11:41</t>
+        </is>
+      </c>
       <c r="AA60" t="inlineStr">
         <is>
           <t>2025-07-24</t>
+        </is>
+      </c>
+      <c r="AB60" t="inlineStr">
+        <is>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6795,12 +6805,12 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon, Cajsa Björkén, Fredrik Wilde, Mattias Dalkvist, Philipp Weiss, Miriam Schenk, Liam Sebestyén, Alva Danielsson, Emil Lindgren</t>
+          <t>Mattias Dalkvist, Fredrik Wilde, Liam Sebestyén, Alva Danielsson, Elke Blöhbaum, Vilhelm Kroon, Miriam Schenk, Cajsa Björkén, Philipp Weiss, Emil Lindgren</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr">
@@ -6811,7 +6821,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>126892812</v>
+        <v>126892809</v>
       </c>
       <c r="B61" t="n">
         <v>79014</v>
@@ -6846,13 +6856,13 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>672685</v>
+        <v>672831</v>
       </c>
       <c r="R61" t="n">
-        <v>7058010</v>
+        <v>7058091</v>
       </c>
       <c r="S61" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -6881,7 +6891,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -6891,7 +6901,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -6911,7 +6921,7 @@
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist, Fredrik Wilde, Emil Lindgren, Philipp Weiss, Cajsa Björkén, Miriam Schenk, Vilhelm Kroon, Elke Blöhbaum, Alva Danielsson, Liam Sebestyén</t>
+          <t>Mattias Dalkvist, Fredrik Wilde, Liam Sebestyén, Alva Danielsson, Elke Blöhbaum, Vilhelm Kroon, Miriam Schenk, Cajsa Björkén, Philipp Weiss, Emil Lindgren</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr">
@@ -6922,53 +6932,48 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>126880199</v>
+        <v>126890296</v>
       </c>
       <c r="B62" t="n">
-        <v>79014</v>
+        <v>80146</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
-      <c r="K62" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Kravattensliden, Kravattensliden, Ång</t>
+          <t>Kravattensliden, Ång</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>672894</v>
+        <v>673025</v>
       </c>
       <c r="R62" t="n">
-        <v>7058198</v>
+        <v>7058244</v>
       </c>
       <c r="S62" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7012,12 +7017,12 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Fredrik Wilde</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Fredrik Wilde</t>
+          <t>Vilhelm Kroon, Cajsa Björkén, Fredrik Wilde, Mattias Dalkvist, Philipp Weiss, Miriam Schenk, Liam Sebestyén, Alva Danielsson, Emil Lindgren</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr">
@@ -7028,7 +7033,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>126892809</v>
+        <v>126880199</v>
       </c>
       <c r="B63" t="n">
         <v>79014</v>
@@ -7057,19 +7062,24 @@
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Kravattensliden, Ång</t>
+          <t>Kravattensliden, Kravattensliden, Ång</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>672831</v>
+        <v>672894</v>
       </c>
       <c r="R63" t="n">
-        <v>7058091</v>
+        <v>7058198</v>
       </c>
       <c r="S63" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7096,19 +7106,9 @@
           <t>2025-07-24</t>
         </is>
       </c>
-      <c r="Z63" t="inlineStr">
-        <is>
-          <t>11:32</t>
-        </is>
-      </c>
       <c r="AA63" t="inlineStr">
         <is>
           <t>2025-07-24</t>
-        </is>
-      </c>
-      <c r="AB63" t="inlineStr">
-        <is>
-          <t>11:32</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7123,12 +7123,12 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Fredrik Wilde</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist, Fredrik Wilde, Emil Lindgren, Philipp Weiss, Cajsa Björkén, Miriam Schenk, Vilhelm Kroon, Elke Blöhbaum, Alva Danielsson, Liam Sebestyén</t>
+          <t>Fredrik Wilde</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr">
@@ -7139,10 +7139,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>126889382</v>
+        <v>126879033</v>
       </c>
       <c r="B64" t="n">
-        <v>57654</v>
+        <v>79046</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7150,39 +7150,43 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>100049</v>
+        <v>185</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr"/>
-      <c r="M64" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Kravattensliden, Ång</t>
+          <t>Kravattensliden, Kravattensliden, Ång</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>672838</v>
+        <v>673046</v>
       </c>
       <c r="R64" t="n">
-        <v>7058134</v>
+        <v>7058286</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7229,12 +7233,12 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Fredrik Wilde</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Fredrik Wilde, Alva Danielsson, Emil Lindgren, Mattias Dalkvist, Elke Blöhbaum, Miriam Schenk, Vilhelm Kroon</t>
+          <t>Fredrik Wilde</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr">
@@ -7245,10 +7249,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>126880532</v>
+        <v>126891312</v>
       </c>
       <c r="B65" t="n">
-        <v>80146</v>
+        <v>91290</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7256,34 +7260,34 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6462</v>
+        <v>5447</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Kravattensliden, Kravattensliden, Ång</t>
+          <t>Kravattensliden, Ång</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>672863</v>
+        <v>673027</v>
       </c>
       <c r="R65" t="n">
-        <v>7058124</v>
+        <v>7058282</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7330,12 +7334,12 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Fredrik Wilde</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Fredrik Wilde</t>
+          <t>Alva Danielsson, Liam Sebestyén, Mattias Dalkvist, Miriam Schenk, Fredrik Wilde, Elke Blöhbaum, Emil Lindgren</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr">
@@ -7346,45 +7350,45 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>126891312</v>
+        <v>126879425</v>
       </c>
       <c r="B66" t="n">
-        <v>91290</v>
+        <v>79014</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Kravattensliden, Ång</t>
+          <t>Kravattensliden, Kravattensliden, Ång</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>673027</v>
+        <v>672947</v>
       </c>
       <c r="R66" t="n">
-        <v>7058282</v>
+        <v>7058198</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7431,12 +7435,12 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Fredrik Wilde</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Liam Sebestyén, Mattias Dalkvist, Miriam Schenk, Fredrik Wilde, Elke Blöhbaum, Emil Lindgren</t>
+          <t>Fredrik Wilde</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr">
@@ -7447,32 +7451,32 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>126879425</v>
+        <v>126880532</v>
       </c>
       <c r="B67" t="n">
-        <v>79014</v>
+        <v>80146</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7482,10 +7486,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>672947</v>
+        <v>672863</v>
       </c>
       <c r="R67" t="n">
-        <v>7058198</v>
+        <v>7058124</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7548,10 +7552,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>126879033</v>
+        <v>126889382</v>
       </c>
       <c r="B68" t="n">
-        <v>79046</v>
+        <v>57654</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7559,43 +7563,39 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>185</v>
+        <v>100049</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J68" t="inlineStr">
-        <is>
-          <t>bålar</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr"/>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Kravattensliden, Kravattensliden, Ång</t>
+          <t>Kravattensliden, Ång</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>673046</v>
+        <v>672838</v>
       </c>
       <c r="R68" t="n">
-        <v>7058286</v>
+        <v>7058134</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7642,12 +7642,12 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Fredrik Wilde</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Fredrik Wilde</t>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Fredrik Wilde, Alva Danielsson, Emil Lindgren, Mattias Dalkvist, Elke Blöhbaum, Miriam Schenk, Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr">
@@ -8163,10 +8163,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>126890407</v>
+        <v>126890387</v>
       </c>
       <c r="B74" t="n">
-        <v>79014</v>
+        <v>80117</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8174,21 +8174,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8198,10 +8198,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>672859</v>
+        <v>672556</v>
       </c>
       <c r="R74" t="n">
-        <v>7058290</v>
+        <v>7058143</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8264,10 +8264,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>126890387</v>
+        <v>126890407</v>
       </c>
       <c r="B75" t="n">
-        <v>80117</v>
+        <v>79014</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8275,21 +8275,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8299,10 +8299,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>672556</v>
+        <v>672859</v>
       </c>
       <c r="R75" t="n">
-        <v>7058143</v>
+        <v>7058290</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8365,10 +8365,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>126890354</v>
+        <v>126890404</v>
       </c>
       <c r="B76" t="n">
-        <v>79046</v>
+        <v>79014</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8376,21 +8376,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8400,10 +8400,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>672891</v>
+        <v>672805</v>
       </c>
       <c r="R76" t="n">
-        <v>7058285</v>
+        <v>7058312</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8466,10 +8466,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>126890404</v>
+        <v>126890354</v>
       </c>
       <c r="B77" t="n">
-        <v>79014</v>
+        <v>79046</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8477,21 +8477,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8501,10 +8501,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>672805</v>
+        <v>672891</v>
       </c>
       <c r="R77" t="n">
-        <v>7058312</v>
+        <v>7058285</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>

--- a/artfynd/A 27938-2023 artfynd.xlsx
+++ b/artfynd/A 27938-2023 artfynd.xlsx
@@ -3179,32 +3179,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>126891313</v>
+        <v>126892816</v>
       </c>
       <c r="B26" t="n">
-        <v>80146</v>
+        <v>79014</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3214,13 +3214,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>672933</v>
+        <v>672627</v>
       </c>
       <c r="R26" t="n">
-        <v>7058201</v>
+        <v>7058024</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3247,9 +3247,19 @@
           <t>2025-07-24</t>
         </is>
       </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>11:52</t>
+        </is>
+      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-07-24</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3264,12 +3274,12 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Liam Sebestyén, Mattias Dalkvist, Miriam Schenk, Fredrik Wilde, Elke Blöhbaum, Emil Lindgren</t>
+          <t>Mattias Dalkvist, Fredrik Wilde, Liam Sebestyén, Alva Danielsson, Elke Blöhbaum, Vilhelm Kroon, Miriam Schenk, Cajsa Björkén, Philipp Weiss, Emil Lindgren</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr">
@@ -3280,7 +3290,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>126892816</v>
+        <v>126893730</v>
       </c>
       <c r="B27" t="n">
         <v>79014</v>
@@ -3315,13 +3325,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>672627</v>
+        <v>672929</v>
       </c>
       <c r="R27" t="n">
-        <v>7058024</v>
+        <v>7058213</v>
       </c>
       <c r="S27" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3348,19 +3358,9 @@
           <t>2025-07-24</t>
         </is>
       </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>11:52</t>
-        </is>
-      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-07-24</t>
-        </is>
-      </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>11:52</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3375,12 +3375,12 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist, Fredrik Wilde, Liam Sebestyén, Alva Danielsson, Elke Blöhbaum, Vilhelm Kroon, Miriam Schenk, Cajsa Björkén, Philipp Weiss, Emil Lindgren</t>
+          <t>Alva Danielsson, Fredrik Wilde, Liam Sebestyén, Elke Blöhbaum, Miriam Schenk, Mattias Dalkvist, Emil Lindgren</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr">
@@ -3391,7 +3391,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>126893730</v>
+        <v>126889502</v>
       </c>
       <c r="B28" t="n">
         <v>79014</v>
@@ -3426,10 +3426,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>672929</v>
+        <v>672801</v>
       </c>
       <c r="R28" t="n">
-        <v>7058213</v>
+        <v>7058095</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3476,12 +3476,12 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Fredrik Wilde, Liam Sebestyén, Elke Blöhbaum, Miriam Schenk, Mattias Dalkvist, Emil Lindgren</t>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Fredrik Wilde, Alva Danielsson, Emil Lindgren, Mattias Dalkvist, Elke Blöhbaum, Miriam Schenk, Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr">
@@ -3492,10 +3492,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>126889502</v>
+        <v>126889847</v>
       </c>
       <c r="B29" t="n">
-        <v>79014</v>
+        <v>57654</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3503,34 +3503,42 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Kravattensliden, Ång</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>672801</v>
+        <v>672981</v>
       </c>
       <c r="R29" t="n">
-        <v>7058095</v>
+        <v>7058264</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3577,12 +3585,12 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Fredrik Wilde, Alva Danielsson, Emil Lindgren, Mattias Dalkvist, Elke Blöhbaum, Miriam Schenk, Vilhelm Kroon</t>
+          <t>Liam Sebestyén, Philipp Weiss, Miriam Schenk, Cajsa Björkén, Fredrik Wilde, Alva Danielsson, Elke Blöhbaum, Vilhelm Kroon, Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr">
@@ -3593,53 +3601,45 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>126889847</v>
+        <v>126891313</v>
       </c>
       <c r="B30" t="n">
-        <v>57654</v>
+        <v>80146</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100049</v>
+        <v>6462</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Kravattensliden, Ång</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>672981</v>
+        <v>672933</v>
       </c>
       <c r="R30" t="n">
-        <v>7058264</v>
+        <v>7058201</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3686,12 +3686,12 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Philipp Weiss, Miriam Schenk, Cajsa Björkén, Fredrik Wilde, Alva Danielsson, Elke Blöhbaum, Vilhelm Kroon, Mattias Dalkvist</t>
+          <t>Alva Danielsson, Liam Sebestyén, Mattias Dalkvist, Miriam Schenk, Fredrik Wilde, Elke Blöhbaum, Emil Lindgren</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr">
@@ -4864,10 +4864,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>126889506</v>
+        <v>126880507</v>
       </c>
       <c r="B42" t="n">
-        <v>79014</v>
+        <v>82855</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4875,34 +4875,34 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Kravattensliden, Ång</t>
+          <t>Kravattensliden, Kravattensliden, Ång</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>672889</v>
+        <v>672859</v>
       </c>
       <c r="R42" t="n">
-        <v>7058145</v>
+        <v>7058136</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4949,12 +4949,12 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Fredrik Wilde</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Fredrik Wilde, Alva Danielsson, Emil Lindgren, Mattias Dalkvist, Elke Blöhbaum, Miriam Schenk, Vilhelm Kroon</t>
+          <t>Fredrik Wilde</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr">
@@ -4965,45 +4965,52 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>126891321</v>
+        <v>126893671</v>
       </c>
       <c r="B43" t="n">
-        <v>80117</v>
+        <v>91290</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6458</v>
+        <v>5447</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr"/>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Kravattensliden, Ång</t>
+          <t>Kravattensliden , Ång</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>673004</v>
+        <v>672808</v>
       </c>
       <c r="R43" t="n">
-        <v>7058209</v>
+        <v>7058090</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5044,18 +5051,19 @@
       <c r="AE43" t="b">
         <v>0</v>
       </c>
+      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Emil Lindgren</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Liam Sebestyén, Mattias Dalkvist, Miriam Schenk, Fredrik Wilde, Elke Blöhbaum, Emil Lindgren</t>
+          <t>Emil Lindgren</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr">
@@ -5066,10 +5074,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>126880507</v>
+        <v>126892804</v>
       </c>
       <c r="B44" t="n">
-        <v>82855</v>
+        <v>79014</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5077,37 +5085,37 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Kravattensliden, Kravattensliden, Ång</t>
+          <t>Kravattensliden, Ång</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>672859</v>
+        <v>673003</v>
       </c>
       <c r="R44" t="n">
-        <v>7058136</v>
+        <v>7058280</v>
       </c>
       <c r="S44" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5134,9 +5142,19 @@
           <t>2025-07-24</t>
         </is>
       </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>10:49</t>
+        </is>
+      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-07-24</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5151,12 +5169,12 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Fredrik Wilde</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Fredrik Wilde</t>
+          <t>Mattias Dalkvist, Fredrik Wilde, Liam Sebestyén, Alva Danielsson, Elke Blöhbaum, Vilhelm Kroon, Miriam Schenk, Cajsa Björkén, Philipp Weiss, Emil Lindgren</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr">
@@ -5167,52 +5185,45 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>126893671</v>
+        <v>126889506</v>
       </c>
       <c r="B45" t="n">
-        <v>91290</v>
+        <v>79014</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="J45" t="inlineStr"/>
-      <c r="K45" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Kravattensliden , Ång</t>
+          <t>Kravattensliden, Ång</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>672808</v>
+        <v>672889</v>
       </c>
       <c r="R45" t="n">
-        <v>7058090</v>
+        <v>7058145</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5253,19 +5264,18 @@
       <c r="AE45" t="b">
         <v>0</v>
       </c>
-      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Emil Lindgren</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Emil Lindgren</t>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Fredrik Wilde, Alva Danielsson, Emil Lindgren, Mattias Dalkvist, Elke Blöhbaum, Miriam Schenk, Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr">
@@ -5276,10 +5286,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>126892804</v>
+        <v>126891321</v>
       </c>
       <c r="B46" t="n">
-        <v>79014</v>
+        <v>80117</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5287,21 +5297,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5311,13 +5321,13 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>673003</v>
+        <v>673004</v>
       </c>
       <c r="R46" t="n">
-        <v>7058280</v>
+        <v>7058209</v>
       </c>
       <c r="S46" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5344,19 +5354,9 @@
           <t>2025-07-24</t>
         </is>
       </c>
-      <c r="Z46" t="inlineStr">
-        <is>
-          <t>10:49</t>
-        </is>
-      </c>
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-07-24</t>
-        </is>
-      </c>
-      <c r="AB46" t="inlineStr">
-        <is>
-          <t>10:49</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5371,12 +5371,12 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist, Fredrik Wilde, Liam Sebestyén, Alva Danielsson, Elke Blöhbaum, Vilhelm Kroon, Miriam Schenk, Cajsa Björkén, Philipp Weiss, Emil Lindgren</t>
+          <t>Alva Danielsson, Liam Sebestyén, Mattias Dalkvist, Miriam Schenk, Fredrik Wilde, Elke Blöhbaum, Emil Lindgren</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr">
@@ -5791,32 +5791,32 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>126889862</v>
+        <v>126893733</v>
       </c>
       <c r="B51" t="n">
-        <v>91343</v>
+        <v>98359</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>5432</v>
+        <v>219790</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5826,10 +5826,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>672981</v>
+        <v>672989</v>
       </c>
       <c r="R51" t="n">
-        <v>7058264</v>
+        <v>7058233</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5876,12 +5876,12 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Philipp Weiss, Miriam Schenk, Cajsa Björkén, Fredrik Wilde, Alva Danielsson, Elke Blöhbaum, Vilhelm Kroon, Mattias Dalkvist</t>
+          <t>Alva Danielsson, Fredrik Wilde, Emil Lindgren, Mattias Dalkvist, Miriam Schenk, Elke Blöhbaum, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr">
@@ -5892,10 +5892,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>126891325</v>
+        <v>126889862</v>
       </c>
       <c r="B52" t="n">
-        <v>79014</v>
+        <v>91343</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5903,21 +5903,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5927,10 +5927,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>672660</v>
+        <v>672981</v>
       </c>
       <c r="R52" t="n">
-        <v>7057985</v>
+        <v>7058264</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5977,12 +5977,12 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Liam Sebestyén, Mattias Dalkvist, Miriam Schenk, Fredrik Wilde, Elke Blöhbaum, Emil Lindgren</t>
+          <t>Liam Sebestyén, Philipp Weiss, Miriam Schenk, Cajsa Björkén, Fredrik Wilde, Alva Danielsson, Elke Blöhbaum, Vilhelm Kroon, Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr">
@@ -5993,32 +5993,32 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>126889856</v>
+        <v>126889837</v>
       </c>
       <c r="B53" t="n">
-        <v>80117</v>
+        <v>91290</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6458</v>
+        <v>5447</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6028,10 +6028,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>672929</v>
+        <v>672912</v>
       </c>
       <c r="R53" t="n">
-        <v>7058201</v>
+        <v>7058191</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6094,32 +6094,32 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>126893733</v>
+        <v>126891325</v>
       </c>
       <c r="B54" t="n">
-        <v>98359</v>
+        <v>79014</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>219790</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6129,10 +6129,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>672989</v>
+        <v>672660</v>
       </c>
       <c r="R54" t="n">
-        <v>7058233</v>
+        <v>7057985</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6184,7 +6184,7 @@
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Fredrik Wilde, Emil Lindgren, Mattias Dalkvist, Miriam Schenk, Elke Blöhbaum, Liam Sebestyén</t>
+          <t>Alva Danielsson, Liam Sebestyén, Mattias Dalkvist, Miriam Schenk, Fredrik Wilde, Elke Blöhbaum, Emil Lindgren</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr">
@@ -6195,45 +6195,45 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>126889837</v>
+        <v>126879684</v>
       </c>
       <c r="B55" t="n">
-        <v>91290</v>
+        <v>79014</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Kravattensliden, Ång</t>
+          <t>Kravattensliden, Kravattensliden, Ång</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>672912</v>
+        <v>672895</v>
       </c>
       <c r="R55" t="n">
-        <v>7058191</v>
+        <v>7058223</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6280,12 +6280,12 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Fredrik Wilde</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Philipp Weiss, Miriam Schenk, Cajsa Björkén, Fredrik Wilde, Alva Danielsson, Elke Blöhbaum, Vilhelm Kroon, Mattias Dalkvist</t>
+          <t>Fredrik Wilde</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr">
@@ -6296,10 +6296,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>126879684</v>
+        <v>126889856</v>
       </c>
       <c r="B56" t="n">
-        <v>79014</v>
+        <v>80117</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6307,34 +6307,34 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Kravattensliden, Kravattensliden, Ång</t>
+          <t>Kravattensliden, Ång</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>672895</v>
+        <v>672929</v>
       </c>
       <c r="R56" t="n">
-        <v>7058223</v>
+        <v>7058201</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6381,12 +6381,12 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Fredrik Wilde</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Fredrik Wilde</t>
+          <t>Liam Sebestyén, Philipp Weiss, Miriam Schenk, Cajsa Björkén, Fredrik Wilde, Alva Danielsson, Elke Blöhbaum, Vilhelm Kroon, Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr">
@@ -6508,10 +6508,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>126879133</v>
+        <v>126889504</v>
       </c>
       <c r="B58" t="n">
-        <v>79046</v>
+        <v>79014</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6519,34 +6519,34 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Kravattensliden, Kravattensliden, Ång</t>
+          <t>Kravattensliden, Ång</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>673041</v>
+        <v>672853</v>
       </c>
       <c r="R58" t="n">
-        <v>7058262</v>
+        <v>7058173</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6593,12 +6593,12 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Fredrik Wilde</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Fredrik Wilde</t>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Fredrik Wilde, Alva Danielsson, Emil Lindgren, Mattias Dalkvist, Elke Blöhbaum, Miriam Schenk, Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr">
@@ -6609,10 +6609,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>126889504</v>
+        <v>126879133</v>
       </c>
       <c r="B59" t="n">
-        <v>79014</v>
+        <v>79046</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6620,34 +6620,34 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Kravattensliden, Ång</t>
+          <t>Kravattensliden, Kravattensliden, Ång</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>672853</v>
+        <v>673041</v>
       </c>
       <c r="R59" t="n">
-        <v>7058173</v>
+        <v>7058262</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6694,12 +6694,12 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Fredrik Wilde</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Fredrik Wilde, Alva Danielsson, Emil Lindgren, Mattias Dalkvist, Elke Blöhbaum, Miriam Schenk, Vilhelm Kroon</t>
+          <t>Fredrik Wilde</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr">
@@ -7139,10 +7139,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>126879033</v>
+        <v>126879425</v>
       </c>
       <c r="B64" t="n">
-        <v>79046</v>
+        <v>79014</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7150,43 +7150,34 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J64" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
           <t>Kravattensliden, Kravattensliden, Ång</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>673046</v>
+        <v>672947</v>
       </c>
       <c r="R64" t="n">
-        <v>7058286</v>
+        <v>7058198</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7249,45 +7240,50 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>126891312</v>
+        <v>126889382</v>
       </c>
       <c r="B65" t="n">
-        <v>91290</v>
+        <v>57654</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>5447</v>
+        <v>100049</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P65" t="inlineStr">
         <is>
           <t>Kravattensliden, Ång</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>673027</v>
+        <v>672838</v>
       </c>
       <c r="R65" t="n">
-        <v>7058282</v>
+        <v>7058134</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7334,12 +7330,12 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Liam Sebestyén, Mattias Dalkvist, Miriam Schenk, Fredrik Wilde, Elke Blöhbaum, Emil Lindgren</t>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Fredrik Wilde, Alva Danielsson, Emil Lindgren, Mattias Dalkvist, Elke Blöhbaum, Miriam Schenk, Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr">
@@ -7350,10 +7346,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>126879425</v>
+        <v>126879033</v>
       </c>
       <c r="B66" t="n">
-        <v>79014</v>
+        <v>79046</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7361,34 +7357,43 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr"/>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P66" t="inlineStr">
         <is>
           <t>Kravattensliden, Kravattensliden, Ång</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>672947</v>
+        <v>673046</v>
       </c>
       <c r="R66" t="n">
-        <v>7058198</v>
+        <v>7058286</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7451,10 +7456,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>126880532</v>
+        <v>126891312</v>
       </c>
       <c r="B67" t="n">
-        <v>80146</v>
+        <v>91290</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7462,34 +7467,34 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6462</v>
+        <v>5447</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Kravattensliden, Kravattensliden, Ång</t>
+          <t>Kravattensliden, Ång</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>672863</v>
+        <v>673027</v>
       </c>
       <c r="R67" t="n">
-        <v>7058124</v>
+        <v>7058282</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7536,12 +7541,12 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Fredrik Wilde</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Fredrik Wilde</t>
+          <t>Alva Danielsson, Liam Sebestyén, Mattias Dalkvist, Miriam Schenk, Fredrik Wilde, Elke Blöhbaum, Emil Lindgren</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr">
@@ -7552,50 +7557,45 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>126889382</v>
+        <v>126880532</v>
       </c>
       <c r="B68" t="n">
-        <v>57654</v>
+        <v>80146</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>100049</v>
+        <v>6462</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
-      <c r="M68" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Kravattensliden, Ång</t>
+          <t>Kravattensliden, Kravattensliden, Ång</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>672838</v>
+        <v>672863</v>
       </c>
       <c r="R68" t="n">
-        <v>7058134</v>
+        <v>7058124</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7642,12 +7642,12 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Fredrik Wilde</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Fredrik Wilde, Alva Danielsson, Emil Lindgren, Mattias Dalkvist, Elke Blöhbaum, Miriam Schenk, Vilhelm Kroon</t>
+          <t>Fredrik Wilde</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr">
@@ -7658,32 +7658,32 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>126890370</v>
+        <v>126890401</v>
       </c>
       <c r="B69" t="n">
-        <v>80146</v>
+        <v>79014</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7693,10 +7693,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>672554</v>
+        <v>672705</v>
       </c>
       <c r="R69" t="n">
-        <v>7058145</v>
+        <v>7058080</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7759,7 +7759,7 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>126890401</v>
+        <v>126890408</v>
       </c>
       <c r="B70" t="n">
         <v>79014</v>
@@ -7794,10 +7794,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>672705</v>
+        <v>672874</v>
       </c>
       <c r="R70" t="n">
-        <v>7058080</v>
+        <v>7058313</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7860,32 +7860,32 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>126890408</v>
+        <v>126890370</v>
       </c>
       <c r="B71" t="n">
-        <v>79014</v>
+        <v>80146</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7895,10 +7895,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>672874</v>
+        <v>672554</v>
       </c>
       <c r="R71" t="n">
-        <v>7058313</v>
+        <v>7058145</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8163,10 +8163,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>126890387</v>
+        <v>126890407</v>
       </c>
       <c r="B74" t="n">
-        <v>80117</v>
+        <v>79014</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8174,21 +8174,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8198,10 +8198,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>672556</v>
+        <v>672859</v>
       </c>
       <c r="R74" t="n">
-        <v>7058143</v>
+        <v>7058290</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8264,10 +8264,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>126890407</v>
+        <v>126890387</v>
       </c>
       <c r="B75" t="n">
-        <v>79014</v>
+        <v>80117</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8275,21 +8275,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8299,10 +8299,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>672859</v>
+        <v>672556</v>
       </c>
       <c r="R75" t="n">
-        <v>7058290</v>
+        <v>7058143</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -9173,10 +9173,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>126890352</v>
+        <v>126890403</v>
       </c>
       <c r="B84" t="n">
-        <v>79046</v>
+        <v>79014</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9184,21 +9184,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9208,10 +9208,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>672847</v>
+        <v>672796</v>
       </c>
       <c r="R84" t="n">
-        <v>7058276</v>
+        <v>7058317</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9274,10 +9274,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>126890403</v>
+        <v>126890352</v>
       </c>
       <c r="B85" t="n">
-        <v>79014</v>
+        <v>79046</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9285,21 +9285,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9309,10 +9309,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>672796</v>
+        <v>672847</v>
       </c>
       <c r="R85" t="n">
-        <v>7058317</v>
+        <v>7058276</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>

--- a/artfynd/A 27938-2023 artfynd.xlsx
+++ b/artfynd/A 27938-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126879850</v>
       </c>
       <c r="B2" t="n">
-        <v>88728</v>
+        <v>88729</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>126889312</v>
       </c>
       <c r="B3" t="n">
-        <v>91290</v>
+        <v>91291</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -880,7 +880,7 @@
         <v>126889833</v>
       </c>
       <c r="B4" t="n">
-        <v>91290</v>
+        <v>91291</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -981,7 +981,7 @@
         <v>126889402</v>
       </c>
       <c r="B5" t="n">
-        <v>97320</v>
+        <v>97321</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1079,10 +1079,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126892811</v>
+        <v>126892805</v>
       </c>
       <c r="B6" t="n">
-        <v>79046</v>
+        <v>57657</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1090,21 +1090,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>185</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1114,10 +1114,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>672792</v>
+        <v>672877</v>
       </c>
       <c r="R6" t="n">
-        <v>7058076</v>
+        <v>7058189</v>
       </c>
       <c r="S6" t="n">
         <v>4</v>
@@ -1149,7 +1149,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1159,7 +1159,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>11:15</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Gamla ringhack</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1291,10 +1296,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126892805</v>
+        <v>126892811</v>
       </c>
       <c r="B8" t="n">
-        <v>57657</v>
+        <v>79046</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1302,21 +1307,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>185</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1326,10 +1331,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>672877</v>
+        <v>672792</v>
       </c>
       <c r="R8" t="n">
-        <v>7058189</v>
+        <v>7058076</v>
       </c>
       <c r="S8" t="n">
         <v>4</v>
@@ -1361,7 +1366,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1371,12 +1376,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:15</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Gamla ringhack</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1410,7 +1410,7 @@
         <v>126891323</v>
       </c>
       <c r="B9" t="n">
-        <v>91343</v>
+        <v>91344</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -2028,32 +2028,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126889835</v>
+        <v>126889492</v>
       </c>
       <c r="B15" t="n">
-        <v>91290</v>
+        <v>79014</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2063,10 +2063,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>672843</v>
+        <v>672638</v>
       </c>
       <c r="R15" t="n">
-        <v>7058124</v>
+        <v>7057953</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2113,12 +2113,12 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Philipp Weiss, Miriam Schenk, Cajsa Björkén, Fredrik Wilde, Alva Danielsson, Elke Blöhbaum, Vilhelm Kroon, Mattias Dalkvist</t>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Fredrik Wilde, Alva Danielsson, Emil Lindgren, Mattias Dalkvist, Elke Blöhbaum, Miriam Schenk, Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
@@ -2129,32 +2129,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>126889492</v>
+        <v>126889835</v>
       </c>
       <c r="B16" t="n">
-        <v>79014</v>
+        <v>91291</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2164,10 +2164,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>672638</v>
+        <v>672843</v>
       </c>
       <c r="R16" t="n">
-        <v>7057953</v>
+        <v>7058124</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2214,12 +2214,12 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Fredrik Wilde, Alva Danielsson, Emil Lindgren, Mattias Dalkvist, Elke Blöhbaum, Miriam Schenk, Vilhelm Kroon</t>
+          <t>Liam Sebestyén, Philipp Weiss, Miriam Schenk, Cajsa Björkén, Fredrik Wilde, Alva Danielsson, Elke Blöhbaum, Vilhelm Kroon, Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
@@ -2233,7 +2233,7 @@
         <v>126891315</v>
       </c>
       <c r="B17" t="n">
-        <v>98463</v>
+        <v>98464</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2331,32 +2331,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>126891131</v>
+        <v>126892810</v>
       </c>
       <c r="B18" t="n">
-        <v>79046</v>
+        <v>91291</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>185</v>
+        <v>5447</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2366,13 +2366,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>672898</v>
+        <v>672801</v>
       </c>
       <c r="R18" t="n">
-        <v>7058209</v>
+        <v>7058081</v>
       </c>
       <c r="S18" t="n">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2399,30 +2399,39 @@
           <t>2025-07-24</t>
         </is>
       </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>11:35</t>
+        </is>
+      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-07-24</t>
         </is>
       </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>11:35</t>
+        </is>
+      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Miriam Schenk</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Miriam Schenk, Cajsa Björkén, Fredrik Wilde, Philipp Weiss, Mattias Dalkvist, Vilhelm Kroon, Liam Sebestyén, Emil Lindgren, Alva Danielsson</t>
+          <t>Mattias Dalkvist, Fredrik Wilde, Liam Sebestyén, Alva Danielsson, Elke Blöhbaum, Vilhelm Kroon, Miriam Schenk, Cajsa Björkén, Philipp Weiss, Emil Lindgren</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
@@ -2433,32 +2442,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>126892810</v>
+        <v>126892808</v>
       </c>
       <c r="B19" t="n">
-        <v>91290</v>
+        <v>79014</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2468,13 +2477,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>672801</v>
+        <v>672862</v>
       </c>
       <c r="R19" t="n">
-        <v>7058081</v>
+        <v>7058125</v>
       </c>
       <c r="S19" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2503,7 +2512,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2513,7 +2522,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2544,10 +2553,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>126892808</v>
+        <v>126891131</v>
       </c>
       <c r="B20" t="n">
-        <v>79014</v>
+        <v>79046</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2555,21 +2564,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2579,13 +2588,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>672862</v>
+        <v>672898</v>
       </c>
       <c r="R20" t="n">
-        <v>7058125</v>
+        <v>7058209</v>
       </c>
       <c r="S20" t="n">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2612,39 +2621,30 @@
           <t>2025-07-24</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>11:25</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-07-24</t>
         </is>
       </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>11:25</t>
-        </is>
-      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Miriam Schenk</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist, Fredrik Wilde, Liam Sebestyén, Alva Danielsson, Elke Blöhbaum, Vilhelm Kroon, Miriam Schenk, Cajsa Björkén, Philipp Weiss, Emil Lindgren</t>
+          <t>Miriam Schenk, Cajsa Björkén, Fredrik Wilde, Philipp Weiss, Mattias Dalkvist, Vilhelm Kroon, Liam Sebestyén, Emil Lindgren, Alva Danielsson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
@@ -2761,10 +2761,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>126889311</v>
+        <v>126889869</v>
       </c>
       <c r="B22" t="n">
-        <v>91290</v>
+        <v>98360</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2772,21 +2772,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5447</v>
+        <v>219790</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2796,10 +2796,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>672799</v>
+        <v>672855</v>
       </c>
       <c r="R22" t="n">
-        <v>7058086</v>
+        <v>7058116</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2846,12 +2846,12 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Fredrik Wilde, Alva Danielsson, Emil Lindgren, Mattias Dalkvist, Elke Blöhbaum, Miriam Schenk, Vilhelm Kroon</t>
+          <t>Liam Sebestyén, Philipp Weiss, Miriam Schenk, Cajsa Björkén, Fredrik Wilde, Alva Danielsson, Elke Blöhbaum, Vilhelm Kroon, Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
@@ -2862,10 +2862,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>126891314</v>
+        <v>126889311</v>
       </c>
       <c r="B23" t="n">
-        <v>80146</v>
+        <v>91291</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2873,21 +2873,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6462</v>
+        <v>5447</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2897,10 +2897,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>672999</v>
+        <v>672799</v>
       </c>
       <c r="R23" t="n">
-        <v>7058211</v>
+        <v>7058086</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2947,12 +2947,12 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Liam Sebestyén, Mattias Dalkvist, Miriam Schenk, Fredrik Wilde, Elke Blöhbaum, Emil Lindgren</t>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Fredrik Wilde, Alva Danielsson, Emil Lindgren, Mattias Dalkvist, Elke Blöhbaum, Miriam Schenk, Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">
@@ -2963,10 +2963,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>126889869</v>
+        <v>126891314</v>
       </c>
       <c r="B24" t="n">
-        <v>98359</v>
+        <v>80146</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2974,21 +2974,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>219790</v>
+        <v>6462</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2998,10 +2998,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>672855</v>
+        <v>672999</v>
       </c>
       <c r="R24" t="n">
-        <v>7058116</v>
+        <v>7058211</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3048,12 +3048,12 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Philipp Weiss, Miriam Schenk, Cajsa Björkén, Fredrik Wilde, Alva Danielsson, Elke Blöhbaum, Vilhelm Kroon, Mattias Dalkvist</t>
+          <t>Alva Danielsson, Liam Sebestyén, Mattias Dalkvist, Miriam Schenk, Fredrik Wilde, Elke Blöhbaum, Emil Lindgren</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr">
@@ -3067,7 +3067,7 @@
         <v>126889374</v>
       </c>
       <c r="B25" t="n">
-        <v>98463</v>
+        <v>98464</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3179,10 +3179,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>126892816</v>
+        <v>126889847</v>
       </c>
       <c r="B26" t="n">
-        <v>79014</v>
+        <v>57654</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3190,37 +3190,45 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Kravattensliden, Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>672627</v>
+        <v>672981</v>
       </c>
       <c r="R26" t="n">
-        <v>7058024</v>
+        <v>7058264</v>
       </c>
       <c r="S26" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3247,19 +3255,9 @@
           <t>2025-07-24</t>
         </is>
       </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>11:52</t>
-        </is>
-      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-07-24</t>
-        </is>
-      </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>11:52</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3274,12 +3272,12 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist, Fredrik Wilde, Liam Sebestyén, Alva Danielsson, Elke Blöhbaum, Vilhelm Kroon, Miriam Schenk, Cajsa Björkén, Philipp Weiss, Emil Lindgren</t>
+          <t>Liam Sebestyén, Philipp Weiss, Miriam Schenk, Cajsa Björkén, Fredrik Wilde, Alva Danielsson, Elke Blöhbaum, Vilhelm Kroon, Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr">
@@ -3290,7 +3288,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>126893730</v>
+        <v>126892816</v>
       </c>
       <c r="B27" t="n">
         <v>79014</v>
@@ -3325,13 +3323,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>672929</v>
+        <v>672627</v>
       </c>
       <c r="R27" t="n">
-        <v>7058213</v>
+        <v>7058024</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3358,9 +3356,19 @@
           <t>2025-07-24</t>
         </is>
       </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>11:52</t>
+        </is>
+      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-07-24</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3375,12 +3383,12 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Fredrik Wilde, Liam Sebestyén, Elke Blöhbaum, Miriam Schenk, Mattias Dalkvist, Emil Lindgren</t>
+          <t>Mattias Dalkvist, Fredrik Wilde, Liam Sebestyén, Alva Danielsson, Elke Blöhbaum, Vilhelm Kroon, Miriam Schenk, Cajsa Björkén, Philipp Weiss, Emil Lindgren</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr">
@@ -3391,7 +3399,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>126889502</v>
+        <v>126893730</v>
       </c>
       <c r="B28" t="n">
         <v>79014</v>
@@ -3426,10 +3434,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>672801</v>
+        <v>672929</v>
       </c>
       <c r="R28" t="n">
-        <v>7058095</v>
+        <v>7058213</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3476,12 +3484,12 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Fredrik Wilde, Alva Danielsson, Emil Lindgren, Mattias Dalkvist, Elke Blöhbaum, Miriam Schenk, Vilhelm Kroon</t>
+          <t>Alva Danielsson, Fredrik Wilde, Liam Sebestyén, Elke Blöhbaum, Miriam Schenk, Mattias Dalkvist, Emil Lindgren</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr">
@@ -3492,10 +3500,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>126889847</v>
+        <v>126889502</v>
       </c>
       <c r="B29" t="n">
-        <v>57654</v>
+        <v>79014</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3503,42 +3511,34 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Kravattensliden, Ång</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>672981</v>
+        <v>672801</v>
       </c>
       <c r="R29" t="n">
-        <v>7058264</v>
+        <v>7058095</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3585,12 +3585,12 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Philipp Weiss, Miriam Schenk, Cajsa Björkén, Fredrik Wilde, Alva Danielsson, Elke Blöhbaum, Vilhelm Kroon, Mattias Dalkvist</t>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Fredrik Wilde, Alva Danielsson, Emil Lindgren, Mattias Dalkvist, Elke Blöhbaum, Miriam Schenk, Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr">
@@ -3803,10 +3803,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>126889536</v>
+        <v>126889377</v>
       </c>
       <c r="B32" t="n">
-        <v>5176</v>
+        <v>98464</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3814,27 +3814,36 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100526</v>
+        <v>221952</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
@@ -3843,10 +3852,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>672659</v>
+        <v>672810</v>
       </c>
       <c r="R32" t="n">
-        <v>7057975</v>
+        <v>7058105</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3909,10 +3918,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>126889377</v>
+        <v>126889536</v>
       </c>
       <c r="B33" t="n">
-        <v>98463</v>
+        <v>5176</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3920,36 +3929,27 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>221952</v>
+        <v>100526</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>överblommad</t>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
@@ -3958,10 +3958,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>672810</v>
+        <v>672659</v>
       </c>
       <c r="R33" t="n">
-        <v>7058105</v>
+        <v>7057975</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4024,10 +4024,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>126889834</v>
+        <v>126891134</v>
       </c>
       <c r="B34" t="n">
-        <v>91290</v>
+        <v>80146</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4035,21 +4035,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>5447</v>
+        <v>6462</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4059,13 +4059,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>672819</v>
+        <v>673029</v>
       </c>
       <c r="R34" t="n">
-        <v>7058089</v>
+        <v>7058247</v>
       </c>
       <c r="S34" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4109,12 +4109,12 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Miriam Schenk</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Philipp Weiss, Miriam Schenk, Cajsa Björkén, Fredrik Wilde, Alva Danielsson, Elke Blöhbaum, Vilhelm Kroon, Mattias Dalkvist</t>
+          <t>Miriam Schenk, Cajsa Björkén, Fredrik Wilde, Philipp Weiss, Mattias Dalkvist, Vilhelm Kroon, Liam Sebestyén, Emil Lindgren, Alva Danielsson</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr">
@@ -4125,10 +4125,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>126891134</v>
+        <v>126889834</v>
       </c>
       <c r="B35" t="n">
-        <v>80146</v>
+        <v>91291</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4136,21 +4136,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6462</v>
+        <v>5447</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4160,13 +4160,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>673029</v>
+        <v>672819</v>
       </c>
       <c r="R35" t="n">
-        <v>7058247</v>
+        <v>7058089</v>
       </c>
       <c r="S35" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4210,12 +4210,12 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Miriam Schenk</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Miriam Schenk, Cajsa Björkén, Fredrik Wilde, Philipp Weiss, Mattias Dalkvist, Vilhelm Kroon, Liam Sebestyén, Emil Lindgren, Alva Danielsson</t>
+          <t>Liam Sebestyén, Philipp Weiss, Miriam Schenk, Cajsa Björkén, Fredrik Wilde, Alva Danielsson, Elke Blöhbaum, Vilhelm Kroon, Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr">
@@ -4229,7 +4229,7 @@
         <v>126893692</v>
       </c>
       <c r="B36" t="n">
-        <v>91325</v>
+        <v>91326</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4335,7 +4335,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>126890308</v>
+        <v>126892813</v>
       </c>
       <c r="B37" t="n">
         <v>79014</v>
@@ -4370,13 +4370,13 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>672880</v>
+        <v>672661</v>
       </c>
       <c r="R37" t="n">
-        <v>7058209</v>
+        <v>7058026</v>
       </c>
       <c r="S37" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4403,9 +4403,19 @@
           <t>2025-07-24</t>
         </is>
       </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>11:51</t>
+        </is>
+      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-07-24</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4420,12 +4430,12 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon, Cajsa Björkén, Fredrik Wilde, Mattias Dalkvist, Philipp Weiss, Miriam Schenk, Liam Sebestyén, Alva Danielsson, Emil Lindgren</t>
+          <t>Mattias Dalkvist, Fredrik Wilde, Liam Sebestyén, Alva Danielsson, Elke Blöhbaum, Vilhelm Kroon, Miriam Schenk, Cajsa Björkén, Philipp Weiss, Emil Lindgren</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr">
@@ -4436,10 +4446,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>126891320</v>
+        <v>126890308</v>
       </c>
       <c r="B38" t="n">
-        <v>80117</v>
+        <v>79014</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4447,21 +4457,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4471,13 +4481,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>672929</v>
+        <v>672880</v>
       </c>
       <c r="R38" t="n">
-        <v>7058203</v>
+        <v>7058209</v>
       </c>
       <c r="S38" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4521,12 +4531,12 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Liam Sebestyén, Mattias Dalkvist, Miriam Schenk, Fredrik Wilde, Elke Blöhbaum, Emil Lindgren</t>
+          <t>Vilhelm Kroon, Cajsa Björkén, Fredrik Wilde, Mattias Dalkvist, Philipp Weiss, Miriam Schenk, Liam Sebestyén, Alva Danielsson, Emil Lindgren</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr">
@@ -4537,10 +4547,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>126892814</v>
+        <v>126891320</v>
       </c>
       <c r="B39" t="n">
-        <v>79046</v>
+        <v>80117</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4548,21 +4558,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>185</v>
+        <v>6458</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4572,13 +4582,13 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>672659</v>
+        <v>672929</v>
       </c>
       <c r="R39" t="n">
-        <v>7058027</v>
+        <v>7058203</v>
       </c>
       <c r="S39" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4605,19 +4615,9 @@
           <t>2025-07-24</t>
         </is>
       </c>
-      <c r="Z39" t="inlineStr">
-        <is>
-          <t>11:51</t>
-        </is>
-      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-07-24</t>
-        </is>
-      </c>
-      <c r="AB39" t="inlineStr">
-        <is>
-          <t>11:51</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4632,12 +4632,12 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist, Fredrik Wilde, Liam Sebestyén, Alva Danielsson, Elke Blöhbaum, Vilhelm Kroon, Miriam Schenk, Cajsa Björkén, Philipp Weiss, Emil Lindgren</t>
+          <t>Alva Danielsson, Liam Sebestyén, Mattias Dalkvist, Miriam Schenk, Fredrik Wilde, Elke Blöhbaum, Emil Lindgren</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr">
@@ -4648,10 +4648,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>126892813</v>
+        <v>126892814</v>
       </c>
       <c r="B40" t="n">
-        <v>79014</v>
+        <v>79046</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4659,21 +4659,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4683,13 +4683,13 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>672661</v>
+        <v>672659</v>
       </c>
       <c r="R40" t="n">
-        <v>7058026</v>
+        <v>7058027</v>
       </c>
       <c r="S40" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4864,45 +4864,52 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>126880507</v>
+        <v>126893671</v>
       </c>
       <c r="B42" t="n">
-        <v>82855</v>
+        <v>91291</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1312</v>
+        <v>5447</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr"/>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Kravattensliden, Kravattensliden, Ång</t>
+          <t>Kravattensliden , Ång</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>672859</v>
+        <v>672808</v>
       </c>
       <c r="R42" t="n">
-        <v>7058136</v>
+        <v>7058090</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4943,18 +4950,19 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
+      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Fredrik Wilde</t>
+          <t>Emil Lindgren</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Fredrik Wilde</t>
+          <t>Emil Lindgren</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr">
@@ -4965,52 +4973,45 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>126893671</v>
+        <v>126880507</v>
       </c>
       <c r="B43" t="n">
-        <v>91290</v>
+        <v>82855</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>5447</v>
+        <v>1312</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="J43" t="inlineStr"/>
-      <c r="K43" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Kravattensliden , Ång</t>
+          <t>Kravattensliden, Kravattensliden, Ång</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>672808</v>
+        <v>672859</v>
       </c>
       <c r="R43" t="n">
-        <v>7058090</v>
+        <v>7058136</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5051,19 +5052,18 @@
       <c r="AE43" t="b">
         <v>0</v>
       </c>
-      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Emil Lindgren</t>
+          <t>Fredrik Wilde</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Emil Lindgren</t>
+          <t>Fredrik Wilde</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr">
@@ -5387,10 +5387,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>126890311</v>
+        <v>126890305</v>
       </c>
       <c r="B47" t="n">
-        <v>88728</v>
+        <v>79014</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5398,21 +5398,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>510</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5422,10 +5422,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>673023</v>
+        <v>672724</v>
       </c>
       <c r="R47" t="n">
-        <v>7058218</v>
+        <v>7058075</v>
       </c>
       <c r="S47" t="n">
         <v>15</v>
@@ -5488,7 +5488,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>126890305</v>
+        <v>126889494</v>
       </c>
       <c r="B48" t="n">
         <v>79014</v>
@@ -5523,13 +5523,13 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>672724</v>
+        <v>672657</v>
       </c>
       <c r="R48" t="n">
-        <v>7058075</v>
+        <v>7057974</v>
       </c>
       <c r="S48" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5573,12 +5573,12 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon, Cajsa Björkén, Fredrik Wilde, Mattias Dalkvist, Philipp Weiss, Miriam Schenk, Liam Sebestyén, Alva Danielsson, Emil Lindgren</t>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Fredrik Wilde, Alva Danielsson, Emil Lindgren, Mattias Dalkvist, Elke Blöhbaum, Miriam Schenk, Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr">
@@ -5589,10 +5589,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>126889494</v>
+        <v>126890311</v>
       </c>
       <c r="B49" t="n">
-        <v>79014</v>
+        <v>88729</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5600,21 +5600,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>510</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5624,13 +5624,13 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>672657</v>
+        <v>673023</v>
       </c>
       <c r="R49" t="n">
-        <v>7057974</v>
+        <v>7058218</v>
       </c>
       <c r="S49" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5674,12 +5674,12 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Fredrik Wilde, Alva Danielsson, Emil Lindgren, Mattias Dalkvist, Elke Blöhbaum, Miriam Schenk, Vilhelm Kroon</t>
+          <t>Vilhelm Kroon, Cajsa Björkén, Fredrik Wilde, Mattias Dalkvist, Philipp Weiss, Miriam Schenk, Liam Sebestyén, Alva Danielsson, Emil Lindgren</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr">
@@ -5791,10 +5791,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>126893733</v>
+        <v>126889837</v>
       </c>
       <c r="B51" t="n">
-        <v>98359</v>
+        <v>91291</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5802,21 +5802,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>219790</v>
+        <v>5447</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5826,10 +5826,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>672989</v>
+        <v>672912</v>
       </c>
       <c r="R51" t="n">
-        <v>7058233</v>
+        <v>7058191</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5876,12 +5876,12 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Fredrik Wilde, Emil Lindgren, Mattias Dalkvist, Miriam Schenk, Elke Blöhbaum, Liam Sebestyén</t>
+          <t>Liam Sebestyén, Philipp Weiss, Miriam Schenk, Cajsa Björkén, Fredrik Wilde, Alva Danielsson, Elke Blöhbaum, Vilhelm Kroon, Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr">
@@ -5895,7 +5895,7 @@
         <v>126889862</v>
       </c>
       <c r="B52" t="n">
-        <v>91343</v>
+        <v>91344</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5993,32 +5993,32 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>126889837</v>
+        <v>126889856</v>
       </c>
       <c r="B53" t="n">
-        <v>91290</v>
+        <v>80117</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>5447</v>
+        <v>6458</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6028,10 +6028,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>672912</v>
+        <v>672929</v>
       </c>
       <c r="R53" t="n">
-        <v>7058191</v>
+        <v>7058201</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6094,7 +6094,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>126891325</v>
+        <v>126879684</v>
       </c>
       <c r="B54" t="n">
         <v>79014</v>
@@ -6125,14 +6125,14 @@
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Kravattensliden, Ång</t>
+          <t>Kravattensliden, Kravattensliden, Ång</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>672660</v>
+        <v>672895</v>
       </c>
       <c r="R54" t="n">
-        <v>7057985</v>
+        <v>7058223</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6179,12 +6179,12 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Fredrik Wilde</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Liam Sebestyén, Mattias Dalkvist, Miriam Schenk, Fredrik Wilde, Elke Blöhbaum, Emil Lindgren</t>
+          <t>Fredrik Wilde</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr">
@@ -6195,7 +6195,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>126879684</v>
+        <v>126891325</v>
       </c>
       <c r="B55" t="n">
         <v>79014</v>
@@ -6226,14 +6226,14 @@
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Kravattensliden, Kravattensliden, Ång</t>
+          <t>Kravattensliden, Ång</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>672895</v>
+        <v>672660</v>
       </c>
       <c r="R55" t="n">
-        <v>7058223</v>
+        <v>7057985</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6280,12 +6280,12 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Fredrik Wilde</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Fredrik Wilde</t>
+          <t>Alva Danielsson, Liam Sebestyén, Mattias Dalkvist, Miriam Schenk, Fredrik Wilde, Elke Blöhbaum, Emil Lindgren</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr">
@@ -6296,32 +6296,32 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>126889856</v>
+        <v>126893733</v>
       </c>
       <c r="B56" t="n">
-        <v>80117</v>
+        <v>98360</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6458</v>
+        <v>219790</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6331,10 +6331,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>672929</v>
+        <v>672989</v>
       </c>
       <c r="R56" t="n">
-        <v>7058201</v>
+        <v>7058233</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6381,12 +6381,12 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Philipp Weiss, Miriam Schenk, Cajsa Björkén, Fredrik Wilde, Alva Danielsson, Elke Blöhbaum, Vilhelm Kroon, Mattias Dalkvist</t>
+          <t>Alva Danielsson, Fredrik Wilde, Liam Sebestyén, Elke Blöhbaum, Miriam Schenk, Mattias Dalkvist, Emil Lindgren</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr">
@@ -6397,7 +6397,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>126892806</v>
+        <v>126889504</v>
       </c>
       <c r="B57" t="n">
         <v>79014</v>
@@ -6432,10 +6432,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>672883</v>
+        <v>672853</v>
       </c>
       <c r="R57" t="n">
-        <v>7058166</v>
+        <v>7058173</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6465,19 +6465,9 @@
           <t>2025-07-24</t>
         </is>
       </c>
-      <c r="Z57" t="inlineStr">
-        <is>
-          <t>11:18</t>
-        </is>
-      </c>
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-07-24</t>
-        </is>
-      </c>
-      <c r="AB57" t="inlineStr">
-        <is>
-          <t>11:18</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6492,12 +6482,12 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist, Fredrik Wilde, Liam Sebestyén, Alva Danielsson, Elke Blöhbaum, Vilhelm Kroon, Miriam Schenk, Cajsa Björkén, Philipp Weiss, Emil Lindgren</t>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Fredrik Wilde, Alva Danielsson, Emil Lindgren, Mattias Dalkvist, Elke Blöhbaum, Miriam Schenk, Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr">
@@ -6508,10 +6498,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>126889504</v>
+        <v>126879133</v>
       </c>
       <c r="B58" t="n">
-        <v>79014</v>
+        <v>79046</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6519,34 +6509,34 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Kravattensliden, Ång</t>
+          <t>Kravattensliden, Kravattensliden, Ång</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>672853</v>
+        <v>673041</v>
       </c>
       <c r="R58" t="n">
-        <v>7058173</v>
+        <v>7058262</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6593,12 +6583,12 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Fredrik Wilde</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Fredrik Wilde, Alva Danielsson, Emil Lindgren, Mattias Dalkvist, Elke Blöhbaum, Miriam Schenk, Vilhelm Kroon</t>
+          <t>Fredrik Wilde</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr">
@@ -6609,10 +6599,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>126879133</v>
+        <v>126892806</v>
       </c>
       <c r="B59" t="n">
-        <v>79046</v>
+        <v>79014</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6620,34 +6610,34 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Kravattensliden, Kravattensliden, Ång</t>
+          <t>Kravattensliden, Ång</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>673041</v>
+        <v>672883</v>
       </c>
       <c r="R59" t="n">
-        <v>7058262</v>
+        <v>7058166</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6677,9 +6667,19 @@
           <t>2025-07-24</t>
         </is>
       </c>
+      <c r="Z59" t="inlineStr">
+        <is>
+          <t>11:18</t>
+        </is>
+      </c>
       <c r="AA59" t="inlineStr">
         <is>
           <t>2025-07-24</t>
+        </is>
+      </c>
+      <c r="AB59" t="inlineStr">
+        <is>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6694,12 +6694,12 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Fredrik Wilde</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Fredrik Wilde</t>
+          <t>Mattias Dalkvist, Fredrik Wilde, Liam Sebestyén, Alva Danielsson, Elke Blöhbaum, Vilhelm Kroon, Miriam Schenk, Cajsa Björkén, Philipp Weiss, Emil Lindgren</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr">
@@ -6710,7 +6710,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>126892812</v>
+        <v>126880199</v>
       </c>
       <c r="B60" t="n">
         <v>79014</v>
@@ -6739,19 +6739,24 @@
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Kravattensliden, Ång</t>
+          <t>Kravattensliden, Kravattensliden, Ång</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>672685</v>
+        <v>672894</v>
       </c>
       <c r="R60" t="n">
-        <v>7058010</v>
+        <v>7058198</v>
       </c>
       <c r="S60" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -6778,19 +6783,9 @@
           <t>2025-07-24</t>
         </is>
       </c>
-      <c r="Z60" t="inlineStr">
-        <is>
-          <t>11:41</t>
-        </is>
-      </c>
       <c r="AA60" t="inlineStr">
         <is>
           <t>2025-07-24</t>
-        </is>
-      </c>
-      <c r="AB60" t="inlineStr">
-        <is>
-          <t>11:41</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6805,12 +6800,12 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Fredrik Wilde</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist, Fredrik Wilde, Liam Sebestyén, Alva Danielsson, Elke Blöhbaum, Vilhelm Kroon, Miriam Schenk, Cajsa Björkén, Philipp Weiss, Emil Lindgren</t>
+          <t>Fredrik Wilde</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr">
@@ -7033,7 +7028,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>126880199</v>
+        <v>126892812</v>
       </c>
       <c r="B63" t="n">
         <v>79014</v>
@@ -7062,24 +7057,19 @@
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
-      <c r="K63" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Kravattensliden, Kravattensliden, Ång</t>
+          <t>Kravattensliden, Ång</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>672894</v>
+        <v>672685</v>
       </c>
       <c r="R63" t="n">
-        <v>7058198</v>
+        <v>7058010</v>
       </c>
       <c r="S63" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7106,9 +7096,19 @@
           <t>2025-07-24</t>
         </is>
       </c>
+      <c r="Z63" t="inlineStr">
+        <is>
+          <t>11:41</t>
+        </is>
+      </c>
       <c r="AA63" t="inlineStr">
         <is>
           <t>2025-07-24</t>
+        </is>
+      </c>
+      <c r="AB63" t="inlineStr">
+        <is>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7123,12 +7123,12 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Fredrik Wilde</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Fredrik Wilde</t>
+          <t>Mattias Dalkvist, Fredrik Wilde, Liam Sebestyén, Alva Danielsson, Elke Blöhbaum, Vilhelm Kroon, Miriam Schenk, Cajsa Björkén, Philipp Weiss, Emil Lindgren</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr">
@@ -7139,45 +7139,45 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>126879425</v>
+        <v>126891312</v>
       </c>
       <c r="B64" t="n">
-        <v>79014</v>
+        <v>91291</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Kravattensliden, Kravattensliden, Ång</t>
+          <t>Kravattensliden, Ång</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>672947</v>
+        <v>673027</v>
       </c>
       <c r="R64" t="n">
-        <v>7058198</v>
+        <v>7058282</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7224,12 +7224,12 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Fredrik Wilde</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Fredrik Wilde</t>
+          <t>Alva Danielsson, Liam Sebestyén, Mattias Dalkvist, Miriam Schenk, Fredrik Wilde, Elke Blöhbaum, Emil Lindgren</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr">
@@ -7240,50 +7240,45 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>126889382</v>
+        <v>126880532</v>
       </c>
       <c r="B65" t="n">
-        <v>57654</v>
+        <v>80146</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>100049</v>
+        <v>6462</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
-      <c r="M65" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Kravattensliden, Ång</t>
+          <t>Kravattensliden, Kravattensliden, Ång</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>672838</v>
+        <v>672863</v>
       </c>
       <c r="R65" t="n">
-        <v>7058134</v>
+        <v>7058124</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7330,12 +7325,12 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Fredrik Wilde</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Fredrik Wilde, Alva Danielsson, Emil Lindgren, Mattias Dalkvist, Elke Blöhbaum, Miriam Schenk, Vilhelm Kroon</t>
+          <t>Fredrik Wilde</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr">
@@ -7346,10 +7341,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>126879033</v>
+        <v>126889382</v>
       </c>
       <c r="B66" t="n">
-        <v>79046</v>
+        <v>57654</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7357,43 +7352,39 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>185</v>
+        <v>100049</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J66" t="inlineStr">
-        <is>
-          <t>bålar</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Kravattensliden, Kravattensliden, Ång</t>
+          <t>Kravattensliden, Ång</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>673046</v>
+        <v>672838</v>
       </c>
       <c r="R66" t="n">
-        <v>7058286</v>
+        <v>7058134</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7440,12 +7431,12 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Fredrik Wilde</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Fredrik Wilde</t>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Fredrik Wilde, Alva Danielsson, Emil Lindgren, Mattias Dalkvist, Elke Blöhbaum, Miriam Schenk, Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr">
@@ -7456,45 +7447,45 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>126891312</v>
+        <v>126879425</v>
       </c>
       <c r="B67" t="n">
-        <v>91290</v>
+        <v>79014</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Kravattensliden, Ång</t>
+          <t>Kravattensliden, Kravattensliden, Ång</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>673027</v>
+        <v>672947</v>
       </c>
       <c r="R67" t="n">
-        <v>7058282</v>
+        <v>7058198</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7541,12 +7532,12 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Fredrik Wilde</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Liam Sebestyén, Mattias Dalkvist, Miriam Schenk, Fredrik Wilde, Elke Blöhbaum, Emil Lindgren</t>
+          <t>Fredrik Wilde</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr">
@@ -7557,45 +7548,54 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>126880532</v>
+        <v>126879033</v>
       </c>
       <c r="B68" t="n">
-        <v>80146</v>
+        <v>79046</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6462</v>
+        <v>185</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr"/>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P68" t="inlineStr">
         <is>
           <t>Kravattensliden, Kravattensliden, Ång</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>672863</v>
+        <v>673046</v>
       </c>
       <c r="R68" t="n">
-        <v>7058124</v>
+        <v>7058286</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8163,10 +8163,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>126890407</v>
+        <v>126890387</v>
       </c>
       <c r="B74" t="n">
-        <v>79014</v>
+        <v>80117</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8174,21 +8174,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8198,10 +8198,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>672859</v>
+        <v>672556</v>
       </c>
       <c r="R74" t="n">
-        <v>7058290</v>
+        <v>7058143</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8264,10 +8264,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>126890387</v>
+        <v>126890407</v>
       </c>
       <c r="B75" t="n">
-        <v>80117</v>
+        <v>79014</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8275,21 +8275,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8299,10 +8299,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>672556</v>
+        <v>672859</v>
       </c>
       <c r="R75" t="n">
-        <v>7058143</v>
+        <v>7058290</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8769,7 +8769,7 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>126890348</v>
+        <v>126890351</v>
       </c>
       <c r="B80" t="n">
         <v>79046</v>
@@ -8804,10 +8804,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>672587</v>
+        <v>672831</v>
       </c>
       <c r="R80" t="n">
-        <v>7058126</v>
+        <v>7058284</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8870,7 +8870,7 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>126890351</v>
+        <v>126890348</v>
       </c>
       <c r="B81" t="n">
         <v>79046</v>
@@ -8905,10 +8905,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>672831</v>
+        <v>672587</v>
       </c>
       <c r="R81" t="n">
-        <v>7058284</v>
+        <v>7058126</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>

--- a/artfynd/A 27938-2023 artfynd.xlsx
+++ b/artfynd/A 27938-2023 artfynd.xlsx
@@ -1811,10 +1811,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126892815</v>
+        <v>126889387</v>
       </c>
       <c r="B13" t="n">
-        <v>79014</v>
+        <v>57654</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1822,37 +1822,42 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Kravattensliden, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>672633</v>
+        <v>672816</v>
       </c>
       <c r="R13" t="n">
-        <v>7058033</v>
+        <v>7058123</v>
       </c>
       <c r="S13" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1879,19 +1884,9 @@
           <t>2025-07-24</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>11:52</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-07-24</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>11:52</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1906,12 +1901,12 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist, Fredrik Wilde, Liam Sebestyén, Alva Danielsson, Elke Blöhbaum, Vilhelm Kroon, Miriam Schenk, Cajsa Björkén, Philipp Weiss, Emil Lindgren</t>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Fredrik Wilde, Alva Danielsson, Emil Lindgren, Mattias Dalkvist, Elke Blöhbaum, Miriam Schenk, Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
@@ -1922,10 +1917,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126889387</v>
+        <v>126892815</v>
       </c>
       <c r="B14" t="n">
-        <v>57654</v>
+        <v>79014</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1933,42 +1928,37 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Kravattensliden, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>672816</v>
+        <v>672633</v>
       </c>
       <c r="R14" t="n">
-        <v>7058123</v>
+        <v>7058033</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -1995,9 +1985,19 @@
           <t>2025-07-24</t>
         </is>
       </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>11:52</t>
+        </is>
+      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-07-24</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2012,12 +2012,12 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Fredrik Wilde, Alva Danielsson, Emil Lindgren, Mattias Dalkvist, Elke Blöhbaum, Miriam Schenk, Vilhelm Kroon</t>
+          <t>Mattias Dalkvist, Fredrik Wilde, Liam Sebestyén, Alva Danielsson, Elke Blöhbaum, Vilhelm Kroon, Miriam Schenk, Cajsa Björkén, Philipp Weiss, Emil Lindgren</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
@@ -2028,32 +2028,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126889492</v>
+        <v>126889835</v>
       </c>
       <c r="B15" t="n">
-        <v>79014</v>
+        <v>91291</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2063,10 +2063,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>672638</v>
+        <v>672843</v>
       </c>
       <c r="R15" t="n">
-        <v>7057953</v>
+        <v>7058124</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2113,12 +2113,12 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Fredrik Wilde, Alva Danielsson, Emil Lindgren, Mattias Dalkvist, Elke Blöhbaum, Miriam Schenk, Vilhelm Kroon</t>
+          <t>Liam Sebestyén, Philipp Weiss, Miriam Schenk, Cajsa Björkén, Fredrik Wilde, Alva Danielsson, Elke Blöhbaum, Vilhelm Kroon, Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
@@ -2129,10 +2129,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>126889835</v>
+        <v>126891315</v>
       </c>
       <c r="B16" t="n">
-        <v>91291</v>
+        <v>98464</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2140,21 +2140,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5447</v>
+        <v>221952</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2164,10 +2164,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>672843</v>
+        <v>672827</v>
       </c>
       <c r="R16" t="n">
-        <v>7058124</v>
+        <v>7058099</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2214,12 +2214,12 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Philipp Weiss, Miriam Schenk, Cajsa Björkén, Fredrik Wilde, Alva Danielsson, Elke Blöhbaum, Vilhelm Kroon, Mattias Dalkvist</t>
+          <t>Alva Danielsson, Liam Sebestyén, Mattias Dalkvist, Miriam Schenk, Fredrik Wilde, Elke Blöhbaum, Emil Lindgren</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
@@ -2230,32 +2230,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>126891315</v>
+        <v>126889492</v>
       </c>
       <c r="B17" t="n">
-        <v>98464</v>
+        <v>79014</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>221952</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2265,10 +2265,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>672827</v>
+        <v>672638</v>
       </c>
       <c r="R17" t="n">
-        <v>7058099</v>
+        <v>7057953</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2315,12 +2315,12 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Liam Sebestyén, Mattias Dalkvist, Miriam Schenk, Fredrik Wilde, Elke Blöhbaum, Emil Lindgren</t>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Fredrik Wilde, Alva Danielsson, Emil Lindgren, Mattias Dalkvist, Elke Blöhbaum, Miriam Schenk, Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
@@ -3702,45 +3702,59 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>126891328</v>
+        <v>126889377</v>
       </c>
       <c r="B31" t="n">
-        <v>79014</v>
+        <v>98464</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>221952</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Kravattensliden, Ång</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>672972</v>
+        <v>672810</v>
       </c>
       <c r="R31" t="n">
-        <v>7058246</v>
+        <v>7058105</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3787,12 +3801,12 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Liam Sebestyén, Mattias Dalkvist, Miriam Schenk, Fredrik Wilde, Elke Blöhbaum, Emil Lindgren</t>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Fredrik Wilde, Alva Danielsson, Emil Lindgren, Mattias Dalkvist, Elke Blöhbaum, Miriam Schenk, Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr">
@@ -3803,59 +3817,45 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>126889377</v>
+        <v>126891328</v>
       </c>
       <c r="B32" t="n">
-        <v>98464</v>
+        <v>79014</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>221952</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K32" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Kravattensliden, Ång</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>672810</v>
+        <v>672972</v>
       </c>
       <c r="R32" t="n">
-        <v>7058105</v>
+        <v>7058246</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3902,12 +3902,12 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Fredrik Wilde, Alva Danielsson, Emil Lindgren, Mattias Dalkvist, Elke Blöhbaum, Miriam Schenk, Vilhelm Kroon</t>
+          <t>Alva Danielsson, Liam Sebestyén, Mattias Dalkvist, Miriam Schenk, Fredrik Wilde, Elke Blöhbaum, Emil Lindgren</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr">
@@ -4024,10 +4024,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>126891134</v>
+        <v>126889834</v>
       </c>
       <c r="B34" t="n">
-        <v>80146</v>
+        <v>91291</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4035,21 +4035,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6462</v>
+        <v>5447</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4059,13 +4059,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>673029</v>
+        <v>672819</v>
       </c>
       <c r="R34" t="n">
-        <v>7058247</v>
+        <v>7058089</v>
       </c>
       <c r="S34" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4109,12 +4109,12 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Miriam Schenk</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Miriam Schenk, Cajsa Björkén, Fredrik Wilde, Philipp Weiss, Mattias Dalkvist, Vilhelm Kroon, Liam Sebestyén, Emil Lindgren, Alva Danielsson</t>
+          <t>Liam Sebestyén, Philipp Weiss, Miriam Schenk, Cajsa Björkén, Fredrik Wilde, Alva Danielsson, Elke Blöhbaum, Vilhelm Kroon, Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr">
@@ -4125,45 +4125,52 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>126889834</v>
+        <v>126893692</v>
       </c>
       <c r="B35" t="n">
-        <v>91291</v>
+        <v>91326</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Kravattensliden, Ång</t>
+          <t>Kravattensliden , Ång</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>672819</v>
+        <v>672811</v>
       </c>
       <c r="R35" t="n">
-        <v>7058089</v>
+        <v>7058091</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4204,18 +4211,19 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
+      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Emil Lindgren</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Philipp Weiss, Miriam Schenk, Cajsa Björkén, Fredrik Wilde, Alva Danielsson, Elke Blöhbaum, Vilhelm Kroon, Mattias Dalkvist</t>
+          <t>Emil Lindgren</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr">
@@ -4226,55 +4234,48 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>126893692</v>
+        <v>126891134</v>
       </c>
       <c r="B36" t="n">
-        <v>91326</v>
+        <v>80146</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1202</v>
+        <v>6462</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Kravattensliden , Ång</t>
+          <t>Kravattensliden, Ång</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>672811</v>
+        <v>673029</v>
       </c>
       <c r="R36" t="n">
-        <v>7058091</v>
+        <v>7058247</v>
       </c>
       <c r="S36" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4312,19 +4313,18 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
-      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Emil Lindgren</t>
+          <t>Miriam Schenk</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Emil Lindgren</t>
+          <t>Miriam Schenk, Cajsa Björkén, Fredrik Wilde, Philipp Weiss, Mattias Dalkvist, Vilhelm Kroon, Liam Sebestyén, Emil Lindgren, Alva Danielsson</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr">
@@ -4973,10 +4973,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>126880507</v>
+        <v>126892804</v>
       </c>
       <c r="B43" t="n">
-        <v>82855</v>
+        <v>79014</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4984,37 +4984,37 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Kravattensliden, Kravattensliden, Ång</t>
+          <t>Kravattensliden, Ång</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>672859</v>
+        <v>673003</v>
       </c>
       <c r="R43" t="n">
-        <v>7058136</v>
+        <v>7058280</v>
       </c>
       <c r="S43" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5041,9 +5041,19 @@
           <t>2025-07-24</t>
         </is>
       </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>10:49</t>
+        </is>
+      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-07-24</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5058,12 +5068,12 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Fredrik Wilde</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Fredrik Wilde</t>
+          <t>Mattias Dalkvist, Fredrik Wilde, Liam Sebestyén, Alva Danielsson, Elke Blöhbaum, Vilhelm Kroon, Miriam Schenk, Cajsa Björkén, Philipp Weiss, Emil Lindgren</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr">
@@ -5074,7 +5084,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>126892804</v>
+        <v>126889506</v>
       </c>
       <c r="B44" t="n">
         <v>79014</v>
@@ -5109,13 +5119,13 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>673003</v>
+        <v>672889</v>
       </c>
       <c r="R44" t="n">
-        <v>7058280</v>
+        <v>7058145</v>
       </c>
       <c r="S44" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5142,19 +5152,9 @@
           <t>2025-07-24</t>
         </is>
       </c>
-      <c r="Z44" t="inlineStr">
-        <is>
-          <t>10:49</t>
-        </is>
-      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-07-24</t>
-        </is>
-      </c>
-      <c r="AB44" t="inlineStr">
-        <is>
-          <t>10:49</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5169,12 +5169,12 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist, Fredrik Wilde, Liam Sebestyén, Alva Danielsson, Elke Blöhbaum, Vilhelm Kroon, Miriam Schenk, Cajsa Björkén, Philipp Weiss, Emil Lindgren</t>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Fredrik Wilde, Alva Danielsson, Emil Lindgren, Mattias Dalkvist, Elke Blöhbaum, Miriam Schenk, Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr">
@@ -5185,10 +5185,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>126889506</v>
+        <v>126880507</v>
       </c>
       <c r="B45" t="n">
-        <v>79014</v>
+        <v>82855</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5196,34 +5196,34 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Kravattensliden, Ång</t>
+          <t>Kravattensliden, Kravattensliden, Ång</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>672889</v>
+        <v>672859</v>
       </c>
       <c r="R45" t="n">
-        <v>7058145</v>
+        <v>7058136</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5270,12 +5270,12 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Fredrik Wilde</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Fredrik Wilde, Alva Danielsson, Emil Lindgren, Mattias Dalkvist, Elke Blöhbaum, Miriam Schenk, Vilhelm Kroon</t>
+          <t>Fredrik Wilde</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr">
@@ -5791,32 +5791,32 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>126889837</v>
+        <v>126889856</v>
       </c>
       <c r="B51" t="n">
-        <v>91291</v>
+        <v>80117</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>5447</v>
+        <v>6458</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5826,10 +5826,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>672912</v>
+        <v>672929</v>
       </c>
       <c r="R51" t="n">
-        <v>7058191</v>
+        <v>7058201</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5892,32 +5892,32 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>126889862</v>
+        <v>126893733</v>
       </c>
       <c r="B52" t="n">
-        <v>91344</v>
+        <v>98360</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>5432</v>
+        <v>219790</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5927,10 +5927,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>672981</v>
+        <v>672989</v>
       </c>
       <c r="R52" t="n">
-        <v>7058264</v>
+        <v>7058233</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5977,12 +5977,12 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Philipp Weiss, Miriam Schenk, Cajsa Björkén, Fredrik Wilde, Alva Danielsson, Elke Blöhbaum, Vilhelm Kroon, Mattias Dalkvist</t>
+          <t>Alva Danielsson, Fredrik Wilde, Liam Sebestyén, Elke Blöhbaum, Miriam Schenk, Mattias Dalkvist, Emil Lindgren</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr">
@@ -5993,32 +5993,32 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>126889856</v>
+        <v>126889837</v>
       </c>
       <c r="B53" t="n">
-        <v>80117</v>
+        <v>91291</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6458</v>
+        <v>5447</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6028,10 +6028,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>672929</v>
+        <v>672912</v>
       </c>
       <c r="R53" t="n">
-        <v>7058201</v>
+        <v>7058191</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6094,10 +6094,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>126879684</v>
+        <v>126889862</v>
       </c>
       <c r="B54" t="n">
-        <v>79014</v>
+        <v>91344</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6105,34 +6105,34 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Kravattensliden, Kravattensliden, Ång</t>
+          <t>Kravattensliden, Ång</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>672895</v>
+        <v>672981</v>
       </c>
       <c r="R54" t="n">
-        <v>7058223</v>
+        <v>7058264</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6179,12 +6179,12 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Fredrik Wilde</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Fredrik Wilde</t>
+          <t>Liam Sebestyén, Philipp Weiss, Miriam Schenk, Cajsa Björkén, Fredrik Wilde, Alva Danielsson, Elke Blöhbaum, Vilhelm Kroon, Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr">
@@ -6195,7 +6195,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>126891325</v>
+        <v>126879684</v>
       </c>
       <c r="B55" t="n">
         <v>79014</v>
@@ -6226,14 +6226,14 @@
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Kravattensliden, Ång</t>
+          <t>Kravattensliden, Kravattensliden, Ång</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>672660</v>
+        <v>672895</v>
       </c>
       <c r="R55" t="n">
-        <v>7057985</v>
+        <v>7058223</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6280,12 +6280,12 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Fredrik Wilde</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Liam Sebestyén, Mattias Dalkvist, Miriam Schenk, Fredrik Wilde, Elke Blöhbaum, Emil Lindgren</t>
+          <t>Fredrik Wilde</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr">
@@ -6296,32 +6296,32 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>126893733</v>
+        <v>126891325</v>
       </c>
       <c r="B56" t="n">
-        <v>98360</v>
+        <v>79014</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>219790</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6331,10 +6331,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>672989</v>
+        <v>672660</v>
       </c>
       <c r="R56" t="n">
-        <v>7058233</v>
+        <v>7057985</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6386,7 +6386,7 @@
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Fredrik Wilde, Liam Sebestyén, Elke Blöhbaum, Miriam Schenk, Mattias Dalkvist, Emil Lindgren</t>
+          <t>Alva Danielsson, Liam Sebestyén, Mattias Dalkvist, Miriam Schenk, Fredrik Wilde, Elke Blöhbaum, Emil Lindgren</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr">
@@ -6710,7 +6710,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>126880199</v>
+        <v>126892812</v>
       </c>
       <c r="B60" t="n">
         <v>79014</v>
@@ -6739,24 +6739,19 @@
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
-      <c r="K60" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Kravattensliden, Kravattensliden, Ång</t>
+          <t>Kravattensliden, Ång</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>672894</v>
+        <v>672685</v>
       </c>
       <c r="R60" t="n">
-        <v>7058198</v>
+        <v>7058010</v>
       </c>
       <c r="S60" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -6783,9 +6778,19 @@
           <t>2025-07-24</t>
         </is>
       </c>
+      <c r="Z60" t="inlineStr">
+        <is>
+          <t>11:41</t>
+        </is>
+      </c>
       <c r="AA60" t="inlineStr">
         <is>
           <t>2025-07-24</t>
+        </is>
+      </c>
+      <c r="AB60" t="inlineStr">
+        <is>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6800,12 +6805,12 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Fredrik Wilde</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Fredrik Wilde</t>
+          <t>Mattias Dalkvist, Fredrik Wilde, Liam Sebestyén, Alva Danielsson, Elke Blöhbaum, Vilhelm Kroon, Miriam Schenk, Cajsa Björkén, Philipp Weiss, Emil Lindgren</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr">
@@ -6816,7 +6821,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>126892809</v>
+        <v>126880199</v>
       </c>
       <c r="B61" t="n">
         <v>79014</v>
@@ -6845,19 +6850,24 @@
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Kravattensliden, Ång</t>
+          <t>Kravattensliden, Kravattensliden, Ång</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>672831</v>
+        <v>672894</v>
       </c>
       <c r="R61" t="n">
-        <v>7058091</v>
+        <v>7058198</v>
       </c>
       <c r="S61" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -6884,19 +6894,9 @@
           <t>2025-07-24</t>
         </is>
       </c>
-      <c r="Z61" t="inlineStr">
-        <is>
-          <t>11:32</t>
-        </is>
-      </c>
       <c r="AA61" t="inlineStr">
         <is>
           <t>2025-07-24</t>
-        </is>
-      </c>
-      <c r="AB61" t="inlineStr">
-        <is>
-          <t>11:32</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -6911,12 +6911,12 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Fredrik Wilde</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist, Fredrik Wilde, Liam Sebestyén, Alva Danielsson, Elke Blöhbaum, Vilhelm Kroon, Miriam Schenk, Cajsa Björkén, Philipp Weiss, Emil Lindgren</t>
+          <t>Fredrik Wilde</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr">
@@ -6927,32 +6927,32 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>126890296</v>
+        <v>126892809</v>
       </c>
       <c r="B62" t="n">
-        <v>80146</v>
+        <v>79014</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6962,13 +6962,13 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>673025</v>
+        <v>672831</v>
       </c>
       <c r="R62" t="n">
-        <v>7058244</v>
+        <v>7058091</v>
       </c>
       <c r="S62" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -6995,9 +6995,19 @@
           <t>2025-07-24</t>
         </is>
       </c>
+      <c r="Z62" t="inlineStr">
+        <is>
+          <t>11:32</t>
+        </is>
+      </c>
       <c r="AA62" t="inlineStr">
         <is>
           <t>2025-07-24</t>
+        </is>
+      </c>
+      <c r="AB62" t="inlineStr">
+        <is>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7012,12 +7022,12 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon, Cajsa Björkén, Fredrik Wilde, Mattias Dalkvist, Philipp Weiss, Miriam Schenk, Liam Sebestyén, Alva Danielsson, Emil Lindgren</t>
+          <t>Mattias Dalkvist, Fredrik Wilde, Liam Sebestyén, Alva Danielsson, Elke Blöhbaum, Vilhelm Kroon, Miriam Schenk, Cajsa Björkén, Philipp Weiss, Emil Lindgren</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr">
@@ -7028,32 +7038,32 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>126892812</v>
+        <v>126890296</v>
       </c>
       <c r="B63" t="n">
-        <v>79014</v>
+        <v>80146</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7063,13 +7073,13 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>672685</v>
+        <v>673025</v>
       </c>
       <c r="R63" t="n">
-        <v>7058010</v>
+        <v>7058244</v>
       </c>
       <c r="S63" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7096,19 +7106,9 @@
           <t>2025-07-24</t>
         </is>
       </c>
-      <c r="Z63" t="inlineStr">
-        <is>
-          <t>11:41</t>
-        </is>
-      </c>
       <c r="AA63" t="inlineStr">
         <is>
           <t>2025-07-24</t>
-        </is>
-      </c>
-      <c r="AB63" t="inlineStr">
-        <is>
-          <t>11:41</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7123,12 +7123,12 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist, Fredrik Wilde, Liam Sebestyén, Alva Danielsson, Elke Blöhbaum, Vilhelm Kroon, Miriam Schenk, Cajsa Björkén, Philipp Weiss, Emil Lindgren</t>
+          <t>Vilhelm Kroon, Cajsa Björkén, Fredrik Wilde, Mattias Dalkvist, Philipp Weiss, Miriam Schenk, Liam Sebestyén, Alva Danielsson, Emil Lindgren</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr">
@@ -7139,45 +7139,50 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>126891312</v>
+        <v>126889382</v>
       </c>
       <c r="B64" t="n">
-        <v>91291</v>
+        <v>57654</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>5447</v>
+        <v>100049</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P64" t="inlineStr">
         <is>
           <t>Kravattensliden, Ång</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>673027</v>
+        <v>672838</v>
       </c>
       <c r="R64" t="n">
-        <v>7058282</v>
+        <v>7058134</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7224,12 +7229,12 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Liam Sebestyén, Mattias Dalkvist, Miriam Schenk, Fredrik Wilde, Elke Blöhbaum, Emil Lindgren</t>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Fredrik Wilde, Alva Danielsson, Emil Lindgren, Mattias Dalkvist, Elke Blöhbaum, Miriam Schenk, Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr">
@@ -7341,50 +7346,45 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>126889382</v>
+        <v>126891312</v>
       </c>
       <c r="B66" t="n">
-        <v>57654</v>
+        <v>91291</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
-      <c r="M66" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P66" t="inlineStr">
         <is>
           <t>Kravattensliden, Ång</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>672838</v>
+        <v>673027</v>
       </c>
       <c r="R66" t="n">
-        <v>7058134</v>
+        <v>7058282</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7431,12 +7431,12 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Fredrik Wilde, Alva Danielsson, Emil Lindgren, Mattias Dalkvist, Elke Blöhbaum, Miriam Schenk, Vilhelm Kroon</t>
+          <t>Alva Danielsson, Liam Sebestyén, Mattias Dalkvist, Miriam Schenk, Fredrik Wilde, Elke Blöhbaum, Emil Lindgren</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr">
@@ -8163,10 +8163,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>126890387</v>
+        <v>126890407</v>
       </c>
       <c r="B74" t="n">
-        <v>80117</v>
+        <v>79014</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8174,21 +8174,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8198,10 +8198,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>672556</v>
+        <v>672859</v>
       </c>
       <c r="R74" t="n">
-        <v>7058143</v>
+        <v>7058290</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8264,10 +8264,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>126890407</v>
+        <v>126890387</v>
       </c>
       <c r="B75" t="n">
-        <v>79014</v>
+        <v>80117</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8275,21 +8275,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8299,10 +8299,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>672859</v>
+        <v>672556</v>
       </c>
       <c r="R75" t="n">
-        <v>7058290</v>
+        <v>7058143</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>

--- a/artfynd/A 27938-2023 artfynd.xlsx
+++ b/artfynd/A 27938-2023 artfynd.xlsx
@@ -1079,10 +1079,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126892805</v>
+        <v>126892811</v>
       </c>
       <c r="B6" t="n">
-        <v>57657</v>
+        <v>79046</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1090,21 +1090,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>185</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1114,10 +1114,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>672877</v>
+        <v>672792</v>
       </c>
       <c r="R6" t="n">
-        <v>7058189</v>
+        <v>7058076</v>
       </c>
       <c r="S6" t="n">
         <v>4</v>
@@ -1149,7 +1149,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1159,12 +1159,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:15</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Gamla ringhack</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1296,10 +1291,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126892811</v>
+        <v>126892805</v>
       </c>
       <c r="B8" t="n">
-        <v>79046</v>
+        <v>57657</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1307,21 +1302,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>185</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1331,10 +1326,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>672792</v>
+        <v>672877</v>
       </c>
       <c r="R8" t="n">
-        <v>7058076</v>
+        <v>7058189</v>
       </c>
       <c r="S8" t="n">
         <v>4</v>
@@ -1366,7 +1361,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1376,7 +1371,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>11:15</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Gamla ringhack</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1407,10 +1407,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126891323</v>
+        <v>126893729</v>
       </c>
       <c r="B9" t="n">
-        <v>91344</v>
+        <v>79014</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1418,21 +1418,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1442,10 +1442,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>672897</v>
+        <v>672603</v>
       </c>
       <c r="R9" t="n">
-        <v>7058210</v>
+        <v>7057959</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1497,7 +1497,7 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Liam Sebestyén, Mattias Dalkvist, Miriam Schenk, Fredrik Wilde, Elke Blöhbaum, Emil Lindgren</t>
+          <t>Alva Danielsson, Fredrik Wilde, Liam Sebestyén, Elke Blöhbaum, Miriam Schenk, Mattias Dalkvist, Emil Lindgren</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
@@ -1508,10 +1508,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126889513</v>
+        <v>126891323</v>
       </c>
       <c r="B10" t="n">
-        <v>79014</v>
+        <v>91344</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1519,21 +1519,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1543,10 +1543,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>673038</v>
+        <v>672897</v>
       </c>
       <c r="R10" t="n">
-        <v>7058279</v>
+        <v>7058210</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1593,12 +1593,12 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Fredrik Wilde, Alva Danielsson, Emil Lindgren, Mattias Dalkvist, Elke Blöhbaum, Miriam Schenk, Vilhelm Kroon</t>
+          <t>Alva Danielsson, Liam Sebestyén, Mattias Dalkvist, Miriam Schenk, Fredrik Wilde, Elke Blöhbaum, Emil Lindgren</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
@@ -1609,7 +1609,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126893729</v>
+        <v>126889513</v>
       </c>
       <c r="B11" t="n">
         <v>79014</v>
@@ -1644,10 +1644,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>672603</v>
+        <v>673038</v>
       </c>
       <c r="R11" t="n">
-        <v>7057959</v>
+        <v>7058279</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1694,12 +1694,12 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Fredrik Wilde, Liam Sebestyén, Elke Blöhbaum, Miriam Schenk, Mattias Dalkvist, Emil Lindgren</t>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Fredrik Wilde, Alva Danielsson, Emil Lindgren, Mattias Dalkvist, Elke Blöhbaum, Miriam Schenk, Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
@@ -1811,10 +1811,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126889387</v>
+        <v>126892815</v>
       </c>
       <c r="B13" t="n">
-        <v>57654</v>
+        <v>79014</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1822,42 +1822,37 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Kravattensliden, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>672816</v>
+        <v>672633</v>
       </c>
       <c r="R13" t="n">
-        <v>7058123</v>
+        <v>7058033</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1884,9 +1879,19 @@
           <t>2025-07-24</t>
         </is>
       </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>11:52</t>
+        </is>
+      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-07-24</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1901,12 +1906,12 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Fredrik Wilde, Alva Danielsson, Emil Lindgren, Mattias Dalkvist, Elke Blöhbaum, Miriam Schenk, Vilhelm Kroon</t>
+          <t>Mattias Dalkvist, Fredrik Wilde, Liam Sebestyén, Alva Danielsson, Elke Blöhbaum, Vilhelm Kroon, Miriam Schenk, Cajsa Björkén, Philipp Weiss, Emil Lindgren</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
@@ -1917,10 +1922,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126892815</v>
+        <v>126889387</v>
       </c>
       <c r="B14" t="n">
-        <v>79014</v>
+        <v>57654</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1928,37 +1933,42 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Kravattensliden, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>672633</v>
+        <v>672816</v>
       </c>
       <c r="R14" t="n">
-        <v>7058033</v>
+        <v>7058123</v>
       </c>
       <c r="S14" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -1985,19 +1995,9 @@
           <t>2025-07-24</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>11:52</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-07-24</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>11:52</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2012,12 +2012,12 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist, Fredrik Wilde, Liam Sebestyén, Alva Danielsson, Elke Blöhbaum, Vilhelm Kroon, Miriam Schenk, Cajsa Björkén, Philipp Weiss, Emil Lindgren</t>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Fredrik Wilde, Alva Danielsson, Emil Lindgren, Mattias Dalkvist, Elke Blöhbaum, Miriam Schenk, Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
@@ -2129,32 +2129,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>126891315</v>
+        <v>126889492</v>
       </c>
       <c r="B16" t="n">
-        <v>98464</v>
+        <v>79014</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>221952</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2164,10 +2164,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>672827</v>
+        <v>672638</v>
       </c>
       <c r="R16" t="n">
-        <v>7058099</v>
+        <v>7057953</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2214,12 +2214,12 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Liam Sebestyén, Mattias Dalkvist, Miriam Schenk, Fredrik Wilde, Elke Blöhbaum, Emil Lindgren</t>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Fredrik Wilde, Alva Danielsson, Emil Lindgren, Mattias Dalkvist, Elke Blöhbaum, Miriam Schenk, Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
@@ -2230,32 +2230,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>126889492</v>
+        <v>126891315</v>
       </c>
       <c r="B17" t="n">
-        <v>79014</v>
+        <v>98464</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>221952</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2265,10 +2265,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>672638</v>
+        <v>672827</v>
       </c>
       <c r="R17" t="n">
-        <v>7057953</v>
+        <v>7058099</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2315,12 +2315,12 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Fredrik Wilde, Alva Danielsson, Emil Lindgren, Mattias Dalkvist, Elke Blöhbaum, Miriam Schenk, Vilhelm Kroon</t>
+          <t>Alva Danielsson, Liam Sebestyén, Mattias Dalkvist, Miriam Schenk, Fredrik Wilde, Elke Blöhbaum, Emil Lindgren</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
@@ -2655,10 +2655,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>126889370</v>
+        <v>126889311</v>
       </c>
       <c r="B21" t="n">
-        <v>4772</v>
+        <v>91291</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2666,39 +2666,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100299</v>
+        <v>5447</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Kravattensliden, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>672839</v>
+        <v>672799</v>
       </c>
       <c r="R21" t="n">
-        <v>7058141</v>
+        <v>7058086</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2761,10 +2756,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>126889869</v>
+        <v>126891314</v>
       </c>
       <c r="B22" t="n">
-        <v>98360</v>
+        <v>80146</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2772,21 +2767,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>219790</v>
+        <v>6462</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2796,10 +2791,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>672855</v>
+        <v>672999</v>
       </c>
       <c r="R22" t="n">
-        <v>7058116</v>
+        <v>7058211</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2846,12 +2841,12 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Philipp Weiss, Miriam Schenk, Cajsa Björkén, Fredrik Wilde, Alva Danielsson, Elke Blöhbaum, Vilhelm Kroon, Mattias Dalkvist</t>
+          <t>Alva Danielsson, Liam Sebestyén, Mattias Dalkvist, Miriam Schenk, Fredrik Wilde, Elke Blöhbaum, Emil Lindgren</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
@@ -2862,10 +2857,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>126889311</v>
+        <v>126889370</v>
       </c>
       <c r="B23" t="n">
-        <v>91291</v>
+        <v>4772</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2873,34 +2868,39 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5447</v>
+        <v>100299</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Kravattensliden, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>672799</v>
+        <v>672839</v>
       </c>
       <c r="R23" t="n">
-        <v>7058086</v>
+        <v>7058141</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2963,10 +2963,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>126891314</v>
+        <v>126889869</v>
       </c>
       <c r="B24" t="n">
-        <v>80146</v>
+        <v>98360</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2974,21 +2974,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6462</v>
+        <v>219790</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2998,10 +2998,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>672999</v>
+        <v>672855</v>
       </c>
       <c r="R24" t="n">
-        <v>7058211</v>
+        <v>7058116</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3048,12 +3048,12 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Liam Sebestyén, Mattias Dalkvist, Miriam Schenk, Fredrik Wilde, Elke Blöhbaum, Emil Lindgren</t>
+          <t>Liam Sebestyén, Philipp Weiss, Miriam Schenk, Cajsa Björkén, Fredrik Wilde, Alva Danielsson, Elke Blöhbaum, Vilhelm Kroon, Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr">
@@ -3179,10 +3179,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>126889847</v>
+        <v>126892816</v>
       </c>
       <c r="B26" t="n">
-        <v>57654</v>
+        <v>79014</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3190,45 +3190,37 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Kravattensliden, Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>672981</v>
+        <v>672627</v>
       </c>
       <c r="R26" t="n">
-        <v>7058264</v>
+        <v>7058024</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3255,9 +3247,19 @@
           <t>2025-07-24</t>
         </is>
       </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>11:52</t>
+        </is>
+      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-07-24</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3272,12 +3274,12 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Philipp Weiss, Miriam Schenk, Cajsa Björkén, Fredrik Wilde, Alva Danielsson, Elke Blöhbaum, Vilhelm Kroon, Mattias Dalkvist</t>
+          <t>Mattias Dalkvist, Fredrik Wilde, Liam Sebestyén, Alva Danielsson, Elke Blöhbaum, Vilhelm Kroon, Miriam Schenk, Cajsa Björkén, Philipp Weiss, Emil Lindgren</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr">
@@ -3288,7 +3290,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>126892816</v>
+        <v>126889502</v>
       </c>
       <c r="B27" t="n">
         <v>79014</v>
@@ -3323,13 +3325,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>672627</v>
+        <v>672801</v>
       </c>
       <c r="R27" t="n">
-        <v>7058024</v>
+        <v>7058095</v>
       </c>
       <c r="S27" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3356,19 +3358,9 @@
           <t>2025-07-24</t>
         </is>
       </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>11:52</t>
-        </is>
-      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-07-24</t>
-        </is>
-      </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>11:52</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3383,12 +3375,12 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist, Fredrik Wilde, Liam Sebestyén, Alva Danielsson, Elke Blöhbaum, Vilhelm Kroon, Miriam Schenk, Cajsa Björkén, Philipp Weiss, Emil Lindgren</t>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Fredrik Wilde, Alva Danielsson, Emil Lindgren, Mattias Dalkvist, Elke Blöhbaum, Miriam Schenk, Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr">
@@ -3500,32 +3492,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>126889502</v>
+        <v>126891313</v>
       </c>
       <c r="B29" t="n">
-        <v>79014</v>
+        <v>80146</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3535,10 +3527,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>672801</v>
+        <v>672933</v>
       </c>
       <c r="R29" t="n">
-        <v>7058095</v>
+        <v>7058201</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3585,12 +3577,12 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Fredrik Wilde, Alva Danielsson, Emil Lindgren, Mattias Dalkvist, Elke Blöhbaum, Miriam Schenk, Vilhelm Kroon</t>
+          <t>Alva Danielsson, Liam Sebestyén, Mattias Dalkvist, Miriam Schenk, Fredrik Wilde, Elke Blöhbaum, Emil Lindgren</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr">
@@ -3601,45 +3593,53 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>126891313</v>
+        <v>126889847</v>
       </c>
       <c r="B30" t="n">
-        <v>80146</v>
+        <v>57654</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6462</v>
+        <v>100049</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Kravattensliden, Ång</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>672933</v>
+        <v>672981</v>
       </c>
       <c r="R30" t="n">
-        <v>7058201</v>
+        <v>7058264</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3686,12 +3686,12 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Liam Sebestyén, Mattias Dalkvist, Miriam Schenk, Fredrik Wilde, Elke Blöhbaum, Emil Lindgren</t>
+          <t>Liam Sebestyén, Philipp Weiss, Miriam Schenk, Cajsa Björkén, Fredrik Wilde, Alva Danielsson, Elke Blöhbaum, Vilhelm Kroon, Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr">
@@ -3702,10 +3702,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>126889377</v>
+        <v>126889536</v>
       </c>
       <c r="B31" t="n">
-        <v>98464</v>
+        <v>5176</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3713,36 +3713,27 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>221952</v>
+        <v>100526</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>överblommad</t>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
@@ -3751,10 +3742,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>672810</v>
+        <v>672659</v>
       </c>
       <c r="R31" t="n">
-        <v>7058105</v>
+        <v>7057975</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3817,45 +3808,59 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>126891328</v>
+        <v>126889377</v>
       </c>
       <c r="B32" t="n">
-        <v>79014</v>
+        <v>98464</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>221952</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Kravattensliden, Ång</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>672972</v>
+        <v>672810</v>
       </c>
       <c r="R32" t="n">
-        <v>7058246</v>
+        <v>7058105</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3902,12 +3907,12 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Liam Sebestyén, Mattias Dalkvist, Miriam Schenk, Fredrik Wilde, Elke Blöhbaum, Emil Lindgren</t>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Fredrik Wilde, Alva Danielsson, Emil Lindgren, Mattias Dalkvist, Elke Blöhbaum, Miriam Schenk, Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr">
@@ -3918,50 +3923,45 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>126889536</v>
+        <v>126891328</v>
       </c>
       <c r="B33" t="n">
-        <v>5176</v>
+        <v>79014</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100526</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Kravattensliden, Ång</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>672659</v>
+        <v>672972</v>
       </c>
       <c r="R33" t="n">
-        <v>7057975</v>
+        <v>7058246</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4008,12 +4008,12 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Fredrik Wilde, Alva Danielsson, Emil Lindgren, Mattias Dalkvist, Elke Blöhbaum, Miriam Schenk, Vilhelm Kroon</t>
+          <t>Alva Danielsson, Liam Sebestyén, Mattias Dalkvist, Miriam Schenk, Fredrik Wilde, Elke Blöhbaum, Emil Lindgren</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr">
@@ -4024,45 +4024,52 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>126889834</v>
+        <v>126893692</v>
       </c>
       <c r="B34" t="n">
-        <v>91291</v>
+        <v>91326</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Kravattensliden, Ång</t>
+          <t>Kravattensliden , Ång</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>672819</v>
+        <v>672811</v>
       </c>
       <c r="R34" t="n">
-        <v>7058089</v>
+        <v>7058091</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4103,18 +4110,19 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
+      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Emil Lindgren</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Philipp Weiss, Miriam Schenk, Cajsa Björkén, Fredrik Wilde, Alva Danielsson, Elke Blöhbaum, Vilhelm Kroon, Mattias Dalkvist</t>
+          <t>Emil Lindgren</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr">
@@ -4125,52 +4133,45 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>126893692</v>
+        <v>126889834</v>
       </c>
       <c r="B35" t="n">
-        <v>91326</v>
+        <v>91291</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr"/>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Kravattensliden , Ång</t>
+          <t>Kravattensliden, Ång</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>672811</v>
+        <v>672819</v>
       </c>
       <c r="R35" t="n">
-        <v>7058091</v>
+        <v>7058089</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4211,19 +4212,18 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
-      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Emil Lindgren</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Emil Lindgren</t>
+          <t>Liam Sebestyén, Philipp Weiss, Miriam Schenk, Cajsa Björkén, Fredrik Wilde, Alva Danielsson, Elke Blöhbaum, Vilhelm Kroon, Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr">
@@ -4335,10 +4335,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>126892813</v>
+        <v>126892814</v>
       </c>
       <c r="B37" t="n">
-        <v>79014</v>
+        <v>79046</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4346,21 +4346,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4370,13 +4370,13 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>672661</v>
+        <v>672659</v>
       </c>
       <c r="R37" t="n">
-        <v>7058026</v>
+        <v>7058027</v>
       </c>
       <c r="S37" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4446,7 +4446,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>126890308</v>
+        <v>126892813</v>
       </c>
       <c r="B38" t="n">
         <v>79014</v>
@@ -4481,13 +4481,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>672880</v>
+        <v>672661</v>
       </c>
       <c r="R38" t="n">
-        <v>7058209</v>
+        <v>7058026</v>
       </c>
       <c r="S38" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4514,9 +4514,19 @@
           <t>2025-07-24</t>
         </is>
       </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>11:51</t>
+        </is>
+      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-07-24</t>
+        </is>
+      </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4531,12 +4541,12 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon, Cajsa Björkén, Fredrik Wilde, Mattias Dalkvist, Philipp Weiss, Miriam Schenk, Liam Sebestyén, Alva Danielsson, Emil Lindgren</t>
+          <t>Mattias Dalkvist, Fredrik Wilde, Liam Sebestyén, Alva Danielsson, Elke Blöhbaum, Vilhelm Kroon, Miriam Schenk, Cajsa Björkén, Philipp Weiss, Emil Lindgren</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr">
@@ -4547,10 +4557,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>126891320</v>
+        <v>126890308</v>
       </c>
       <c r="B39" t="n">
-        <v>80117</v>
+        <v>79014</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4558,21 +4568,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4582,13 +4592,13 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>672929</v>
+        <v>672880</v>
       </c>
       <c r="R39" t="n">
-        <v>7058203</v>
+        <v>7058209</v>
       </c>
       <c r="S39" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4632,12 +4642,12 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Liam Sebestyén, Mattias Dalkvist, Miriam Schenk, Fredrik Wilde, Elke Blöhbaum, Emil Lindgren</t>
+          <t>Vilhelm Kroon, Cajsa Björkén, Fredrik Wilde, Mattias Dalkvist, Philipp Weiss, Miriam Schenk, Liam Sebestyén, Alva Danielsson, Emil Lindgren</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr">
@@ -4648,10 +4658,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>126892814</v>
+        <v>126891320</v>
       </c>
       <c r="B40" t="n">
-        <v>79046</v>
+        <v>80117</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4659,21 +4669,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>185</v>
+        <v>6458</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4683,13 +4693,13 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>672659</v>
+        <v>672929</v>
       </c>
       <c r="R40" t="n">
-        <v>7058027</v>
+        <v>7058203</v>
       </c>
       <c r="S40" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4716,19 +4726,9 @@
           <t>2025-07-24</t>
         </is>
       </c>
-      <c r="Z40" t="inlineStr">
-        <is>
-          <t>11:51</t>
-        </is>
-      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-07-24</t>
-        </is>
-      </c>
-      <c r="AB40" t="inlineStr">
-        <is>
-          <t>11:51</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4743,12 +4743,12 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist, Fredrik Wilde, Liam Sebestyén, Alva Danielsson, Elke Blöhbaum, Vilhelm Kroon, Miriam Schenk, Cajsa Björkén, Philipp Weiss, Emil Lindgren</t>
+          <t>Alva Danielsson, Liam Sebestyén, Mattias Dalkvist, Miriam Schenk, Fredrik Wilde, Elke Blöhbaum, Emil Lindgren</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr">
@@ -4864,52 +4864,45 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>126893671</v>
+        <v>126880507</v>
       </c>
       <c r="B42" t="n">
-        <v>91291</v>
+        <v>82855</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>5447</v>
+        <v>1312</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="J42" t="inlineStr"/>
-      <c r="K42" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Kravattensliden , Ång</t>
+          <t>Kravattensliden, Kravattensliden, Ång</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>672808</v>
+        <v>672859</v>
       </c>
       <c r="R42" t="n">
-        <v>7058090</v>
+        <v>7058136</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4950,19 +4943,18 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
-      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Emil Lindgren</t>
+          <t>Fredrik Wilde</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Emil Lindgren</t>
+          <t>Fredrik Wilde</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr">
@@ -5084,10 +5076,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>126889506</v>
+        <v>126891321</v>
       </c>
       <c r="B44" t="n">
-        <v>79014</v>
+        <v>80117</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5095,21 +5087,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5119,10 +5111,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>672889</v>
+        <v>673004</v>
       </c>
       <c r="R44" t="n">
-        <v>7058145</v>
+        <v>7058209</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5169,12 +5161,12 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Fredrik Wilde, Alva Danielsson, Emil Lindgren, Mattias Dalkvist, Elke Blöhbaum, Miriam Schenk, Vilhelm Kroon</t>
+          <t>Alva Danielsson, Liam Sebestyén, Mattias Dalkvist, Miriam Schenk, Fredrik Wilde, Elke Blöhbaum, Emil Lindgren</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr">
@@ -5185,45 +5177,52 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>126880507</v>
+        <v>126893671</v>
       </c>
       <c r="B45" t="n">
-        <v>82855</v>
+        <v>91291</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1312</v>
+        <v>5447</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="J45" t="inlineStr"/>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Kravattensliden, Kravattensliden, Ång</t>
+          <t>Kravattensliden , Ång</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>672859</v>
+        <v>672808</v>
       </c>
       <c r="R45" t="n">
-        <v>7058136</v>
+        <v>7058090</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5264,18 +5263,19 @@
       <c r="AE45" t="b">
         <v>0</v>
       </c>
+      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Fredrik Wilde</t>
+          <t>Emil Lindgren</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Fredrik Wilde</t>
+          <t>Emil Lindgren</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr">
@@ -5286,10 +5286,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>126891321</v>
+        <v>126889506</v>
       </c>
       <c r="B46" t="n">
-        <v>80117</v>
+        <v>79014</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5297,21 +5297,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5321,10 +5321,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>673004</v>
+        <v>672889</v>
       </c>
       <c r="R46" t="n">
-        <v>7058209</v>
+        <v>7058145</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5371,12 +5371,12 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Liam Sebestyén, Mattias Dalkvist, Miriam Schenk, Fredrik Wilde, Elke Blöhbaum, Emil Lindgren</t>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Fredrik Wilde, Alva Danielsson, Emil Lindgren, Mattias Dalkvist, Elke Blöhbaum, Miriam Schenk, Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr">
@@ -5387,10 +5387,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>126890305</v>
+        <v>126890311</v>
       </c>
       <c r="B47" t="n">
-        <v>79014</v>
+        <v>88729</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5398,21 +5398,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>510</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5422,10 +5422,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>672724</v>
+        <v>673023</v>
       </c>
       <c r="R47" t="n">
-        <v>7058075</v>
+        <v>7058218</v>
       </c>
       <c r="S47" t="n">
         <v>15</v>
@@ -5488,7 +5488,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>126889494</v>
+        <v>126890305</v>
       </c>
       <c r="B48" t="n">
         <v>79014</v>
@@ -5523,13 +5523,13 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>672657</v>
+        <v>672724</v>
       </c>
       <c r="R48" t="n">
-        <v>7057974</v>
+        <v>7058075</v>
       </c>
       <c r="S48" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5573,12 +5573,12 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Fredrik Wilde, Alva Danielsson, Emil Lindgren, Mattias Dalkvist, Elke Blöhbaum, Miriam Schenk, Vilhelm Kroon</t>
+          <t>Vilhelm Kroon, Cajsa Björkén, Fredrik Wilde, Mattias Dalkvist, Philipp Weiss, Miriam Schenk, Liam Sebestyén, Alva Danielsson, Emil Lindgren</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr">
@@ -5589,10 +5589,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>126890311</v>
+        <v>126889494</v>
       </c>
       <c r="B49" t="n">
-        <v>88729</v>
+        <v>79014</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5600,21 +5600,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>510</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5624,13 +5624,13 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>673023</v>
+        <v>672657</v>
       </c>
       <c r="R49" t="n">
-        <v>7058218</v>
+        <v>7057974</v>
       </c>
       <c r="S49" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5674,12 +5674,12 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon, Cajsa Björkén, Fredrik Wilde, Mattias Dalkvist, Philipp Weiss, Miriam Schenk, Liam Sebestyén, Alva Danielsson, Emil Lindgren</t>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Fredrik Wilde, Alva Danielsson, Emil Lindgren, Mattias Dalkvist, Elke Blöhbaum, Miriam Schenk, Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr">
@@ -5791,10 +5791,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>126889856</v>
+        <v>126879684</v>
       </c>
       <c r="B51" t="n">
-        <v>80117</v>
+        <v>79014</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5802,34 +5802,34 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Kravattensliden, Ång</t>
+          <t>Kravattensliden, Kravattensliden, Ång</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>672929</v>
+        <v>672895</v>
       </c>
       <c r="R51" t="n">
-        <v>7058201</v>
+        <v>7058223</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5876,12 +5876,12 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Fredrik Wilde</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Philipp Weiss, Miriam Schenk, Cajsa Björkén, Fredrik Wilde, Alva Danielsson, Elke Blöhbaum, Vilhelm Kroon, Mattias Dalkvist</t>
+          <t>Fredrik Wilde</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr">
@@ -5892,32 +5892,32 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>126893733</v>
+        <v>126889856</v>
       </c>
       <c r="B52" t="n">
-        <v>98360</v>
+        <v>80117</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>219790</v>
+        <v>6458</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5927,10 +5927,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>672989</v>
+        <v>672929</v>
       </c>
       <c r="R52" t="n">
-        <v>7058233</v>
+        <v>7058201</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5977,12 +5977,12 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Fredrik Wilde, Liam Sebestyén, Elke Blöhbaum, Miriam Schenk, Mattias Dalkvist, Emil Lindgren</t>
+          <t>Liam Sebestyén, Philipp Weiss, Miriam Schenk, Cajsa Björkén, Fredrik Wilde, Alva Danielsson, Elke Blöhbaum, Vilhelm Kroon, Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr">
@@ -5993,32 +5993,32 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>126889837</v>
+        <v>126889862</v>
       </c>
       <c r="B53" t="n">
-        <v>91291</v>
+        <v>91344</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>5447</v>
+        <v>5432</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6028,10 +6028,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>672912</v>
+        <v>672981</v>
       </c>
       <c r="R53" t="n">
-        <v>7058191</v>
+        <v>7058264</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6094,32 +6094,32 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>126889862</v>
+        <v>126889837</v>
       </c>
       <c r="B54" t="n">
-        <v>91344</v>
+        <v>91291</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>5432</v>
+        <v>5447</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6129,10 +6129,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>672981</v>
+        <v>672912</v>
       </c>
       <c r="R54" t="n">
-        <v>7058264</v>
+        <v>7058191</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6195,7 +6195,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>126879684</v>
+        <v>126891325</v>
       </c>
       <c r="B55" t="n">
         <v>79014</v>
@@ -6226,14 +6226,14 @@
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Kravattensliden, Kravattensliden, Ång</t>
+          <t>Kravattensliden, Ång</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>672895</v>
+        <v>672660</v>
       </c>
       <c r="R55" t="n">
-        <v>7058223</v>
+        <v>7057985</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6280,12 +6280,12 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Fredrik Wilde</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Fredrik Wilde</t>
+          <t>Alva Danielsson, Liam Sebestyén, Mattias Dalkvist, Miriam Schenk, Fredrik Wilde, Elke Blöhbaum, Emil Lindgren</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr">
@@ -6296,32 +6296,32 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>126891325</v>
+        <v>126893733</v>
       </c>
       <c r="B56" t="n">
-        <v>79014</v>
+        <v>98360</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>219790</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6331,10 +6331,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>672660</v>
+        <v>672989</v>
       </c>
       <c r="R56" t="n">
-        <v>7057985</v>
+        <v>7058233</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6386,7 +6386,7 @@
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Liam Sebestyén, Mattias Dalkvist, Miriam Schenk, Fredrik Wilde, Elke Blöhbaum, Emil Lindgren</t>
+          <t>Alva Danielsson, Fredrik Wilde, Liam Sebestyén, Elke Blöhbaum, Miriam Schenk, Mattias Dalkvist, Emil Lindgren</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr">
@@ -6397,10 +6397,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>126889504</v>
+        <v>126879133</v>
       </c>
       <c r="B57" t="n">
-        <v>79014</v>
+        <v>79046</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6408,34 +6408,34 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Kravattensliden, Ång</t>
+          <t>Kravattensliden, Kravattensliden, Ång</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>672853</v>
+        <v>673041</v>
       </c>
       <c r="R57" t="n">
-        <v>7058173</v>
+        <v>7058262</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6482,12 +6482,12 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Fredrik Wilde</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Fredrik Wilde, Alva Danielsson, Emil Lindgren, Mattias Dalkvist, Elke Blöhbaum, Miriam Schenk, Vilhelm Kroon</t>
+          <t>Fredrik Wilde</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr">
@@ -6498,10 +6498,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>126879133</v>
+        <v>126889504</v>
       </c>
       <c r="B58" t="n">
-        <v>79046</v>
+        <v>79014</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6509,34 +6509,34 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Kravattensliden, Kravattensliden, Ång</t>
+          <t>Kravattensliden, Ång</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>673041</v>
+        <v>672853</v>
       </c>
       <c r="R58" t="n">
-        <v>7058262</v>
+        <v>7058173</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6583,12 +6583,12 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Fredrik Wilde</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Fredrik Wilde</t>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Fredrik Wilde, Alva Danielsson, Emil Lindgren, Mattias Dalkvist, Elke Blöhbaum, Miriam Schenk, Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr">
@@ -6710,7 +6710,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>126892812</v>
+        <v>126892809</v>
       </c>
       <c r="B60" t="n">
         <v>79014</v>
@@ -6745,13 +6745,13 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>672685</v>
+        <v>672831</v>
       </c>
       <c r="R60" t="n">
-        <v>7058010</v>
+        <v>7058091</v>
       </c>
       <c r="S60" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -6780,7 +6780,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -6790,7 +6790,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6821,53 +6821,48 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>126880199</v>
+        <v>126890296</v>
       </c>
       <c r="B61" t="n">
-        <v>79014</v>
+        <v>80146</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
-      <c r="K61" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Kravattensliden, Kravattensliden, Ång</t>
+          <t>Kravattensliden, Ång</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>672894</v>
+        <v>673025</v>
       </c>
       <c r="R61" t="n">
-        <v>7058198</v>
+        <v>7058244</v>
       </c>
       <c r="S61" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -6911,12 +6906,12 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Fredrik Wilde</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Fredrik Wilde</t>
+          <t>Vilhelm Kroon, Cajsa Björkén, Fredrik Wilde, Mattias Dalkvist, Philipp Weiss, Miriam Schenk, Liam Sebestyén, Alva Danielsson, Emil Lindgren</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr">
@@ -6927,7 +6922,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>126892809</v>
+        <v>126892812</v>
       </c>
       <c r="B62" t="n">
         <v>79014</v>
@@ -6962,13 +6957,13 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>672831</v>
+        <v>672685</v>
       </c>
       <c r="R62" t="n">
-        <v>7058091</v>
+        <v>7058010</v>
       </c>
       <c r="S62" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -6997,7 +6992,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7007,7 +7002,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7038,48 +7033,53 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>126890296</v>
+        <v>126880199</v>
       </c>
       <c r="B63" t="n">
-        <v>80146</v>
+        <v>79014</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Kravattensliden, Ång</t>
+          <t>Kravattensliden, Kravattensliden, Ång</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>673025</v>
+        <v>672894</v>
       </c>
       <c r="R63" t="n">
-        <v>7058244</v>
+        <v>7058198</v>
       </c>
       <c r="S63" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7123,12 +7123,12 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Fredrik Wilde</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon, Cajsa Björkén, Fredrik Wilde, Mattias Dalkvist, Philipp Weiss, Miriam Schenk, Liam Sebestyén, Alva Danielsson, Emil Lindgren</t>
+          <t>Fredrik Wilde</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr">
@@ -7139,50 +7139,45 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>126889382</v>
+        <v>126891312</v>
       </c>
       <c r="B64" t="n">
-        <v>57654</v>
+        <v>91291</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
-      <c r="M64" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P64" t="inlineStr">
         <is>
           <t>Kravattensliden, Ång</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>672838</v>
+        <v>673027</v>
       </c>
       <c r="R64" t="n">
-        <v>7058134</v>
+        <v>7058282</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7229,12 +7224,12 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Fredrik Wilde, Alva Danielsson, Emil Lindgren, Mattias Dalkvist, Elke Blöhbaum, Miriam Schenk, Vilhelm Kroon</t>
+          <t>Alva Danielsson, Liam Sebestyén, Mattias Dalkvist, Miriam Schenk, Fredrik Wilde, Elke Blöhbaum, Emil Lindgren</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr">
@@ -7245,32 +7240,32 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>126880532</v>
+        <v>126879425</v>
       </c>
       <c r="B65" t="n">
-        <v>80146</v>
+        <v>79014</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7280,10 +7275,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>672863</v>
+        <v>672947</v>
       </c>
       <c r="R65" t="n">
-        <v>7058124</v>
+        <v>7058198</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7346,10 +7341,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>126891312</v>
+        <v>126880532</v>
       </c>
       <c r="B66" t="n">
-        <v>91291</v>
+        <v>80146</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7357,34 +7352,34 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>5447</v>
+        <v>6462</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Kravattensliden, Ång</t>
+          <t>Kravattensliden, Kravattensliden, Ång</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>673027</v>
+        <v>672863</v>
       </c>
       <c r="R66" t="n">
-        <v>7058282</v>
+        <v>7058124</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7431,12 +7426,12 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Fredrik Wilde</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Liam Sebestyén, Mattias Dalkvist, Miriam Schenk, Fredrik Wilde, Elke Blöhbaum, Emil Lindgren</t>
+          <t>Fredrik Wilde</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr">
@@ -7447,10 +7442,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>126879425</v>
+        <v>126879033</v>
       </c>
       <c r="B67" t="n">
-        <v>79014</v>
+        <v>79046</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7458,34 +7453,43 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr"/>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P67" t="inlineStr">
         <is>
           <t>Kravattensliden, Kravattensliden, Ång</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>672947</v>
+        <v>673046</v>
       </c>
       <c r="R67" t="n">
-        <v>7058198</v>
+        <v>7058286</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7548,10 +7552,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>126879033</v>
+        <v>126889382</v>
       </c>
       <c r="B68" t="n">
-        <v>79046</v>
+        <v>57654</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7559,43 +7563,39 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>185</v>
+        <v>100049</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J68" t="inlineStr">
-        <is>
-          <t>bålar</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr"/>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Kravattensliden, Kravattensliden, Ång</t>
+          <t>Kravattensliden, Ång</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>673046</v>
+        <v>672838</v>
       </c>
       <c r="R68" t="n">
-        <v>7058286</v>
+        <v>7058134</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7642,12 +7642,12 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Fredrik Wilde</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Fredrik Wilde</t>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Fredrik Wilde, Alva Danielsson, Emil Lindgren, Mattias Dalkvist, Elke Blöhbaum, Miriam Schenk, Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr">
@@ -7658,32 +7658,32 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>126890401</v>
+        <v>126890370</v>
       </c>
       <c r="B69" t="n">
-        <v>79014</v>
+        <v>80146</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7693,10 +7693,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>672705</v>
+        <v>672554</v>
       </c>
       <c r="R69" t="n">
-        <v>7058080</v>
+        <v>7058145</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7860,32 +7860,32 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>126890370</v>
+        <v>126890401</v>
       </c>
       <c r="B71" t="n">
-        <v>80146</v>
+        <v>79014</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7895,10 +7895,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>672554</v>
+        <v>672705</v>
       </c>
       <c r="R71" t="n">
-        <v>7058145</v>
+        <v>7058080</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8365,10 +8365,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>126890404</v>
+        <v>126890354</v>
       </c>
       <c r="B76" t="n">
-        <v>79014</v>
+        <v>79046</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8376,21 +8376,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8400,10 +8400,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>672805</v>
+        <v>672891</v>
       </c>
       <c r="R76" t="n">
-        <v>7058312</v>
+        <v>7058285</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8466,10 +8466,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>126890354</v>
+        <v>126890404</v>
       </c>
       <c r="B77" t="n">
-        <v>79046</v>
+        <v>79014</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8477,21 +8477,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8501,10 +8501,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>672891</v>
+        <v>672805</v>
       </c>
       <c r="R77" t="n">
-        <v>7058285</v>
+        <v>7058312</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8769,7 +8769,7 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>126890351</v>
+        <v>126890348</v>
       </c>
       <c r="B80" t="n">
         <v>79046</v>
@@ -8804,10 +8804,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>672831</v>
+        <v>672587</v>
       </c>
       <c r="R80" t="n">
-        <v>7058284</v>
+        <v>7058126</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8870,7 +8870,7 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>126890348</v>
+        <v>126890351</v>
       </c>
       <c r="B81" t="n">
         <v>79046</v>
@@ -8905,10 +8905,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>672587</v>
+        <v>672831</v>
       </c>
       <c r="R81" t="n">
-        <v>7058126</v>
+        <v>7058284</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>

--- a/artfynd/A 27938-2023 artfynd.xlsx
+++ b/artfynd/A 27938-2023 artfynd.xlsx
@@ -1079,10 +1079,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126892811</v>
+        <v>126889505</v>
       </c>
       <c r="B6" t="n">
-        <v>79046</v>
+        <v>79014</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1090,21 +1090,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1114,13 +1114,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>672792</v>
+        <v>672864</v>
       </c>
       <c r="R6" t="n">
-        <v>7058076</v>
+        <v>7058181</v>
       </c>
       <c r="S6" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1147,19 +1147,9 @@
           <t>2025-07-24</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>11:35</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-07-24</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>11:35</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1174,12 +1164,12 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist, Fredrik Wilde, Liam Sebestyén, Alva Danielsson, Elke Blöhbaum, Vilhelm Kroon, Miriam Schenk, Cajsa Björkén, Philipp Weiss, Emil Lindgren</t>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Fredrik Wilde, Alva Danielsson, Emil Lindgren, Mattias Dalkvist, Elke Blöhbaum, Miriam Schenk, Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
@@ -1190,10 +1180,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126889505</v>
+        <v>126892805</v>
       </c>
       <c r="B7" t="n">
-        <v>79014</v>
+        <v>57657</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1201,21 +1191,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,13 +1215,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>672864</v>
+        <v>672877</v>
       </c>
       <c r="R7" t="n">
-        <v>7058181</v>
+        <v>7058189</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1258,9 +1248,24 @@
           <t>2025-07-24</t>
         </is>
       </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>11:15</t>
+        </is>
+      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-07-24</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>11:15</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Gamla ringhack</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1275,12 +1280,12 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Fredrik Wilde, Alva Danielsson, Emil Lindgren, Mattias Dalkvist, Elke Blöhbaum, Miriam Schenk, Vilhelm Kroon</t>
+          <t>Mattias Dalkvist, Fredrik Wilde, Liam Sebestyén, Alva Danielsson, Elke Blöhbaum, Vilhelm Kroon, Miriam Schenk, Cajsa Björkén, Philipp Weiss, Emil Lindgren</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
@@ -1291,10 +1296,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126892805</v>
+        <v>126892811</v>
       </c>
       <c r="B8" t="n">
-        <v>57657</v>
+        <v>79046</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1302,21 +1307,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>185</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1326,10 +1331,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>672877</v>
+        <v>672792</v>
       </c>
       <c r="R8" t="n">
-        <v>7058189</v>
+        <v>7058076</v>
       </c>
       <c r="S8" t="n">
         <v>4</v>
@@ -1361,7 +1366,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1371,12 +1376,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:15</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Gamla ringhack</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -2331,32 +2331,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>126892810</v>
+        <v>126891131</v>
       </c>
       <c r="B18" t="n">
-        <v>91291</v>
+        <v>79046</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5447</v>
+        <v>185</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2366,13 +2366,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>672801</v>
+        <v>672898</v>
       </c>
       <c r="R18" t="n">
-        <v>7058081</v>
+        <v>7058209</v>
       </c>
       <c r="S18" t="n">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2399,39 +2399,30 @@
           <t>2025-07-24</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>11:35</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-07-24</t>
         </is>
       </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>11:35</t>
-        </is>
-      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Miriam Schenk</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist, Fredrik Wilde, Liam Sebestyén, Alva Danielsson, Elke Blöhbaum, Vilhelm Kroon, Miriam Schenk, Cajsa Björkén, Philipp Weiss, Emil Lindgren</t>
+          <t>Miriam Schenk, Cajsa Björkén, Fredrik Wilde, Philipp Weiss, Mattias Dalkvist, Vilhelm Kroon, Liam Sebestyén, Emil Lindgren, Alva Danielsson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
@@ -2442,32 +2433,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>126892808</v>
+        <v>126892810</v>
       </c>
       <c r="B19" t="n">
-        <v>79014</v>
+        <v>91291</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2477,13 +2468,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>672862</v>
+        <v>672801</v>
       </c>
       <c r="R19" t="n">
-        <v>7058125</v>
+        <v>7058081</v>
       </c>
       <c r="S19" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2512,7 +2503,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2522,7 +2513,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2553,10 +2544,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>126891131</v>
+        <v>126892808</v>
       </c>
       <c r="B20" t="n">
-        <v>79046</v>
+        <v>79014</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2564,21 +2555,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2588,13 +2579,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>672898</v>
+        <v>672862</v>
       </c>
       <c r="R20" t="n">
-        <v>7058209</v>
+        <v>7058125</v>
       </c>
       <c r="S20" t="n">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2621,30 +2612,39 @@
           <t>2025-07-24</t>
         </is>
       </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>11:25</t>
+        </is>
+      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-07-24</t>
         </is>
       </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>11:25</t>
+        </is>
+      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Miriam Schenk</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Miriam Schenk, Cajsa Björkén, Fredrik Wilde, Philipp Weiss, Mattias Dalkvist, Vilhelm Kroon, Liam Sebestyén, Emil Lindgren, Alva Danielsson</t>
+          <t>Mattias Dalkvist, Fredrik Wilde, Liam Sebestyén, Alva Danielsson, Elke Blöhbaum, Vilhelm Kroon, Miriam Schenk, Cajsa Björkén, Philipp Weiss, Emil Lindgren</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
@@ -2655,10 +2655,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>126889311</v>
+        <v>126891314</v>
       </c>
       <c r="B21" t="n">
-        <v>91291</v>
+        <v>80146</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2666,21 +2666,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5447</v>
+        <v>6462</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2690,10 +2690,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>672799</v>
+        <v>672999</v>
       </c>
       <c r="R21" t="n">
-        <v>7058086</v>
+        <v>7058211</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2740,12 +2740,12 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Fredrik Wilde, Alva Danielsson, Emil Lindgren, Mattias Dalkvist, Elke Blöhbaum, Miriam Schenk, Vilhelm Kroon</t>
+          <t>Alva Danielsson, Liam Sebestyén, Mattias Dalkvist, Miriam Schenk, Fredrik Wilde, Elke Blöhbaum, Emil Lindgren</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
@@ -2756,10 +2756,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>126891314</v>
+        <v>126889370</v>
       </c>
       <c r="B22" t="n">
-        <v>80146</v>
+        <v>4772</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2767,34 +2767,39 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6462</v>
+        <v>100299</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Kravattensliden, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>672999</v>
+        <v>672839</v>
       </c>
       <c r="R22" t="n">
-        <v>7058211</v>
+        <v>7058141</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2841,12 +2846,12 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Liam Sebestyén, Mattias Dalkvist, Miriam Schenk, Fredrik Wilde, Elke Blöhbaum, Emil Lindgren</t>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Fredrik Wilde, Alva Danielsson, Emil Lindgren, Mattias Dalkvist, Elke Blöhbaum, Miriam Schenk, Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
@@ -2857,10 +2862,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>126889370</v>
+        <v>126889311</v>
       </c>
       <c r="B23" t="n">
-        <v>4772</v>
+        <v>91291</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2868,39 +2873,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100299</v>
+        <v>5447</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Kravattensliden, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>672839</v>
+        <v>672799</v>
       </c>
       <c r="R23" t="n">
-        <v>7058141</v>
+        <v>7058086</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3391,10 +3391,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>126893730</v>
+        <v>126889847</v>
       </c>
       <c r="B28" t="n">
-        <v>79014</v>
+        <v>57654</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3402,34 +3402,42 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Kravattensliden, Ång</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>672929</v>
+        <v>672981</v>
       </c>
       <c r="R28" t="n">
-        <v>7058213</v>
+        <v>7058264</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3476,12 +3484,12 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Fredrik Wilde, Liam Sebestyén, Elke Blöhbaum, Miriam Schenk, Mattias Dalkvist, Emil Lindgren</t>
+          <t>Liam Sebestyén, Philipp Weiss, Miriam Schenk, Cajsa Björkén, Fredrik Wilde, Alva Danielsson, Elke Blöhbaum, Vilhelm Kroon, Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr">
@@ -3492,32 +3500,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>126891313</v>
+        <v>126893730</v>
       </c>
       <c r="B29" t="n">
-        <v>80146</v>
+        <v>79014</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3527,10 +3535,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>672933</v>
+        <v>672929</v>
       </c>
       <c r="R29" t="n">
-        <v>7058201</v>
+        <v>7058213</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3582,7 +3590,7 @@
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Liam Sebestyén, Mattias Dalkvist, Miriam Schenk, Fredrik Wilde, Elke Blöhbaum, Emil Lindgren</t>
+          <t>Alva Danielsson, Fredrik Wilde, Liam Sebestyén, Elke Blöhbaum, Miriam Schenk, Mattias Dalkvist, Emil Lindgren</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr">
@@ -3593,53 +3601,45 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>126889847</v>
+        <v>126891313</v>
       </c>
       <c r="B30" t="n">
-        <v>57654</v>
+        <v>80146</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100049</v>
+        <v>6462</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Kravattensliden, Ång</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>672981</v>
+        <v>672933</v>
       </c>
       <c r="R30" t="n">
-        <v>7058264</v>
+        <v>7058201</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3686,12 +3686,12 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Philipp Weiss, Miriam Schenk, Cajsa Björkén, Fredrik Wilde, Alva Danielsson, Elke Blöhbaum, Vilhelm Kroon, Mattias Dalkvist</t>
+          <t>Alva Danielsson, Liam Sebestyén, Mattias Dalkvist, Miriam Schenk, Fredrik Wilde, Elke Blöhbaum, Emil Lindgren</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr">
@@ -4335,10 +4335,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>126892814</v>
+        <v>126892813</v>
       </c>
       <c r="B37" t="n">
-        <v>79046</v>
+        <v>79014</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4346,21 +4346,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4370,13 +4370,13 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>672659</v>
+        <v>672661</v>
       </c>
       <c r="R37" t="n">
-        <v>7058027</v>
+        <v>7058026</v>
       </c>
       <c r="S37" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4446,7 +4446,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>126892813</v>
+        <v>126890308</v>
       </c>
       <c r="B38" t="n">
         <v>79014</v>
@@ -4481,13 +4481,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>672661</v>
+        <v>672880</v>
       </c>
       <c r="R38" t="n">
-        <v>7058026</v>
+        <v>7058209</v>
       </c>
       <c r="S38" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4514,19 +4514,9 @@
           <t>2025-07-24</t>
         </is>
       </c>
-      <c r="Z38" t="inlineStr">
-        <is>
-          <t>11:51</t>
-        </is>
-      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-07-24</t>
-        </is>
-      </c>
-      <c r="AB38" t="inlineStr">
-        <is>
-          <t>11:51</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4541,12 +4531,12 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist, Fredrik Wilde, Liam Sebestyén, Alva Danielsson, Elke Blöhbaum, Vilhelm Kroon, Miriam Schenk, Cajsa Björkén, Philipp Weiss, Emil Lindgren</t>
+          <t>Vilhelm Kroon, Cajsa Björkén, Fredrik Wilde, Mattias Dalkvist, Philipp Weiss, Miriam Schenk, Liam Sebestyén, Alva Danielsson, Emil Lindgren</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr">
@@ -4557,10 +4547,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>126890308</v>
+        <v>126892814</v>
       </c>
       <c r="B39" t="n">
-        <v>79014</v>
+        <v>79046</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4568,21 +4558,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4592,13 +4582,13 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>672880</v>
+        <v>672659</v>
       </c>
       <c r="R39" t="n">
-        <v>7058209</v>
+        <v>7058027</v>
       </c>
       <c r="S39" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4625,9 +4615,19 @@
           <t>2025-07-24</t>
         </is>
       </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>11:51</t>
+        </is>
+      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-07-24</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4642,12 +4642,12 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon, Cajsa Björkén, Fredrik Wilde, Mattias Dalkvist, Philipp Weiss, Miriam Schenk, Liam Sebestyén, Alva Danielsson, Emil Lindgren</t>
+          <t>Mattias Dalkvist, Fredrik Wilde, Liam Sebestyén, Alva Danielsson, Elke Blöhbaum, Vilhelm Kroon, Miriam Schenk, Cajsa Björkén, Philipp Weiss, Emil Lindgren</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr">
@@ -4864,45 +4864,52 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>126880507</v>
+        <v>126893671</v>
       </c>
       <c r="B42" t="n">
-        <v>82855</v>
+        <v>91291</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1312</v>
+        <v>5447</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr"/>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Kravattensliden, Kravattensliden, Ång</t>
+          <t>Kravattensliden , Ång</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>672859</v>
+        <v>672808</v>
       </c>
       <c r="R42" t="n">
-        <v>7058136</v>
+        <v>7058090</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4943,18 +4950,19 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
+      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Fredrik Wilde</t>
+          <t>Emil Lindgren</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Fredrik Wilde</t>
+          <t>Emil Lindgren</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr">
@@ -5177,52 +5185,45 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>126893671</v>
+        <v>126889506</v>
       </c>
       <c r="B45" t="n">
-        <v>91291</v>
+        <v>79014</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="J45" t="inlineStr"/>
-      <c r="K45" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Kravattensliden , Ång</t>
+          <t>Kravattensliden, Ång</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>672808</v>
+        <v>672889</v>
       </c>
       <c r="R45" t="n">
-        <v>7058090</v>
+        <v>7058145</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5263,19 +5264,18 @@
       <c r="AE45" t="b">
         <v>0</v>
       </c>
-      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Emil Lindgren</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Emil Lindgren</t>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Fredrik Wilde, Alva Danielsson, Emil Lindgren, Mattias Dalkvist, Elke Blöhbaum, Miriam Schenk, Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr">
@@ -5286,10 +5286,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>126889506</v>
+        <v>126880507</v>
       </c>
       <c r="B46" t="n">
-        <v>79014</v>
+        <v>82855</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5297,34 +5297,34 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Kravattensliden, Ång</t>
+          <t>Kravattensliden, Kravattensliden, Ång</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>672889</v>
+        <v>672859</v>
       </c>
       <c r="R46" t="n">
-        <v>7058145</v>
+        <v>7058136</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5371,12 +5371,12 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Fredrik Wilde</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Fredrik Wilde, Alva Danielsson, Emil Lindgren, Mattias Dalkvist, Elke Blöhbaum, Miriam Schenk, Vilhelm Kroon</t>
+          <t>Fredrik Wilde</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr">
@@ -7658,32 +7658,32 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>126890370</v>
+        <v>126890401</v>
       </c>
       <c r="B69" t="n">
-        <v>80146</v>
+        <v>79014</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7693,10 +7693,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>672554</v>
+        <v>672705</v>
       </c>
       <c r="R69" t="n">
-        <v>7058145</v>
+        <v>7058080</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7860,32 +7860,32 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>126890401</v>
+        <v>126890370</v>
       </c>
       <c r="B71" t="n">
-        <v>79014</v>
+        <v>80146</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7895,10 +7895,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>672705</v>
+        <v>672554</v>
       </c>
       <c r="R71" t="n">
-        <v>7058080</v>
+        <v>7058145</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8365,10 +8365,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>126890354</v>
+        <v>126890404</v>
       </c>
       <c r="B76" t="n">
-        <v>79046</v>
+        <v>79014</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8376,21 +8376,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8400,10 +8400,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>672891</v>
+        <v>672805</v>
       </c>
       <c r="R76" t="n">
-        <v>7058285</v>
+        <v>7058312</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8466,10 +8466,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>126890404</v>
+        <v>126890354</v>
       </c>
       <c r="B77" t="n">
-        <v>79014</v>
+        <v>79046</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8477,21 +8477,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8501,10 +8501,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>672805</v>
+        <v>672891</v>
       </c>
       <c r="R77" t="n">
-        <v>7058312</v>
+        <v>7058285</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -9173,10 +9173,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>126890403</v>
+        <v>126890352</v>
       </c>
       <c r="B84" t="n">
-        <v>79014</v>
+        <v>79046</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9184,21 +9184,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9208,10 +9208,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>672796</v>
+        <v>672847</v>
       </c>
       <c r="R84" t="n">
-        <v>7058317</v>
+        <v>7058276</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9274,10 +9274,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>126890352</v>
+        <v>126890403</v>
       </c>
       <c r="B85" t="n">
-        <v>79046</v>
+        <v>79014</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9285,21 +9285,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9309,10 +9309,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>672847</v>
+        <v>672796</v>
       </c>
       <c r="R85" t="n">
-        <v>7058276</v>
+        <v>7058317</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>

--- a/artfynd/A 27938-2023 artfynd.xlsx
+++ b/artfynd/A 27938-2023 artfynd.xlsx
@@ -2331,32 +2331,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>126891131</v>
+        <v>126892810</v>
       </c>
       <c r="B18" t="n">
-        <v>79046</v>
+        <v>91291</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>185</v>
+        <v>5447</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2366,13 +2366,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>672898</v>
+        <v>672801</v>
       </c>
       <c r="R18" t="n">
-        <v>7058209</v>
+        <v>7058081</v>
       </c>
       <c r="S18" t="n">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2399,30 +2399,39 @@
           <t>2025-07-24</t>
         </is>
       </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>11:35</t>
+        </is>
+      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-07-24</t>
         </is>
       </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>11:35</t>
+        </is>
+      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Miriam Schenk</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Miriam Schenk, Cajsa Björkén, Fredrik Wilde, Philipp Weiss, Mattias Dalkvist, Vilhelm Kroon, Liam Sebestyén, Emil Lindgren, Alva Danielsson</t>
+          <t>Mattias Dalkvist, Fredrik Wilde, Liam Sebestyén, Alva Danielsson, Elke Blöhbaum, Vilhelm Kroon, Miriam Schenk, Cajsa Björkén, Philipp Weiss, Emil Lindgren</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
@@ -2433,32 +2442,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>126892810</v>
+        <v>126892808</v>
       </c>
       <c r="B19" t="n">
-        <v>91291</v>
+        <v>79014</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2468,13 +2477,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>672801</v>
+        <v>672862</v>
       </c>
       <c r="R19" t="n">
-        <v>7058081</v>
+        <v>7058125</v>
       </c>
       <c r="S19" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2503,7 +2512,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2513,7 +2522,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2544,10 +2553,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>126892808</v>
+        <v>126891131</v>
       </c>
       <c r="B20" t="n">
-        <v>79014</v>
+        <v>79046</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2555,21 +2564,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2579,13 +2588,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>672862</v>
+        <v>672898</v>
       </c>
       <c r="R20" t="n">
-        <v>7058125</v>
+        <v>7058209</v>
       </c>
       <c r="S20" t="n">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2612,39 +2621,30 @@
           <t>2025-07-24</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>11:25</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-07-24</t>
         </is>
       </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>11:25</t>
-        </is>
-      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Miriam Schenk</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist, Fredrik Wilde, Liam Sebestyén, Alva Danielsson, Elke Blöhbaum, Vilhelm Kroon, Miriam Schenk, Cajsa Björkén, Philipp Weiss, Emil Lindgren</t>
+          <t>Miriam Schenk, Cajsa Björkén, Fredrik Wilde, Philipp Weiss, Mattias Dalkvist, Vilhelm Kroon, Liam Sebestyén, Emil Lindgren, Alva Danielsson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
@@ -3391,10 +3391,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>126889847</v>
+        <v>126893730</v>
       </c>
       <c r="B28" t="n">
-        <v>57654</v>
+        <v>79014</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3402,42 +3402,34 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Kravattensliden, Ång</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>672981</v>
+        <v>672929</v>
       </c>
       <c r="R28" t="n">
-        <v>7058264</v>
+        <v>7058213</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3484,12 +3476,12 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Philipp Weiss, Miriam Schenk, Cajsa Björkén, Fredrik Wilde, Alva Danielsson, Elke Blöhbaum, Vilhelm Kroon, Mattias Dalkvist</t>
+          <t>Alva Danielsson, Fredrik Wilde, Liam Sebestyén, Elke Blöhbaum, Miriam Schenk, Mattias Dalkvist, Emil Lindgren</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr">
@@ -3500,32 +3492,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>126893730</v>
+        <v>126891313</v>
       </c>
       <c r="B29" t="n">
-        <v>79014</v>
+        <v>80146</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3535,10 +3527,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>672929</v>
+        <v>672933</v>
       </c>
       <c r="R29" t="n">
-        <v>7058213</v>
+        <v>7058201</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3590,7 +3582,7 @@
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Fredrik Wilde, Liam Sebestyén, Elke Blöhbaum, Miriam Schenk, Mattias Dalkvist, Emil Lindgren</t>
+          <t>Alva Danielsson, Liam Sebestyén, Mattias Dalkvist, Miriam Schenk, Fredrik Wilde, Elke Blöhbaum, Emil Lindgren</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr">
@@ -3601,45 +3593,53 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>126891313</v>
+        <v>126889847</v>
       </c>
       <c r="B30" t="n">
-        <v>80146</v>
+        <v>57654</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6462</v>
+        <v>100049</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Kravattensliden, Ång</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>672933</v>
+        <v>672981</v>
       </c>
       <c r="R30" t="n">
-        <v>7058201</v>
+        <v>7058264</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3686,12 +3686,12 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Liam Sebestyén, Mattias Dalkvist, Miriam Schenk, Fredrik Wilde, Elke Blöhbaum, Emil Lindgren</t>
+          <t>Liam Sebestyén, Philipp Weiss, Miriam Schenk, Cajsa Björkén, Fredrik Wilde, Alva Danielsson, Elke Blöhbaum, Vilhelm Kroon, Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr">
@@ -4864,52 +4864,45 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>126893671</v>
+        <v>126880507</v>
       </c>
       <c r="B42" t="n">
-        <v>91291</v>
+        <v>82855</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>5447</v>
+        <v>1312</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="J42" t="inlineStr"/>
-      <c r="K42" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Kravattensliden , Ång</t>
+          <t>Kravattensliden, Kravattensliden, Ång</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>672808</v>
+        <v>672859</v>
       </c>
       <c r="R42" t="n">
-        <v>7058090</v>
+        <v>7058136</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4950,19 +4943,18 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
-      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Emil Lindgren</t>
+          <t>Fredrik Wilde</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Emil Lindgren</t>
+          <t>Fredrik Wilde</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr">
@@ -5185,45 +5177,52 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>126889506</v>
+        <v>126893671</v>
       </c>
       <c r="B45" t="n">
-        <v>79014</v>
+        <v>91291</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="J45" t="inlineStr"/>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Kravattensliden, Ång</t>
+          <t>Kravattensliden , Ång</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>672889</v>
+        <v>672808</v>
       </c>
       <c r="R45" t="n">
-        <v>7058145</v>
+        <v>7058090</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5264,18 +5263,19 @@
       <c r="AE45" t="b">
         <v>0</v>
       </c>
+      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Emil Lindgren</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Fredrik Wilde, Alva Danielsson, Emil Lindgren, Mattias Dalkvist, Elke Blöhbaum, Miriam Schenk, Vilhelm Kroon</t>
+          <t>Emil Lindgren</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr">
@@ -5286,10 +5286,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>126880507</v>
+        <v>126889506</v>
       </c>
       <c r="B46" t="n">
-        <v>82855</v>
+        <v>79014</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5297,34 +5297,34 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Kravattensliden, Kravattensliden, Ång</t>
+          <t>Kravattensliden, Ång</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>672859</v>
+        <v>672889</v>
       </c>
       <c r="R46" t="n">
-        <v>7058136</v>
+        <v>7058145</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5371,12 +5371,12 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Fredrik Wilde</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Fredrik Wilde</t>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Fredrik Wilde, Alva Danielsson, Emil Lindgren, Mattias Dalkvist, Elke Blöhbaum, Miriam Schenk, Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr">
@@ -5791,45 +5791,45 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>126879684</v>
+        <v>126889837</v>
       </c>
       <c r="B51" t="n">
-        <v>79014</v>
+        <v>91291</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Kravattensliden, Kravattensliden, Ång</t>
+          <t>Kravattensliden, Ång</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>672895</v>
+        <v>672912</v>
       </c>
       <c r="R51" t="n">
-        <v>7058223</v>
+        <v>7058191</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5876,12 +5876,12 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Fredrik Wilde</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Fredrik Wilde</t>
+          <t>Liam Sebestyén, Philipp Weiss, Miriam Schenk, Cajsa Björkén, Fredrik Wilde, Alva Danielsson, Elke Blöhbaum, Vilhelm Kroon, Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr">
@@ -5993,10 +5993,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>126889862</v>
+        <v>126891325</v>
       </c>
       <c r="B53" t="n">
-        <v>91344</v>
+        <v>79014</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6004,21 +6004,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6028,10 +6028,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>672981</v>
+        <v>672660</v>
       </c>
       <c r="R53" t="n">
-        <v>7058264</v>
+        <v>7057985</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6078,12 +6078,12 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Philipp Weiss, Miriam Schenk, Cajsa Björkén, Fredrik Wilde, Alva Danielsson, Elke Blöhbaum, Vilhelm Kroon, Mattias Dalkvist</t>
+          <t>Alva Danielsson, Liam Sebestyén, Mattias Dalkvist, Miriam Schenk, Fredrik Wilde, Elke Blöhbaum, Emil Lindgren</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr">
@@ -6094,32 +6094,32 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>126889837</v>
+        <v>126889862</v>
       </c>
       <c r="B54" t="n">
-        <v>91291</v>
+        <v>91344</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>5447</v>
+        <v>5432</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6129,10 +6129,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>672912</v>
+        <v>672981</v>
       </c>
       <c r="R54" t="n">
-        <v>7058191</v>
+        <v>7058264</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6195,7 +6195,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>126891325</v>
+        <v>126879684</v>
       </c>
       <c r="B55" t="n">
         <v>79014</v>
@@ -6226,14 +6226,14 @@
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Kravattensliden, Ång</t>
+          <t>Kravattensliden, Kravattensliden, Ång</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>672660</v>
+        <v>672895</v>
       </c>
       <c r="R55" t="n">
-        <v>7057985</v>
+        <v>7058223</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6280,12 +6280,12 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Fredrik Wilde</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Liam Sebestyén, Mattias Dalkvist, Miriam Schenk, Fredrik Wilde, Elke Blöhbaum, Emil Lindgren</t>
+          <t>Fredrik Wilde</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr">
@@ -6710,7 +6710,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>126892809</v>
+        <v>126892812</v>
       </c>
       <c r="B60" t="n">
         <v>79014</v>
@@ -6745,13 +6745,13 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>672831</v>
+        <v>672685</v>
       </c>
       <c r="R60" t="n">
-        <v>7058091</v>
+        <v>7058010</v>
       </c>
       <c r="S60" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -6780,7 +6780,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -6790,7 +6790,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6821,48 +6821,53 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>126890296</v>
+        <v>126880199</v>
       </c>
       <c r="B61" t="n">
-        <v>80146</v>
+        <v>79014</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Kravattensliden, Ång</t>
+          <t>Kravattensliden, Kravattensliden, Ång</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>673025</v>
+        <v>672894</v>
       </c>
       <c r="R61" t="n">
-        <v>7058244</v>
+        <v>7058198</v>
       </c>
       <c r="S61" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -6906,12 +6911,12 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Fredrik Wilde</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon, Cajsa Björkén, Fredrik Wilde, Mattias Dalkvist, Philipp Weiss, Miriam Schenk, Liam Sebestyén, Alva Danielsson, Emil Lindgren</t>
+          <t>Fredrik Wilde</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr">
@@ -6922,7 +6927,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>126892812</v>
+        <v>126892809</v>
       </c>
       <c r="B62" t="n">
         <v>79014</v>
@@ -6957,13 +6962,13 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>672685</v>
+        <v>672831</v>
       </c>
       <c r="R62" t="n">
-        <v>7058010</v>
+        <v>7058091</v>
       </c>
       <c r="S62" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -6992,7 +6997,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7002,7 +7007,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7033,53 +7038,48 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>126880199</v>
+        <v>126890296</v>
       </c>
       <c r="B63" t="n">
-        <v>79014</v>
+        <v>80146</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
-      <c r="K63" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Kravattensliden, Kravattensliden, Ång</t>
+          <t>Kravattensliden, Ång</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>672894</v>
+        <v>673025</v>
       </c>
       <c r="R63" t="n">
-        <v>7058198</v>
+        <v>7058244</v>
       </c>
       <c r="S63" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7123,12 +7123,12 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Fredrik Wilde</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Fredrik Wilde</t>
+          <t>Vilhelm Kroon, Cajsa Björkén, Fredrik Wilde, Mattias Dalkvist, Philipp Weiss, Miriam Schenk, Liam Sebestyén, Alva Danielsson, Emil Lindgren</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr">
@@ -7139,45 +7139,54 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>126891312</v>
+        <v>126879033</v>
       </c>
       <c r="B64" t="n">
-        <v>91291</v>
+        <v>79046</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>5447</v>
+        <v>185</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr"/>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Kravattensliden, Ång</t>
+          <t>Kravattensliden, Kravattensliden, Ång</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>673027</v>
+        <v>673046</v>
       </c>
       <c r="R64" t="n">
-        <v>7058282</v>
+        <v>7058286</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7224,12 +7233,12 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Fredrik Wilde</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Liam Sebestyén, Mattias Dalkvist, Miriam Schenk, Fredrik Wilde, Elke Blöhbaum, Emil Lindgren</t>
+          <t>Fredrik Wilde</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr">
@@ -7240,32 +7249,32 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>126879425</v>
+        <v>126880532</v>
       </c>
       <c r="B65" t="n">
-        <v>79014</v>
+        <v>80146</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7275,10 +7284,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>672947</v>
+        <v>672863</v>
       </c>
       <c r="R65" t="n">
-        <v>7058198</v>
+        <v>7058124</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7341,45 +7350,50 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>126880532</v>
+        <v>126889382</v>
       </c>
       <c r="B66" t="n">
-        <v>80146</v>
+        <v>57654</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6462</v>
+        <v>100049</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Kravattensliden, Kravattensliden, Ång</t>
+          <t>Kravattensliden, Ång</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>672863</v>
+        <v>672838</v>
       </c>
       <c r="R66" t="n">
-        <v>7058124</v>
+        <v>7058134</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7426,12 +7440,12 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Fredrik Wilde</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Fredrik Wilde</t>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Fredrik Wilde, Alva Danielsson, Emil Lindgren, Mattias Dalkvist, Elke Blöhbaum, Miriam Schenk, Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr">
@@ -7442,54 +7456,45 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>126879033</v>
+        <v>126891312</v>
       </c>
       <c r="B67" t="n">
-        <v>79046</v>
+        <v>91291</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>185</v>
+        <v>5447</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J67" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Kravattensliden, Kravattensliden, Ång</t>
+          <t>Kravattensliden, Ång</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>673046</v>
+        <v>673027</v>
       </c>
       <c r="R67" t="n">
-        <v>7058286</v>
+        <v>7058282</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7536,12 +7541,12 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Fredrik Wilde</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Fredrik Wilde</t>
+          <t>Alva Danielsson, Liam Sebestyén, Mattias Dalkvist, Miriam Schenk, Fredrik Wilde, Elke Blöhbaum, Emil Lindgren</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr">
@@ -7552,10 +7557,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>126889382</v>
+        <v>126879425</v>
       </c>
       <c r="B68" t="n">
-        <v>57654</v>
+        <v>79014</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7563,39 +7568,34 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
-      <c r="M68" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Kravattensliden, Ång</t>
+          <t>Kravattensliden, Kravattensliden, Ång</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>672838</v>
+        <v>672947</v>
       </c>
       <c r="R68" t="n">
-        <v>7058134</v>
+        <v>7058198</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7642,12 +7642,12 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Fredrik Wilde</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Fredrik Wilde, Alva Danielsson, Emil Lindgren, Mattias Dalkvist, Elke Blöhbaum, Miriam Schenk, Vilhelm Kroon</t>
+          <t>Fredrik Wilde</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr">
@@ -7658,32 +7658,32 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>126890401</v>
+        <v>126890370</v>
       </c>
       <c r="B69" t="n">
-        <v>79014</v>
+        <v>80146</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7693,10 +7693,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>672705</v>
+        <v>672554</v>
       </c>
       <c r="R69" t="n">
-        <v>7058080</v>
+        <v>7058145</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7860,32 +7860,32 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>126890370</v>
+        <v>126890401</v>
       </c>
       <c r="B71" t="n">
-        <v>80146</v>
+        <v>79014</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7895,10 +7895,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>672554</v>
+        <v>672705</v>
       </c>
       <c r="R71" t="n">
-        <v>7058145</v>
+        <v>7058080</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -9173,10 +9173,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>126890352</v>
+        <v>126890403</v>
       </c>
       <c r="B84" t="n">
-        <v>79046</v>
+        <v>79014</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9184,21 +9184,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9208,10 +9208,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>672847</v>
+        <v>672796</v>
       </c>
       <c r="R84" t="n">
-        <v>7058276</v>
+        <v>7058317</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9274,10 +9274,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>126890403</v>
+        <v>126890352</v>
       </c>
       <c r="B85" t="n">
-        <v>79014</v>
+        <v>79046</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9285,21 +9285,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9309,10 +9309,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>672796</v>
+        <v>672847</v>
       </c>
       <c r="R85" t="n">
-        <v>7058317</v>
+        <v>7058276</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>

--- a/artfynd/A 27938-2023 artfynd.xlsx
+++ b/artfynd/A 27938-2023 artfynd.xlsx
@@ -675,45 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>126879850</v>
+        <v>126889833</v>
       </c>
       <c r="B2" t="n">
-        <v>88729</v>
+        <v>91295</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>510</v>
+        <v>5447</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Kravattensliden, Kravattensliden, Ång</t>
+          <t>Kravattensliden, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>672873</v>
+        <v>672799</v>
       </c>
       <c r="R2" t="n">
-        <v>7058228</v>
+        <v>7058073</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -760,12 +760,12 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Fredrik Wilde</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Fredrik Wilde</t>
+          <t>Liam Sebestyén, Philipp Weiss, Miriam Schenk, Cajsa Björkén, Fredrik Wilde, Alva Danielsson, Elke Blöhbaum, Vilhelm Kroon, Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -779,7 +779,7 @@
         <v>126889312</v>
       </c>
       <c r="B3" t="n">
-        <v>91291</v>
+        <v>91295</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -877,45 +877,45 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126889833</v>
+        <v>126879850</v>
       </c>
       <c r="B4" t="n">
-        <v>91291</v>
+        <v>88733</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5447</v>
+        <v>510</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Kravattensliden, Ång</t>
+          <t>Kravattensliden, Kravattensliden, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>672799</v>
+        <v>672873</v>
       </c>
       <c r="R4" t="n">
-        <v>7058073</v>
+        <v>7058228</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -962,12 +962,12 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Fredrik Wilde</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Philipp Weiss, Miriam Schenk, Cajsa Björkén, Fredrik Wilde, Alva Danielsson, Elke Blöhbaum, Vilhelm Kroon, Mattias Dalkvist</t>
+          <t>Fredrik Wilde</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
@@ -981,7 +981,7 @@
         <v>126889402</v>
       </c>
       <c r="B5" t="n">
-        <v>97321</v>
+        <v>97325</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1082,7 +1082,7 @@
         <v>126889505</v>
       </c>
       <c r="B6" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1183,7 +1183,7 @@
         <v>126892805</v>
       </c>
       <c r="B7" t="n">
-        <v>57657</v>
+        <v>57661</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1299,7 +1299,7 @@
         <v>126892811</v>
       </c>
       <c r="B8" t="n">
-        <v>79046</v>
+        <v>79050</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1407,10 +1407,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126893729</v>
+        <v>126891323</v>
       </c>
       <c r="B9" t="n">
-        <v>79014</v>
+        <v>91348</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1418,21 +1418,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1442,10 +1442,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>672603</v>
+        <v>672897</v>
       </c>
       <c r="R9" t="n">
-        <v>7057959</v>
+        <v>7058210</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1497,7 +1497,7 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Fredrik Wilde, Liam Sebestyén, Elke Blöhbaum, Miriam Schenk, Mattias Dalkvist, Emil Lindgren</t>
+          <t>Alva Danielsson, Liam Sebestyén, Mattias Dalkvist, Miriam Schenk, Fredrik Wilde, Elke Blöhbaum, Emil Lindgren</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
@@ -1508,10 +1508,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126891323</v>
+        <v>126889513</v>
       </c>
       <c r="B10" t="n">
-        <v>91344</v>
+        <v>79018</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1519,21 +1519,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1543,10 +1543,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>672897</v>
+        <v>673038</v>
       </c>
       <c r="R10" t="n">
-        <v>7058210</v>
+        <v>7058279</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1593,12 +1593,12 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Liam Sebestyén, Mattias Dalkvist, Miriam Schenk, Fredrik Wilde, Elke Blöhbaum, Emil Lindgren</t>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Fredrik Wilde, Alva Danielsson, Emil Lindgren, Mattias Dalkvist, Elke Blöhbaum, Miriam Schenk, Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
@@ -1609,10 +1609,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126889513</v>
+        <v>126893729</v>
       </c>
       <c r="B11" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1644,10 +1644,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>673038</v>
+        <v>672603</v>
       </c>
       <c r="R11" t="n">
-        <v>7058279</v>
+        <v>7057959</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1694,12 +1694,12 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Fredrik Wilde, Alva Danielsson, Emil Lindgren, Mattias Dalkvist, Elke Blöhbaum, Miriam Schenk, Vilhelm Kroon</t>
+          <t>Alva Danielsson, Fredrik Wilde, Liam Sebestyén, Elke Blöhbaum, Miriam Schenk, Mattias Dalkvist, Emil Lindgren</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
@@ -1713,7 +1713,7 @@
         <v>126889493</v>
       </c>
       <c r="B12" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1814,7 +1814,7 @@
         <v>126892815</v>
       </c>
       <c r="B13" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1925,7 +1925,7 @@
         <v>126889387</v>
       </c>
       <c r="B14" t="n">
-        <v>57654</v>
+        <v>57658</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2031,7 +2031,7 @@
         <v>126889835</v>
       </c>
       <c r="B15" t="n">
-        <v>91291</v>
+        <v>91295</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2129,32 +2129,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>126889492</v>
+        <v>126891315</v>
       </c>
       <c r="B16" t="n">
-        <v>79014</v>
+        <v>98468</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>221952</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2164,10 +2164,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>672638</v>
+        <v>672827</v>
       </c>
       <c r="R16" t="n">
-        <v>7057953</v>
+        <v>7058099</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2214,12 +2214,12 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Fredrik Wilde, Alva Danielsson, Emil Lindgren, Mattias Dalkvist, Elke Blöhbaum, Miriam Schenk, Vilhelm Kroon</t>
+          <t>Alva Danielsson, Liam Sebestyén, Mattias Dalkvist, Miriam Schenk, Fredrik Wilde, Elke Blöhbaum, Emil Lindgren</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
@@ -2230,32 +2230,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>126891315</v>
+        <v>126889492</v>
       </c>
       <c r="B17" t="n">
-        <v>98464</v>
+        <v>79018</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>221952</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2265,10 +2265,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>672827</v>
+        <v>672638</v>
       </c>
       <c r="R17" t="n">
-        <v>7058099</v>
+        <v>7057953</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2315,12 +2315,12 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Liam Sebestyén, Mattias Dalkvist, Miriam Schenk, Fredrik Wilde, Elke Blöhbaum, Emil Lindgren</t>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Fredrik Wilde, Alva Danielsson, Emil Lindgren, Mattias Dalkvist, Elke Blöhbaum, Miriam Schenk, Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
@@ -2331,32 +2331,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>126892810</v>
+        <v>126891131</v>
       </c>
       <c r="B18" t="n">
-        <v>91291</v>
+        <v>79050</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5447</v>
+        <v>185</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2366,13 +2366,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>672801</v>
+        <v>672898</v>
       </c>
       <c r="R18" t="n">
-        <v>7058081</v>
+        <v>7058209</v>
       </c>
       <c r="S18" t="n">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2399,39 +2399,30 @@
           <t>2025-07-24</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>11:35</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-07-24</t>
         </is>
       </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>11:35</t>
-        </is>
-      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Miriam Schenk</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist, Fredrik Wilde, Liam Sebestyén, Alva Danielsson, Elke Blöhbaum, Vilhelm Kroon, Miriam Schenk, Cajsa Björkén, Philipp Weiss, Emil Lindgren</t>
+          <t>Miriam Schenk, Cajsa Björkén, Fredrik Wilde, Philipp Weiss, Mattias Dalkvist, Vilhelm Kroon, Liam Sebestyén, Emil Lindgren, Alva Danielsson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
@@ -2442,32 +2433,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>126892808</v>
+        <v>126892810</v>
       </c>
       <c r="B19" t="n">
-        <v>79014</v>
+        <v>91295</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2477,13 +2468,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>672862</v>
+        <v>672801</v>
       </c>
       <c r="R19" t="n">
-        <v>7058125</v>
+        <v>7058081</v>
       </c>
       <c r="S19" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2512,7 +2503,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2522,7 +2513,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2553,10 +2544,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>126891131</v>
+        <v>126892808</v>
       </c>
       <c r="B20" t="n">
-        <v>79046</v>
+        <v>79018</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2564,21 +2555,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2588,13 +2579,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>672898</v>
+        <v>672862</v>
       </c>
       <c r="R20" t="n">
-        <v>7058209</v>
+        <v>7058125</v>
       </c>
       <c r="S20" t="n">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2621,30 +2612,39 @@
           <t>2025-07-24</t>
         </is>
       </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>11:25</t>
+        </is>
+      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-07-24</t>
         </is>
       </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>11:25</t>
+        </is>
+      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Miriam Schenk</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Miriam Schenk, Cajsa Björkén, Fredrik Wilde, Philipp Weiss, Mattias Dalkvist, Vilhelm Kroon, Liam Sebestyén, Emil Lindgren, Alva Danielsson</t>
+          <t>Mattias Dalkvist, Fredrik Wilde, Liam Sebestyén, Alva Danielsson, Elke Blöhbaum, Vilhelm Kroon, Miriam Schenk, Cajsa Björkén, Philipp Weiss, Emil Lindgren</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
@@ -2655,10 +2655,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>126891314</v>
+        <v>126889311</v>
       </c>
       <c r="B21" t="n">
-        <v>80146</v>
+        <v>91295</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2666,21 +2666,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6462</v>
+        <v>5447</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2690,10 +2690,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>672999</v>
+        <v>672799</v>
       </c>
       <c r="R21" t="n">
-        <v>7058211</v>
+        <v>7058086</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2740,12 +2740,12 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Liam Sebestyén, Mattias Dalkvist, Miriam Schenk, Fredrik Wilde, Elke Blöhbaum, Emil Lindgren</t>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Fredrik Wilde, Alva Danielsson, Emil Lindgren, Mattias Dalkvist, Elke Blöhbaum, Miriam Schenk, Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
@@ -2756,10 +2756,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>126889370</v>
+        <v>126891314</v>
       </c>
       <c r="B22" t="n">
-        <v>4772</v>
+        <v>80150</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2767,39 +2767,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100299</v>
+        <v>6462</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Kravattensliden, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>672839</v>
+        <v>672999</v>
       </c>
       <c r="R22" t="n">
-        <v>7058141</v>
+        <v>7058211</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2846,12 +2841,12 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Fredrik Wilde, Alva Danielsson, Emil Lindgren, Mattias Dalkvist, Elke Blöhbaum, Miriam Schenk, Vilhelm Kroon</t>
+          <t>Alva Danielsson, Liam Sebestyén, Mattias Dalkvist, Miriam Schenk, Fredrik Wilde, Elke Blöhbaum, Emil Lindgren</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
@@ -2862,10 +2857,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>126889311</v>
+        <v>126889370</v>
       </c>
       <c r="B23" t="n">
-        <v>91291</v>
+        <v>4773</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2873,34 +2868,39 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5447</v>
+        <v>100299</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Kravattensliden, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>672799</v>
+        <v>672839</v>
       </c>
       <c r="R23" t="n">
-        <v>7058086</v>
+        <v>7058141</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2966,7 +2966,7 @@
         <v>126889869</v>
       </c>
       <c r="B24" t="n">
-        <v>98360</v>
+        <v>98364</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3067,7 +3067,7 @@
         <v>126889374</v>
       </c>
       <c r="B25" t="n">
-        <v>98464</v>
+        <v>98468</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3179,32 +3179,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>126892816</v>
+        <v>126891313</v>
       </c>
       <c r="B26" t="n">
-        <v>79014</v>
+        <v>80150</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3214,13 +3214,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>672627</v>
+        <v>672933</v>
       </c>
       <c r="R26" t="n">
-        <v>7058024</v>
+        <v>7058201</v>
       </c>
       <c r="S26" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3247,19 +3247,9 @@
           <t>2025-07-24</t>
         </is>
       </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>11:52</t>
-        </is>
-      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-07-24</t>
-        </is>
-      </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>11:52</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3274,12 +3264,12 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist, Fredrik Wilde, Liam Sebestyén, Alva Danielsson, Elke Blöhbaum, Vilhelm Kroon, Miriam Schenk, Cajsa Björkén, Philipp Weiss, Emil Lindgren</t>
+          <t>Alva Danielsson, Liam Sebestyén, Mattias Dalkvist, Miriam Schenk, Fredrik Wilde, Elke Blöhbaum, Emil Lindgren</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr">
@@ -3290,10 +3280,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>126889502</v>
+        <v>126889847</v>
       </c>
       <c r="B27" t="n">
-        <v>79014</v>
+        <v>57658</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3301,34 +3291,42 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Kravattensliden, Ång</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>672801</v>
+        <v>672981</v>
       </c>
       <c r="R27" t="n">
-        <v>7058095</v>
+        <v>7058264</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3375,12 +3373,12 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Fredrik Wilde, Alva Danielsson, Emil Lindgren, Mattias Dalkvist, Elke Blöhbaum, Miriam Schenk, Vilhelm Kroon</t>
+          <t>Liam Sebestyén, Philipp Weiss, Miriam Schenk, Cajsa Björkén, Fredrik Wilde, Alva Danielsson, Elke Blöhbaum, Vilhelm Kroon, Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr">
@@ -3391,10 +3389,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>126893730</v>
+        <v>126889502</v>
       </c>
       <c r="B28" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3426,10 +3424,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>672929</v>
+        <v>672801</v>
       </c>
       <c r="R28" t="n">
-        <v>7058213</v>
+        <v>7058095</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3476,12 +3474,12 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Fredrik Wilde, Liam Sebestyén, Elke Blöhbaum, Miriam Schenk, Mattias Dalkvist, Emil Lindgren</t>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Fredrik Wilde, Alva Danielsson, Emil Lindgren, Mattias Dalkvist, Elke Blöhbaum, Miriam Schenk, Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr">
@@ -3492,32 +3490,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>126891313</v>
+        <v>126892816</v>
       </c>
       <c r="B29" t="n">
-        <v>80146</v>
+        <v>79018</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3527,13 +3525,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>672933</v>
+        <v>672627</v>
       </c>
       <c r="R29" t="n">
-        <v>7058201</v>
+        <v>7058024</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3560,9 +3558,19 @@
           <t>2025-07-24</t>
         </is>
       </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>11:52</t>
+        </is>
+      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-07-24</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3577,12 +3585,12 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Liam Sebestyén, Mattias Dalkvist, Miriam Schenk, Fredrik Wilde, Elke Blöhbaum, Emil Lindgren</t>
+          <t>Mattias Dalkvist, Fredrik Wilde, Liam Sebestyén, Alva Danielsson, Elke Blöhbaum, Vilhelm Kroon, Miriam Schenk, Cajsa Björkén, Philipp Weiss, Emil Lindgren</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr">
@@ -3593,10 +3601,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>126889847</v>
+        <v>126893730</v>
       </c>
       <c r="B30" t="n">
-        <v>57654</v>
+        <v>79018</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3604,42 +3612,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Kravattensliden, Ång</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>672981</v>
+        <v>672929</v>
       </c>
       <c r="R30" t="n">
-        <v>7058264</v>
+        <v>7058213</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3686,12 +3686,12 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Philipp Weiss, Miriam Schenk, Cajsa Björkén, Fredrik Wilde, Alva Danielsson, Elke Blöhbaum, Vilhelm Kroon, Mattias Dalkvist</t>
+          <t>Alva Danielsson, Fredrik Wilde, Liam Sebestyén, Elke Blöhbaum, Miriam Schenk, Mattias Dalkvist, Emil Lindgren</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr">
@@ -3702,10 +3702,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>126889536</v>
+        <v>126889377</v>
       </c>
       <c r="B31" t="n">
-        <v>5176</v>
+        <v>98468</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3713,27 +3713,36 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100526</v>
+        <v>221952</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
@@ -3742,10 +3751,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>672659</v>
+        <v>672810</v>
       </c>
       <c r="R31" t="n">
-        <v>7057975</v>
+        <v>7058105</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3808,10 +3817,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>126889377</v>
+        <v>126889536</v>
       </c>
       <c r="B32" t="n">
-        <v>98464</v>
+        <v>5177</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3819,36 +3828,27 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>221952</v>
+        <v>100526</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K32" t="inlineStr">
-        <is>
-          <t>överblommad</t>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
@@ -3857,10 +3857,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>672810</v>
+        <v>672659</v>
       </c>
       <c r="R32" t="n">
-        <v>7058105</v>
+        <v>7057975</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3926,7 +3926,7 @@
         <v>126891328</v>
       </c>
       <c r="B33" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4027,7 +4027,7 @@
         <v>126893692</v>
       </c>
       <c r="B34" t="n">
-        <v>91326</v>
+        <v>91330</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4136,7 +4136,7 @@
         <v>126889834</v>
       </c>
       <c r="B35" t="n">
-        <v>91291</v>
+        <v>91295</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4237,7 +4237,7 @@
         <v>126891134</v>
       </c>
       <c r="B36" t="n">
-        <v>80146</v>
+        <v>80150</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4335,10 +4335,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>126892813</v>
+        <v>126892814</v>
       </c>
       <c r="B37" t="n">
-        <v>79014</v>
+        <v>79050</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4346,21 +4346,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4370,13 +4370,13 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>672661</v>
+        <v>672659</v>
       </c>
       <c r="R37" t="n">
-        <v>7058026</v>
+        <v>7058027</v>
       </c>
       <c r="S37" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4449,7 +4449,7 @@
         <v>126890308</v>
       </c>
       <c r="B38" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4547,10 +4547,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>126892814</v>
+        <v>126892813</v>
       </c>
       <c r="B39" t="n">
-        <v>79046</v>
+        <v>79018</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4558,21 +4558,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4582,13 +4582,13 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>672659</v>
+        <v>672661</v>
       </c>
       <c r="R39" t="n">
-        <v>7058027</v>
+        <v>7058026</v>
       </c>
       <c r="S39" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4661,7 +4661,7 @@
         <v>126891320</v>
       </c>
       <c r="B40" t="n">
-        <v>80117</v>
+        <v>80121</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4762,7 +4762,7 @@
         <v>126893847</v>
       </c>
       <c r="B41" t="n">
-        <v>80117</v>
+        <v>80121</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4867,7 +4867,7 @@
         <v>126880507</v>
       </c>
       <c r="B42" t="n">
-        <v>82855</v>
+        <v>82859</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4965,48 +4965,55 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>126892804</v>
+        <v>126893671</v>
       </c>
       <c r="B43" t="n">
-        <v>79014</v>
+        <v>91295</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr"/>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Kravattensliden, Ång</t>
+          <t>Kravattensliden , Ång</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>673003</v>
+        <v>672808</v>
       </c>
       <c r="R43" t="n">
-        <v>7058280</v>
+        <v>7058090</v>
       </c>
       <c r="S43" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5033,39 +5040,30 @@
           <t>2025-07-24</t>
         </is>
       </c>
-      <c r="Z43" t="inlineStr">
-        <is>
-          <t>10:49</t>
-        </is>
-      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-07-24</t>
         </is>
       </c>
-      <c r="AB43" t="inlineStr">
-        <is>
-          <t>10:49</t>
-        </is>
-      </c>
       <c r="AD43" t="b">
         <v>0</v>
       </c>
       <c r="AE43" t="b">
         <v>0</v>
       </c>
+      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Emil Lindgren</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist, Fredrik Wilde, Liam Sebestyén, Alva Danielsson, Elke Blöhbaum, Vilhelm Kroon, Miriam Schenk, Cajsa Björkén, Philipp Weiss, Emil Lindgren</t>
+          <t>Emil Lindgren</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr">
@@ -5076,10 +5074,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>126891321</v>
+        <v>126889506</v>
       </c>
       <c r="B44" t="n">
-        <v>80117</v>
+        <v>79018</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5087,21 +5085,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5111,10 +5109,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>673004</v>
+        <v>672889</v>
       </c>
       <c r="R44" t="n">
-        <v>7058209</v>
+        <v>7058145</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5161,12 +5159,12 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Liam Sebestyén, Mattias Dalkvist, Miriam Schenk, Fredrik Wilde, Elke Blöhbaum, Emil Lindgren</t>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Fredrik Wilde, Alva Danielsson, Emil Lindgren, Mattias Dalkvist, Elke Blöhbaum, Miriam Schenk, Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr">
@@ -5177,52 +5175,45 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>126893671</v>
+        <v>126891321</v>
       </c>
       <c r="B45" t="n">
-        <v>91291</v>
+        <v>80121</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>5447</v>
+        <v>6458</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="J45" t="inlineStr"/>
-      <c r="K45" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Kravattensliden , Ång</t>
+          <t>Kravattensliden, Ång</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>672808</v>
+        <v>673004</v>
       </c>
       <c r="R45" t="n">
-        <v>7058090</v>
+        <v>7058209</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5263,19 +5254,18 @@
       <c r="AE45" t="b">
         <v>0</v>
       </c>
-      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Emil Lindgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Emil Lindgren</t>
+          <t>Alva Danielsson, Liam Sebestyén, Mattias Dalkvist, Miriam Schenk, Fredrik Wilde, Elke Blöhbaum, Emil Lindgren</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr">
@@ -5286,10 +5276,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>126889506</v>
+        <v>126892804</v>
       </c>
       <c r="B46" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5321,13 +5311,13 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>672889</v>
+        <v>673003</v>
       </c>
       <c r="R46" t="n">
-        <v>7058145</v>
+        <v>7058280</v>
       </c>
       <c r="S46" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5354,9 +5344,19 @@
           <t>2025-07-24</t>
         </is>
       </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>10:49</t>
+        </is>
+      </c>
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-07-24</t>
+        </is>
+      </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5371,12 +5371,12 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Fredrik Wilde, Alva Danielsson, Emil Lindgren, Mattias Dalkvist, Elke Blöhbaum, Miriam Schenk, Vilhelm Kroon</t>
+          <t>Mattias Dalkvist, Fredrik Wilde, Liam Sebestyén, Alva Danielsson, Elke Blöhbaum, Vilhelm Kroon, Miriam Schenk, Cajsa Björkén, Philipp Weiss, Emil Lindgren</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr">
@@ -5390,7 +5390,7 @@
         <v>126890311</v>
       </c>
       <c r="B47" t="n">
-        <v>88729</v>
+        <v>88733</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5491,7 +5491,7 @@
         <v>126890305</v>
       </c>
       <c r="B48" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5592,7 +5592,7 @@
         <v>126889494</v>
       </c>
       <c r="B49" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5693,7 +5693,7 @@
         <v>126889503</v>
       </c>
       <c r="B50" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5791,10 +5791,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>126889837</v>
+        <v>126893733</v>
       </c>
       <c r="B51" t="n">
-        <v>91291</v>
+        <v>98364</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5802,21 +5802,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>5447</v>
+        <v>219790</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5826,10 +5826,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>672912</v>
+        <v>672989</v>
       </c>
       <c r="R51" t="n">
-        <v>7058191</v>
+        <v>7058233</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5876,12 +5876,12 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Philipp Weiss, Miriam Schenk, Cajsa Björkén, Fredrik Wilde, Alva Danielsson, Elke Blöhbaum, Vilhelm Kroon, Mattias Dalkvist</t>
+          <t>Alva Danielsson, Fredrik Wilde, Liam Sebestyén, Elke Blöhbaum, Miriam Schenk, Mattias Dalkvist, Emil Lindgren</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr">
@@ -5892,10 +5892,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>126889856</v>
+        <v>126889862</v>
       </c>
       <c r="B52" t="n">
-        <v>80117</v>
+        <v>91348</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5903,21 +5903,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5927,10 +5927,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>672929</v>
+        <v>672981</v>
       </c>
       <c r="R52" t="n">
-        <v>7058201</v>
+        <v>7058264</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5993,32 +5993,32 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>126891325</v>
+        <v>126889837</v>
       </c>
       <c r="B53" t="n">
-        <v>79014</v>
+        <v>91295</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6028,10 +6028,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>672660</v>
+        <v>672912</v>
       </c>
       <c r="R53" t="n">
-        <v>7057985</v>
+        <v>7058191</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6078,12 +6078,12 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Liam Sebestyén, Mattias Dalkvist, Miriam Schenk, Fredrik Wilde, Elke Blöhbaum, Emil Lindgren</t>
+          <t>Liam Sebestyén, Philipp Weiss, Miriam Schenk, Cajsa Björkén, Fredrik Wilde, Alva Danielsson, Elke Blöhbaum, Vilhelm Kroon, Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr">
@@ -6094,10 +6094,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>126889862</v>
+        <v>126879684</v>
       </c>
       <c r="B54" t="n">
-        <v>91344</v>
+        <v>79018</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6105,34 +6105,34 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Kravattensliden, Ång</t>
+          <t>Kravattensliden, Kravattensliden, Ång</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>672981</v>
+        <v>672895</v>
       </c>
       <c r="R54" t="n">
-        <v>7058264</v>
+        <v>7058223</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6179,12 +6179,12 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Fredrik Wilde</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Philipp Weiss, Miriam Schenk, Cajsa Björkén, Fredrik Wilde, Alva Danielsson, Elke Blöhbaum, Vilhelm Kroon, Mattias Dalkvist</t>
+          <t>Fredrik Wilde</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr">
@@ -6195,10 +6195,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>126879684</v>
+        <v>126891325</v>
       </c>
       <c r="B55" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6226,14 +6226,14 @@
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Kravattensliden, Kravattensliden, Ång</t>
+          <t>Kravattensliden, Ång</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>672895</v>
+        <v>672660</v>
       </c>
       <c r="R55" t="n">
-        <v>7058223</v>
+        <v>7057985</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6280,12 +6280,12 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Fredrik Wilde</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Fredrik Wilde</t>
+          <t>Alva Danielsson, Liam Sebestyén, Mattias Dalkvist, Miriam Schenk, Fredrik Wilde, Elke Blöhbaum, Emil Lindgren</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr">
@@ -6296,32 +6296,32 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>126893733</v>
+        <v>126889856</v>
       </c>
       <c r="B56" t="n">
-        <v>98360</v>
+        <v>80121</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>219790</v>
+        <v>6458</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6331,10 +6331,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>672989</v>
+        <v>672929</v>
       </c>
       <c r="R56" t="n">
-        <v>7058233</v>
+        <v>7058201</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6381,12 +6381,12 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Fredrik Wilde, Liam Sebestyén, Elke Blöhbaum, Miriam Schenk, Mattias Dalkvist, Emil Lindgren</t>
+          <t>Liam Sebestyén, Philipp Weiss, Miriam Schenk, Cajsa Björkén, Fredrik Wilde, Alva Danielsson, Elke Blöhbaum, Vilhelm Kroon, Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr">
@@ -6397,10 +6397,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>126879133</v>
+        <v>126889504</v>
       </c>
       <c r="B57" t="n">
-        <v>79046</v>
+        <v>79018</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6408,34 +6408,34 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Kravattensliden, Kravattensliden, Ång</t>
+          <t>Kravattensliden, Ång</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>673041</v>
+        <v>672853</v>
       </c>
       <c r="R57" t="n">
-        <v>7058262</v>
+        <v>7058173</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6482,12 +6482,12 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Fredrik Wilde</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Fredrik Wilde</t>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Fredrik Wilde, Alva Danielsson, Emil Lindgren, Mattias Dalkvist, Elke Blöhbaum, Miriam Schenk, Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr">
@@ -6498,10 +6498,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>126889504</v>
+        <v>126879133</v>
       </c>
       <c r="B58" t="n">
-        <v>79014</v>
+        <v>79050</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6509,34 +6509,34 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Kravattensliden, Ång</t>
+          <t>Kravattensliden, Kravattensliden, Ång</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>672853</v>
+        <v>673041</v>
       </c>
       <c r="R58" t="n">
-        <v>7058173</v>
+        <v>7058262</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6583,12 +6583,12 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Fredrik Wilde</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Fredrik Wilde, Alva Danielsson, Emil Lindgren, Mattias Dalkvist, Elke Blöhbaum, Miriam Schenk, Vilhelm Kroon</t>
+          <t>Fredrik Wilde</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr">
@@ -6602,7 +6602,7 @@
         <v>126892806</v>
       </c>
       <c r="B59" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6710,10 +6710,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>126892812</v>
+        <v>126880199</v>
       </c>
       <c r="B60" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6739,19 +6739,24 @@
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Kravattensliden, Ång</t>
+          <t>Kravattensliden, Kravattensliden, Ång</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>672685</v>
+        <v>672894</v>
       </c>
       <c r="R60" t="n">
-        <v>7058010</v>
+        <v>7058198</v>
       </c>
       <c r="S60" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -6778,19 +6783,9 @@
           <t>2025-07-24</t>
         </is>
       </c>
-      <c r="Z60" t="inlineStr">
-        <is>
-          <t>11:41</t>
-        </is>
-      </c>
       <c r="AA60" t="inlineStr">
         <is>
           <t>2025-07-24</t>
-        </is>
-      </c>
-      <c r="AB60" t="inlineStr">
-        <is>
-          <t>11:41</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6805,12 +6800,12 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Fredrik Wilde</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist, Fredrik Wilde, Liam Sebestyén, Alva Danielsson, Elke Blöhbaum, Vilhelm Kroon, Miriam Schenk, Cajsa Björkén, Philipp Weiss, Emil Lindgren</t>
+          <t>Fredrik Wilde</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr">
@@ -6821,53 +6816,48 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>126880199</v>
+        <v>126890296</v>
       </c>
       <c r="B61" t="n">
-        <v>79014</v>
+        <v>80150</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
-      <c r="K61" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Kravattensliden, Kravattensliden, Ång</t>
+          <t>Kravattensliden, Ång</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>672894</v>
+        <v>673025</v>
       </c>
       <c r="R61" t="n">
-        <v>7058198</v>
+        <v>7058244</v>
       </c>
       <c r="S61" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -6911,12 +6901,12 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Fredrik Wilde</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Fredrik Wilde</t>
+          <t>Vilhelm Kroon, Cajsa Björkén, Fredrik Wilde, Mattias Dalkvist, Philipp Weiss, Miriam Schenk, Liam Sebestyén, Alva Danielsson, Emil Lindgren</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr">
@@ -6927,10 +6917,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>126892809</v>
+        <v>126892812</v>
       </c>
       <c r="B62" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6962,13 +6952,13 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>672831</v>
+        <v>672685</v>
       </c>
       <c r="R62" t="n">
-        <v>7058091</v>
+        <v>7058010</v>
       </c>
       <c r="S62" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -6997,7 +6987,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7007,7 +6997,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7038,32 +7028,32 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>126890296</v>
+        <v>126892809</v>
       </c>
       <c r="B63" t="n">
-        <v>80146</v>
+        <v>79018</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7073,13 +7063,13 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>673025</v>
+        <v>672831</v>
       </c>
       <c r="R63" t="n">
-        <v>7058244</v>
+        <v>7058091</v>
       </c>
       <c r="S63" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7106,9 +7096,19 @@
           <t>2025-07-24</t>
         </is>
       </c>
+      <c r="Z63" t="inlineStr">
+        <is>
+          <t>11:32</t>
+        </is>
+      </c>
       <c r="AA63" t="inlineStr">
         <is>
           <t>2025-07-24</t>
+        </is>
+      </c>
+      <c r="AB63" t="inlineStr">
+        <is>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7123,12 +7123,12 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon, Cajsa Björkén, Fredrik Wilde, Mattias Dalkvist, Philipp Weiss, Miriam Schenk, Liam Sebestyén, Alva Danielsson, Emil Lindgren</t>
+          <t>Mattias Dalkvist, Fredrik Wilde, Liam Sebestyén, Alva Danielsson, Elke Blöhbaum, Vilhelm Kroon, Miriam Schenk, Cajsa Björkén, Philipp Weiss, Emil Lindgren</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr">
@@ -7139,54 +7139,45 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>126879033</v>
+        <v>126891312</v>
       </c>
       <c r="B64" t="n">
-        <v>79046</v>
+        <v>91295</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>185</v>
+        <v>5447</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J64" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Kravattensliden, Kravattensliden, Ång</t>
+          <t>Kravattensliden, Ång</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>673046</v>
+        <v>673027</v>
       </c>
       <c r="R64" t="n">
-        <v>7058286</v>
+        <v>7058282</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7233,12 +7224,12 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Fredrik Wilde</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Fredrik Wilde</t>
+          <t>Alva Danielsson, Liam Sebestyén, Mattias Dalkvist, Miriam Schenk, Fredrik Wilde, Elke Blöhbaum, Emil Lindgren</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr">
@@ -7252,7 +7243,7 @@
         <v>126880532</v>
       </c>
       <c r="B65" t="n">
-        <v>80146</v>
+        <v>80150</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7350,10 +7341,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>126889382</v>
+        <v>126879033</v>
       </c>
       <c r="B66" t="n">
-        <v>57654</v>
+        <v>79050</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7361,39 +7352,43 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>100049</v>
+        <v>185</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr"/>
-      <c r="M66" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Kravattensliden, Ång</t>
+          <t>Kravattensliden, Kravattensliden, Ång</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>672838</v>
+        <v>673046</v>
       </c>
       <c r="R66" t="n">
-        <v>7058134</v>
+        <v>7058286</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7440,12 +7435,12 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Fredrik Wilde</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Fredrik Wilde, Alva Danielsson, Emil Lindgren, Mattias Dalkvist, Elke Blöhbaum, Miriam Schenk, Vilhelm Kroon</t>
+          <t>Fredrik Wilde</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr">
@@ -7456,45 +7451,45 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>126891312</v>
+        <v>126879425</v>
       </c>
       <c r="B67" t="n">
-        <v>91291</v>
+        <v>79018</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Kravattensliden, Ång</t>
+          <t>Kravattensliden, Kravattensliden, Ång</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>673027</v>
+        <v>672947</v>
       </c>
       <c r="R67" t="n">
-        <v>7058282</v>
+        <v>7058198</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7541,12 +7536,12 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Fredrik Wilde</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Liam Sebestyén, Mattias Dalkvist, Miriam Schenk, Fredrik Wilde, Elke Blöhbaum, Emil Lindgren</t>
+          <t>Fredrik Wilde</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr">
@@ -7557,10 +7552,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>126879425</v>
+        <v>126889382</v>
       </c>
       <c r="B68" t="n">
-        <v>79014</v>
+        <v>57658</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7568,34 +7563,39 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Kravattensliden, Kravattensliden, Ång</t>
+          <t>Kravattensliden, Ång</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>672947</v>
+        <v>672838</v>
       </c>
       <c r="R68" t="n">
-        <v>7058198</v>
+        <v>7058134</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7642,12 +7642,12 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Fredrik Wilde</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Fredrik Wilde</t>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Fredrik Wilde, Alva Danielsson, Emil Lindgren, Mattias Dalkvist, Elke Blöhbaum, Miriam Schenk, Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr">
@@ -7658,32 +7658,32 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>126890370</v>
+        <v>126890408</v>
       </c>
       <c r="B69" t="n">
-        <v>80146</v>
+        <v>79018</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7693,10 +7693,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>672554</v>
+        <v>672874</v>
       </c>
       <c r="R69" t="n">
-        <v>7058145</v>
+        <v>7058313</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7759,32 +7759,32 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>126890408</v>
+        <v>126890370</v>
       </c>
       <c r="B70" t="n">
-        <v>79014</v>
+        <v>80150</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7794,10 +7794,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>672874</v>
+        <v>672554</v>
       </c>
       <c r="R70" t="n">
-        <v>7058313</v>
+        <v>7058145</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7863,7 +7863,7 @@
         <v>126890401</v>
       </c>
       <c r="B71" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7964,7 +7964,7 @@
         <v>126890405</v>
       </c>
       <c r="B72" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8065,7 +8065,7 @@
         <v>126890409</v>
       </c>
       <c r="B73" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8163,10 +8163,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>126890407</v>
+        <v>126890387</v>
       </c>
       <c r="B74" t="n">
-        <v>79014</v>
+        <v>80121</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8174,21 +8174,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8198,10 +8198,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>672859</v>
+        <v>672556</v>
       </c>
       <c r="R74" t="n">
-        <v>7058290</v>
+        <v>7058143</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8264,10 +8264,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>126890387</v>
+        <v>126890407</v>
       </c>
       <c r="B75" t="n">
-        <v>80117</v>
+        <v>79018</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8275,21 +8275,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8299,10 +8299,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>672556</v>
+        <v>672859</v>
       </c>
       <c r="R75" t="n">
-        <v>7058143</v>
+        <v>7058290</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8365,10 +8365,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>126890404</v>
+        <v>126890354</v>
       </c>
       <c r="B76" t="n">
-        <v>79014</v>
+        <v>79050</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8376,21 +8376,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8400,10 +8400,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>672805</v>
+        <v>672891</v>
       </c>
       <c r="R76" t="n">
-        <v>7058312</v>
+        <v>7058285</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8466,10 +8466,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>126890354</v>
+        <v>126890404</v>
       </c>
       <c r="B77" t="n">
-        <v>79046</v>
+        <v>79018</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8477,21 +8477,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8501,10 +8501,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>672891</v>
+        <v>672805</v>
       </c>
       <c r="R77" t="n">
-        <v>7058285</v>
+        <v>7058312</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8570,7 +8570,7 @@
         <v>126890353</v>
       </c>
       <c r="B78" t="n">
-        <v>79046</v>
+        <v>79050</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8671,7 +8671,7 @@
         <v>126890349</v>
       </c>
       <c r="B79" t="n">
-        <v>79046</v>
+        <v>79050</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8769,10 +8769,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>126890348</v>
+        <v>126890351</v>
       </c>
       <c r="B80" t="n">
-        <v>79046</v>
+        <v>79050</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8804,10 +8804,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>672587</v>
+        <v>672831</v>
       </c>
       <c r="R80" t="n">
-        <v>7058126</v>
+        <v>7058284</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8870,10 +8870,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>126890351</v>
+        <v>126890348</v>
       </c>
       <c r="B81" t="n">
-        <v>79046</v>
+        <v>79050</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8905,10 +8905,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>672831</v>
+        <v>672587</v>
       </c>
       <c r="R81" t="n">
-        <v>7058284</v>
+        <v>7058126</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8974,7 +8974,7 @@
         <v>126890350</v>
       </c>
       <c r="B82" t="n">
-        <v>79046</v>
+        <v>79050</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9075,7 +9075,7 @@
         <v>126890416</v>
       </c>
       <c r="B83" t="n">
-        <v>80152</v>
+        <v>80156</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9176,7 +9176,7 @@
         <v>126890403</v>
       </c>
       <c r="B84" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9277,7 +9277,7 @@
         <v>126890352</v>
       </c>
       <c r="B85" t="n">
-        <v>79046</v>
+        <v>79050</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>

--- a/artfynd/A 27938-2023 artfynd.xlsx
+++ b/artfynd/A 27938-2023 artfynd.xlsx
@@ -675,45 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>126889833</v>
+        <v>126879850</v>
       </c>
       <c r="B2" t="n">
-        <v>91295</v>
+        <v>88733</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5447</v>
+        <v>510</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Kravattensliden, Ång</t>
+          <t>Kravattensliden, Kravattensliden, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>672799</v>
+        <v>672873</v>
       </c>
       <c r="R2" t="n">
-        <v>7058073</v>
+        <v>7058228</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -760,12 +760,12 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Fredrik Wilde</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Philipp Weiss, Miriam Schenk, Cajsa Björkén, Fredrik Wilde, Alva Danielsson, Elke Blöhbaum, Vilhelm Kroon, Mattias Dalkvist</t>
+          <t>Fredrik Wilde</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -877,45 +877,45 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126879850</v>
+        <v>126889833</v>
       </c>
       <c r="B4" t="n">
-        <v>88733</v>
+        <v>91295</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>510</v>
+        <v>5447</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Kravattensliden, Kravattensliden, Ång</t>
+          <t>Kravattensliden, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>672873</v>
+        <v>672799</v>
       </c>
       <c r="R4" t="n">
-        <v>7058228</v>
+        <v>7058073</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -962,12 +962,12 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Fredrik Wilde</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Fredrik Wilde</t>
+          <t>Liam Sebestyén, Philipp Weiss, Miriam Schenk, Cajsa Björkén, Fredrik Wilde, Alva Danielsson, Elke Blöhbaum, Vilhelm Kroon, Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
@@ -1079,10 +1079,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126889505</v>
+        <v>126892811</v>
       </c>
       <c r="B6" t="n">
-        <v>79018</v>
+        <v>79050</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1090,21 +1090,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1114,13 +1114,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>672864</v>
+        <v>672792</v>
       </c>
       <c r="R6" t="n">
-        <v>7058181</v>
+        <v>7058076</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1147,9 +1147,19 @@
           <t>2025-07-24</t>
         </is>
       </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>11:35</t>
+        </is>
+      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-07-24</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1164,12 +1174,12 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Fredrik Wilde, Alva Danielsson, Emil Lindgren, Mattias Dalkvist, Elke Blöhbaum, Miriam Schenk, Vilhelm Kroon</t>
+          <t>Mattias Dalkvist, Fredrik Wilde, Liam Sebestyén, Alva Danielsson, Elke Blöhbaum, Vilhelm Kroon, Miriam Schenk, Cajsa Björkén, Philipp Weiss, Emil Lindgren</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
@@ -1180,10 +1190,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126892805</v>
+        <v>126889505</v>
       </c>
       <c r="B7" t="n">
-        <v>57661</v>
+        <v>79018</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1191,21 +1201,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1215,13 +1225,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>672877</v>
+        <v>672864</v>
       </c>
       <c r="R7" t="n">
-        <v>7058189</v>
+        <v>7058181</v>
       </c>
       <c r="S7" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1248,24 +1258,9 @@
           <t>2025-07-24</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>11:15</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-07-24</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>11:15</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Gamla ringhack</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1280,12 +1275,12 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist, Fredrik Wilde, Liam Sebestyén, Alva Danielsson, Elke Blöhbaum, Vilhelm Kroon, Miriam Schenk, Cajsa Björkén, Philipp Weiss, Emil Lindgren</t>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Fredrik Wilde, Alva Danielsson, Emil Lindgren, Mattias Dalkvist, Elke Blöhbaum, Miriam Schenk, Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
@@ -1296,10 +1291,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126892811</v>
+        <v>126892805</v>
       </c>
       <c r="B8" t="n">
-        <v>79050</v>
+        <v>57661</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1307,21 +1302,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>185</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1331,10 +1326,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>672792</v>
+        <v>672877</v>
       </c>
       <c r="R8" t="n">
-        <v>7058076</v>
+        <v>7058189</v>
       </c>
       <c r="S8" t="n">
         <v>4</v>
@@ -1366,7 +1361,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1376,7 +1371,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>11:15</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Gamla ringhack</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1407,10 +1407,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126891323</v>
+        <v>126889513</v>
       </c>
       <c r="B9" t="n">
-        <v>91348</v>
+        <v>79018</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1418,21 +1418,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1442,10 +1442,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>672897</v>
+        <v>673038</v>
       </c>
       <c r="R9" t="n">
-        <v>7058210</v>
+        <v>7058279</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1492,12 +1492,12 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Liam Sebestyén, Mattias Dalkvist, Miriam Schenk, Fredrik Wilde, Elke Blöhbaum, Emil Lindgren</t>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Fredrik Wilde, Alva Danielsson, Emil Lindgren, Mattias Dalkvist, Elke Blöhbaum, Miriam Schenk, Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
@@ -1508,7 +1508,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126889513</v>
+        <v>126893729</v>
       </c>
       <c r="B10" t="n">
         <v>79018</v>
@@ -1543,10 +1543,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>673038</v>
+        <v>672603</v>
       </c>
       <c r="R10" t="n">
-        <v>7058279</v>
+        <v>7057959</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1593,12 +1593,12 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Fredrik Wilde, Alva Danielsson, Emil Lindgren, Mattias Dalkvist, Elke Blöhbaum, Miriam Schenk, Vilhelm Kroon</t>
+          <t>Alva Danielsson, Fredrik Wilde, Liam Sebestyén, Elke Blöhbaum, Miriam Schenk, Mattias Dalkvist, Emil Lindgren</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
@@ -1609,7 +1609,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126893729</v>
+        <v>126889493</v>
       </c>
       <c r="B11" t="n">
         <v>79018</v>
@@ -1644,10 +1644,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>672603</v>
+        <v>672651</v>
       </c>
       <c r="R11" t="n">
-        <v>7057959</v>
+        <v>7057972</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1694,12 +1694,12 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Fredrik Wilde, Liam Sebestyén, Elke Blöhbaum, Miriam Schenk, Mattias Dalkvist, Emil Lindgren</t>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Fredrik Wilde, Alva Danielsson, Emil Lindgren, Mattias Dalkvist, Elke Blöhbaum, Miriam Schenk, Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
@@ -1710,10 +1710,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126889493</v>
+        <v>126891323</v>
       </c>
       <c r="B12" t="n">
-        <v>79018</v>
+        <v>91348</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1721,21 +1721,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1745,10 +1745,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>672651</v>
+        <v>672897</v>
       </c>
       <c r="R12" t="n">
-        <v>7057972</v>
+        <v>7058210</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1795,12 +1795,12 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Fredrik Wilde, Alva Danielsson, Emil Lindgren, Mattias Dalkvist, Elke Blöhbaum, Miriam Schenk, Vilhelm Kroon</t>
+          <t>Alva Danielsson, Liam Sebestyén, Mattias Dalkvist, Miriam Schenk, Fredrik Wilde, Elke Blöhbaum, Emil Lindgren</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
@@ -2129,32 +2129,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>126891315</v>
+        <v>126889492</v>
       </c>
       <c r="B16" t="n">
-        <v>98468</v>
+        <v>79018</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>221952</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2164,10 +2164,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>672827</v>
+        <v>672638</v>
       </c>
       <c r="R16" t="n">
-        <v>7058099</v>
+        <v>7057953</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2214,12 +2214,12 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Liam Sebestyén, Mattias Dalkvist, Miriam Schenk, Fredrik Wilde, Elke Blöhbaum, Emil Lindgren</t>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Fredrik Wilde, Alva Danielsson, Emil Lindgren, Mattias Dalkvist, Elke Blöhbaum, Miriam Schenk, Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
@@ -2230,32 +2230,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>126889492</v>
+        <v>126891315</v>
       </c>
       <c r="B17" t="n">
-        <v>79018</v>
+        <v>98468</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>221952</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2265,10 +2265,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>672638</v>
+        <v>672827</v>
       </c>
       <c r="R17" t="n">
-        <v>7057953</v>
+        <v>7058099</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2315,12 +2315,12 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Fredrik Wilde, Alva Danielsson, Emil Lindgren, Mattias Dalkvist, Elke Blöhbaum, Miriam Schenk, Vilhelm Kroon</t>
+          <t>Alva Danielsson, Liam Sebestyén, Mattias Dalkvist, Miriam Schenk, Fredrik Wilde, Elke Blöhbaum, Emil Lindgren</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
@@ -2331,32 +2331,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>126891131</v>
+        <v>126892810</v>
       </c>
       <c r="B18" t="n">
-        <v>79050</v>
+        <v>91295</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>185</v>
+        <v>5447</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2366,13 +2366,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>672898</v>
+        <v>672801</v>
       </c>
       <c r="R18" t="n">
-        <v>7058209</v>
+        <v>7058081</v>
       </c>
       <c r="S18" t="n">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2399,30 +2399,39 @@
           <t>2025-07-24</t>
         </is>
       </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>11:35</t>
+        </is>
+      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-07-24</t>
         </is>
       </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>11:35</t>
+        </is>
+      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Miriam Schenk</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Miriam Schenk, Cajsa Björkén, Fredrik Wilde, Philipp Weiss, Mattias Dalkvist, Vilhelm Kroon, Liam Sebestyén, Emil Lindgren, Alva Danielsson</t>
+          <t>Mattias Dalkvist, Fredrik Wilde, Liam Sebestyén, Alva Danielsson, Elke Blöhbaum, Vilhelm Kroon, Miriam Schenk, Cajsa Björkén, Philipp Weiss, Emil Lindgren</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
@@ -2433,32 +2442,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>126892810</v>
+        <v>126892808</v>
       </c>
       <c r="B19" t="n">
-        <v>91295</v>
+        <v>79018</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2468,13 +2477,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>672801</v>
+        <v>672862</v>
       </c>
       <c r="R19" t="n">
-        <v>7058081</v>
+        <v>7058125</v>
       </c>
       <c r="S19" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2503,7 +2512,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2513,7 +2522,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2544,10 +2553,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>126892808</v>
+        <v>126891131</v>
       </c>
       <c r="B20" t="n">
-        <v>79018</v>
+        <v>79050</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2555,21 +2564,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2579,13 +2588,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>672862</v>
+        <v>672898</v>
       </c>
       <c r="R20" t="n">
-        <v>7058125</v>
+        <v>7058209</v>
       </c>
       <c r="S20" t="n">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2612,39 +2621,30 @@
           <t>2025-07-24</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>11:25</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-07-24</t>
         </is>
       </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>11:25</t>
-        </is>
-      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Miriam Schenk</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist, Fredrik Wilde, Liam Sebestyén, Alva Danielsson, Elke Blöhbaum, Vilhelm Kroon, Miriam Schenk, Cajsa Björkén, Philipp Weiss, Emil Lindgren</t>
+          <t>Miriam Schenk, Cajsa Björkén, Fredrik Wilde, Philipp Weiss, Mattias Dalkvist, Vilhelm Kroon, Liam Sebestyén, Emil Lindgren, Alva Danielsson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
@@ -2655,10 +2655,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>126889311</v>
+        <v>126891314</v>
       </c>
       <c r="B21" t="n">
-        <v>91295</v>
+        <v>80150</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2666,21 +2666,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5447</v>
+        <v>6462</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2690,10 +2690,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>672799</v>
+        <v>672999</v>
       </c>
       <c r="R21" t="n">
-        <v>7058086</v>
+        <v>7058211</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2740,12 +2740,12 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Fredrik Wilde, Alva Danielsson, Emil Lindgren, Mattias Dalkvist, Elke Blöhbaum, Miriam Schenk, Vilhelm Kroon</t>
+          <t>Alva Danielsson, Liam Sebestyén, Mattias Dalkvist, Miriam Schenk, Fredrik Wilde, Elke Blöhbaum, Emil Lindgren</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
@@ -2756,10 +2756,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>126891314</v>
+        <v>126889311</v>
       </c>
       <c r="B22" t="n">
-        <v>80150</v>
+        <v>91295</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2767,21 +2767,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6462</v>
+        <v>5447</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2791,10 +2791,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>672999</v>
+        <v>672799</v>
       </c>
       <c r="R22" t="n">
-        <v>7058211</v>
+        <v>7058086</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2841,12 +2841,12 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Liam Sebestyén, Mattias Dalkvist, Miriam Schenk, Fredrik Wilde, Elke Blöhbaum, Emil Lindgren</t>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Fredrik Wilde, Alva Danielsson, Emil Lindgren, Mattias Dalkvist, Elke Blöhbaum, Miriam Schenk, Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
@@ -2963,10 +2963,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>126889869</v>
+        <v>126889374</v>
       </c>
       <c r="B24" t="n">
-        <v>98364</v>
+        <v>98468</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2974,34 +2974,48 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>219790</v>
+        <v>221952</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Kravattensliden, Ång</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>672855</v>
+        <v>672898</v>
       </c>
       <c r="R24" t="n">
-        <v>7058116</v>
+        <v>7058146</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3048,12 +3062,12 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Philipp Weiss, Miriam Schenk, Cajsa Björkén, Fredrik Wilde, Alva Danielsson, Elke Blöhbaum, Vilhelm Kroon, Mattias Dalkvist</t>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Fredrik Wilde, Alva Danielsson, Emil Lindgren, Mattias Dalkvist, Elke Blöhbaum, Miriam Schenk, Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr">
@@ -3064,10 +3078,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>126889374</v>
+        <v>126889869</v>
       </c>
       <c r="B25" t="n">
-        <v>98468</v>
+        <v>98364</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3075,48 +3089,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>221952</v>
+        <v>219790</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Kravattensliden, Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>672898</v>
+        <v>672855</v>
       </c>
       <c r="R25" t="n">
-        <v>7058146</v>
+        <v>7058116</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3163,12 +3163,12 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Fredrik Wilde, Alva Danielsson, Emil Lindgren, Mattias Dalkvist, Elke Blöhbaum, Miriam Schenk, Vilhelm Kroon</t>
+          <t>Liam Sebestyén, Philipp Weiss, Miriam Schenk, Cajsa Björkén, Fredrik Wilde, Alva Danielsson, Elke Blöhbaum, Vilhelm Kroon, Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr">
@@ -3280,10 +3280,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>126889847</v>
+        <v>126892816</v>
       </c>
       <c r="B27" t="n">
-        <v>57658</v>
+        <v>79018</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3291,45 +3291,37 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Kravattensliden, Ång</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>672981</v>
+        <v>672627</v>
       </c>
       <c r="R27" t="n">
-        <v>7058264</v>
+        <v>7058024</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3356,9 +3348,19 @@
           <t>2025-07-24</t>
         </is>
       </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>11:52</t>
+        </is>
+      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-07-24</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3373,12 +3375,12 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Philipp Weiss, Miriam Schenk, Cajsa Björkén, Fredrik Wilde, Alva Danielsson, Elke Blöhbaum, Vilhelm Kroon, Mattias Dalkvist</t>
+          <t>Mattias Dalkvist, Fredrik Wilde, Liam Sebestyén, Alva Danielsson, Elke Blöhbaum, Vilhelm Kroon, Miriam Schenk, Cajsa Björkén, Philipp Weiss, Emil Lindgren</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr">
@@ -3389,7 +3391,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>126889502</v>
+        <v>126893730</v>
       </c>
       <c r="B28" t="n">
         <v>79018</v>
@@ -3424,10 +3426,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>672801</v>
+        <v>672929</v>
       </c>
       <c r="R28" t="n">
-        <v>7058095</v>
+        <v>7058213</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3474,12 +3476,12 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Fredrik Wilde, Alva Danielsson, Emil Lindgren, Mattias Dalkvist, Elke Blöhbaum, Miriam Schenk, Vilhelm Kroon</t>
+          <t>Alva Danielsson, Fredrik Wilde, Liam Sebestyén, Elke Blöhbaum, Miriam Schenk, Mattias Dalkvist, Emil Lindgren</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr">
@@ -3490,7 +3492,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>126892816</v>
+        <v>126889502</v>
       </c>
       <c r="B29" t="n">
         <v>79018</v>
@@ -3525,13 +3527,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>672627</v>
+        <v>672801</v>
       </c>
       <c r="R29" t="n">
-        <v>7058024</v>
+        <v>7058095</v>
       </c>
       <c r="S29" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3558,19 +3560,9 @@
           <t>2025-07-24</t>
         </is>
       </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>11:52</t>
-        </is>
-      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-07-24</t>
-        </is>
-      </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>11:52</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3585,12 +3577,12 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist, Fredrik Wilde, Liam Sebestyén, Alva Danielsson, Elke Blöhbaum, Vilhelm Kroon, Miriam Schenk, Cajsa Björkén, Philipp Weiss, Emil Lindgren</t>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Fredrik Wilde, Alva Danielsson, Emil Lindgren, Mattias Dalkvist, Elke Blöhbaum, Miriam Schenk, Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr">
@@ -3601,10 +3593,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>126893730</v>
+        <v>126889847</v>
       </c>
       <c r="B30" t="n">
-        <v>79018</v>
+        <v>57658</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3612,34 +3604,42 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Kravattensliden, Ång</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>672929</v>
+        <v>672981</v>
       </c>
       <c r="R30" t="n">
-        <v>7058213</v>
+        <v>7058264</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3686,12 +3686,12 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Fredrik Wilde, Liam Sebestyén, Elke Blöhbaum, Miriam Schenk, Mattias Dalkvist, Emil Lindgren</t>
+          <t>Liam Sebestyén, Philipp Weiss, Miriam Schenk, Cajsa Björkén, Fredrik Wilde, Alva Danielsson, Elke Blöhbaum, Vilhelm Kroon, Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr">
@@ -3702,59 +3702,45 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>126889377</v>
+        <v>126891328</v>
       </c>
       <c r="B31" t="n">
-        <v>98468</v>
+        <v>79018</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>221952</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Kravattensliden, Ång</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>672810</v>
+        <v>672972</v>
       </c>
       <c r="R31" t="n">
-        <v>7058105</v>
+        <v>7058246</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3801,12 +3787,12 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Fredrik Wilde, Alva Danielsson, Emil Lindgren, Mattias Dalkvist, Elke Blöhbaum, Miriam Schenk, Vilhelm Kroon</t>
+          <t>Alva Danielsson, Liam Sebestyén, Mattias Dalkvist, Miriam Schenk, Fredrik Wilde, Elke Blöhbaum, Emil Lindgren</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr">
@@ -3923,45 +3909,59 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>126891328</v>
+        <v>126889377</v>
       </c>
       <c r="B33" t="n">
-        <v>79018</v>
+        <v>98468</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>221952</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Kravattensliden, Ång</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>672972</v>
+        <v>672810</v>
       </c>
       <c r="R33" t="n">
-        <v>7058246</v>
+        <v>7058105</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4008,12 +4008,12 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Liam Sebestyén, Mattias Dalkvist, Miriam Schenk, Fredrik Wilde, Elke Blöhbaum, Emil Lindgren</t>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Fredrik Wilde, Alva Danielsson, Emil Lindgren, Mattias Dalkvist, Elke Blöhbaum, Miriam Schenk, Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr">
@@ -4446,10 +4446,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>126890308</v>
+        <v>126891320</v>
       </c>
       <c r="B38" t="n">
-        <v>79018</v>
+        <v>80121</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4457,21 +4457,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4481,13 +4481,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>672880</v>
+        <v>672929</v>
       </c>
       <c r="R38" t="n">
-        <v>7058209</v>
+        <v>7058203</v>
       </c>
       <c r="S38" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4531,12 +4531,12 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon, Cajsa Björkén, Fredrik Wilde, Mattias Dalkvist, Philipp Weiss, Miriam Schenk, Liam Sebestyén, Alva Danielsson, Emil Lindgren</t>
+          <t>Alva Danielsson, Liam Sebestyén, Mattias Dalkvist, Miriam Schenk, Fredrik Wilde, Elke Blöhbaum, Emil Lindgren</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr">
@@ -4658,10 +4658,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>126891320</v>
+        <v>126890308</v>
       </c>
       <c r="B40" t="n">
-        <v>80121</v>
+        <v>79018</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4669,21 +4669,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4693,13 +4693,13 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>672929</v>
+        <v>672880</v>
       </c>
       <c r="R40" t="n">
-        <v>7058203</v>
+        <v>7058209</v>
       </c>
       <c r="S40" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4743,12 +4743,12 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Liam Sebestyén, Mattias Dalkvist, Miriam Schenk, Fredrik Wilde, Elke Blöhbaum, Emil Lindgren</t>
+          <t>Vilhelm Kroon, Cajsa Björkén, Fredrik Wilde, Mattias Dalkvist, Philipp Weiss, Miriam Schenk, Liam Sebestyén, Alva Danielsson, Emil Lindgren</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr">
@@ -5074,10 +5074,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>126889506</v>
+        <v>126891321</v>
       </c>
       <c r="B44" t="n">
-        <v>79018</v>
+        <v>80121</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5085,21 +5085,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5109,10 +5109,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>672889</v>
+        <v>673004</v>
       </c>
       <c r="R44" t="n">
-        <v>7058145</v>
+        <v>7058209</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5159,12 +5159,12 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Fredrik Wilde, Alva Danielsson, Emil Lindgren, Mattias Dalkvist, Elke Blöhbaum, Miriam Schenk, Vilhelm Kroon</t>
+          <t>Alva Danielsson, Liam Sebestyén, Mattias Dalkvist, Miriam Schenk, Fredrik Wilde, Elke Blöhbaum, Emil Lindgren</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr">
@@ -5175,10 +5175,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>126891321</v>
+        <v>126892804</v>
       </c>
       <c r="B45" t="n">
-        <v>80121</v>
+        <v>79018</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5186,21 +5186,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5210,13 +5210,13 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>673004</v>
+        <v>673003</v>
       </c>
       <c r="R45" t="n">
-        <v>7058209</v>
+        <v>7058280</v>
       </c>
       <c r="S45" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5243,9 +5243,19 @@
           <t>2025-07-24</t>
         </is>
       </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>10:49</t>
+        </is>
+      </c>
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-07-24</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5260,12 +5270,12 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Liam Sebestyén, Mattias Dalkvist, Miriam Schenk, Fredrik Wilde, Elke Blöhbaum, Emil Lindgren</t>
+          <t>Mattias Dalkvist, Fredrik Wilde, Liam Sebestyén, Alva Danielsson, Elke Blöhbaum, Vilhelm Kroon, Miriam Schenk, Cajsa Björkén, Philipp Weiss, Emil Lindgren</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr">
@@ -5276,7 +5286,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>126892804</v>
+        <v>126889506</v>
       </c>
       <c r="B46" t="n">
         <v>79018</v>
@@ -5311,13 +5321,13 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>673003</v>
+        <v>672889</v>
       </c>
       <c r="R46" t="n">
-        <v>7058280</v>
+        <v>7058145</v>
       </c>
       <c r="S46" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5344,19 +5354,9 @@
           <t>2025-07-24</t>
         </is>
       </c>
-      <c r="Z46" t="inlineStr">
-        <is>
-          <t>10:49</t>
-        </is>
-      </c>
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-07-24</t>
-        </is>
-      </c>
-      <c r="AB46" t="inlineStr">
-        <is>
-          <t>10:49</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5371,12 +5371,12 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist, Fredrik Wilde, Liam Sebestyén, Alva Danielsson, Elke Blöhbaum, Vilhelm Kroon, Miriam Schenk, Cajsa Björkén, Philipp Weiss, Emil Lindgren</t>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Fredrik Wilde, Alva Danielsson, Emil Lindgren, Mattias Dalkvist, Elke Blöhbaum, Miriam Schenk, Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr">
@@ -5791,10 +5791,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>126893733</v>
+        <v>126889837</v>
       </c>
       <c r="B51" t="n">
-        <v>98364</v>
+        <v>91295</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5802,21 +5802,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>219790</v>
+        <v>5447</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5826,10 +5826,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>672989</v>
+        <v>672912</v>
       </c>
       <c r="R51" t="n">
-        <v>7058233</v>
+        <v>7058191</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5876,12 +5876,12 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Fredrik Wilde, Liam Sebestyén, Elke Blöhbaum, Miriam Schenk, Mattias Dalkvist, Emil Lindgren</t>
+          <t>Liam Sebestyén, Philipp Weiss, Miriam Schenk, Cajsa Björkén, Fredrik Wilde, Alva Danielsson, Elke Blöhbaum, Vilhelm Kroon, Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr">
@@ -5993,32 +5993,32 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>126889837</v>
+        <v>126889856</v>
       </c>
       <c r="B53" t="n">
-        <v>91295</v>
+        <v>80121</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>5447</v>
+        <v>6458</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6028,10 +6028,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>672912</v>
+        <v>672929</v>
       </c>
       <c r="R53" t="n">
-        <v>7058191</v>
+        <v>7058201</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6296,32 +6296,32 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>126889856</v>
+        <v>126893733</v>
       </c>
       <c r="B56" t="n">
-        <v>80121</v>
+        <v>98364</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6458</v>
+        <v>219790</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6331,10 +6331,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>672929</v>
+        <v>672989</v>
       </c>
       <c r="R56" t="n">
-        <v>7058201</v>
+        <v>7058233</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6381,12 +6381,12 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Philipp Weiss, Miriam Schenk, Cajsa Björkén, Fredrik Wilde, Alva Danielsson, Elke Blöhbaum, Vilhelm Kroon, Mattias Dalkvist</t>
+          <t>Alva Danielsson, Fredrik Wilde, Liam Sebestyén, Elke Blöhbaum, Miriam Schenk, Mattias Dalkvist, Emil Lindgren</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr">
@@ -6397,7 +6397,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>126889504</v>
+        <v>126892806</v>
       </c>
       <c r="B57" t="n">
         <v>79018</v>
@@ -6432,10 +6432,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>672853</v>
+        <v>672883</v>
       </c>
       <c r="R57" t="n">
-        <v>7058173</v>
+        <v>7058166</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6465,9 +6465,19 @@
           <t>2025-07-24</t>
         </is>
       </c>
+      <c r="Z57" t="inlineStr">
+        <is>
+          <t>11:18</t>
+        </is>
+      </c>
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-07-24</t>
+        </is>
+      </c>
+      <c r="AB57" t="inlineStr">
+        <is>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6482,12 +6492,12 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Fredrik Wilde, Alva Danielsson, Emil Lindgren, Mattias Dalkvist, Elke Blöhbaum, Miriam Schenk, Vilhelm Kroon</t>
+          <t>Mattias Dalkvist, Fredrik Wilde, Liam Sebestyén, Alva Danielsson, Elke Blöhbaum, Vilhelm Kroon, Miriam Schenk, Cajsa Björkén, Philipp Weiss, Emil Lindgren</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr">
@@ -6498,10 +6508,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>126879133</v>
+        <v>126889504</v>
       </c>
       <c r="B58" t="n">
-        <v>79050</v>
+        <v>79018</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6509,34 +6519,34 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Kravattensliden, Kravattensliden, Ång</t>
+          <t>Kravattensliden, Ång</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>673041</v>
+        <v>672853</v>
       </c>
       <c r="R58" t="n">
-        <v>7058262</v>
+        <v>7058173</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6583,12 +6593,12 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Fredrik Wilde</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Fredrik Wilde</t>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Fredrik Wilde, Alva Danielsson, Emil Lindgren, Mattias Dalkvist, Elke Blöhbaum, Miriam Schenk, Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr">
@@ -6599,10 +6609,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>126892806</v>
+        <v>126879133</v>
       </c>
       <c r="B59" t="n">
-        <v>79018</v>
+        <v>79050</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6610,34 +6620,34 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Kravattensliden, Ång</t>
+          <t>Kravattensliden, Kravattensliden, Ång</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>672883</v>
+        <v>673041</v>
       </c>
       <c r="R59" t="n">
-        <v>7058166</v>
+        <v>7058262</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6667,19 +6677,9 @@
           <t>2025-07-24</t>
         </is>
       </c>
-      <c r="Z59" t="inlineStr">
-        <is>
-          <t>11:18</t>
-        </is>
-      </c>
       <c r="AA59" t="inlineStr">
         <is>
           <t>2025-07-24</t>
-        </is>
-      </c>
-      <c r="AB59" t="inlineStr">
-        <is>
-          <t>11:18</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6694,12 +6694,12 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Fredrik Wilde</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist, Fredrik Wilde, Liam Sebestyén, Alva Danielsson, Elke Blöhbaum, Vilhelm Kroon, Miriam Schenk, Cajsa Björkén, Philipp Weiss, Emil Lindgren</t>
+          <t>Fredrik Wilde</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr">
@@ -6710,53 +6710,48 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>126880199</v>
+        <v>126890296</v>
       </c>
       <c r="B60" t="n">
-        <v>79018</v>
+        <v>80150</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
-      <c r="K60" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Kravattensliden, Kravattensliden, Ång</t>
+          <t>Kravattensliden, Ång</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>672894</v>
+        <v>673025</v>
       </c>
       <c r="R60" t="n">
-        <v>7058198</v>
+        <v>7058244</v>
       </c>
       <c r="S60" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -6800,12 +6795,12 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Fredrik Wilde</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Fredrik Wilde</t>
+          <t>Vilhelm Kroon, Cajsa Björkén, Fredrik Wilde, Mattias Dalkvist, Philipp Weiss, Miriam Schenk, Liam Sebestyén, Alva Danielsson, Emil Lindgren</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr">
@@ -6816,32 +6811,32 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>126890296</v>
+        <v>126892812</v>
       </c>
       <c r="B61" t="n">
-        <v>80150</v>
+        <v>79018</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6851,13 +6846,13 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>673025</v>
+        <v>672685</v>
       </c>
       <c r="R61" t="n">
-        <v>7058244</v>
+        <v>7058010</v>
       </c>
       <c r="S61" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -6884,9 +6879,19 @@
           <t>2025-07-24</t>
         </is>
       </c>
+      <c r="Z61" t="inlineStr">
+        <is>
+          <t>11:41</t>
+        </is>
+      </c>
       <c r="AA61" t="inlineStr">
         <is>
           <t>2025-07-24</t>
+        </is>
+      </c>
+      <c r="AB61" t="inlineStr">
+        <is>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -6901,12 +6906,12 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon, Cajsa Björkén, Fredrik Wilde, Mattias Dalkvist, Philipp Weiss, Miriam Schenk, Liam Sebestyén, Alva Danielsson, Emil Lindgren</t>
+          <t>Mattias Dalkvist, Fredrik Wilde, Liam Sebestyén, Alva Danielsson, Elke Blöhbaum, Vilhelm Kroon, Miriam Schenk, Cajsa Björkén, Philipp Weiss, Emil Lindgren</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr">
@@ -6917,7 +6922,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>126892812</v>
+        <v>126880199</v>
       </c>
       <c r="B62" t="n">
         <v>79018</v>
@@ -6946,19 +6951,24 @@
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Kravattensliden, Ång</t>
+          <t>Kravattensliden, Kravattensliden, Ång</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>672685</v>
+        <v>672894</v>
       </c>
       <c r="R62" t="n">
-        <v>7058010</v>
+        <v>7058198</v>
       </c>
       <c r="S62" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -6985,19 +6995,9 @@
           <t>2025-07-24</t>
         </is>
       </c>
-      <c r="Z62" t="inlineStr">
-        <is>
-          <t>11:41</t>
-        </is>
-      </c>
       <c r="AA62" t="inlineStr">
         <is>
           <t>2025-07-24</t>
-        </is>
-      </c>
-      <c r="AB62" t="inlineStr">
-        <is>
-          <t>11:41</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7012,12 +7012,12 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Fredrik Wilde</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist, Fredrik Wilde, Liam Sebestyén, Alva Danielsson, Elke Blöhbaum, Vilhelm Kroon, Miriam Schenk, Cajsa Björkén, Philipp Weiss, Emil Lindgren</t>
+          <t>Fredrik Wilde</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr">
@@ -7139,10 +7139,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>126891312</v>
+        <v>126880532</v>
       </c>
       <c r="B64" t="n">
-        <v>91295</v>
+        <v>80150</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7150,34 +7150,34 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>5447</v>
+        <v>6462</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Kravattensliden, Ång</t>
+          <t>Kravattensliden, Kravattensliden, Ång</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>673027</v>
+        <v>672863</v>
       </c>
       <c r="R64" t="n">
-        <v>7058282</v>
+        <v>7058124</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7224,12 +7224,12 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Fredrik Wilde</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Liam Sebestyén, Mattias Dalkvist, Miriam Schenk, Fredrik Wilde, Elke Blöhbaum, Emil Lindgren</t>
+          <t>Fredrik Wilde</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr">
@@ -7240,32 +7240,32 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>126880532</v>
+        <v>126879425</v>
       </c>
       <c r="B65" t="n">
-        <v>80150</v>
+        <v>79018</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7275,10 +7275,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>672863</v>
+        <v>672947</v>
       </c>
       <c r="R65" t="n">
-        <v>7058124</v>
+        <v>7058198</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7341,10 +7341,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>126879033</v>
+        <v>126889382</v>
       </c>
       <c r="B66" t="n">
-        <v>79050</v>
+        <v>57658</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7352,43 +7352,39 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>185</v>
+        <v>100049</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J66" t="inlineStr">
-        <is>
-          <t>bålar</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Kravattensliden, Kravattensliden, Ång</t>
+          <t>Kravattensliden, Ång</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>673046</v>
+        <v>672838</v>
       </c>
       <c r="R66" t="n">
-        <v>7058286</v>
+        <v>7058134</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7435,12 +7431,12 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Fredrik Wilde</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Fredrik Wilde</t>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Fredrik Wilde, Alva Danielsson, Emil Lindgren, Mattias Dalkvist, Elke Blöhbaum, Miriam Schenk, Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr">
@@ -7451,10 +7447,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>126879425</v>
+        <v>126879033</v>
       </c>
       <c r="B67" t="n">
-        <v>79018</v>
+        <v>79050</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7462,34 +7458,43 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr"/>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P67" t="inlineStr">
         <is>
           <t>Kravattensliden, Kravattensliden, Ång</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>672947</v>
+        <v>673046</v>
       </c>
       <c r="R67" t="n">
-        <v>7058198</v>
+        <v>7058286</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7552,50 +7557,45 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>126889382</v>
+        <v>126891312</v>
       </c>
       <c r="B68" t="n">
-        <v>57658</v>
+        <v>91295</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
-      <c r="M68" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P68" t="inlineStr">
         <is>
           <t>Kravattensliden, Ång</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>672838</v>
+        <v>673027</v>
       </c>
       <c r="R68" t="n">
-        <v>7058134</v>
+        <v>7058282</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7642,12 +7642,12 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Fredrik Wilde, Alva Danielsson, Emil Lindgren, Mattias Dalkvist, Elke Blöhbaum, Miriam Schenk, Vilhelm Kroon</t>
+          <t>Alva Danielsson, Liam Sebestyén, Mattias Dalkvist, Miriam Schenk, Fredrik Wilde, Elke Blöhbaum, Emil Lindgren</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr">
@@ -7658,32 +7658,32 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>126890408</v>
+        <v>126890370</v>
       </c>
       <c r="B69" t="n">
-        <v>79018</v>
+        <v>80150</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7693,10 +7693,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>672874</v>
+        <v>672554</v>
       </c>
       <c r="R69" t="n">
-        <v>7058313</v>
+        <v>7058145</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7759,32 +7759,32 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>126890370</v>
+        <v>126890401</v>
       </c>
       <c r="B70" t="n">
-        <v>80150</v>
+        <v>79018</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7794,10 +7794,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>672554</v>
+        <v>672705</v>
       </c>
       <c r="R70" t="n">
-        <v>7058145</v>
+        <v>7058080</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7860,7 +7860,7 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>126890401</v>
+        <v>126890408</v>
       </c>
       <c r="B71" t="n">
         <v>79018</v>
@@ -7895,10 +7895,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>672705</v>
+        <v>672874</v>
       </c>
       <c r="R71" t="n">
-        <v>7058080</v>
+        <v>7058313</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8769,7 +8769,7 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>126890351</v>
+        <v>126890348</v>
       </c>
       <c r="B80" t="n">
         <v>79050</v>
@@ -8804,10 +8804,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>672831</v>
+        <v>672587</v>
       </c>
       <c r="R80" t="n">
-        <v>7058284</v>
+        <v>7058126</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8870,7 +8870,7 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>126890348</v>
+        <v>126890351</v>
       </c>
       <c r="B81" t="n">
         <v>79050</v>
@@ -8905,10 +8905,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>672587</v>
+        <v>672831</v>
       </c>
       <c r="R81" t="n">
-        <v>7058126</v>
+        <v>7058284</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>

--- a/artfynd/A 27938-2023 artfynd.xlsx
+++ b/artfynd/A 27938-2023 artfynd.xlsx
@@ -1407,10 +1407,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126889513</v>
+        <v>126891323</v>
       </c>
       <c r="B9" t="n">
-        <v>79018</v>
+        <v>91348</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1418,21 +1418,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1442,10 +1442,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>673038</v>
+        <v>672897</v>
       </c>
       <c r="R9" t="n">
-        <v>7058279</v>
+        <v>7058210</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1492,12 +1492,12 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Fredrik Wilde, Alva Danielsson, Emil Lindgren, Mattias Dalkvist, Elke Blöhbaum, Miriam Schenk, Vilhelm Kroon</t>
+          <t>Alva Danielsson, Liam Sebestyén, Mattias Dalkvist, Miriam Schenk, Fredrik Wilde, Elke Blöhbaum, Emil Lindgren</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
@@ -1508,7 +1508,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126893729</v>
+        <v>126889513</v>
       </c>
       <c r="B10" t="n">
         <v>79018</v>
@@ -1543,10 +1543,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>672603</v>
+        <v>673038</v>
       </c>
       <c r="R10" t="n">
-        <v>7057959</v>
+        <v>7058279</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1593,12 +1593,12 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Fredrik Wilde, Liam Sebestyén, Elke Blöhbaum, Miriam Schenk, Mattias Dalkvist, Emil Lindgren</t>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Fredrik Wilde, Alva Danielsson, Emil Lindgren, Mattias Dalkvist, Elke Blöhbaum, Miriam Schenk, Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
@@ -1609,7 +1609,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126889493</v>
+        <v>126893729</v>
       </c>
       <c r="B11" t="n">
         <v>79018</v>
@@ -1644,10 +1644,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>672651</v>
+        <v>672603</v>
       </c>
       <c r="R11" t="n">
-        <v>7057972</v>
+        <v>7057959</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1694,12 +1694,12 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Fredrik Wilde, Alva Danielsson, Emil Lindgren, Mattias Dalkvist, Elke Blöhbaum, Miriam Schenk, Vilhelm Kroon</t>
+          <t>Alva Danielsson, Fredrik Wilde, Liam Sebestyén, Elke Blöhbaum, Miriam Schenk, Mattias Dalkvist, Emil Lindgren</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
@@ -1710,10 +1710,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126891323</v>
+        <v>126889493</v>
       </c>
       <c r="B12" t="n">
-        <v>91348</v>
+        <v>79018</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1721,21 +1721,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1745,10 +1745,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>672897</v>
+        <v>672651</v>
       </c>
       <c r="R12" t="n">
-        <v>7058210</v>
+        <v>7057972</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1795,12 +1795,12 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Liam Sebestyén, Mattias Dalkvist, Miriam Schenk, Fredrik Wilde, Elke Blöhbaum, Emil Lindgren</t>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Fredrik Wilde, Alva Danielsson, Emil Lindgren, Mattias Dalkvist, Elke Blöhbaum, Miriam Schenk, Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
@@ -2331,32 +2331,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>126892810</v>
+        <v>126891131</v>
       </c>
       <c r="B18" t="n">
-        <v>91295</v>
+        <v>79050</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5447</v>
+        <v>185</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2366,13 +2366,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>672801</v>
+        <v>672898</v>
       </c>
       <c r="R18" t="n">
-        <v>7058081</v>
+        <v>7058209</v>
       </c>
       <c r="S18" t="n">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2399,39 +2399,30 @@
           <t>2025-07-24</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>11:35</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-07-24</t>
         </is>
       </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>11:35</t>
-        </is>
-      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Miriam Schenk</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist, Fredrik Wilde, Liam Sebestyén, Alva Danielsson, Elke Blöhbaum, Vilhelm Kroon, Miriam Schenk, Cajsa Björkén, Philipp Weiss, Emil Lindgren</t>
+          <t>Miriam Schenk, Cajsa Björkén, Fredrik Wilde, Philipp Weiss, Mattias Dalkvist, Vilhelm Kroon, Liam Sebestyén, Emil Lindgren, Alva Danielsson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
@@ -2442,32 +2433,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>126892808</v>
+        <v>126892810</v>
       </c>
       <c r="B19" t="n">
-        <v>79018</v>
+        <v>91295</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2477,13 +2468,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>672862</v>
+        <v>672801</v>
       </c>
       <c r="R19" t="n">
-        <v>7058125</v>
+        <v>7058081</v>
       </c>
       <c r="S19" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2512,7 +2503,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2522,7 +2513,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2553,10 +2544,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>126891131</v>
+        <v>126892808</v>
       </c>
       <c r="B20" t="n">
-        <v>79050</v>
+        <v>79018</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2564,21 +2555,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2588,13 +2579,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>672898</v>
+        <v>672862</v>
       </c>
       <c r="R20" t="n">
-        <v>7058209</v>
+        <v>7058125</v>
       </c>
       <c r="S20" t="n">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2621,30 +2612,39 @@
           <t>2025-07-24</t>
         </is>
       </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>11:25</t>
+        </is>
+      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-07-24</t>
         </is>
       </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>11:25</t>
+        </is>
+      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Miriam Schenk</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Miriam Schenk, Cajsa Björkén, Fredrik Wilde, Philipp Weiss, Mattias Dalkvist, Vilhelm Kroon, Liam Sebestyén, Emil Lindgren, Alva Danielsson</t>
+          <t>Mattias Dalkvist, Fredrik Wilde, Liam Sebestyén, Alva Danielsson, Elke Blöhbaum, Vilhelm Kroon, Miriam Schenk, Cajsa Björkén, Philipp Weiss, Emil Lindgren</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
@@ -2655,10 +2655,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>126891314</v>
+        <v>126889311</v>
       </c>
       <c r="B21" t="n">
-        <v>80150</v>
+        <v>91295</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2666,21 +2666,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6462</v>
+        <v>5447</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2690,10 +2690,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>672999</v>
+        <v>672799</v>
       </c>
       <c r="R21" t="n">
-        <v>7058211</v>
+        <v>7058086</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2740,12 +2740,12 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Liam Sebestyén, Mattias Dalkvist, Miriam Schenk, Fredrik Wilde, Elke Blöhbaum, Emil Lindgren</t>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Fredrik Wilde, Alva Danielsson, Emil Lindgren, Mattias Dalkvist, Elke Blöhbaum, Miriam Schenk, Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
@@ -2756,10 +2756,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>126889311</v>
+        <v>126891314</v>
       </c>
       <c r="B22" t="n">
-        <v>91295</v>
+        <v>80150</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2767,21 +2767,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5447</v>
+        <v>6462</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2791,10 +2791,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>672799</v>
+        <v>672999</v>
       </c>
       <c r="R22" t="n">
-        <v>7058086</v>
+        <v>7058211</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2841,12 +2841,12 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Fredrik Wilde, Alva Danielsson, Emil Lindgren, Mattias Dalkvist, Elke Blöhbaum, Miriam Schenk, Vilhelm Kroon</t>
+          <t>Alva Danielsson, Liam Sebestyén, Mattias Dalkvist, Miriam Schenk, Fredrik Wilde, Elke Blöhbaum, Emil Lindgren</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
@@ -2857,10 +2857,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>126889370</v>
+        <v>126889374</v>
       </c>
       <c r="B23" t="n">
-        <v>4773</v>
+        <v>98468</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2868,27 +2868,36 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100299</v>
+        <v>221952</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
@@ -2897,10 +2906,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>672839</v>
+        <v>672898</v>
       </c>
       <c r="R23" t="n">
-        <v>7058141</v>
+        <v>7058146</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2963,10 +2972,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>126889374</v>
+        <v>126889370</v>
       </c>
       <c r="B24" t="n">
-        <v>98468</v>
+        <v>4773</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2974,36 +2983,27 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>221952</v>
+        <v>100299</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>överblommad</t>
+          <t>(Kraatz, 1881)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
@@ -3012,10 +3012,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>672898</v>
+        <v>672839</v>
       </c>
       <c r="R24" t="n">
-        <v>7058146</v>
+        <v>7058141</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -6397,10 +6397,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>126892806</v>
+        <v>126879133</v>
       </c>
       <c r="B57" t="n">
-        <v>79018</v>
+        <v>79050</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6408,34 +6408,34 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Kravattensliden, Ång</t>
+          <t>Kravattensliden, Kravattensliden, Ång</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>672883</v>
+        <v>673041</v>
       </c>
       <c r="R57" t="n">
-        <v>7058166</v>
+        <v>7058262</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6465,19 +6465,9 @@
           <t>2025-07-24</t>
         </is>
       </c>
-      <c r="Z57" t="inlineStr">
-        <is>
-          <t>11:18</t>
-        </is>
-      </c>
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-07-24</t>
-        </is>
-      </c>
-      <c r="AB57" t="inlineStr">
-        <is>
-          <t>11:18</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6492,12 +6482,12 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Fredrik Wilde</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist, Fredrik Wilde, Liam Sebestyén, Alva Danielsson, Elke Blöhbaum, Vilhelm Kroon, Miriam Schenk, Cajsa Björkén, Philipp Weiss, Emil Lindgren</t>
+          <t>Fredrik Wilde</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr">
@@ -6508,7 +6498,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>126889504</v>
+        <v>126892806</v>
       </c>
       <c r="B58" t="n">
         <v>79018</v>
@@ -6543,10 +6533,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>672853</v>
+        <v>672883</v>
       </c>
       <c r="R58" t="n">
-        <v>7058173</v>
+        <v>7058166</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6576,9 +6566,19 @@
           <t>2025-07-24</t>
         </is>
       </c>
+      <c r="Z58" t="inlineStr">
+        <is>
+          <t>11:18</t>
+        </is>
+      </c>
       <c r="AA58" t="inlineStr">
         <is>
           <t>2025-07-24</t>
+        </is>
+      </c>
+      <c r="AB58" t="inlineStr">
+        <is>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6593,12 +6593,12 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Fredrik Wilde, Alva Danielsson, Emil Lindgren, Mattias Dalkvist, Elke Blöhbaum, Miriam Schenk, Vilhelm Kroon</t>
+          <t>Mattias Dalkvist, Fredrik Wilde, Liam Sebestyén, Alva Danielsson, Elke Blöhbaum, Vilhelm Kroon, Miriam Schenk, Cajsa Björkén, Philipp Weiss, Emil Lindgren</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr">
@@ -6609,10 +6609,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>126879133</v>
+        <v>126889504</v>
       </c>
       <c r="B59" t="n">
-        <v>79050</v>
+        <v>79018</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6620,34 +6620,34 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Kravattensliden, Kravattensliden, Ång</t>
+          <t>Kravattensliden, Ång</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>673041</v>
+        <v>672853</v>
       </c>
       <c r="R59" t="n">
-        <v>7058262</v>
+        <v>7058173</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6694,12 +6694,12 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Fredrik Wilde</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Fredrik Wilde</t>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Fredrik Wilde, Alva Danielsson, Emil Lindgren, Mattias Dalkvist, Elke Blöhbaum, Miriam Schenk, Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr">
@@ -7139,10 +7139,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>126880532</v>
+        <v>126891312</v>
       </c>
       <c r="B64" t="n">
-        <v>80150</v>
+        <v>91295</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7150,34 +7150,34 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6462</v>
+        <v>5447</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Kravattensliden, Kravattensliden, Ång</t>
+          <t>Kravattensliden, Ång</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>672863</v>
+        <v>673027</v>
       </c>
       <c r="R64" t="n">
-        <v>7058124</v>
+        <v>7058282</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7224,12 +7224,12 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Fredrik Wilde</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Fredrik Wilde</t>
+          <t>Alva Danielsson, Liam Sebestyén, Mattias Dalkvist, Miriam Schenk, Fredrik Wilde, Elke Blöhbaum, Emil Lindgren</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr">
@@ -7240,32 +7240,32 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>126879425</v>
+        <v>126880532</v>
       </c>
       <c r="B65" t="n">
-        <v>79018</v>
+        <v>80150</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7275,10 +7275,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>672947</v>
+        <v>672863</v>
       </c>
       <c r="R65" t="n">
-        <v>7058198</v>
+        <v>7058124</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7341,10 +7341,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>126889382</v>
+        <v>126879425</v>
       </c>
       <c r="B66" t="n">
-        <v>57658</v>
+        <v>79018</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7352,39 +7352,34 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
-      <c r="M66" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Kravattensliden, Ång</t>
+          <t>Kravattensliden, Kravattensliden, Ång</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>672838</v>
+        <v>672947</v>
       </c>
       <c r="R66" t="n">
-        <v>7058134</v>
+        <v>7058198</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7431,12 +7426,12 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Fredrik Wilde</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Fredrik Wilde, Alva Danielsson, Emil Lindgren, Mattias Dalkvist, Elke Blöhbaum, Miriam Schenk, Vilhelm Kroon</t>
+          <t>Fredrik Wilde</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr">
@@ -7447,10 +7442,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>126879033</v>
+        <v>126889382</v>
       </c>
       <c r="B67" t="n">
-        <v>79050</v>
+        <v>57658</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7458,43 +7453,39 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>185</v>
+        <v>100049</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J67" t="inlineStr">
-        <is>
-          <t>bålar</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr"/>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Kravattensliden, Kravattensliden, Ång</t>
+          <t>Kravattensliden, Ång</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>673046</v>
+        <v>672838</v>
       </c>
       <c r="R67" t="n">
-        <v>7058286</v>
+        <v>7058134</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7541,12 +7532,12 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Fredrik Wilde</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Fredrik Wilde</t>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Fredrik Wilde, Alva Danielsson, Emil Lindgren, Mattias Dalkvist, Elke Blöhbaum, Miriam Schenk, Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr">
@@ -7557,45 +7548,54 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>126891312</v>
+        <v>126879033</v>
       </c>
       <c r="B68" t="n">
-        <v>91295</v>
+        <v>79050</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>5447</v>
+        <v>185</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr"/>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Kravattensliden, Ång</t>
+          <t>Kravattensliden, Kravattensliden, Ång</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>673027</v>
+        <v>673046</v>
       </c>
       <c r="R68" t="n">
-        <v>7058282</v>
+        <v>7058286</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7642,12 +7642,12 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Fredrik Wilde</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Liam Sebestyén, Mattias Dalkvist, Miriam Schenk, Fredrik Wilde, Elke Blöhbaum, Emil Lindgren</t>
+          <t>Fredrik Wilde</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr">
@@ -8163,10 +8163,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>126890387</v>
+        <v>126890407</v>
       </c>
       <c r="B74" t="n">
-        <v>80121</v>
+        <v>79018</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8174,21 +8174,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8198,10 +8198,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>672556</v>
+        <v>672859</v>
       </c>
       <c r="R74" t="n">
-        <v>7058143</v>
+        <v>7058290</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8264,10 +8264,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>126890407</v>
+        <v>126890387</v>
       </c>
       <c r="B75" t="n">
-        <v>79018</v>
+        <v>80121</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8275,21 +8275,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8299,10 +8299,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>672859</v>
+        <v>672556</v>
       </c>
       <c r="R75" t="n">
-        <v>7058290</v>
+        <v>7058143</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>

--- a/artfynd/A 27938-2023 artfynd.xlsx
+++ b/artfynd/A 27938-2023 artfynd.xlsx
@@ -2331,32 +2331,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>126891131</v>
+        <v>126892810</v>
       </c>
       <c r="B18" t="n">
-        <v>79050</v>
+        <v>91295</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>185</v>
+        <v>5447</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2366,13 +2366,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>672898</v>
+        <v>672801</v>
       </c>
       <c r="R18" t="n">
-        <v>7058209</v>
+        <v>7058081</v>
       </c>
       <c r="S18" t="n">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2399,30 +2399,39 @@
           <t>2025-07-24</t>
         </is>
       </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>11:35</t>
+        </is>
+      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-07-24</t>
         </is>
       </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>11:35</t>
+        </is>
+      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Miriam Schenk</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Miriam Schenk, Cajsa Björkén, Fredrik Wilde, Philipp Weiss, Mattias Dalkvist, Vilhelm Kroon, Liam Sebestyén, Emil Lindgren, Alva Danielsson</t>
+          <t>Mattias Dalkvist, Fredrik Wilde, Liam Sebestyén, Alva Danielsson, Elke Blöhbaum, Vilhelm Kroon, Miriam Schenk, Cajsa Björkén, Philipp Weiss, Emil Lindgren</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
@@ -2433,32 +2442,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>126892810</v>
+        <v>126892808</v>
       </c>
       <c r="B19" t="n">
-        <v>91295</v>
+        <v>79018</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2468,13 +2477,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>672801</v>
+        <v>672862</v>
       </c>
       <c r="R19" t="n">
-        <v>7058081</v>
+        <v>7058125</v>
       </c>
       <c r="S19" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2503,7 +2512,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2513,7 +2522,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2544,10 +2553,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>126892808</v>
+        <v>126891131</v>
       </c>
       <c r="B20" t="n">
-        <v>79018</v>
+        <v>79050</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2555,21 +2564,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2579,13 +2588,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>672862</v>
+        <v>672898</v>
       </c>
       <c r="R20" t="n">
-        <v>7058125</v>
+        <v>7058209</v>
       </c>
       <c r="S20" t="n">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2612,39 +2621,30 @@
           <t>2025-07-24</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>11:25</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-07-24</t>
         </is>
       </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>11:25</t>
-        </is>
-      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Miriam Schenk</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist, Fredrik Wilde, Liam Sebestyén, Alva Danielsson, Elke Blöhbaum, Vilhelm Kroon, Miriam Schenk, Cajsa Björkén, Philipp Weiss, Emil Lindgren</t>
+          <t>Miriam Schenk, Cajsa Björkén, Fredrik Wilde, Philipp Weiss, Mattias Dalkvist, Vilhelm Kroon, Liam Sebestyén, Emil Lindgren, Alva Danielsson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
@@ -3702,45 +3702,59 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>126891328</v>
+        <v>126889377</v>
       </c>
       <c r="B31" t="n">
-        <v>79018</v>
+        <v>98468</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>221952</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Kravattensliden, Ång</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>672972</v>
+        <v>672810</v>
       </c>
       <c r="R31" t="n">
-        <v>7058246</v>
+        <v>7058105</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3787,12 +3801,12 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Liam Sebestyén, Mattias Dalkvist, Miriam Schenk, Fredrik Wilde, Elke Blöhbaum, Emil Lindgren</t>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Fredrik Wilde, Alva Danielsson, Emil Lindgren, Mattias Dalkvist, Elke Blöhbaum, Miriam Schenk, Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr">
@@ -3803,50 +3817,45 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>126889536</v>
+        <v>126891328</v>
       </c>
       <c r="B32" t="n">
-        <v>5177</v>
+        <v>79018</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100526</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Kravattensliden, Ång</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>672659</v>
+        <v>672972</v>
       </c>
       <c r="R32" t="n">
-        <v>7057975</v>
+        <v>7058246</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3893,12 +3902,12 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Fredrik Wilde, Alva Danielsson, Emil Lindgren, Mattias Dalkvist, Elke Blöhbaum, Miriam Schenk, Vilhelm Kroon</t>
+          <t>Alva Danielsson, Liam Sebestyén, Mattias Dalkvist, Miriam Schenk, Fredrik Wilde, Elke Blöhbaum, Emil Lindgren</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr">
@@ -3909,10 +3918,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>126889377</v>
+        <v>126889536</v>
       </c>
       <c r="B33" t="n">
-        <v>98468</v>
+        <v>5177</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3920,36 +3929,27 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>221952</v>
+        <v>100526</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>överblommad</t>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
@@ -3958,10 +3958,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>672810</v>
+        <v>672659</v>
       </c>
       <c r="R33" t="n">
-        <v>7058105</v>
+        <v>7057975</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -5387,10 +5387,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>126890311</v>
+        <v>126890305</v>
       </c>
       <c r="B47" t="n">
-        <v>88733</v>
+        <v>79018</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5398,21 +5398,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>510</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5422,10 +5422,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>673023</v>
+        <v>672724</v>
       </c>
       <c r="R47" t="n">
-        <v>7058218</v>
+        <v>7058075</v>
       </c>
       <c r="S47" t="n">
         <v>15</v>
@@ -5488,7 +5488,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>126890305</v>
+        <v>126889494</v>
       </c>
       <c r="B48" t="n">
         <v>79018</v>
@@ -5523,13 +5523,13 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>672724</v>
+        <v>672657</v>
       </c>
       <c r="R48" t="n">
-        <v>7058075</v>
+        <v>7057974</v>
       </c>
       <c r="S48" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5573,12 +5573,12 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon, Cajsa Björkén, Fredrik Wilde, Mattias Dalkvist, Philipp Weiss, Miriam Schenk, Liam Sebestyén, Alva Danielsson, Emil Lindgren</t>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Fredrik Wilde, Alva Danielsson, Emil Lindgren, Mattias Dalkvist, Elke Blöhbaum, Miriam Schenk, Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr">
@@ -5589,10 +5589,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>126889494</v>
+        <v>126890311</v>
       </c>
       <c r="B49" t="n">
-        <v>79018</v>
+        <v>88733</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5600,21 +5600,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>510</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5624,13 +5624,13 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>672657</v>
+        <v>673023</v>
       </c>
       <c r="R49" t="n">
-        <v>7057974</v>
+        <v>7058218</v>
       </c>
       <c r="S49" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5674,12 +5674,12 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Fredrik Wilde, Alva Danielsson, Emil Lindgren, Mattias Dalkvist, Elke Blöhbaum, Miriam Schenk, Vilhelm Kroon</t>
+          <t>Vilhelm Kroon, Cajsa Björkén, Fredrik Wilde, Mattias Dalkvist, Philipp Weiss, Miriam Schenk, Liam Sebestyén, Alva Danielsson, Emil Lindgren</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr">
@@ -8163,10 +8163,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>126890407</v>
+        <v>126890387</v>
       </c>
       <c r="B74" t="n">
-        <v>79018</v>
+        <v>80121</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8174,21 +8174,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8198,10 +8198,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>672859</v>
+        <v>672556</v>
       </c>
       <c r="R74" t="n">
-        <v>7058290</v>
+        <v>7058143</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8264,10 +8264,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>126890387</v>
+        <v>126890407</v>
       </c>
       <c r="B75" t="n">
-        <v>80121</v>
+        <v>79018</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8275,21 +8275,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8299,10 +8299,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>672556</v>
+        <v>672859</v>
       </c>
       <c r="R75" t="n">
-        <v>7058143</v>
+        <v>7058290</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>

--- a/artfynd/A 27938-2023 artfynd.xlsx
+++ b/artfynd/A 27938-2023 artfynd.xlsx
@@ -675,45 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>126879850</v>
+        <v>126889833</v>
       </c>
       <c r="B2" t="n">
-        <v>88733</v>
+        <v>91295</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>510</v>
+        <v>5447</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Kravattensliden, Kravattensliden, Ång</t>
+          <t>Kravattensliden, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>672873</v>
+        <v>672799</v>
       </c>
       <c r="R2" t="n">
-        <v>7058228</v>
+        <v>7058073</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -760,12 +760,12 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Fredrik Wilde</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Fredrik Wilde</t>
+          <t>Liam Sebestyén, Philipp Weiss, Miriam Schenk, Cajsa Björkén, Fredrik Wilde, Alva Danielsson, Elke Blöhbaum, Vilhelm Kroon, Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -776,45 +776,45 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126889312</v>
+        <v>126879850</v>
       </c>
       <c r="B3" t="n">
-        <v>91295</v>
+        <v>88733</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5447</v>
+        <v>510</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Kravattensliden, Ång</t>
+          <t>Kravattensliden, Kravattensliden, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>672839</v>
+        <v>672873</v>
       </c>
       <c r="R3" t="n">
-        <v>7058142</v>
+        <v>7058228</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -861,12 +861,12 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Fredrik Wilde</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Fredrik Wilde, Alva Danielsson, Emil Lindgren, Mattias Dalkvist, Elke Blöhbaum, Miriam Schenk, Vilhelm Kroon</t>
+          <t>Fredrik Wilde</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
@@ -877,7 +877,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126889833</v>
+        <v>126889312</v>
       </c>
       <c r="B4" t="n">
         <v>91295</v>
@@ -912,10 +912,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>672799</v>
+        <v>672839</v>
       </c>
       <c r="R4" t="n">
-        <v>7058073</v>
+        <v>7058142</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -962,12 +962,12 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Philipp Weiss, Miriam Schenk, Cajsa Björkén, Fredrik Wilde, Alva Danielsson, Elke Blöhbaum, Vilhelm Kroon, Mattias Dalkvist</t>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Fredrik Wilde, Alva Danielsson, Emil Lindgren, Mattias Dalkvist, Elke Blöhbaum, Miriam Schenk, Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
@@ -1068,7 +1068,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Fredrik Wilde, Alva Danielsson, Emil Lindgren, Mattias Dalkvist, Elke Blöhbaum, Miriam Schenk, Vilhelm Kroon</t>
+          <t>Mattias Dalkvist, Elke Blöhbaum, Miriam Schenk, Vilhelm Kroon, Fredrik Wilde, Alva Danielsson, Emil Lindgren, Philipp Weiss, Cajsa Björkén, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
@@ -1079,10 +1079,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126892811</v>
+        <v>126889505</v>
       </c>
       <c r="B6" t="n">
-        <v>79050</v>
+        <v>79018</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1090,21 +1090,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1114,13 +1114,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>672792</v>
+        <v>672864</v>
       </c>
       <c r="R6" t="n">
-        <v>7058076</v>
+        <v>7058181</v>
       </c>
       <c r="S6" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1147,19 +1147,9 @@
           <t>2025-07-24</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>11:35</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-07-24</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>11:35</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1174,12 +1164,12 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist, Fredrik Wilde, Liam Sebestyén, Alva Danielsson, Elke Blöhbaum, Vilhelm Kroon, Miriam Schenk, Cajsa Björkén, Philipp Weiss, Emil Lindgren</t>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Fredrik Wilde, Alva Danielsson, Emil Lindgren, Mattias Dalkvist, Elke Blöhbaum, Miriam Schenk, Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
@@ -1190,10 +1180,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126889505</v>
+        <v>126892811</v>
       </c>
       <c r="B7" t="n">
-        <v>79018</v>
+        <v>79050</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1201,21 +1191,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,13 +1215,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>672864</v>
+        <v>672792</v>
       </c>
       <c r="R7" t="n">
-        <v>7058181</v>
+        <v>7058076</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1258,9 +1248,19 @@
           <t>2025-07-24</t>
         </is>
       </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>11:35</t>
+        </is>
+      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-07-24</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1275,12 +1275,12 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Fredrik Wilde, Alva Danielsson, Emil Lindgren, Mattias Dalkvist, Elke Blöhbaum, Miriam Schenk, Vilhelm Kroon</t>
+          <t>Mattias Dalkvist, Fredrik Wilde, Liam Sebestyén, Alva Danielsson, Elke Blöhbaum, Vilhelm Kroon, Miriam Schenk, Cajsa Björkén, Philipp Weiss, Emil Lindgren</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
@@ -2017,7 +2017,7 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Fredrik Wilde, Alva Danielsson, Emil Lindgren, Mattias Dalkvist, Elke Blöhbaum, Miriam Schenk, Vilhelm Kroon</t>
+          <t>Vilhelm Kroon, Miriam Schenk, Elke Blöhbaum, Mattias Dalkvist, Emil Lindgren, Alva Danielsson, Fredrik Wilde, Liam Sebestyén, Cajsa Björkén, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
@@ -2028,32 +2028,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126889835</v>
+        <v>126889492</v>
       </c>
       <c r="B15" t="n">
-        <v>91295</v>
+        <v>79018</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2063,10 +2063,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>672843</v>
+        <v>672638</v>
       </c>
       <c r="R15" t="n">
-        <v>7058124</v>
+        <v>7057953</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2113,12 +2113,12 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Philipp Weiss, Miriam Schenk, Cajsa Björkén, Fredrik Wilde, Alva Danielsson, Elke Blöhbaum, Vilhelm Kroon, Mattias Dalkvist</t>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Fredrik Wilde, Alva Danielsson, Emil Lindgren, Mattias Dalkvist, Elke Blöhbaum, Miriam Schenk, Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
@@ -2129,32 +2129,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>126889492</v>
+        <v>126891315</v>
       </c>
       <c r="B16" t="n">
-        <v>79018</v>
+        <v>98469</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>221952</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2164,10 +2164,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>672638</v>
+        <v>672827</v>
       </c>
       <c r="R16" t="n">
-        <v>7057953</v>
+        <v>7058099</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2214,12 +2214,12 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Fredrik Wilde, Alva Danielsson, Emil Lindgren, Mattias Dalkvist, Elke Blöhbaum, Miriam Schenk, Vilhelm Kroon</t>
+          <t>Alva Danielsson, Liam Sebestyén, Mattias Dalkvist, Miriam Schenk, Fredrik Wilde, Elke Blöhbaum, Emil Lindgren</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
@@ -2230,10 +2230,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>126891315</v>
+        <v>126889835</v>
       </c>
       <c r="B17" t="n">
-        <v>98468</v>
+        <v>91295</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2241,21 +2241,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>221952</v>
+        <v>5447</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2265,10 +2265,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>672827</v>
+        <v>672843</v>
       </c>
       <c r="R17" t="n">
-        <v>7058099</v>
+        <v>7058124</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2315,12 +2315,12 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Liam Sebestyén, Mattias Dalkvist, Miriam Schenk, Fredrik Wilde, Elke Blöhbaum, Emil Lindgren</t>
+          <t>Liam Sebestyén, Philipp Weiss, Miriam Schenk, Cajsa Björkén, Fredrik Wilde, Alva Danielsson, Elke Blöhbaum, Vilhelm Kroon, Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
@@ -2331,32 +2331,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>126892810</v>
+        <v>126891131</v>
       </c>
       <c r="B18" t="n">
-        <v>91295</v>
+        <v>79050</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5447</v>
+        <v>185</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2366,13 +2366,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>672801</v>
+        <v>672898</v>
       </c>
       <c r="R18" t="n">
-        <v>7058081</v>
+        <v>7058209</v>
       </c>
       <c r="S18" t="n">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2399,39 +2399,30 @@
           <t>2025-07-24</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>11:35</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-07-24</t>
         </is>
       </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>11:35</t>
-        </is>
-      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Miriam Schenk</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist, Fredrik Wilde, Liam Sebestyén, Alva Danielsson, Elke Blöhbaum, Vilhelm Kroon, Miriam Schenk, Cajsa Björkén, Philipp Weiss, Emil Lindgren</t>
+          <t>Miriam Schenk, Cajsa Björkén, Fredrik Wilde, Philipp Weiss, Mattias Dalkvist, Vilhelm Kroon, Liam Sebestyén, Emil Lindgren, Alva Danielsson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
@@ -2442,32 +2433,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>126892808</v>
+        <v>126892810</v>
       </c>
       <c r="B19" t="n">
-        <v>79018</v>
+        <v>91295</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2477,13 +2468,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>672862</v>
+        <v>672801</v>
       </c>
       <c r="R19" t="n">
-        <v>7058125</v>
+        <v>7058081</v>
       </c>
       <c r="S19" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2512,7 +2503,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2522,7 +2513,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2553,10 +2544,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>126891131</v>
+        <v>126892808</v>
       </c>
       <c r="B20" t="n">
-        <v>79050</v>
+        <v>79018</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2564,21 +2555,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2588,13 +2579,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>672898</v>
+        <v>672862</v>
       </c>
       <c r="R20" t="n">
-        <v>7058209</v>
+        <v>7058125</v>
       </c>
       <c r="S20" t="n">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2621,30 +2612,39 @@
           <t>2025-07-24</t>
         </is>
       </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>11:25</t>
+        </is>
+      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-07-24</t>
         </is>
       </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>11:25</t>
+        </is>
+      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Miriam Schenk</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Miriam Schenk, Cajsa Björkén, Fredrik Wilde, Philipp Weiss, Mattias Dalkvist, Vilhelm Kroon, Liam Sebestyén, Emil Lindgren, Alva Danielsson</t>
+          <t>Mattias Dalkvist, Fredrik Wilde, Liam Sebestyén, Alva Danielsson, Elke Blöhbaum, Vilhelm Kroon, Miriam Schenk, Cajsa Björkén, Philipp Weiss, Emil Lindgren</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
@@ -2655,10 +2655,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>126889311</v>
+        <v>126889374</v>
       </c>
       <c r="B21" t="n">
-        <v>91295</v>
+        <v>98469</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2666,34 +2666,48 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5447</v>
+        <v>221952</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Kravattensliden, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>672799</v>
+        <v>672898</v>
       </c>
       <c r="R21" t="n">
-        <v>7058086</v>
+        <v>7058146</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2857,10 +2871,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>126889374</v>
+        <v>126889311</v>
       </c>
       <c r="B23" t="n">
-        <v>98468</v>
+        <v>91295</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2868,48 +2882,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>221952</v>
+        <v>5447</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Kravattensliden, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>672898</v>
+        <v>672799</v>
       </c>
       <c r="R23" t="n">
-        <v>7058146</v>
+        <v>7058086</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3067,7 +3067,7 @@
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Fredrik Wilde, Alva Danielsson, Emil Lindgren, Mattias Dalkvist, Elke Blöhbaum, Miriam Schenk, Vilhelm Kroon</t>
+          <t>Vilhelm Kroon, Miriam Schenk, Elke Blöhbaum, Mattias Dalkvist, Emil Lindgren, Alva Danielsson, Fredrik Wilde, Liam Sebestyén, Cajsa Björkén, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr">
@@ -3081,7 +3081,7 @@
         <v>126889869</v>
       </c>
       <c r="B25" t="n">
-        <v>98364</v>
+        <v>98365</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3179,45 +3179,53 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>126891313</v>
+        <v>126889847</v>
       </c>
       <c r="B26" t="n">
-        <v>80150</v>
+        <v>57658</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6462</v>
+        <v>100049</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Kravattensliden, Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>672933</v>
+        <v>672981</v>
       </c>
       <c r="R26" t="n">
-        <v>7058201</v>
+        <v>7058264</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3264,12 +3272,12 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Liam Sebestyén, Mattias Dalkvist, Miriam Schenk, Fredrik Wilde, Elke Blöhbaum, Emil Lindgren</t>
+          <t>Liam Sebestyén, Philipp Weiss, Miriam Schenk, Cajsa Björkén, Fredrik Wilde, Alva Danielsson, Elke Blöhbaum, Vilhelm Kroon, Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr">
@@ -3280,32 +3288,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>126892816</v>
+        <v>126891313</v>
       </c>
       <c r="B27" t="n">
-        <v>79018</v>
+        <v>80150</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3315,13 +3323,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>672627</v>
+        <v>672933</v>
       </c>
       <c r="R27" t="n">
-        <v>7058024</v>
+        <v>7058201</v>
       </c>
       <c r="S27" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3348,19 +3356,9 @@
           <t>2025-07-24</t>
         </is>
       </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>11:52</t>
-        </is>
-      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-07-24</t>
-        </is>
-      </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>11:52</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3375,12 +3373,12 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist, Fredrik Wilde, Liam Sebestyén, Alva Danielsson, Elke Blöhbaum, Vilhelm Kroon, Miriam Schenk, Cajsa Björkén, Philipp Weiss, Emil Lindgren</t>
+          <t>Alva Danielsson, Liam Sebestyén, Mattias Dalkvist, Miriam Schenk, Fredrik Wilde, Elke Blöhbaum, Emil Lindgren</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr">
@@ -3391,7 +3389,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>126893730</v>
+        <v>126892816</v>
       </c>
       <c r="B28" t="n">
         <v>79018</v>
@@ -3426,13 +3424,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>672929</v>
+        <v>672627</v>
       </c>
       <c r="R28" t="n">
-        <v>7058213</v>
+        <v>7058024</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3459,9 +3457,19 @@
           <t>2025-07-24</t>
         </is>
       </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>11:52</t>
+        </is>
+      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-07-24</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3476,12 +3484,12 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Fredrik Wilde, Liam Sebestyén, Elke Blöhbaum, Miriam Schenk, Mattias Dalkvist, Emil Lindgren</t>
+          <t>Mattias Dalkvist, Fredrik Wilde, Liam Sebestyén, Alva Danielsson, Elke Blöhbaum, Vilhelm Kroon, Miriam Schenk, Cajsa Björkén, Philipp Weiss, Emil Lindgren</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr">
@@ -3492,7 +3500,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>126889502</v>
+        <v>126893730</v>
       </c>
       <c r="B29" t="n">
         <v>79018</v>
@@ -3527,10 +3535,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>672801</v>
+        <v>672929</v>
       </c>
       <c r="R29" t="n">
-        <v>7058095</v>
+        <v>7058213</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3577,12 +3585,12 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Fredrik Wilde, Alva Danielsson, Emil Lindgren, Mattias Dalkvist, Elke Blöhbaum, Miriam Schenk, Vilhelm Kroon</t>
+          <t>Alva Danielsson, Fredrik Wilde, Liam Sebestyén, Elke Blöhbaum, Miriam Schenk, Mattias Dalkvist, Emil Lindgren</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr">
@@ -3593,10 +3601,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>126889847</v>
+        <v>126889502</v>
       </c>
       <c r="B30" t="n">
-        <v>57658</v>
+        <v>79018</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3604,42 +3612,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Kravattensliden, Ång</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>672981</v>
+        <v>672801</v>
       </c>
       <c r="R30" t="n">
-        <v>7058264</v>
+        <v>7058095</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3686,12 +3686,12 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Philipp Weiss, Miriam Schenk, Cajsa Björkén, Fredrik Wilde, Alva Danielsson, Elke Blöhbaum, Vilhelm Kroon, Mattias Dalkvist</t>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Fredrik Wilde, Alva Danielsson, Emil Lindgren, Mattias Dalkvist, Elke Blöhbaum, Miriam Schenk, Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr">
@@ -3705,7 +3705,7 @@
         <v>126889377</v>
       </c>
       <c r="B31" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3806,7 +3806,7 @@
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Fredrik Wilde, Alva Danielsson, Emil Lindgren, Mattias Dalkvist, Elke Blöhbaum, Miriam Schenk, Vilhelm Kroon</t>
+          <t>Vilhelm Kroon, Miriam Schenk, Elke Blöhbaum, Mattias Dalkvist, Emil Lindgren, Alva Danielsson, Fredrik Wilde, Liam Sebestyén, Cajsa Björkén, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr">
@@ -3817,45 +3817,50 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>126891328</v>
+        <v>126889536</v>
       </c>
       <c r="B32" t="n">
-        <v>79018</v>
+        <v>5177</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>100526</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Kravattensliden, Ång</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>672972</v>
+        <v>672659</v>
       </c>
       <c r="R32" t="n">
-        <v>7058246</v>
+        <v>7057975</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3902,12 +3907,12 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Liam Sebestyén, Mattias Dalkvist, Miriam Schenk, Fredrik Wilde, Elke Blöhbaum, Emil Lindgren</t>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Fredrik Wilde, Alva Danielsson, Emil Lindgren, Mattias Dalkvist, Elke Blöhbaum, Miriam Schenk, Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr">
@@ -3918,50 +3923,45 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>126889536</v>
+        <v>126891328</v>
       </c>
       <c r="B33" t="n">
-        <v>5177</v>
+        <v>79018</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100526</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Kravattensliden, Ång</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>672659</v>
+        <v>672972</v>
       </c>
       <c r="R33" t="n">
-        <v>7057975</v>
+        <v>7058246</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4008,12 +4008,12 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Fredrik Wilde, Alva Danielsson, Emil Lindgren, Mattias Dalkvist, Elke Blöhbaum, Miriam Schenk, Vilhelm Kroon</t>
+          <t>Alva Danielsson, Liam Sebestyén, Mattias Dalkvist, Miriam Schenk, Fredrik Wilde, Elke Blöhbaum, Emil Lindgren</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr">
@@ -4024,55 +4024,48 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>126893692</v>
+        <v>126891134</v>
       </c>
       <c r="B34" t="n">
-        <v>91330</v>
+        <v>80150</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1202</v>
+        <v>6462</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Kravattensliden , Ång</t>
+          <t>Kravattensliden, Ång</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>672811</v>
+        <v>673029</v>
       </c>
       <c r="R34" t="n">
-        <v>7058091</v>
+        <v>7058247</v>
       </c>
       <c r="S34" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4110,19 +4103,18 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
-      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Emil Lindgren</t>
+          <t>Miriam Schenk</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Emil Lindgren</t>
+          <t>Miriam Schenk, Cajsa Björkén, Fredrik Wilde, Philipp Weiss, Mattias Dalkvist, Vilhelm Kroon, Liam Sebestyén, Emil Lindgren, Alva Danielsson</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr">
@@ -4234,48 +4226,55 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>126891134</v>
+        <v>126893692</v>
       </c>
       <c r="B36" t="n">
-        <v>80150</v>
+        <v>91330</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6462</v>
+        <v>1202</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Kravattensliden, Ång</t>
+          <t>Kravattensliden , Ång</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>673029</v>
+        <v>672811</v>
       </c>
       <c r="R36" t="n">
-        <v>7058247</v>
+        <v>7058091</v>
       </c>
       <c r="S36" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4313,18 +4312,19 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
+      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Miriam Schenk</t>
+          <t>Emil Lindgren</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Miriam Schenk, Cajsa Björkén, Fredrik Wilde, Philipp Weiss, Mattias Dalkvist, Vilhelm Kroon, Liam Sebestyén, Emil Lindgren, Alva Danielsson</t>
+          <t>Emil Lindgren</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr">
@@ -4335,10 +4335,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>126892814</v>
+        <v>126892813</v>
       </c>
       <c r="B37" t="n">
-        <v>79050</v>
+        <v>79018</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4346,21 +4346,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4370,13 +4370,13 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>672659</v>
+        <v>672661</v>
       </c>
       <c r="R37" t="n">
-        <v>7058027</v>
+        <v>7058026</v>
       </c>
       <c r="S37" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4446,10 +4446,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>126891320</v>
+        <v>126892814</v>
       </c>
       <c r="B38" t="n">
-        <v>80121</v>
+        <v>79050</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4457,21 +4457,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6458</v>
+        <v>185</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4481,13 +4481,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>672929</v>
+        <v>672659</v>
       </c>
       <c r="R38" t="n">
-        <v>7058203</v>
+        <v>7058027</v>
       </c>
       <c r="S38" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4514,9 +4514,19 @@
           <t>2025-07-24</t>
         </is>
       </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>11:51</t>
+        </is>
+      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-07-24</t>
+        </is>
+      </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4531,12 +4541,12 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Liam Sebestyén, Mattias Dalkvist, Miriam Schenk, Fredrik Wilde, Elke Blöhbaum, Emil Lindgren</t>
+          <t>Mattias Dalkvist, Fredrik Wilde, Liam Sebestyén, Alva Danielsson, Elke Blöhbaum, Vilhelm Kroon, Miriam Schenk, Cajsa Björkén, Philipp Weiss, Emil Lindgren</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr">
@@ -4547,10 +4557,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>126892813</v>
+        <v>126891320</v>
       </c>
       <c r="B39" t="n">
-        <v>79018</v>
+        <v>80121</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4558,21 +4568,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4582,13 +4592,13 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>672661</v>
+        <v>672929</v>
       </c>
       <c r="R39" t="n">
-        <v>7058026</v>
+        <v>7058203</v>
       </c>
       <c r="S39" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4615,19 +4625,9 @@
           <t>2025-07-24</t>
         </is>
       </c>
-      <c r="Z39" t="inlineStr">
-        <is>
-          <t>11:51</t>
-        </is>
-      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-07-24</t>
-        </is>
-      </c>
-      <c r="AB39" t="inlineStr">
-        <is>
-          <t>11:51</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4642,12 +4642,12 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist, Fredrik Wilde, Liam Sebestyén, Alva Danielsson, Elke Blöhbaum, Vilhelm Kroon, Miriam Schenk, Cajsa Björkén, Philipp Weiss, Emil Lindgren</t>
+          <t>Alva Danielsson, Liam Sebestyén, Mattias Dalkvist, Miriam Schenk, Fredrik Wilde, Elke Blöhbaum, Emil Lindgren</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr">
@@ -4965,52 +4965,45 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>126893671</v>
+        <v>126891321</v>
       </c>
       <c r="B43" t="n">
-        <v>91295</v>
+        <v>80121</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>5447</v>
+        <v>6458</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="J43" t="inlineStr"/>
-      <c r="K43" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Kravattensliden , Ång</t>
+          <t>Kravattensliden, Ång</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>672808</v>
+        <v>673004</v>
       </c>
       <c r="R43" t="n">
-        <v>7058090</v>
+        <v>7058209</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5051,19 +5044,18 @@
       <c r="AE43" t="b">
         <v>0</v>
       </c>
-      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Emil Lindgren</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Emil Lindgren</t>
+          <t>Alva Danielsson, Liam Sebestyén, Mattias Dalkvist, Miriam Schenk, Fredrik Wilde, Elke Blöhbaum, Emil Lindgren</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr">
@@ -5074,45 +5066,52 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>126891321</v>
+        <v>126893671</v>
       </c>
       <c r="B44" t="n">
-        <v>80121</v>
+        <v>91295</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6458</v>
+        <v>5447</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="J44" t="inlineStr"/>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Kravattensliden, Ång</t>
+          <t>Kravattensliden , Ång</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>673004</v>
+        <v>672808</v>
       </c>
       <c r="R44" t="n">
-        <v>7058209</v>
+        <v>7058090</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5153,18 +5152,19 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
+      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Emil Lindgren</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Liam Sebestyén, Mattias Dalkvist, Miriam Schenk, Fredrik Wilde, Elke Blöhbaum, Emil Lindgren</t>
+          <t>Emil Lindgren</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr">
@@ -5387,10 +5387,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>126890305</v>
+        <v>126890311</v>
       </c>
       <c r="B47" t="n">
-        <v>79018</v>
+        <v>88733</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5398,21 +5398,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>510</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5422,10 +5422,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>672724</v>
+        <v>673023</v>
       </c>
       <c r="R47" t="n">
-        <v>7058075</v>
+        <v>7058218</v>
       </c>
       <c r="S47" t="n">
         <v>15</v>
@@ -5488,7 +5488,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>126889494</v>
+        <v>126890305</v>
       </c>
       <c r="B48" t="n">
         <v>79018</v>
@@ -5523,13 +5523,13 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>672657</v>
+        <v>672724</v>
       </c>
       <c r="R48" t="n">
-        <v>7057974</v>
+        <v>7058075</v>
       </c>
       <c r="S48" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5573,12 +5573,12 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Fredrik Wilde, Alva Danielsson, Emil Lindgren, Mattias Dalkvist, Elke Blöhbaum, Miriam Schenk, Vilhelm Kroon</t>
+          <t>Vilhelm Kroon, Cajsa Björkén, Fredrik Wilde, Mattias Dalkvist, Philipp Weiss, Miriam Schenk, Liam Sebestyén, Alva Danielsson, Emil Lindgren</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr">
@@ -5589,10 +5589,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>126890311</v>
+        <v>126889494</v>
       </c>
       <c r="B49" t="n">
-        <v>88733</v>
+        <v>79018</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5600,21 +5600,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>510</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5624,13 +5624,13 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>673023</v>
+        <v>672657</v>
       </c>
       <c r="R49" t="n">
-        <v>7058218</v>
+        <v>7057974</v>
       </c>
       <c r="S49" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5674,12 +5674,12 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon, Cajsa Björkén, Fredrik Wilde, Mattias Dalkvist, Philipp Weiss, Miriam Schenk, Liam Sebestyén, Alva Danielsson, Emil Lindgren</t>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Fredrik Wilde, Alva Danielsson, Emil Lindgren, Mattias Dalkvist, Elke Blöhbaum, Miriam Schenk, Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr">
@@ -5791,32 +5791,32 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>126889837</v>
+        <v>126889862</v>
       </c>
       <c r="B51" t="n">
-        <v>91295</v>
+        <v>91348</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>5447</v>
+        <v>5432</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5826,10 +5826,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>672912</v>
+        <v>672981</v>
       </c>
       <c r="R51" t="n">
-        <v>7058191</v>
+        <v>7058264</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5892,10 +5892,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>126889862</v>
+        <v>126879684</v>
       </c>
       <c r="B52" t="n">
-        <v>91348</v>
+        <v>79018</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5903,34 +5903,34 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Kravattensliden, Ång</t>
+          <t>Kravattensliden, Kravattensliden, Ång</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>672981</v>
+        <v>672895</v>
       </c>
       <c r="R52" t="n">
-        <v>7058264</v>
+        <v>7058223</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5977,12 +5977,12 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Fredrik Wilde</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Philipp Weiss, Miriam Schenk, Cajsa Björkén, Fredrik Wilde, Alva Danielsson, Elke Blöhbaum, Vilhelm Kroon, Mattias Dalkvist</t>
+          <t>Fredrik Wilde</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr">
@@ -5993,32 +5993,32 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>126889856</v>
+        <v>126889837</v>
       </c>
       <c r="B53" t="n">
-        <v>80121</v>
+        <v>91295</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6458</v>
+        <v>5447</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6028,10 +6028,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>672929</v>
+        <v>672912</v>
       </c>
       <c r="R53" t="n">
-        <v>7058201</v>
+        <v>7058191</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6094,7 +6094,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>126879684</v>
+        <v>126891325</v>
       </c>
       <c r="B54" t="n">
         <v>79018</v>
@@ -6125,14 +6125,14 @@
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Kravattensliden, Kravattensliden, Ång</t>
+          <t>Kravattensliden, Ång</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>672895</v>
+        <v>672660</v>
       </c>
       <c r="R54" t="n">
-        <v>7058223</v>
+        <v>7057985</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6179,12 +6179,12 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Fredrik Wilde</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Fredrik Wilde</t>
+          <t>Alva Danielsson, Liam Sebestyén, Mattias Dalkvist, Miriam Schenk, Fredrik Wilde, Elke Blöhbaum, Emil Lindgren</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr">
@@ -6195,10 +6195,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>126891325</v>
+        <v>126889856</v>
       </c>
       <c r="B55" t="n">
-        <v>79018</v>
+        <v>80121</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6206,21 +6206,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6230,10 +6230,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>672660</v>
+        <v>672929</v>
       </c>
       <c r="R55" t="n">
-        <v>7057985</v>
+        <v>7058201</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6280,12 +6280,12 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Liam Sebestyén, Mattias Dalkvist, Miriam Schenk, Fredrik Wilde, Elke Blöhbaum, Emil Lindgren</t>
+          <t>Liam Sebestyén, Philipp Weiss, Miriam Schenk, Cajsa Björkén, Fredrik Wilde, Alva Danielsson, Elke Blöhbaum, Vilhelm Kroon, Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr">
@@ -6299,7 +6299,7 @@
         <v>126893733</v>
       </c>
       <c r="B56" t="n">
-        <v>98364</v>
+        <v>98365</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6710,32 +6710,32 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>126890296</v>
+        <v>126892812</v>
       </c>
       <c r="B60" t="n">
-        <v>80150</v>
+        <v>79018</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6745,13 +6745,13 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>673025</v>
+        <v>672685</v>
       </c>
       <c r="R60" t="n">
-        <v>7058244</v>
+        <v>7058010</v>
       </c>
       <c r="S60" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -6778,9 +6778,19 @@
           <t>2025-07-24</t>
         </is>
       </c>
+      <c r="Z60" t="inlineStr">
+        <is>
+          <t>11:41</t>
+        </is>
+      </c>
       <c r="AA60" t="inlineStr">
         <is>
           <t>2025-07-24</t>
+        </is>
+      </c>
+      <c r="AB60" t="inlineStr">
+        <is>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6795,12 +6805,12 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon, Cajsa Björkén, Fredrik Wilde, Mattias Dalkvist, Philipp Weiss, Miriam Schenk, Liam Sebestyén, Alva Danielsson, Emil Lindgren</t>
+          <t>Mattias Dalkvist, Fredrik Wilde, Liam Sebestyén, Alva Danielsson, Elke Blöhbaum, Vilhelm Kroon, Miriam Schenk, Cajsa Björkén, Philipp Weiss, Emil Lindgren</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr">
@@ -6811,7 +6821,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>126892812</v>
+        <v>126892809</v>
       </c>
       <c r="B61" t="n">
         <v>79018</v>
@@ -6846,13 +6856,13 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>672685</v>
+        <v>672831</v>
       </c>
       <c r="R61" t="n">
-        <v>7058010</v>
+        <v>7058091</v>
       </c>
       <c r="S61" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -6881,7 +6891,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -6891,7 +6901,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7028,32 +7038,32 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>126892809</v>
+        <v>126890296</v>
       </c>
       <c r="B63" t="n">
-        <v>79018</v>
+        <v>80150</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7063,13 +7073,13 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>672831</v>
+        <v>673025</v>
       </c>
       <c r="R63" t="n">
-        <v>7058091</v>
+        <v>7058244</v>
       </c>
       <c r="S63" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7096,19 +7106,9 @@
           <t>2025-07-24</t>
         </is>
       </c>
-      <c r="Z63" t="inlineStr">
-        <is>
-          <t>11:32</t>
-        </is>
-      </c>
       <c r="AA63" t="inlineStr">
         <is>
           <t>2025-07-24</t>
-        </is>
-      </c>
-      <c r="AB63" t="inlineStr">
-        <is>
-          <t>11:32</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7123,12 +7123,12 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist, Fredrik Wilde, Liam Sebestyén, Alva Danielsson, Elke Blöhbaum, Vilhelm Kroon, Miriam Schenk, Cajsa Björkén, Philipp Weiss, Emil Lindgren</t>
+          <t>Vilhelm Kroon, Cajsa Björkén, Fredrik Wilde, Mattias Dalkvist, Philipp Weiss, Miriam Schenk, Liam Sebestyén, Alva Danielsson, Emil Lindgren</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr">
@@ -7139,10 +7139,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>126891312</v>
+        <v>126880532</v>
       </c>
       <c r="B64" t="n">
-        <v>91295</v>
+        <v>80150</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7150,34 +7150,34 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>5447</v>
+        <v>6462</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Kravattensliden, Ång</t>
+          <t>Kravattensliden, Kravattensliden, Ång</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>673027</v>
+        <v>672863</v>
       </c>
       <c r="R64" t="n">
-        <v>7058282</v>
+        <v>7058124</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7224,12 +7224,12 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Fredrik Wilde</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Liam Sebestyén, Mattias Dalkvist, Miriam Schenk, Fredrik Wilde, Elke Blöhbaum, Emil Lindgren</t>
+          <t>Fredrik Wilde</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr">
@@ -7240,45 +7240,50 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>126880532</v>
+        <v>126889382</v>
       </c>
       <c r="B65" t="n">
-        <v>80150</v>
+        <v>57658</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6462</v>
+        <v>100049</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Kravattensliden, Kravattensliden, Ång</t>
+          <t>Kravattensliden, Ång</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>672863</v>
+        <v>672838</v>
       </c>
       <c r="R65" t="n">
-        <v>7058124</v>
+        <v>7058134</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7325,12 +7330,12 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Fredrik Wilde</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Fredrik Wilde</t>
+          <t>Vilhelm Kroon, Miriam Schenk, Elke Blöhbaum, Mattias Dalkvist, Emil Lindgren, Alva Danielsson, Fredrik Wilde, Liam Sebestyén, Cajsa Björkén, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr">
@@ -7341,10 +7346,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>126879425</v>
+        <v>126879033</v>
       </c>
       <c r="B66" t="n">
-        <v>79018</v>
+        <v>79050</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7352,34 +7357,43 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr"/>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P66" t="inlineStr">
         <is>
           <t>Kravattensliden, Kravattensliden, Ång</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>672947</v>
+        <v>673046</v>
       </c>
       <c r="R66" t="n">
-        <v>7058198</v>
+        <v>7058286</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7442,10 +7456,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>126889382</v>
+        <v>126879425</v>
       </c>
       <c r="B67" t="n">
-        <v>57658</v>
+        <v>79018</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7453,39 +7467,34 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
-      <c r="M67" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Kravattensliden, Ång</t>
+          <t>Kravattensliden, Kravattensliden, Ång</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>672838</v>
+        <v>672947</v>
       </c>
       <c r="R67" t="n">
-        <v>7058134</v>
+        <v>7058198</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7532,12 +7541,12 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Fredrik Wilde</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Fredrik Wilde, Alva Danielsson, Emil Lindgren, Mattias Dalkvist, Elke Blöhbaum, Miriam Schenk, Vilhelm Kroon</t>
+          <t>Fredrik Wilde</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr">
@@ -7548,54 +7557,45 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>126879033</v>
+        <v>126891312</v>
       </c>
       <c r="B68" t="n">
-        <v>79050</v>
+        <v>91295</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>185</v>
+        <v>5447</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J68" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Kravattensliden, Kravattensliden, Ång</t>
+          <t>Kravattensliden, Ång</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>673046</v>
+        <v>673027</v>
       </c>
       <c r="R68" t="n">
-        <v>7058286</v>
+        <v>7058282</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7642,12 +7642,12 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Fredrik Wilde</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Fredrik Wilde</t>
+          <t>Alva Danielsson, Liam Sebestyén, Mattias Dalkvist, Miriam Schenk, Fredrik Wilde, Elke Blöhbaum, Emil Lindgren</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr">
@@ -7658,32 +7658,32 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>126890370</v>
+        <v>126890408</v>
       </c>
       <c r="B69" t="n">
-        <v>80150</v>
+        <v>79018</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7693,10 +7693,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>672554</v>
+        <v>672874</v>
       </c>
       <c r="R69" t="n">
-        <v>7058145</v>
+        <v>7058313</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7759,32 +7759,32 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>126890401</v>
+        <v>126890370</v>
       </c>
       <c r="B70" t="n">
-        <v>79018</v>
+        <v>80150</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7794,10 +7794,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>672705</v>
+        <v>672554</v>
       </c>
       <c r="R70" t="n">
-        <v>7058080</v>
+        <v>7058145</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7860,7 +7860,7 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>126890408</v>
+        <v>126890401</v>
       </c>
       <c r="B71" t="n">
         <v>79018</v>
@@ -7895,10 +7895,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>672874</v>
+        <v>672705</v>
       </c>
       <c r="R71" t="n">
-        <v>7058313</v>
+        <v>7058080</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -9173,10 +9173,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>126890403</v>
+        <v>126890352</v>
       </c>
       <c r="B84" t="n">
-        <v>79018</v>
+        <v>79050</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9184,21 +9184,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9208,10 +9208,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>672796</v>
+        <v>672847</v>
       </c>
       <c r="R84" t="n">
-        <v>7058317</v>
+        <v>7058276</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9274,10 +9274,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>126890352</v>
+        <v>126890403</v>
       </c>
       <c r="B85" t="n">
-        <v>79050</v>
+        <v>79018</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9285,21 +9285,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9309,10 +9309,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>672847</v>
+        <v>672796</v>
       </c>
       <c r="R85" t="n">
-        <v>7058276</v>
+        <v>7058317</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>

--- a/artfynd/A 27938-2023 artfynd.xlsx
+++ b/artfynd/A 27938-2023 artfynd.xlsx
@@ -675,45 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>126889833</v>
+        <v>126879850</v>
       </c>
       <c r="B2" t="n">
-        <v>91295</v>
+        <v>88733</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5447</v>
+        <v>510</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Kravattensliden, Ång</t>
+          <t>Kravattensliden, Kravattensliden, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>672799</v>
+        <v>672873</v>
       </c>
       <c r="R2" t="n">
-        <v>7058073</v>
+        <v>7058228</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -760,12 +760,12 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Fredrik Wilde</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Philipp Weiss, Miriam Schenk, Cajsa Björkén, Fredrik Wilde, Alva Danielsson, Elke Blöhbaum, Vilhelm Kroon, Mattias Dalkvist</t>
+          <t>Fredrik Wilde</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -776,45 +776,45 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126879850</v>
+        <v>126889312</v>
       </c>
       <c r="B3" t="n">
-        <v>88733</v>
+        <v>91295</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>510</v>
+        <v>5447</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Kravattensliden, Kravattensliden, Ång</t>
+          <t>Kravattensliden, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>672873</v>
+        <v>672839</v>
       </c>
       <c r="R3" t="n">
-        <v>7058228</v>
+        <v>7058142</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -861,12 +861,12 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Fredrik Wilde</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Fredrik Wilde</t>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Fredrik Wilde, Alva Danielsson, Emil Lindgren, Mattias Dalkvist, Elke Blöhbaum, Miriam Schenk, Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
@@ -877,7 +877,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126889312</v>
+        <v>126889833</v>
       </c>
       <c r="B4" t="n">
         <v>91295</v>
@@ -912,10 +912,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>672839</v>
+        <v>672799</v>
       </c>
       <c r="R4" t="n">
-        <v>7058142</v>
+        <v>7058073</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -962,12 +962,12 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Fredrik Wilde, Alva Danielsson, Emil Lindgren, Mattias Dalkvist, Elke Blöhbaum, Miriam Schenk, Vilhelm Kroon</t>
+          <t>Liam Sebestyén, Philipp Weiss, Miriam Schenk, Cajsa Björkén, Fredrik Wilde, Alva Danielsson, Elke Blöhbaum, Vilhelm Kroon, Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
@@ -1079,10 +1079,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126889505</v>
+        <v>126892811</v>
       </c>
       <c r="B6" t="n">
-        <v>79018</v>
+        <v>79050</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1090,21 +1090,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1114,13 +1114,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>672864</v>
+        <v>672792</v>
       </c>
       <c r="R6" t="n">
-        <v>7058181</v>
+        <v>7058076</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1147,9 +1147,19 @@
           <t>2025-07-24</t>
         </is>
       </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>11:35</t>
+        </is>
+      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-07-24</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1164,12 +1174,12 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Fredrik Wilde, Alva Danielsson, Emil Lindgren, Mattias Dalkvist, Elke Blöhbaum, Miriam Schenk, Vilhelm Kroon</t>
+          <t>Mattias Dalkvist, Fredrik Wilde, Liam Sebestyén, Alva Danielsson, Elke Blöhbaum, Vilhelm Kroon, Miriam Schenk, Cajsa Björkén, Philipp Weiss, Emil Lindgren</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
@@ -1180,10 +1190,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126892811</v>
+        <v>126892805</v>
       </c>
       <c r="B7" t="n">
-        <v>79050</v>
+        <v>57661</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1191,21 +1201,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>185</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1215,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>672792</v>
+        <v>672877</v>
       </c>
       <c r="R7" t="n">
-        <v>7058076</v>
+        <v>7058189</v>
       </c>
       <c r="S7" t="n">
         <v>4</v>
@@ -1250,7 +1260,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1260,7 +1270,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>11:15</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Gamla ringhack</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1291,10 +1306,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126892805</v>
+        <v>126889505</v>
       </c>
       <c r="B8" t="n">
-        <v>57661</v>
+        <v>79018</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1302,21 +1317,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1326,13 +1341,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>672877</v>
+        <v>672864</v>
       </c>
       <c r="R8" t="n">
-        <v>7058189</v>
+        <v>7058181</v>
       </c>
       <c r="S8" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1359,24 +1374,9 @@
           <t>2025-07-24</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>11:15</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-07-24</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>11:15</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Gamla ringhack</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1391,12 +1391,12 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist, Fredrik Wilde, Liam Sebestyén, Alva Danielsson, Elke Blöhbaum, Vilhelm Kroon, Miriam Schenk, Cajsa Björkén, Philipp Weiss, Emil Lindgren</t>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Fredrik Wilde, Alva Danielsson, Emil Lindgren, Mattias Dalkvist, Elke Blöhbaum, Miriam Schenk, Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
@@ -1811,10 +1811,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126892815</v>
+        <v>126889387</v>
       </c>
       <c r="B13" t="n">
-        <v>79018</v>
+        <v>57658</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1822,37 +1822,42 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Kravattensliden, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>672633</v>
+        <v>672816</v>
       </c>
       <c r="R13" t="n">
-        <v>7058033</v>
+        <v>7058123</v>
       </c>
       <c r="S13" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1879,19 +1884,9 @@
           <t>2025-07-24</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>11:52</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-07-24</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>11:52</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1906,12 +1901,12 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist, Fredrik Wilde, Liam Sebestyén, Alva Danielsson, Elke Blöhbaum, Vilhelm Kroon, Miriam Schenk, Cajsa Björkén, Philipp Weiss, Emil Lindgren</t>
+          <t>Vilhelm Kroon, Miriam Schenk, Elke Blöhbaum, Mattias Dalkvist, Emil Lindgren, Alva Danielsson, Fredrik Wilde, Liam Sebestyén, Cajsa Björkén, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
@@ -1922,10 +1917,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126889387</v>
+        <v>126892815</v>
       </c>
       <c r="B14" t="n">
-        <v>57658</v>
+        <v>79018</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1933,42 +1928,37 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Kravattensliden, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>672816</v>
+        <v>672633</v>
       </c>
       <c r="R14" t="n">
-        <v>7058123</v>
+        <v>7058033</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -1995,9 +1985,19 @@
           <t>2025-07-24</t>
         </is>
       </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>11:52</t>
+        </is>
+      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-07-24</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2012,12 +2012,12 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon, Miriam Schenk, Elke Blöhbaum, Mattias Dalkvist, Emil Lindgren, Alva Danielsson, Fredrik Wilde, Liam Sebestyén, Cajsa Björkén, Philipp Weiss</t>
+          <t>Mattias Dalkvist, Fredrik Wilde, Liam Sebestyén, Alva Danielsson, Elke Blöhbaum, Vilhelm Kroon, Miriam Schenk, Cajsa Björkén, Philipp Weiss, Emil Lindgren</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
@@ -2129,10 +2129,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>126891315</v>
+        <v>126889835</v>
       </c>
       <c r="B16" t="n">
-        <v>98469</v>
+        <v>91295</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2140,21 +2140,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>221952</v>
+        <v>5447</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2164,10 +2164,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>672827</v>
+        <v>672843</v>
       </c>
       <c r="R16" t="n">
-        <v>7058099</v>
+        <v>7058124</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2214,12 +2214,12 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Liam Sebestyén, Mattias Dalkvist, Miriam Schenk, Fredrik Wilde, Elke Blöhbaum, Emil Lindgren</t>
+          <t>Liam Sebestyén, Philipp Weiss, Miriam Schenk, Cajsa Björkén, Fredrik Wilde, Alva Danielsson, Elke Blöhbaum, Vilhelm Kroon, Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
@@ -2230,10 +2230,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>126889835</v>
+        <v>126891315</v>
       </c>
       <c r="B17" t="n">
-        <v>91295</v>
+        <v>98469</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2241,21 +2241,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5447</v>
+        <v>221952</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2265,10 +2265,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>672843</v>
+        <v>672827</v>
       </c>
       <c r="R17" t="n">
-        <v>7058124</v>
+        <v>7058099</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2315,12 +2315,12 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Philipp Weiss, Miriam Schenk, Cajsa Björkén, Fredrik Wilde, Alva Danielsson, Elke Blöhbaum, Vilhelm Kroon, Mattias Dalkvist</t>
+          <t>Alva Danielsson, Liam Sebestyén, Mattias Dalkvist, Miriam Schenk, Fredrik Wilde, Elke Blöhbaum, Emil Lindgren</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
@@ -2655,10 +2655,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>126889374</v>
+        <v>126889311</v>
       </c>
       <c r="B21" t="n">
-        <v>98469</v>
+        <v>91295</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2666,48 +2666,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>221952</v>
+        <v>5447</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Kravattensliden, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>672898</v>
+        <v>672799</v>
       </c>
       <c r="R21" t="n">
-        <v>7058146</v>
+        <v>7058086</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2770,10 +2756,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>126891314</v>
+        <v>126889869</v>
       </c>
       <c r="B22" t="n">
-        <v>80150</v>
+        <v>98365</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2781,21 +2767,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6462</v>
+        <v>219790</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2805,10 +2791,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>672999</v>
+        <v>672855</v>
       </c>
       <c r="R22" t="n">
-        <v>7058211</v>
+        <v>7058116</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2855,12 +2841,12 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Liam Sebestyén, Mattias Dalkvist, Miriam Schenk, Fredrik Wilde, Elke Blöhbaum, Emil Lindgren</t>
+          <t>Liam Sebestyén, Philipp Weiss, Miriam Schenk, Cajsa Björkén, Fredrik Wilde, Alva Danielsson, Elke Blöhbaum, Vilhelm Kroon, Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
@@ -2871,10 +2857,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>126889311</v>
+        <v>126889374</v>
       </c>
       <c r="B23" t="n">
-        <v>91295</v>
+        <v>98469</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2882,34 +2868,48 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5447</v>
+        <v>221952</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Kravattensliden, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>672799</v>
+        <v>672898</v>
       </c>
       <c r="R23" t="n">
-        <v>7058086</v>
+        <v>7058146</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2972,10 +2972,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>126889370</v>
+        <v>126891314</v>
       </c>
       <c r="B24" t="n">
-        <v>4773</v>
+        <v>80150</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2983,39 +2983,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100299</v>
+        <v>6462</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Kravattensliden, Ång</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>672839</v>
+        <v>672999</v>
       </c>
       <c r="R24" t="n">
-        <v>7058141</v>
+        <v>7058211</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3062,12 +3057,12 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon, Miriam Schenk, Elke Blöhbaum, Mattias Dalkvist, Emil Lindgren, Alva Danielsson, Fredrik Wilde, Liam Sebestyén, Cajsa Björkén, Philipp Weiss</t>
+          <t>Alva Danielsson, Liam Sebestyén, Mattias Dalkvist, Miriam Schenk, Fredrik Wilde, Elke Blöhbaum, Emil Lindgren</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr">
@@ -3078,10 +3073,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>126889869</v>
+        <v>126889370</v>
       </c>
       <c r="B25" t="n">
-        <v>98365</v>
+        <v>4773</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3089,34 +3084,39 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>219790</v>
+        <v>100299</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Kravattensliden, Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>672855</v>
+        <v>672839</v>
       </c>
       <c r="R25" t="n">
-        <v>7058116</v>
+        <v>7058141</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3163,12 +3163,12 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Philipp Weiss, Miriam Schenk, Cajsa Björkén, Fredrik Wilde, Alva Danielsson, Elke Blöhbaum, Vilhelm Kroon, Mattias Dalkvist</t>
+          <t>Vilhelm Kroon, Miriam Schenk, Elke Blöhbaum, Mattias Dalkvist, Emil Lindgren, Alva Danielsson, Fredrik Wilde, Liam Sebestyén, Cajsa Björkén, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr">
@@ -3179,53 +3179,45 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>126889847</v>
+        <v>126891313</v>
       </c>
       <c r="B26" t="n">
-        <v>57658</v>
+        <v>80150</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100049</v>
+        <v>6462</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Kravattensliden, Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>672981</v>
+        <v>672933</v>
       </c>
       <c r="R26" t="n">
-        <v>7058264</v>
+        <v>7058201</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3272,12 +3264,12 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Philipp Weiss, Miriam Schenk, Cajsa Björkén, Fredrik Wilde, Alva Danielsson, Elke Blöhbaum, Vilhelm Kroon, Mattias Dalkvist</t>
+          <t>Alva Danielsson, Liam Sebestyén, Mattias Dalkvist, Miriam Schenk, Fredrik Wilde, Elke Blöhbaum, Emil Lindgren</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr">
@@ -3288,45 +3280,53 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>126891313</v>
+        <v>126889847</v>
       </c>
       <c r="B27" t="n">
-        <v>80150</v>
+        <v>57658</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6462</v>
+        <v>100049</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Kravattensliden, Ång</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>672933</v>
+        <v>672981</v>
       </c>
       <c r="R27" t="n">
-        <v>7058201</v>
+        <v>7058264</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3373,12 +3373,12 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Liam Sebestyén, Mattias Dalkvist, Miriam Schenk, Fredrik Wilde, Elke Blöhbaum, Emil Lindgren</t>
+          <t>Liam Sebestyén, Philipp Weiss, Miriam Schenk, Cajsa Björkén, Fredrik Wilde, Alva Danielsson, Elke Blöhbaum, Vilhelm Kroon, Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr">
@@ -3389,7 +3389,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>126892816</v>
+        <v>126893730</v>
       </c>
       <c r="B28" t="n">
         <v>79018</v>
@@ -3424,13 +3424,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>672627</v>
+        <v>672929</v>
       </c>
       <c r="R28" t="n">
-        <v>7058024</v>
+        <v>7058213</v>
       </c>
       <c r="S28" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3457,19 +3457,9 @@
           <t>2025-07-24</t>
         </is>
       </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>11:52</t>
-        </is>
-      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-07-24</t>
-        </is>
-      </c>
-      <c r="AB28" t="inlineStr">
-        <is>
-          <t>11:52</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3484,12 +3474,12 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist, Fredrik Wilde, Liam Sebestyén, Alva Danielsson, Elke Blöhbaum, Vilhelm Kroon, Miriam Schenk, Cajsa Björkén, Philipp Weiss, Emil Lindgren</t>
+          <t>Alva Danielsson, Fredrik Wilde, Liam Sebestyén, Elke Blöhbaum, Miriam Schenk, Mattias Dalkvist, Emil Lindgren</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr">
@@ -3500,7 +3490,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>126893730</v>
+        <v>126892816</v>
       </c>
       <c r="B29" t="n">
         <v>79018</v>
@@ -3535,13 +3525,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>672929</v>
+        <v>672627</v>
       </c>
       <c r="R29" t="n">
-        <v>7058213</v>
+        <v>7058024</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3568,9 +3558,19 @@
           <t>2025-07-24</t>
         </is>
       </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>11:52</t>
+        </is>
+      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-07-24</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3585,12 +3585,12 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Fredrik Wilde, Liam Sebestyén, Elke Blöhbaum, Miriam Schenk, Mattias Dalkvist, Emil Lindgren</t>
+          <t>Mattias Dalkvist, Fredrik Wilde, Liam Sebestyén, Alva Danielsson, Elke Blöhbaum, Vilhelm Kroon, Miriam Schenk, Cajsa Björkén, Philipp Weiss, Emil Lindgren</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr">
@@ -3817,50 +3817,45 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>126889536</v>
+        <v>126891328</v>
       </c>
       <c r="B32" t="n">
-        <v>5177</v>
+        <v>79018</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100526</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Kravattensliden, Ång</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>672659</v>
+        <v>672972</v>
       </c>
       <c r="R32" t="n">
-        <v>7057975</v>
+        <v>7058246</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3907,12 +3902,12 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Fredrik Wilde, Alva Danielsson, Emil Lindgren, Mattias Dalkvist, Elke Blöhbaum, Miriam Schenk, Vilhelm Kroon</t>
+          <t>Alva Danielsson, Liam Sebestyén, Mattias Dalkvist, Miriam Schenk, Fredrik Wilde, Elke Blöhbaum, Emil Lindgren</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr">
@@ -3923,45 +3918,50 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>126891328</v>
+        <v>126889536</v>
       </c>
       <c r="B33" t="n">
-        <v>79018</v>
+        <v>5177</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>100526</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Kravattensliden, Ång</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>672972</v>
+        <v>672659</v>
       </c>
       <c r="R33" t="n">
-        <v>7058246</v>
+        <v>7057975</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4008,12 +4008,12 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Liam Sebestyén, Mattias Dalkvist, Miriam Schenk, Fredrik Wilde, Elke Blöhbaum, Emil Lindgren</t>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Fredrik Wilde, Alva Danielsson, Emil Lindgren, Mattias Dalkvist, Elke Blöhbaum, Miriam Schenk, Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr">
@@ -4335,10 +4335,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>126892813</v>
+        <v>126892814</v>
       </c>
       <c r="B37" t="n">
-        <v>79018</v>
+        <v>79050</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4346,21 +4346,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4370,13 +4370,13 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>672661</v>
+        <v>672659</v>
       </c>
       <c r="R37" t="n">
-        <v>7058026</v>
+        <v>7058027</v>
       </c>
       <c r="S37" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4446,10 +4446,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>126892814</v>
+        <v>126891320</v>
       </c>
       <c r="B38" t="n">
-        <v>79050</v>
+        <v>80121</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4457,21 +4457,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>185</v>
+        <v>6458</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4481,13 +4481,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>672659</v>
+        <v>672929</v>
       </c>
       <c r="R38" t="n">
-        <v>7058027</v>
+        <v>7058203</v>
       </c>
       <c r="S38" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4514,19 +4514,9 @@
           <t>2025-07-24</t>
         </is>
       </c>
-      <c r="Z38" t="inlineStr">
-        <is>
-          <t>11:51</t>
-        </is>
-      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-07-24</t>
-        </is>
-      </c>
-      <c r="AB38" t="inlineStr">
-        <is>
-          <t>11:51</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4541,12 +4531,12 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist, Fredrik Wilde, Liam Sebestyén, Alva Danielsson, Elke Blöhbaum, Vilhelm Kroon, Miriam Schenk, Cajsa Björkén, Philipp Weiss, Emil Lindgren</t>
+          <t>Alva Danielsson, Liam Sebestyén, Mattias Dalkvist, Miriam Schenk, Fredrik Wilde, Elke Blöhbaum, Emil Lindgren</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr">
@@ -4557,10 +4547,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>126891320</v>
+        <v>126890308</v>
       </c>
       <c r="B39" t="n">
-        <v>80121</v>
+        <v>79018</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4568,21 +4558,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4592,13 +4582,13 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>672929</v>
+        <v>672880</v>
       </c>
       <c r="R39" t="n">
-        <v>7058203</v>
+        <v>7058209</v>
       </c>
       <c r="S39" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4642,12 +4632,12 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Liam Sebestyén, Mattias Dalkvist, Miriam Schenk, Fredrik Wilde, Elke Blöhbaum, Emil Lindgren</t>
+          <t>Vilhelm Kroon, Cajsa Björkén, Fredrik Wilde, Mattias Dalkvist, Philipp Weiss, Miriam Schenk, Liam Sebestyén, Alva Danielsson, Emil Lindgren</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr">
@@ -4658,7 +4648,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>126890308</v>
+        <v>126892813</v>
       </c>
       <c r="B40" t="n">
         <v>79018</v>
@@ -4693,13 +4683,13 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>672880</v>
+        <v>672661</v>
       </c>
       <c r="R40" t="n">
-        <v>7058209</v>
+        <v>7058026</v>
       </c>
       <c r="S40" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4726,9 +4716,19 @@
           <t>2025-07-24</t>
         </is>
       </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>11:51</t>
+        </is>
+      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-07-24</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4743,12 +4743,12 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon, Cajsa Björkén, Fredrik Wilde, Mattias Dalkvist, Philipp Weiss, Miriam Schenk, Liam Sebestyén, Alva Danielsson, Emil Lindgren</t>
+          <t>Mattias Dalkvist, Fredrik Wilde, Liam Sebestyén, Alva Danielsson, Elke Blöhbaum, Vilhelm Kroon, Miriam Schenk, Cajsa Björkén, Philipp Weiss, Emil Lindgren</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr">
@@ -6710,7 +6710,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>126892812</v>
+        <v>126892809</v>
       </c>
       <c r="B60" t="n">
         <v>79018</v>
@@ -6745,13 +6745,13 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>672685</v>
+        <v>672831</v>
       </c>
       <c r="R60" t="n">
-        <v>7058010</v>
+        <v>7058091</v>
       </c>
       <c r="S60" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -6780,7 +6780,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -6790,7 +6790,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6821,32 +6821,32 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>126892809</v>
+        <v>126890296</v>
       </c>
       <c r="B61" t="n">
-        <v>79018</v>
+        <v>80150</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6856,13 +6856,13 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>672831</v>
+        <v>673025</v>
       </c>
       <c r="R61" t="n">
-        <v>7058091</v>
+        <v>7058244</v>
       </c>
       <c r="S61" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -6889,19 +6889,9 @@
           <t>2025-07-24</t>
         </is>
       </c>
-      <c r="Z61" t="inlineStr">
-        <is>
-          <t>11:32</t>
-        </is>
-      </c>
       <c r="AA61" t="inlineStr">
         <is>
           <t>2025-07-24</t>
-        </is>
-      </c>
-      <c r="AB61" t="inlineStr">
-        <is>
-          <t>11:32</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -6916,12 +6906,12 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist, Fredrik Wilde, Liam Sebestyén, Alva Danielsson, Elke Blöhbaum, Vilhelm Kroon, Miriam Schenk, Cajsa Björkén, Philipp Weiss, Emil Lindgren</t>
+          <t>Vilhelm Kroon, Cajsa Björkén, Fredrik Wilde, Mattias Dalkvist, Philipp Weiss, Miriam Schenk, Liam Sebestyén, Alva Danielsson, Emil Lindgren</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr">
@@ -6932,7 +6922,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>126880199</v>
+        <v>126892812</v>
       </c>
       <c r="B62" t="n">
         <v>79018</v>
@@ -6961,24 +6951,19 @@
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
-      <c r="K62" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Kravattensliden, Kravattensliden, Ång</t>
+          <t>Kravattensliden, Ång</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>672894</v>
+        <v>672685</v>
       </c>
       <c r="R62" t="n">
-        <v>7058198</v>
+        <v>7058010</v>
       </c>
       <c r="S62" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7005,9 +6990,19 @@
           <t>2025-07-24</t>
         </is>
       </c>
+      <c r="Z62" t="inlineStr">
+        <is>
+          <t>11:41</t>
+        </is>
+      </c>
       <c r="AA62" t="inlineStr">
         <is>
           <t>2025-07-24</t>
+        </is>
+      </c>
+      <c r="AB62" t="inlineStr">
+        <is>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7022,12 +7017,12 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Fredrik Wilde</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Fredrik Wilde</t>
+          <t>Mattias Dalkvist, Fredrik Wilde, Liam Sebestyén, Alva Danielsson, Elke Blöhbaum, Vilhelm Kroon, Miriam Schenk, Cajsa Björkén, Philipp Weiss, Emil Lindgren</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr">
@@ -7038,48 +7033,53 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>126890296</v>
+        <v>126880199</v>
       </c>
       <c r="B63" t="n">
-        <v>80150</v>
+        <v>79018</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Kravattensliden, Ång</t>
+          <t>Kravattensliden, Kravattensliden, Ång</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>673025</v>
+        <v>672894</v>
       </c>
       <c r="R63" t="n">
-        <v>7058244</v>
+        <v>7058198</v>
       </c>
       <c r="S63" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7123,12 +7123,12 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Fredrik Wilde</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon, Cajsa Björkén, Fredrik Wilde, Mattias Dalkvist, Philipp Weiss, Miriam Schenk, Liam Sebestyén, Alva Danielsson, Emil Lindgren</t>
+          <t>Fredrik Wilde</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr">
@@ -7139,45 +7139,50 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>126880532</v>
+        <v>126889382</v>
       </c>
       <c r="B64" t="n">
-        <v>80150</v>
+        <v>57658</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6462</v>
+        <v>100049</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Kravattensliden, Kravattensliden, Ång</t>
+          <t>Kravattensliden, Ång</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>672863</v>
+        <v>672838</v>
       </c>
       <c r="R64" t="n">
-        <v>7058124</v>
+        <v>7058134</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7224,12 +7229,12 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Fredrik Wilde</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Fredrik Wilde</t>
+          <t>Vilhelm Kroon, Miriam Schenk, Elke Blöhbaum, Mattias Dalkvist, Emil Lindgren, Alva Danielsson, Fredrik Wilde, Liam Sebestyén, Cajsa Björkén, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr">
@@ -7240,10 +7245,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>126889382</v>
+        <v>126879033</v>
       </c>
       <c r="B65" t="n">
-        <v>57658</v>
+        <v>79050</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7251,39 +7256,43 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>100049</v>
+        <v>185</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr"/>
-      <c r="M65" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Kravattensliden, Ång</t>
+          <t>Kravattensliden, Kravattensliden, Ång</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>672838</v>
+        <v>673046</v>
       </c>
       <c r="R65" t="n">
-        <v>7058134</v>
+        <v>7058286</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7330,12 +7339,12 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Fredrik Wilde</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon, Miriam Schenk, Elke Blöhbaum, Mattias Dalkvist, Emil Lindgren, Alva Danielsson, Fredrik Wilde, Liam Sebestyén, Cajsa Björkén, Philipp Weiss</t>
+          <t>Fredrik Wilde</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr">
@@ -7346,54 +7355,45 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>126879033</v>
+        <v>126880532</v>
       </c>
       <c r="B66" t="n">
-        <v>79050</v>
+        <v>80150</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>185</v>
+        <v>6462</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J66" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
           <t>Kravattensliden, Kravattensliden, Ång</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>673046</v>
+        <v>672863</v>
       </c>
       <c r="R66" t="n">
-        <v>7058286</v>
+        <v>7058124</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7658,32 +7658,32 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>126890408</v>
+        <v>126890370</v>
       </c>
       <c r="B69" t="n">
-        <v>79018</v>
+        <v>80150</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7693,10 +7693,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>672874</v>
+        <v>672554</v>
       </c>
       <c r="R69" t="n">
-        <v>7058313</v>
+        <v>7058145</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7759,32 +7759,32 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>126890370</v>
+        <v>126890408</v>
       </c>
       <c r="B70" t="n">
-        <v>80150</v>
+        <v>79018</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7794,10 +7794,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>672554</v>
+        <v>672874</v>
       </c>
       <c r="R70" t="n">
-        <v>7058145</v>
+        <v>7058313</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>

--- a/artfynd/A 27938-2023 artfynd.xlsx
+++ b/artfynd/A 27938-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126879850</v>
       </c>
       <c r="B2" t="n">
-        <v>88733</v>
+        <v>88735</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>126889312</v>
       </c>
       <c r="B3" t="n">
-        <v>91295</v>
+        <v>91297</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -880,7 +880,7 @@
         <v>126889833</v>
       </c>
       <c r="B4" t="n">
-        <v>91295</v>
+        <v>91297</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -981,7 +981,7 @@
         <v>126889402</v>
       </c>
       <c r="B5" t="n">
-        <v>97325</v>
+        <v>97327</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1068,7 +1068,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist, Elke Blöhbaum, Miriam Schenk, Vilhelm Kroon, Fredrik Wilde, Alva Danielsson, Emil Lindgren, Philipp Weiss, Cajsa Björkén, Liam Sebestyén</t>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Fredrik Wilde, Alva Danielsson, Emil Lindgren, Mattias Dalkvist, Elke Blöhbaum, Miriam Schenk, Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
@@ -1079,10 +1079,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126892811</v>
+        <v>126889505</v>
       </c>
       <c r="B6" t="n">
-        <v>79050</v>
+        <v>79020</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1090,21 +1090,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1114,13 +1114,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>672792</v>
+        <v>672864</v>
       </c>
       <c r="R6" t="n">
-        <v>7058076</v>
+        <v>7058181</v>
       </c>
       <c r="S6" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1147,19 +1147,9 @@
           <t>2025-07-24</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>11:35</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-07-24</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>11:35</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1174,12 +1164,12 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist, Fredrik Wilde, Liam Sebestyén, Alva Danielsson, Elke Blöhbaum, Vilhelm Kroon, Miriam Schenk, Cajsa Björkén, Philipp Weiss, Emil Lindgren</t>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Fredrik Wilde, Alva Danielsson, Emil Lindgren, Mattias Dalkvist, Elke Blöhbaum, Miriam Schenk, Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
@@ -1190,10 +1180,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126892805</v>
+        <v>126892811</v>
       </c>
       <c r="B7" t="n">
-        <v>57661</v>
+        <v>79052</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1201,21 +1191,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>185</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,10 +1215,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>672877</v>
+        <v>672792</v>
       </c>
       <c r="R7" t="n">
-        <v>7058189</v>
+        <v>7058076</v>
       </c>
       <c r="S7" t="n">
         <v>4</v>
@@ -1260,7 +1250,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1270,12 +1260,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:15</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Gamla ringhack</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1306,10 +1291,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126889505</v>
+        <v>126892805</v>
       </c>
       <c r="B8" t="n">
-        <v>79018</v>
+        <v>57663</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1317,21 +1302,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1341,13 +1326,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>672864</v>
+        <v>672877</v>
       </c>
       <c r="R8" t="n">
-        <v>7058181</v>
+        <v>7058189</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1374,9 +1359,24 @@
           <t>2025-07-24</t>
         </is>
       </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>11:15</t>
+        </is>
+      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-07-24</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>11:15</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Gamla ringhack</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1391,12 +1391,12 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Fredrik Wilde, Alva Danielsson, Emil Lindgren, Mattias Dalkvist, Elke Blöhbaum, Miriam Schenk, Vilhelm Kroon</t>
+          <t>Mattias Dalkvist, Fredrik Wilde, Liam Sebestyén, Alva Danielsson, Elke Blöhbaum, Vilhelm Kroon, Miriam Schenk, Cajsa Björkén, Philipp Weiss, Emil Lindgren</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
@@ -1410,7 +1410,7 @@
         <v>126891323</v>
       </c>
       <c r="B9" t="n">
-        <v>91348</v>
+        <v>91350</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1511,7 +1511,7 @@
         <v>126889513</v>
       </c>
       <c r="B10" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1609,10 +1609,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126893729</v>
+        <v>126889493</v>
       </c>
       <c r="B11" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1644,10 +1644,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>672603</v>
+        <v>672651</v>
       </c>
       <c r="R11" t="n">
-        <v>7057959</v>
+        <v>7057972</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1694,12 +1694,12 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Fredrik Wilde, Liam Sebestyén, Elke Blöhbaum, Miriam Schenk, Mattias Dalkvist, Emil Lindgren</t>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Fredrik Wilde, Alva Danielsson, Emil Lindgren, Mattias Dalkvist, Elke Blöhbaum, Miriam Schenk, Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
@@ -1710,10 +1710,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126889493</v>
+        <v>126893729</v>
       </c>
       <c r="B12" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1745,10 +1745,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>672651</v>
+        <v>672603</v>
       </c>
       <c r="R12" t="n">
-        <v>7057972</v>
+        <v>7057959</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1795,12 +1795,12 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Fredrik Wilde, Alva Danielsson, Emil Lindgren, Mattias Dalkvist, Elke Blöhbaum, Miriam Schenk, Vilhelm Kroon</t>
+          <t>Alva Danielsson, Fredrik Wilde, Liam Sebestyén, Elke Blöhbaum, Miriam Schenk, Mattias Dalkvist, Emil Lindgren</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
@@ -1811,10 +1811,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126889387</v>
+        <v>126892815</v>
       </c>
       <c r="B13" t="n">
-        <v>57658</v>
+        <v>79020</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1822,42 +1822,37 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Kravattensliden, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>672816</v>
+        <v>672633</v>
       </c>
       <c r="R13" t="n">
-        <v>7058123</v>
+        <v>7058033</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1884,9 +1879,19 @@
           <t>2025-07-24</t>
         </is>
       </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>11:52</t>
+        </is>
+      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-07-24</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1901,12 +1906,12 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon, Miriam Schenk, Elke Blöhbaum, Mattias Dalkvist, Emil Lindgren, Alva Danielsson, Fredrik Wilde, Liam Sebestyén, Cajsa Björkén, Philipp Weiss</t>
+          <t>Mattias Dalkvist, Fredrik Wilde, Liam Sebestyén, Alva Danielsson, Elke Blöhbaum, Vilhelm Kroon, Miriam Schenk, Cajsa Björkén, Philipp Weiss, Emil Lindgren</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
@@ -1917,10 +1922,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126892815</v>
+        <v>126889387</v>
       </c>
       <c r="B14" t="n">
-        <v>79018</v>
+        <v>57660</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1928,37 +1933,42 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Kravattensliden, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>672633</v>
+        <v>672816</v>
       </c>
       <c r="R14" t="n">
-        <v>7058033</v>
+        <v>7058123</v>
       </c>
       <c r="S14" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -1985,19 +1995,9 @@
           <t>2025-07-24</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>11:52</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-07-24</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>11:52</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2012,12 +2012,12 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist, Fredrik Wilde, Liam Sebestyén, Alva Danielsson, Elke Blöhbaum, Vilhelm Kroon, Miriam Schenk, Cajsa Björkén, Philipp Weiss, Emil Lindgren</t>
+          <t>Vilhelm Kroon, Miriam Schenk, Elke Blöhbaum, Mattias Dalkvist, Emil Lindgren, Alva Danielsson, Fredrik Wilde, Liam Sebestyén, Cajsa Björkén, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
@@ -2028,32 +2028,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126889492</v>
+        <v>126889835</v>
       </c>
       <c r="B15" t="n">
-        <v>79018</v>
+        <v>91297</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2063,10 +2063,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>672638</v>
+        <v>672843</v>
       </c>
       <c r="R15" t="n">
-        <v>7057953</v>
+        <v>7058124</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2113,12 +2113,12 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Fredrik Wilde, Alva Danielsson, Emil Lindgren, Mattias Dalkvist, Elke Blöhbaum, Miriam Schenk, Vilhelm Kroon</t>
+          <t>Liam Sebestyén, Philipp Weiss, Miriam Schenk, Cajsa Björkén, Fredrik Wilde, Alva Danielsson, Elke Blöhbaum, Vilhelm Kroon, Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
@@ -2129,32 +2129,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>126889835</v>
+        <v>126889492</v>
       </c>
       <c r="B16" t="n">
-        <v>91295</v>
+        <v>79020</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2164,10 +2164,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>672843</v>
+        <v>672638</v>
       </c>
       <c r="R16" t="n">
-        <v>7058124</v>
+        <v>7057953</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2214,12 +2214,12 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Philipp Weiss, Miriam Schenk, Cajsa Björkén, Fredrik Wilde, Alva Danielsson, Elke Blöhbaum, Vilhelm Kroon, Mattias Dalkvist</t>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Fredrik Wilde, Alva Danielsson, Emil Lindgren, Mattias Dalkvist, Elke Blöhbaum, Miriam Schenk, Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
@@ -2233,7 +2233,7 @@
         <v>126891315</v>
       </c>
       <c r="B17" t="n">
-        <v>98469</v>
+        <v>98471</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2334,7 +2334,7 @@
         <v>126891131</v>
       </c>
       <c r="B18" t="n">
-        <v>79050</v>
+        <v>79052</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2436,7 +2436,7 @@
         <v>126892810</v>
       </c>
       <c r="B19" t="n">
-        <v>91295</v>
+        <v>91297</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2547,7 +2547,7 @@
         <v>126892808</v>
       </c>
       <c r="B20" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2655,10 +2655,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>126889311</v>
+        <v>126889370</v>
       </c>
       <c r="B21" t="n">
-        <v>91295</v>
+        <v>4773</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2666,34 +2666,39 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5447</v>
+        <v>100299</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Kravattensliden, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>672799</v>
+        <v>672839</v>
       </c>
       <c r="R21" t="n">
-        <v>7058086</v>
+        <v>7058141</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2745,7 +2750,7 @@
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Fredrik Wilde, Alva Danielsson, Emil Lindgren, Mattias Dalkvist, Elke Blöhbaum, Miriam Schenk, Vilhelm Kroon</t>
+          <t>Vilhelm Kroon, Miriam Schenk, Elke Blöhbaum, Mattias Dalkvist, Emil Lindgren, Alva Danielsson, Fredrik Wilde, Liam Sebestyén, Cajsa Björkén, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
@@ -2759,7 +2764,7 @@
         <v>126889869</v>
       </c>
       <c r="B22" t="n">
-        <v>98365</v>
+        <v>98367</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2846,7 +2851,7 @@
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Philipp Weiss, Miriam Schenk, Cajsa Björkén, Fredrik Wilde, Alva Danielsson, Elke Blöhbaum, Vilhelm Kroon, Mattias Dalkvist</t>
+          <t>Liam Sebestyén, Mattias Dalkvist, Vilhelm Kroon, Elke Blöhbaum, Alva Danielsson, Fredrik Wilde, Cajsa Björkén, Miriam Schenk, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
@@ -2860,7 +2865,7 @@
         <v>126889374</v>
       </c>
       <c r="B23" t="n">
-        <v>98469</v>
+        <v>98471</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2961,7 +2966,7 @@
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Fredrik Wilde, Alva Danielsson, Emil Lindgren, Mattias Dalkvist, Elke Blöhbaum, Miriam Schenk, Vilhelm Kroon</t>
+          <t>Vilhelm Kroon, Miriam Schenk, Elke Blöhbaum, Mattias Dalkvist, Emil Lindgren, Alva Danielsson, Fredrik Wilde, Liam Sebestyén, Cajsa Björkén, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">
@@ -2972,10 +2977,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>126891314</v>
+        <v>126889311</v>
       </c>
       <c r="B24" t="n">
-        <v>80150</v>
+        <v>91297</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2983,21 +2988,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6462</v>
+        <v>5447</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3007,10 +3012,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>672999</v>
+        <v>672799</v>
       </c>
       <c r="R24" t="n">
-        <v>7058211</v>
+        <v>7058086</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3057,12 +3062,12 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Liam Sebestyén, Mattias Dalkvist, Miriam Schenk, Fredrik Wilde, Elke Blöhbaum, Emil Lindgren</t>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Fredrik Wilde, Alva Danielsson, Emil Lindgren, Mattias Dalkvist, Elke Blöhbaum, Miriam Schenk, Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr">
@@ -3073,10 +3078,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>126889370</v>
+        <v>126891314</v>
       </c>
       <c r="B25" t="n">
-        <v>4773</v>
+        <v>80152</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3084,39 +3089,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100299</v>
+        <v>6462</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Kravattensliden, Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>672839</v>
+        <v>672999</v>
       </c>
       <c r="R25" t="n">
-        <v>7058141</v>
+        <v>7058211</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3163,12 +3163,12 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon, Miriam Schenk, Elke Blöhbaum, Mattias Dalkvist, Emil Lindgren, Alva Danielsson, Fredrik Wilde, Liam Sebestyén, Cajsa Björkén, Philipp Weiss</t>
+          <t>Alva Danielsson, Liam Sebestyén, Mattias Dalkvist, Miriam Schenk, Fredrik Wilde, Elke Blöhbaum, Emil Lindgren</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr">
@@ -3179,32 +3179,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>126891313</v>
+        <v>126893730</v>
       </c>
       <c r="B26" t="n">
-        <v>80150</v>
+        <v>79020</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3214,10 +3214,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>672933</v>
+        <v>672929</v>
       </c>
       <c r="R26" t="n">
-        <v>7058201</v>
+        <v>7058213</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3269,7 +3269,7 @@
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Liam Sebestyén, Mattias Dalkvist, Miriam Schenk, Fredrik Wilde, Elke Blöhbaum, Emil Lindgren</t>
+          <t>Alva Danielsson, Fredrik Wilde, Liam Sebestyén, Elke Blöhbaum, Miriam Schenk, Mattias Dalkvist, Emil Lindgren</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr">
@@ -3280,10 +3280,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>126889847</v>
+        <v>126892816</v>
       </c>
       <c r="B27" t="n">
-        <v>57658</v>
+        <v>79020</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3291,45 +3291,37 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Kravattensliden, Ång</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>672981</v>
+        <v>672627</v>
       </c>
       <c r="R27" t="n">
-        <v>7058264</v>
+        <v>7058024</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3356,9 +3348,19 @@
           <t>2025-07-24</t>
         </is>
       </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>11:52</t>
+        </is>
+      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-07-24</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3373,12 +3375,12 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Philipp Weiss, Miriam Schenk, Cajsa Björkén, Fredrik Wilde, Alva Danielsson, Elke Blöhbaum, Vilhelm Kroon, Mattias Dalkvist</t>
+          <t>Mattias Dalkvist, Fredrik Wilde, Liam Sebestyén, Alva Danielsson, Elke Blöhbaum, Vilhelm Kroon, Miriam Schenk, Cajsa Björkén, Philipp Weiss, Emil Lindgren</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr">
@@ -3389,10 +3391,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>126893730</v>
+        <v>126889502</v>
       </c>
       <c r="B28" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3424,10 +3426,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>672929</v>
+        <v>672801</v>
       </c>
       <c r="R28" t="n">
-        <v>7058213</v>
+        <v>7058095</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3474,12 +3476,12 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Fredrik Wilde, Liam Sebestyén, Elke Blöhbaum, Miriam Schenk, Mattias Dalkvist, Emil Lindgren</t>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Fredrik Wilde, Alva Danielsson, Emil Lindgren, Mattias Dalkvist, Elke Blöhbaum, Miriam Schenk, Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr">
@@ -3490,32 +3492,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>126892816</v>
+        <v>126891313</v>
       </c>
       <c r="B29" t="n">
-        <v>79018</v>
+        <v>80152</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3525,13 +3527,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>672627</v>
+        <v>672933</v>
       </c>
       <c r="R29" t="n">
-        <v>7058024</v>
+        <v>7058201</v>
       </c>
       <c r="S29" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3558,19 +3560,9 @@
           <t>2025-07-24</t>
         </is>
       </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>11:52</t>
-        </is>
-      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-07-24</t>
-        </is>
-      </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>11:52</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3585,12 +3577,12 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist, Fredrik Wilde, Liam Sebestyén, Alva Danielsson, Elke Blöhbaum, Vilhelm Kroon, Miriam Schenk, Cajsa Björkén, Philipp Weiss, Emil Lindgren</t>
+          <t>Alva Danielsson, Liam Sebestyén, Mattias Dalkvist, Miriam Schenk, Fredrik Wilde, Elke Blöhbaum, Emil Lindgren</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr">
@@ -3601,10 +3593,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>126889502</v>
+        <v>126889847</v>
       </c>
       <c r="B30" t="n">
-        <v>79018</v>
+        <v>57660</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3612,34 +3604,42 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Kravattensliden, Ång</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>672801</v>
+        <v>672981</v>
       </c>
       <c r="R30" t="n">
-        <v>7058095</v>
+        <v>7058264</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3686,12 +3686,12 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Fredrik Wilde, Alva Danielsson, Emil Lindgren, Mattias Dalkvist, Elke Blöhbaum, Miriam Schenk, Vilhelm Kroon</t>
+          <t>Liam Sebestyén, Mattias Dalkvist, Vilhelm Kroon, Elke Blöhbaum, Alva Danielsson, Fredrik Wilde, Cajsa Björkén, Miriam Schenk, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr">
@@ -3702,59 +3702,45 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>126889377</v>
+        <v>126891328</v>
       </c>
       <c r="B31" t="n">
-        <v>98469</v>
+        <v>79020</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>221952</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Kravattensliden, Ång</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>672810</v>
+        <v>672972</v>
       </c>
       <c r="R31" t="n">
-        <v>7058105</v>
+        <v>7058246</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3801,12 +3787,12 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon, Miriam Schenk, Elke Blöhbaum, Mattias Dalkvist, Emil Lindgren, Alva Danielsson, Fredrik Wilde, Liam Sebestyén, Cajsa Björkén, Philipp Weiss</t>
+          <t>Alva Danielsson, Liam Sebestyén, Mattias Dalkvist, Miriam Schenk, Fredrik Wilde, Elke Blöhbaum, Emil Lindgren</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr">
@@ -3817,45 +3803,50 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>126891328</v>
+        <v>126889536</v>
       </c>
       <c r="B32" t="n">
-        <v>79018</v>
+        <v>5177</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>100526</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Kravattensliden, Ång</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>672972</v>
+        <v>672659</v>
       </c>
       <c r="R32" t="n">
-        <v>7058246</v>
+        <v>7057975</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3902,12 +3893,12 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Liam Sebestyén, Mattias Dalkvist, Miriam Schenk, Fredrik Wilde, Elke Blöhbaum, Emil Lindgren</t>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Fredrik Wilde, Alva Danielsson, Emil Lindgren, Mattias Dalkvist, Elke Blöhbaum, Miriam Schenk, Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr">
@@ -3918,10 +3909,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>126889536</v>
+        <v>126889377</v>
       </c>
       <c r="B33" t="n">
-        <v>5177</v>
+        <v>98471</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3929,27 +3920,36 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100526</v>
+        <v>221952</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
@@ -3958,10 +3958,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>672659</v>
+        <v>672810</v>
       </c>
       <c r="R33" t="n">
-        <v>7057975</v>
+        <v>7058105</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4013,7 +4013,7 @@
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Fredrik Wilde, Alva Danielsson, Emil Lindgren, Mattias Dalkvist, Elke Blöhbaum, Miriam Schenk, Vilhelm Kroon</t>
+          <t>Vilhelm Kroon, Miriam Schenk, Elke Blöhbaum, Mattias Dalkvist, Emil Lindgren, Alva Danielsson, Fredrik Wilde, Liam Sebestyén, Cajsa Björkén, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr">
@@ -4024,10 +4024,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>126891134</v>
+        <v>126889834</v>
       </c>
       <c r="B34" t="n">
-        <v>80150</v>
+        <v>91297</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4035,21 +4035,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6462</v>
+        <v>5447</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4059,13 +4059,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>673029</v>
+        <v>672819</v>
       </c>
       <c r="R34" t="n">
-        <v>7058247</v>
+        <v>7058089</v>
       </c>
       <c r="S34" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4109,12 +4109,12 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Miriam Schenk</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Miriam Schenk, Cajsa Björkén, Fredrik Wilde, Philipp Weiss, Mattias Dalkvist, Vilhelm Kroon, Liam Sebestyén, Emil Lindgren, Alva Danielsson</t>
+          <t>Liam Sebestyén, Philipp Weiss, Miriam Schenk, Cajsa Björkén, Fredrik Wilde, Alva Danielsson, Elke Blöhbaum, Vilhelm Kroon, Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr">
@@ -4125,45 +4125,52 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>126889834</v>
+        <v>126893692</v>
       </c>
       <c r="B35" t="n">
-        <v>91295</v>
+        <v>91332</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Kravattensliden, Ång</t>
+          <t>Kravattensliden , Ång</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>672819</v>
+        <v>672811</v>
       </c>
       <c r="R35" t="n">
-        <v>7058089</v>
+        <v>7058091</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4204,18 +4211,19 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
+      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Emil Lindgren</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Philipp Weiss, Miriam Schenk, Cajsa Björkén, Fredrik Wilde, Alva Danielsson, Elke Blöhbaum, Vilhelm Kroon, Mattias Dalkvist</t>
+          <t>Emil Lindgren</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr">
@@ -4226,55 +4234,48 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>126893692</v>
+        <v>126891134</v>
       </c>
       <c r="B36" t="n">
-        <v>91330</v>
+        <v>80152</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1202</v>
+        <v>6462</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Kravattensliden , Ång</t>
+          <t>Kravattensliden, Ång</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>672811</v>
+        <v>673029</v>
       </c>
       <c r="R36" t="n">
-        <v>7058091</v>
+        <v>7058247</v>
       </c>
       <c r="S36" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4312,19 +4313,18 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
-      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Emil Lindgren</t>
+          <t>Miriam Schenk</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Emil Lindgren</t>
+          <t>Miriam Schenk, Cajsa Björkén, Fredrik Wilde, Philipp Weiss, Mattias Dalkvist, Vilhelm Kroon, Liam Sebestyén, Emil Lindgren, Alva Danielsson</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr">
@@ -4338,7 +4338,7 @@
         <v>126892814</v>
       </c>
       <c r="B37" t="n">
-        <v>79050</v>
+        <v>79052</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4446,10 +4446,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>126891320</v>
+        <v>126892813</v>
       </c>
       <c r="B38" t="n">
-        <v>80121</v>
+        <v>79020</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4457,21 +4457,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4481,13 +4481,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>672929</v>
+        <v>672661</v>
       </c>
       <c r="R38" t="n">
-        <v>7058203</v>
+        <v>7058026</v>
       </c>
       <c r="S38" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4514,9 +4514,19 @@
           <t>2025-07-24</t>
         </is>
       </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>11:51</t>
+        </is>
+      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-07-24</t>
+        </is>
+      </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4531,12 +4541,12 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Liam Sebestyén, Mattias Dalkvist, Miriam Schenk, Fredrik Wilde, Elke Blöhbaum, Emil Lindgren</t>
+          <t>Mattias Dalkvist, Fredrik Wilde, Liam Sebestyén, Alva Danielsson, Elke Blöhbaum, Vilhelm Kroon, Miriam Schenk, Cajsa Björkén, Philipp Weiss, Emil Lindgren</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr">
@@ -4550,7 +4560,7 @@
         <v>126890308</v>
       </c>
       <c r="B39" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4648,10 +4658,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>126892813</v>
+        <v>126891320</v>
       </c>
       <c r="B40" t="n">
-        <v>79018</v>
+        <v>80123</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4659,21 +4669,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4683,13 +4693,13 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>672661</v>
+        <v>672929</v>
       </c>
       <c r="R40" t="n">
-        <v>7058026</v>
+        <v>7058203</v>
       </c>
       <c r="S40" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4716,19 +4726,9 @@
           <t>2025-07-24</t>
         </is>
       </c>
-      <c r="Z40" t="inlineStr">
-        <is>
-          <t>11:51</t>
-        </is>
-      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-07-24</t>
-        </is>
-      </c>
-      <c r="AB40" t="inlineStr">
-        <is>
-          <t>11:51</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4743,12 +4743,12 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist, Fredrik Wilde, Liam Sebestyén, Alva Danielsson, Elke Blöhbaum, Vilhelm Kroon, Miriam Schenk, Cajsa Björkén, Philipp Weiss, Emil Lindgren</t>
+          <t>Alva Danielsson, Liam Sebestyén, Mattias Dalkvist, Miriam Schenk, Fredrik Wilde, Elke Blöhbaum, Emil Lindgren</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr">
@@ -4762,7 +4762,7 @@
         <v>126893847</v>
       </c>
       <c r="B41" t="n">
-        <v>80121</v>
+        <v>80123</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4867,7 +4867,7 @@
         <v>126880507</v>
       </c>
       <c r="B42" t="n">
-        <v>82859</v>
+        <v>82861</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4965,45 +4965,52 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>126891321</v>
+        <v>126893671</v>
       </c>
       <c r="B43" t="n">
-        <v>80121</v>
+        <v>91297</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6458</v>
+        <v>5447</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr"/>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Kravattensliden, Ång</t>
+          <t>Kravattensliden , Ång</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>673004</v>
+        <v>672808</v>
       </c>
       <c r="R43" t="n">
-        <v>7058209</v>
+        <v>7058090</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5044,18 +5051,19 @@
       <c r="AE43" t="b">
         <v>0</v>
       </c>
+      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Emil Lindgren</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Liam Sebestyén, Mattias Dalkvist, Miriam Schenk, Fredrik Wilde, Elke Blöhbaum, Emil Lindgren</t>
+          <t>Emil Lindgren</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr">
@@ -5066,55 +5074,48 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>126893671</v>
+        <v>126892804</v>
       </c>
       <c r="B44" t="n">
-        <v>91295</v>
+        <v>79020</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="J44" t="inlineStr"/>
-      <c r="K44" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Kravattensliden , Ång</t>
+          <t>Kravattensliden, Ång</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>672808</v>
+        <v>673003</v>
       </c>
       <c r="R44" t="n">
-        <v>7058090</v>
+        <v>7058280</v>
       </c>
       <c r="S44" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5141,30 +5142,39 @@
           <t>2025-07-24</t>
         </is>
       </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>10:49</t>
+        </is>
+      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-07-24</t>
         </is>
       </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>10:49</t>
+        </is>
+      </c>
       <c r="AD44" t="b">
         <v>0</v>
       </c>
       <c r="AE44" t="b">
         <v>0</v>
       </c>
-      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Emil Lindgren</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Emil Lindgren</t>
+          <t>Mattias Dalkvist, Fredrik Wilde, Liam Sebestyén, Alva Danielsson, Elke Blöhbaum, Vilhelm Kroon, Miriam Schenk, Cajsa Björkén, Philipp Weiss, Emil Lindgren</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr">
@@ -5175,10 +5185,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>126892804</v>
+        <v>126889506</v>
       </c>
       <c r="B45" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5210,13 +5220,13 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>673003</v>
+        <v>672889</v>
       </c>
       <c r="R45" t="n">
-        <v>7058280</v>
+        <v>7058145</v>
       </c>
       <c r="S45" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5243,19 +5253,9 @@
           <t>2025-07-24</t>
         </is>
       </c>
-      <c r="Z45" t="inlineStr">
-        <is>
-          <t>10:49</t>
-        </is>
-      </c>
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-07-24</t>
-        </is>
-      </c>
-      <c r="AB45" t="inlineStr">
-        <is>
-          <t>10:49</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5270,12 +5270,12 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist, Fredrik Wilde, Liam Sebestyén, Alva Danielsson, Elke Blöhbaum, Vilhelm Kroon, Miriam Schenk, Cajsa Björkén, Philipp Weiss, Emil Lindgren</t>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Fredrik Wilde, Alva Danielsson, Emil Lindgren, Mattias Dalkvist, Elke Blöhbaum, Miriam Schenk, Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr">
@@ -5286,10 +5286,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>126889506</v>
+        <v>126891321</v>
       </c>
       <c r="B46" t="n">
-        <v>79018</v>
+        <v>80123</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5297,21 +5297,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5321,10 +5321,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>672889</v>
+        <v>673004</v>
       </c>
       <c r="R46" t="n">
-        <v>7058145</v>
+        <v>7058209</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5371,12 +5371,12 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Fredrik Wilde, Alva Danielsson, Emil Lindgren, Mattias Dalkvist, Elke Blöhbaum, Miriam Schenk, Vilhelm Kroon</t>
+          <t>Alva Danielsson, Liam Sebestyén, Mattias Dalkvist, Miriam Schenk, Fredrik Wilde, Elke Blöhbaum, Emil Lindgren</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr">
@@ -5390,7 +5390,7 @@
         <v>126890311</v>
       </c>
       <c r="B47" t="n">
-        <v>88733</v>
+        <v>88735</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5491,7 +5491,7 @@
         <v>126890305</v>
       </c>
       <c r="B48" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5592,7 +5592,7 @@
         <v>126889494</v>
       </c>
       <c r="B49" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5693,7 +5693,7 @@
         <v>126889503</v>
       </c>
       <c r="B50" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5791,10 +5791,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>126889862</v>
+        <v>126879684</v>
       </c>
       <c r="B51" t="n">
-        <v>91348</v>
+        <v>79020</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5802,34 +5802,34 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Kravattensliden, Ång</t>
+          <t>Kravattensliden, Kravattensliden, Ång</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>672981</v>
+        <v>672895</v>
       </c>
       <c r="R51" t="n">
-        <v>7058264</v>
+        <v>7058223</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5876,12 +5876,12 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Fredrik Wilde</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Philipp Weiss, Miriam Schenk, Cajsa Björkén, Fredrik Wilde, Alva Danielsson, Elke Blöhbaum, Vilhelm Kroon, Mattias Dalkvist</t>
+          <t>Fredrik Wilde</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr">
@@ -5892,10 +5892,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>126879684</v>
+        <v>126891325</v>
       </c>
       <c r="B52" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5923,14 +5923,14 @@
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Kravattensliden, Kravattensliden, Ång</t>
+          <t>Kravattensliden, Ång</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>672895</v>
+        <v>672660</v>
       </c>
       <c r="R52" t="n">
-        <v>7058223</v>
+        <v>7057985</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5977,12 +5977,12 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Fredrik Wilde</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Fredrik Wilde</t>
+          <t>Alva Danielsson, Liam Sebestyén, Mattias Dalkvist, Miriam Schenk, Fredrik Wilde, Elke Blöhbaum, Emil Lindgren</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr">
@@ -5993,32 +5993,32 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>126889837</v>
+        <v>126889856</v>
       </c>
       <c r="B53" t="n">
-        <v>91295</v>
+        <v>80123</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>5447</v>
+        <v>6458</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6028,10 +6028,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>672912</v>
+        <v>672929</v>
       </c>
       <c r="R53" t="n">
-        <v>7058191</v>
+        <v>7058201</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6083,7 +6083,7 @@
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Philipp Weiss, Miriam Schenk, Cajsa Björkén, Fredrik Wilde, Alva Danielsson, Elke Blöhbaum, Vilhelm Kroon, Mattias Dalkvist</t>
+          <t>Liam Sebestyén, Mattias Dalkvist, Vilhelm Kroon, Elke Blöhbaum, Alva Danielsson, Fredrik Wilde, Cajsa Björkén, Miriam Schenk, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr">
@@ -6094,32 +6094,32 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>126891325</v>
+        <v>126893733</v>
       </c>
       <c r="B54" t="n">
-        <v>79018</v>
+        <v>98367</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>219790</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6129,10 +6129,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>672660</v>
+        <v>672989</v>
       </c>
       <c r="R54" t="n">
-        <v>7057985</v>
+        <v>7058233</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6184,7 +6184,7 @@
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Liam Sebestyén, Mattias Dalkvist, Miriam Schenk, Fredrik Wilde, Elke Blöhbaum, Emil Lindgren</t>
+          <t>Alva Danielsson, Fredrik Wilde, Emil Lindgren, Mattias Dalkvist, Miriam Schenk, Elke Blöhbaum, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr">
@@ -6195,32 +6195,32 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>126889856</v>
+        <v>126889837</v>
       </c>
       <c r="B55" t="n">
-        <v>80121</v>
+        <v>91297</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6458</v>
+        <v>5447</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6230,10 +6230,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>672929</v>
+        <v>672912</v>
       </c>
       <c r="R55" t="n">
-        <v>7058201</v>
+        <v>7058191</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6296,32 +6296,32 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>126893733</v>
+        <v>126889862</v>
       </c>
       <c r="B56" t="n">
-        <v>98365</v>
+        <v>91350</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>219790</v>
+        <v>5432</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6331,10 +6331,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>672989</v>
+        <v>672981</v>
       </c>
       <c r="R56" t="n">
-        <v>7058233</v>
+        <v>7058264</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6381,12 +6381,12 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Fredrik Wilde, Liam Sebestyén, Elke Blöhbaum, Miriam Schenk, Mattias Dalkvist, Emil Lindgren</t>
+          <t>Liam Sebestyén, Mattias Dalkvist, Vilhelm Kroon, Elke Blöhbaum, Alva Danielsson, Fredrik Wilde, Cajsa Björkén, Miriam Schenk, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr">
@@ -6400,7 +6400,7 @@
         <v>126879133</v>
       </c>
       <c r="B57" t="n">
-        <v>79050</v>
+        <v>79052</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6501,7 +6501,7 @@
         <v>126892806</v>
       </c>
       <c r="B58" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6612,7 +6612,7 @@
         <v>126889504</v>
       </c>
       <c r="B59" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6710,32 +6710,32 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>126892809</v>
+        <v>126890296</v>
       </c>
       <c r="B60" t="n">
-        <v>79018</v>
+        <v>80152</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6745,13 +6745,13 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>672831</v>
+        <v>673025</v>
       </c>
       <c r="R60" t="n">
-        <v>7058091</v>
+        <v>7058244</v>
       </c>
       <c r="S60" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -6778,19 +6778,9 @@
           <t>2025-07-24</t>
         </is>
       </c>
-      <c r="Z60" t="inlineStr">
-        <is>
-          <t>11:32</t>
-        </is>
-      </c>
       <c r="AA60" t="inlineStr">
         <is>
           <t>2025-07-24</t>
-        </is>
-      </c>
-      <c r="AB60" t="inlineStr">
-        <is>
-          <t>11:32</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6805,12 +6795,12 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist, Fredrik Wilde, Liam Sebestyén, Alva Danielsson, Elke Blöhbaum, Vilhelm Kroon, Miriam Schenk, Cajsa Björkén, Philipp Weiss, Emil Lindgren</t>
+          <t>Vilhelm Kroon, Cajsa Björkén, Fredrik Wilde, Mattias Dalkvist, Philipp Weiss, Miriam Schenk, Liam Sebestyén, Alva Danielsson, Emil Lindgren</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr">
@@ -6821,32 +6811,32 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>126890296</v>
+        <v>126892812</v>
       </c>
       <c r="B61" t="n">
-        <v>80150</v>
+        <v>79020</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6856,13 +6846,13 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>673025</v>
+        <v>672685</v>
       </c>
       <c r="R61" t="n">
-        <v>7058244</v>
+        <v>7058010</v>
       </c>
       <c r="S61" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -6889,9 +6879,19 @@
           <t>2025-07-24</t>
         </is>
       </c>
+      <c r="Z61" t="inlineStr">
+        <is>
+          <t>11:41</t>
+        </is>
+      </c>
       <c r="AA61" t="inlineStr">
         <is>
           <t>2025-07-24</t>
+        </is>
+      </c>
+      <c r="AB61" t="inlineStr">
+        <is>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -6906,12 +6906,12 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon, Cajsa Björkén, Fredrik Wilde, Mattias Dalkvist, Philipp Weiss, Miriam Schenk, Liam Sebestyén, Alva Danielsson, Emil Lindgren</t>
+          <t>Mattias Dalkvist, Fredrik Wilde, Liam Sebestyén, Alva Danielsson, Elke Blöhbaum, Vilhelm Kroon, Miriam Schenk, Cajsa Björkén, Philipp Weiss, Emil Lindgren</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr">
@@ -6922,10 +6922,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>126892812</v>
+        <v>126880199</v>
       </c>
       <c r="B62" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6951,19 +6951,24 @@
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Kravattensliden, Ång</t>
+          <t>Kravattensliden, Kravattensliden, Ång</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>672685</v>
+        <v>672894</v>
       </c>
       <c r="R62" t="n">
-        <v>7058010</v>
+        <v>7058198</v>
       </c>
       <c r="S62" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -6990,19 +6995,9 @@
           <t>2025-07-24</t>
         </is>
       </c>
-      <c r="Z62" t="inlineStr">
-        <is>
-          <t>11:41</t>
-        </is>
-      </c>
       <c r="AA62" t="inlineStr">
         <is>
           <t>2025-07-24</t>
-        </is>
-      </c>
-      <c r="AB62" t="inlineStr">
-        <is>
-          <t>11:41</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7017,12 +7012,12 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Fredrik Wilde</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist, Fredrik Wilde, Liam Sebestyén, Alva Danielsson, Elke Blöhbaum, Vilhelm Kroon, Miriam Schenk, Cajsa Björkén, Philipp Weiss, Emil Lindgren</t>
+          <t>Fredrik Wilde</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr">
@@ -7033,10 +7028,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>126880199</v>
+        <v>126892809</v>
       </c>
       <c r="B63" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7062,24 +7057,19 @@
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
-      <c r="K63" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Kravattensliden, Kravattensliden, Ång</t>
+          <t>Kravattensliden, Ång</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>672894</v>
+        <v>672831</v>
       </c>
       <c r="R63" t="n">
-        <v>7058198</v>
+        <v>7058091</v>
       </c>
       <c r="S63" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7106,9 +7096,19 @@
           <t>2025-07-24</t>
         </is>
       </c>
+      <c r="Z63" t="inlineStr">
+        <is>
+          <t>11:32</t>
+        </is>
+      </c>
       <c r="AA63" t="inlineStr">
         <is>
           <t>2025-07-24</t>
+        </is>
+      </c>
+      <c r="AB63" t="inlineStr">
+        <is>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7123,12 +7123,12 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Fredrik Wilde</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Fredrik Wilde</t>
+          <t>Mattias Dalkvist, Fredrik Wilde, Liam Sebestyén, Alva Danielsson, Elke Blöhbaum, Vilhelm Kroon, Miriam Schenk, Cajsa Björkén, Philipp Weiss, Emil Lindgren</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr">
@@ -7139,10 +7139,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>126889382</v>
+        <v>126879033</v>
       </c>
       <c r="B64" t="n">
-        <v>57658</v>
+        <v>79052</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7150,39 +7150,43 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>100049</v>
+        <v>185</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr"/>
-      <c r="M64" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Kravattensliden, Ång</t>
+          <t>Kravattensliden, Kravattensliden, Ång</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>672838</v>
+        <v>673046</v>
       </c>
       <c r="R64" t="n">
-        <v>7058134</v>
+        <v>7058286</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7229,12 +7233,12 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Fredrik Wilde</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon, Miriam Schenk, Elke Blöhbaum, Mattias Dalkvist, Emil Lindgren, Alva Danielsson, Fredrik Wilde, Liam Sebestyén, Cajsa Björkén, Philipp Weiss</t>
+          <t>Fredrik Wilde</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr">
@@ -7245,54 +7249,45 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>126879033</v>
+        <v>126891312</v>
       </c>
       <c r="B65" t="n">
-        <v>79050</v>
+        <v>91297</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>185</v>
+        <v>5447</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J65" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Kravattensliden, Kravattensliden, Ång</t>
+          <t>Kravattensliden, Ång</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>673046</v>
+        <v>673027</v>
       </c>
       <c r="R65" t="n">
-        <v>7058286</v>
+        <v>7058282</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7339,12 +7334,12 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Fredrik Wilde</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Fredrik Wilde</t>
+          <t>Alva Danielsson, Liam Sebestyén, Mattias Dalkvist, Miriam Schenk, Fredrik Wilde, Elke Blöhbaum, Emil Lindgren</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr">
@@ -7355,32 +7350,32 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>126880532</v>
+        <v>126879425</v>
       </c>
       <c r="B66" t="n">
-        <v>80150</v>
+        <v>79020</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7390,10 +7385,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>672863</v>
+        <v>672947</v>
       </c>
       <c r="R66" t="n">
-        <v>7058124</v>
+        <v>7058198</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7456,32 +7451,32 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>126879425</v>
+        <v>126880532</v>
       </c>
       <c r="B67" t="n">
-        <v>79018</v>
+        <v>80152</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7491,10 +7486,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>672947</v>
+        <v>672863</v>
       </c>
       <c r="R67" t="n">
-        <v>7058198</v>
+        <v>7058124</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7557,45 +7552,50 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>126891312</v>
+        <v>126889382</v>
       </c>
       <c r="B68" t="n">
-        <v>91295</v>
+        <v>57660</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>5447</v>
+        <v>100049</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P68" t="inlineStr">
         <is>
           <t>Kravattensliden, Ång</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>673027</v>
+        <v>672838</v>
       </c>
       <c r="R68" t="n">
-        <v>7058282</v>
+        <v>7058134</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7642,12 +7642,12 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Liam Sebestyén, Mattias Dalkvist, Miriam Schenk, Fredrik Wilde, Elke Blöhbaum, Emil Lindgren</t>
+          <t>Vilhelm Kroon, Miriam Schenk, Elke Blöhbaum, Mattias Dalkvist, Emil Lindgren, Alva Danielsson, Fredrik Wilde, Liam Sebestyén, Cajsa Björkén, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr">
@@ -7658,32 +7658,32 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>126890370</v>
+        <v>126890408</v>
       </c>
       <c r="B69" t="n">
-        <v>80150</v>
+        <v>79020</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7693,10 +7693,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>672554</v>
+        <v>672874</v>
       </c>
       <c r="R69" t="n">
-        <v>7058145</v>
+        <v>7058313</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7759,32 +7759,32 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>126890408</v>
+        <v>126890370</v>
       </c>
       <c r="B70" t="n">
-        <v>79018</v>
+        <v>80152</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7794,10 +7794,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>672874</v>
+        <v>672554</v>
       </c>
       <c r="R70" t="n">
-        <v>7058313</v>
+        <v>7058145</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7863,7 +7863,7 @@
         <v>126890401</v>
       </c>
       <c r="B71" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7964,7 +7964,7 @@
         <v>126890405</v>
       </c>
       <c r="B72" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8065,7 +8065,7 @@
         <v>126890409</v>
       </c>
       <c r="B73" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8163,10 +8163,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>126890387</v>
+        <v>126890407</v>
       </c>
       <c r="B74" t="n">
-        <v>80121</v>
+        <v>79020</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8174,21 +8174,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8198,10 +8198,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>672556</v>
+        <v>672859</v>
       </c>
       <c r="R74" t="n">
-        <v>7058143</v>
+        <v>7058290</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8264,10 +8264,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>126890407</v>
+        <v>126890387</v>
       </c>
       <c r="B75" t="n">
-        <v>79018</v>
+        <v>80123</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8275,21 +8275,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8299,10 +8299,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>672859</v>
+        <v>672556</v>
       </c>
       <c r="R75" t="n">
-        <v>7058290</v>
+        <v>7058143</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8368,7 +8368,7 @@
         <v>126890354</v>
       </c>
       <c r="B76" t="n">
-        <v>79050</v>
+        <v>79052</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8469,7 +8469,7 @@
         <v>126890404</v>
       </c>
       <c r="B77" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8570,7 +8570,7 @@
         <v>126890353</v>
       </c>
       <c r="B78" t="n">
-        <v>79050</v>
+        <v>79052</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8671,7 +8671,7 @@
         <v>126890349</v>
       </c>
       <c r="B79" t="n">
-        <v>79050</v>
+        <v>79052</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8772,7 +8772,7 @@
         <v>126890348</v>
       </c>
       <c r="B80" t="n">
-        <v>79050</v>
+        <v>79052</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8873,7 +8873,7 @@
         <v>126890351</v>
       </c>
       <c r="B81" t="n">
-        <v>79050</v>
+        <v>79052</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8974,7 +8974,7 @@
         <v>126890350</v>
       </c>
       <c r="B82" t="n">
-        <v>79050</v>
+        <v>79052</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9075,7 +9075,7 @@
         <v>126890416</v>
       </c>
       <c r="B83" t="n">
-        <v>80156</v>
+        <v>80158</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9176,7 +9176,7 @@
         <v>126890352</v>
       </c>
       <c r="B84" t="n">
-        <v>79050</v>
+        <v>79052</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9277,7 +9277,7 @@
         <v>126890403</v>
       </c>
       <c r="B85" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>

--- a/artfynd/A 27938-2023 artfynd.xlsx
+++ b/artfynd/A 27938-2023 artfynd.xlsx
@@ -7759,32 +7759,32 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>126890370</v>
+        <v>126890401</v>
       </c>
       <c r="B70" t="n">
-        <v>80152</v>
+        <v>79020</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7794,10 +7794,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>672554</v>
+        <v>672705</v>
       </c>
       <c r="R70" t="n">
-        <v>7058145</v>
+        <v>7058080</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7860,32 +7860,32 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>126890401</v>
+        <v>126890370</v>
       </c>
       <c r="B71" t="n">
-        <v>79020</v>
+        <v>80152</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7895,10 +7895,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>672705</v>
+        <v>672554</v>
       </c>
       <c r="R71" t="n">
-        <v>7058080</v>
+        <v>7058145</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8365,10 +8365,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>126890354</v>
+        <v>126890404</v>
       </c>
       <c r="B76" t="n">
-        <v>79052</v>
+        <v>79020</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8376,21 +8376,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8400,10 +8400,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>672891</v>
+        <v>672805</v>
       </c>
       <c r="R76" t="n">
-        <v>7058285</v>
+        <v>7058312</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8466,10 +8466,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>126890404</v>
+        <v>126890354</v>
       </c>
       <c r="B77" t="n">
-        <v>79020</v>
+        <v>79052</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8477,21 +8477,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8501,10 +8501,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>672805</v>
+        <v>672891</v>
       </c>
       <c r="R77" t="n">
-        <v>7058312</v>
+        <v>7058285</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -9173,10 +9173,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>126890352</v>
+        <v>126890403</v>
       </c>
       <c r="B84" t="n">
-        <v>79052</v>
+        <v>79020</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9184,21 +9184,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9208,10 +9208,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>672847</v>
+        <v>672796</v>
       </c>
       <c r="R84" t="n">
-        <v>7058276</v>
+        <v>7058317</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9274,10 +9274,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>126890403</v>
+        <v>126890352</v>
       </c>
       <c r="B85" t="n">
-        <v>79020</v>
+        <v>79052</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9285,21 +9285,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9309,10 +9309,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>672796</v>
+        <v>672847</v>
       </c>
       <c r="R85" t="n">
-        <v>7058317</v>
+        <v>7058276</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>

--- a/artfynd/A 27938-2023 artfynd.xlsx
+++ b/artfynd/A 27938-2023 artfynd.xlsx
@@ -7658,7 +7658,7 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>126890408</v>
+        <v>126890401</v>
       </c>
       <c r="B69" t="n">
         <v>79020</v>
@@ -7693,10 +7693,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>672874</v>
+        <v>672705</v>
       </c>
       <c r="R69" t="n">
-        <v>7058313</v>
+        <v>7058080</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7759,7 +7759,7 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>126890401</v>
+        <v>126890408</v>
       </c>
       <c r="B70" t="n">
         <v>79020</v>
@@ -7794,10 +7794,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>672705</v>
+        <v>672874</v>
       </c>
       <c r="R70" t="n">
-        <v>7058080</v>
+        <v>7058313</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>

--- a/artfynd/A 27938-2023 artfynd.xlsx
+++ b/artfynd/A 27938-2023 artfynd.xlsx
@@ -7658,32 +7658,32 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>126890401</v>
+        <v>126890370</v>
       </c>
       <c r="B69" t="n">
-        <v>79020</v>
+        <v>80152</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7693,10 +7693,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>672705</v>
+        <v>672554</v>
       </c>
       <c r="R69" t="n">
-        <v>7058080</v>
+        <v>7058145</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7759,7 +7759,7 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>126890408</v>
+        <v>126890401</v>
       </c>
       <c r="B70" t="n">
         <v>79020</v>
@@ -7794,10 +7794,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>672874</v>
+        <v>672705</v>
       </c>
       <c r="R70" t="n">
-        <v>7058313</v>
+        <v>7058080</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7860,32 +7860,32 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>126890370</v>
+        <v>126890408</v>
       </c>
       <c r="B71" t="n">
-        <v>80152</v>
+        <v>79020</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7895,10 +7895,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>672554</v>
+        <v>672874</v>
       </c>
       <c r="R71" t="n">
-        <v>7058145</v>
+        <v>7058313</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8163,10 +8163,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>126890407</v>
+        <v>126890387</v>
       </c>
       <c r="B74" t="n">
-        <v>79020</v>
+        <v>80123</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8174,21 +8174,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8198,10 +8198,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>672859</v>
+        <v>672556</v>
       </c>
       <c r="R74" t="n">
-        <v>7058290</v>
+        <v>7058143</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8264,10 +8264,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>126890387</v>
+        <v>126890407</v>
       </c>
       <c r="B75" t="n">
-        <v>80123</v>
+        <v>79020</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8275,21 +8275,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8299,10 +8299,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>672556</v>
+        <v>672859</v>
       </c>
       <c r="R75" t="n">
-        <v>7058143</v>
+        <v>7058290</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8365,10 +8365,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>126890404</v>
+        <v>126890354</v>
       </c>
       <c r="B76" t="n">
-        <v>79020</v>
+        <v>79052</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8376,21 +8376,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8400,10 +8400,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>672805</v>
+        <v>672891</v>
       </c>
       <c r="R76" t="n">
-        <v>7058312</v>
+        <v>7058285</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8466,10 +8466,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>126890354</v>
+        <v>126890404</v>
       </c>
       <c r="B77" t="n">
-        <v>79052</v>
+        <v>79020</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8477,21 +8477,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8501,10 +8501,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>672891</v>
+        <v>672805</v>
       </c>
       <c r="R77" t="n">
-        <v>7058285</v>
+        <v>7058312</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -9173,10 +9173,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>126890403</v>
+        <v>126890352</v>
       </c>
       <c r="B84" t="n">
-        <v>79020</v>
+        <v>79052</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9184,21 +9184,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9208,10 +9208,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>672796</v>
+        <v>672847</v>
       </c>
       <c r="R84" t="n">
-        <v>7058317</v>
+        <v>7058276</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9274,10 +9274,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>126890352</v>
+        <v>126890403</v>
       </c>
       <c r="B85" t="n">
-        <v>79052</v>
+        <v>79020</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9285,21 +9285,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9309,10 +9309,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>672847</v>
+        <v>672796</v>
       </c>
       <c r="R85" t="n">
-        <v>7058276</v>
+        <v>7058317</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>

--- a/artfynd/A 27938-2023 artfynd.xlsx
+++ b/artfynd/A 27938-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126879850</v>
       </c>
       <c r="B2" t="n">
-        <v>88735</v>
+        <v>88722</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>126889312</v>
       </c>
       <c r="B3" t="n">
-        <v>91297</v>
+        <v>91284</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -880,7 +880,7 @@
         <v>126889833</v>
       </c>
       <c r="B4" t="n">
-        <v>91297</v>
+        <v>91284</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -981,7 +981,7 @@
         <v>126889402</v>
       </c>
       <c r="B5" t="n">
-        <v>97327</v>
+        <v>97314</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1079,10 +1079,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126889505</v>
+        <v>126892811</v>
       </c>
       <c r="B6" t="n">
-        <v>79020</v>
+        <v>79043</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1090,21 +1090,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1114,13 +1114,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>672864</v>
+        <v>672792</v>
       </c>
       <c r="R6" t="n">
-        <v>7058181</v>
+        <v>7058076</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1147,9 +1147,19 @@
           <t>2025-07-24</t>
         </is>
       </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>11:35</t>
+        </is>
+      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-07-24</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1164,12 +1174,12 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Fredrik Wilde, Alva Danielsson, Emil Lindgren, Mattias Dalkvist, Elke Blöhbaum, Miriam Schenk, Vilhelm Kroon</t>
+          <t>Mattias Dalkvist, Fredrik Wilde, Liam Sebestyén, Alva Danielsson, Elke Blöhbaum, Vilhelm Kroon, Miriam Schenk, Cajsa Björkén, Philipp Weiss, Emil Lindgren</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
@@ -1180,10 +1190,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126892811</v>
+        <v>126889505</v>
       </c>
       <c r="B7" t="n">
-        <v>79052</v>
+        <v>79011</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1191,21 +1201,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1215,13 +1225,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>672792</v>
+        <v>672864</v>
       </c>
       <c r="R7" t="n">
-        <v>7058076</v>
+        <v>7058181</v>
       </c>
       <c r="S7" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1248,19 +1258,9 @@
           <t>2025-07-24</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>11:35</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-07-24</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>11:35</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1275,12 +1275,12 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist, Fredrik Wilde, Liam Sebestyén, Alva Danielsson, Elke Blöhbaum, Vilhelm Kroon, Miriam Schenk, Cajsa Björkén, Philipp Weiss, Emil Lindgren</t>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Fredrik Wilde, Alva Danielsson, Emil Lindgren, Mattias Dalkvist, Elke Blöhbaum, Miriam Schenk, Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
@@ -1294,7 +1294,7 @@
         <v>126892805</v>
       </c>
       <c r="B8" t="n">
-        <v>57663</v>
+        <v>57657</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1407,10 +1407,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126891323</v>
+        <v>126889513</v>
       </c>
       <c r="B9" t="n">
-        <v>91350</v>
+        <v>79011</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1418,21 +1418,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1442,10 +1442,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>672897</v>
+        <v>673038</v>
       </c>
       <c r="R9" t="n">
-        <v>7058210</v>
+        <v>7058279</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1492,12 +1492,12 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Liam Sebestyén, Mattias Dalkvist, Miriam Schenk, Fredrik Wilde, Elke Blöhbaum, Emil Lindgren</t>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Fredrik Wilde, Alva Danielsson, Emil Lindgren, Mattias Dalkvist, Elke Blöhbaum, Miriam Schenk, Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
@@ -1508,10 +1508,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126889513</v>
+        <v>126891323</v>
       </c>
       <c r="B10" t="n">
-        <v>79020</v>
+        <v>91337</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1519,21 +1519,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1543,10 +1543,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>673038</v>
+        <v>672897</v>
       </c>
       <c r="R10" t="n">
-        <v>7058279</v>
+        <v>7058210</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1593,12 +1593,12 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Fredrik Wilde, Alva Danielsson, Emil Lindgren, Mattias Dalkvist, Elke Blöhbaum, Miriam Schenk, Vilhelm Kroon</t>
+          <t>Alva Danielsson, Emil Lindgren, Elke Blöhbaum, Fredrik Wilde, Miriam Schenk, Mattias Dalkvist, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
@@ -1609,10 +1609,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126889493</v>
+        <v>126893729</v>
       </c>
       <c r="B11" t="n">
-        <v>79020</v>
+        <v>79011</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1644,10 +1644,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>672651</v>
+        <v>672603</v>
       </c>
       <c r="R11" t="n">
-        <v>7057972</v>
+        <v>7057959</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1694,12 +1694,12 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Fredrik Wilde, Alva Danielsson, Emil Lindgren, Mattias Dalkvist, Elke Blöhbaum, Miriam Schenk, Vilhelm Kroon</t>
+          <t>Alva Danielsson, Fredrik Wilde, Liam Sebestyén, Elke Blöhbaum, Miriam Schenk, Mattias Dalkvist, Emil Lindgren</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
@@ -1710,10 +1710,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126893729</v>
+        <v>126889493</v>
       </c>
       <c r="B12" t="n">
-        <v>79020</v>
+        <v>79011</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1745,10 +1745,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>672603</v>
+        <v>672651</v>
       </c>
       <c r="R12" t="n">
-        <v>7057959</v>
+        <v>7057972</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1795,12 +1795,12 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Fredrik Wilde, Liam Sebestyén, Elke Blöhbaum, Miriam Schenk, Mattias Dalkvist, Emil Lindgren</t>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Fredrik Wilde, Alva Danielsson, Emil Lindgren, Mattias Dalkvist, Elke Blöhbaum, Miriam Schenk, Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
@@ -1814,7 +1814,7 @@
         <v>126892815</v>
       </c>
       <c r="B13" t="n">
-        <v>79020</v>
+        <v>79011</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1925,7 +1925,7 @@
         <v>126889387</v>
       </c>
       <c r="B14" t="n">
-        <v>57660</v>
+        <v>57654</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2017,7 +2017,7 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon, Miriam Schenk, Elke Blöhbaum, Mattias Dalkvist, Emil Lindgren, Alva Danielsson, Fredrik Wilde, Liam Sebestyén, Cajsa Björkén, Philipp Weiss</t>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Fredrik Wilde, Alva Danielsson, Emil Lindgren, Mattias Dalkvist, Elke Blöhbaum, Miriam Schenk, Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
@@ -2028,32 +2028,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126889835</v>
+        <v>126889492</v>
       </c>
       <c r="B15" t="n">
-        <v>91297</v>
+        <v>79011</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2063,10 +2063,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>672843</v>
+        <v>672638</v>
       </c>
       <c r="R15" t="n">
-        <v>7058124</v>
+        <v>7057953</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2113,12 +2113,12 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Philipp Weiss, Miriam Schenk, Cajsa Björkén, Fredrik Wilde, Alva Danielsson, Elke Blöhbaum, Vilhelm Kroon, Mattias Dalkvist</t>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Fredrik Wilde, Alva Danielsson, Emil Lindgren, Mattias Dalkvist, Elke Blöhbaum, Miriam Schenk, Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
@@ -2129,32 +2129,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>126889492</v>
+        <v>126889835</v>
       </c>
       <c r="B16" t="n">
-        <v>79020</v>
+        <v>91284</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2164,10 +2164,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>672638</v>
+        <v>672843</v>
       </c>
       <c r="R16" t="n">
-        <v>7057953</v>
+        <v>7058124</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2214,12 +2214,12 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Fredrik Wilde, Alva Danielsson, Emil Lindgren, Mattias Dalkvist, Elke Blöhbaum, Miriam Schenk, Vilhelm Kroon</t>
+          <t>Liam Sebestyén, Philipp Weiss, Miriam Schenk, Cajsa Björkén, Fredrik Wilde, Alva Danielsson, Elke Blöhbaum, Vilhelm Kroon, Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
@@ -2233,7 +2233,7 @@
         <v>126891315</v>
       </c>
       <c r="B17" t="n">
-        <v>98471</v>
+        <v>98457</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2320,7 +2320,7 @@
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Liam Sebestyén, Mattias Dalkvist, Miriam Schenk, Fredrik Wilde, Elke Blöhbaum, Emil Lindgren</t>
+          <t>Alva Danielsson, Emil Lindgren, Elke Blöhbaum, Fredrik Wilde, Miriam Schenk, Mattias Dalkvist, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
@@ -2331,32 +2331,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>126891131</v>
+        <v>126892810</v>
       </c>
       <c r="B18" t="n">
-        <v>79052</v>
+        <v>91284</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>185</v>
+        <v>5447</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2366,13 +2366,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>672898</v>
+        <v>672801</v>
       </c>
       <c r="R18" t="n">
-        <v>7058209</v>
+        <v>7058081</v>
       </c>
       <c r="S18" t="n">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2399,30 +2399,39 @@
           <t>2025-07-24</t>
         </is>
       </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>11:35</t>
+        </is>
+      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-07-24</t>
         </is>
       </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>11:35</t>
+        </is>
+      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Miriam Schenk</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Miriam Schenk, Cajsa Björkén, Fredrik Wilde, Philipp Weiss, Mattias Dalkvist, Vilhelm Kroon, Liam Sebestyén, Emil Lindgren, Alva Danielsson</t>
+          <t>Mattias Dalkvist, Fredrik Wilde, Liam Sebestyén, Alva Danielsson, Elke Blöhbaum, Vilhelm Kroon, Miriam Schenk, Cajsa Björkén, Philipp Weiss, Emil Lindgren</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
@@ -2433,32 +2442,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>126892810</v>
+        <v>126891131</v>
       </c>
       <c r="B19" t="n">
-        <v>91297</v>
+        <v>79043</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5447</v>
+        <v>185</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2468,13 +2477,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>672801</v>
+        <v>672898</v>
       </c>
       <c r="R19" t="n">
-        <v>7058081</v>
+        <v>7058209</v>
       </c>
       <c r="S19" t="n">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2501,39 +2510,30 @@
           <t>2025-07-24</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>11:35</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-07-24</t>
         </is>
       </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>11:35</t>
-        </is>
-      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Miriam Schenk</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist, Fredrik Wilde, Liam Sebestyén, Alva Danielsson, Elke Blöhbaum, Vilhelm Kroon, Miriam Schenk, Cajsa Björkén, Philipp Weiss, Emil Lindgren</t>
+          <t>Miriam Schenk, Cajsa Björkén, Fredrik Wilde, Philipp Weiss, Mattias Dalkvist, Vilhelm Kroon, Liam Sebestyén, Emil Lindgren, Alva Danielsson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
@@ -2547,7 +2547,7 @@
         <v>126892808</v>
       </c>
       <c r="B20" t="n">
-        <v>79020</v>
+        <v>79011</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2655,10 +2655,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>126889370</v>
+        <v>126889374</v>
       </c>
       <c r="B21" t="n">
-        <v>4773</v>
+        <v>98457</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2666,27 +2666,36 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100299</v>
+        <v>221952</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -2695,10 +2704,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>672839</v>
+        <v>672898</v>
       </c>
       <c r="R21" t="n">
-        <v>7058141</v>
+        <v>7058146</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2750,7 +2759,7 @@
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon, Miriam Schenk, Elke Blöhbaum, Mattias Dalkvist, Emil Lindgren, Alva Danielsson, Fredrik Wilde, Liam Sebestyén, Cajsa Björkén, Philipp Weiss</t>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Fredrik Wilde, Alva Danielsson, Emil Lindgren, Mattias Dalkvist, Elke Blöhbaum, Miriam Schenk, Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
@@ -2764,7 +2773,7 @@
         <v>126889869</v>
       </c>
       <c r="B22" t="n">
-        <v>98367</v>
+        <v>98353</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2851,7 +2860,7 @@
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Mattias Dalkvist, Vilhelm Kroon, Elke Blöhbaum, Alva Danielsson, Fredrik Wilde, Cajsa Björkén, Miriam Schenk, Philipp Weiss</t>
+          <t>Liam Sebestyén, Philipp Weiss, Miriam Schenk, Cajsa Björkén, Fredrik Wilde, Alva Danielsson, Elke Blöhbaum, Vilhelm Kroon, Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
@@ -2862,10 +2871,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>126889374</v>
+        <v>126889311</v>
       </c>
       <c r="B23" t="n">
-        <v>98471</v>
+        <v>91284</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2873,48 +2882,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>221952</v>
+        <v>5447</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Kravattensliden, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>672898</v>
+        <v>672799</v>
       </c>
       <c r="R23" t="n">
-        <v>7058146</v>
+        <v>7058086</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2966,7 +2961,7 @@
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon, Miriam Schenk, Elke Blöhbaum, Mattias Dalkvist, Emil Lindgren, Alva Danielsson, Fredrik Wilde, Liam Sebestyén, Cajsa Björkén, Philipp Weiss</t>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Fredrik Wilde, Alva Danielsson, Emil Lindgren, Mattias Dalkvist, Elke Blöhbaum, Miriam Schenk, Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">
@@ -2977,10 +2972,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>126889311</v>
+        <v>126891314</v>
       </c>
       <c r="B24" t="n">
-        <v>91297</v>
+        <v>80143</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2988,21 +2983,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5447</v>
+        <v>6462</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3012,10 +3007,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>672799</v>
+        <v>672999</v>
       </c>
       <c r="R24" t="n">
-        <v>7058086</v>
+        <v>7058211</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3062,12 +3057,12 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Fredrik Wilde, Alva Danielsson, Emil Lindgren, Mattias Dalkvist, Elke Blöhbaum, Miriam Schenk, Vilhelm Kroon</t>
+          <t>Alva Danielsson, Emil Lindgren, Elke Blöhbaum, Fredrik Wilde, Miriam Schenk, Mattias Dalkvist, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr">
@@ -3078,10 +3073,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>126891314</v>
+        <v>126889370</v>
       </c>
       <c r="B25" t="n">
-        <v>80152</v>
+        <v>4772</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3089,34 +3084,39 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6462</v>
+        <v>100299</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Kravattensliden, Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>672999</v>
+        <v>672839</v>
       </c>
       <c r="R25" t="n">
-        <v>7058211</v>
+        <v>7058141</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3163,12 +3163,12 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Liam Sebestyén, Mattias Dalkvist, Miriam Schenk, Fredrik Wilde, Elke Blöhbaum, Emil Lindgren</t>
+          <t>Vilhelm Kroon, Miriam Schenk, Elke Blöhbaum, Mattias Dalkvist, Emil Lindgren, Alva Danielsson, Fredrik Wilde, Liam Sebestyén, Cajsa Björkén, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr">
@@ -3179,10 +3179,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>126893730</v>
+        <v>126889502</v>
       </c>
       <c r="B26" t="n">
-        <v>79020</v>
+        <v>79011</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3214,10 +3214,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>672929</v>
+        <v>672801</v>
       </c>
       <c r="R26" t="n">
-        <v>7058213</v>
+        <v>7058095</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3264,12 +3264,12 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Fredrik Wilde, Liam Sebestyén, Elke Blöhbaum, Miriam Schenk, Mattias Dalkvist, Emil Lindgren</t>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Fredrik Wilde, Alva Danielsson, Emil Lindgren, Mattias Dalkvist, Elke Blöhbaum, Miriam Schenk, Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr">
@@ -3280,32 +3280,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>126892816</v>
+        <v>126891313</v>
       </c>
       <c r="B27" t="n">
-        <v>79020</v>
+        <v>80143</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3315,13 +3315,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>672627</v>
+        <v>672933</v>
       </c>
       <c r="R27" t="n">
-        <v>7058024</v>
+        <v>7058201</v>
       </c>
       <c r="S27" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3348,19 +3348,9 @@
           <t>2025-07-24</t>
         </is>
       </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>11:52</t>
-        </is>
-      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-07-24</t>
-        </is>
-      </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>11:52</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3375,12 +3365,12 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist, Fredrik Wilde, Liam Sebestyén, Alva Danielsson, Elke Blöhbaum, Vilhelm Kroon, Miriam Schenk, Cajsa Björkén, Philipp Weiss, Emil Lindgren</t>
+          <t>Alva Danielsson, Emil Lindgren, Elke Blöhbaum, Fredrik Wilde, Miriam Schenk, Mattias Dalkvist, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr">
@@ -3391,10 +3381,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>126889502</v>
+        <v>126889847</v>
       </c>
       <c r="B28" t="n">
-        <v>79020</v>
+        <v>57654</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3402,34 +3392,42 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Kravattensliden, Ång</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>672801</v>
+        <v>672981</v>
       </c>
       <c r="R28" t="n">
-        <v>7058095</v>
+        <v>7058264</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3476,12 +3474,12 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Fredrik Wilde, Alva Danielsson, Emil Lindgren, Mattias Dalkvist, Elke Blöhbaum, Miriam Schenk, Vilhelm Kroon</t>
+          <t>Liam Sebestyén, Philipp Weiss, Miriam Schenk, Cajsa Björkén, Fredrik Wilde, Alva Danielsson, Elke Blöhbaum, Vilhelm Kroon, Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr">
@@ -3492,32 +3490,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>126891313</v>
+        <v>126892816</v>
       </c>
       <c r="B29" t="n">
-        <v>80152</v>
+        <v>79011</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3527,13 +3525,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>672933</v>
+        <v>672627</v>
       </c>
       <c r="R29" t="n">
-        <v>7058201</v>
+        <v>7058024</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3560,9 +3558,19 @@
           <t>2025-07-24</t>
         </is>
       </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>11:52</t>
+        </is>
+      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-07-24</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3577,12 +3585,12 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Liam Sebestyén, Mattias Dalkvist, Miriam Schenk, Fredrik Wilde, Elke Blöhbaum, Emil Lindgren</t>
+          <t>Mattias Dalkvist, Fredrik Wilde, Liam Sebestyén, Alva Danielsson, Elke Blöhbaum, Vilhelm Kroon, Miriam Schenk, Cajsa Björkén, Philipp Weiss, Emil Lindgren</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr">
@@ -3593,10 +3601,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>126889847</v>
+        <v>126893730</v>
       </c>
       <c r="B30" t="n">
-        <v>57660</v>
+        <v>79011</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3604,42 +3612,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Kravattensliden, Ång</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>672981</v>
+        <v>672929</v>
       </c>
       <c r="R30" t="n">
-        <v>7058264</v>
+        <v>7058213</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3686,12 +3686,12 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Mattias Dalkvist, Vilhelm Kroon, Elke Blöhbaum, Alva Danielsson, Fredrik Wilde, Cajsa Björkén, Miriam Schenk, Philipp Weiss</t>
+          <t>Alva Danielsson, Fredrik Wilde, Liam Sebestyén, Elke Blöhbaum, Miriam Schenk, Mattias Dalkvist, Emil Lindgren</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr">
@@ -3702,45 +3702,50 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>126891328</v>
+        <v>126889536</v>
       </c>
       <c r="B31" t="n">
-        <v>79020</v>
+        <v>5176</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>100526</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Kravattensliden, Ång</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>672972</v>
+        <v>672659</v>
       </c>
       <c r="R31" t="n">
-        <v>7058246</v>
+        <v>7057975</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3787,12 +3792,12 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Liam Sebestyén, Mattias Dalkvist, Miriam Schenk, Fredrik Wilde, Elke Blöhbaum, Emil Lindgren</t>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Fredrik Wilde, Alva Danielsson, Emil Lindgren, Mattias Dalkvist, Elke Blöhbaum, Miriam Schenk, Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr">
@@ -3803,10 +3808,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>126889536</v>
+        <v>126889377</v>
       </c>
       <c r="B32" t="n">
-        <v>5177</v>
+        <v>98457</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3814,27 +3819,36 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100526</v>
+        <v>221952</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
@@ -3843,10 +3857,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>672659</v>
+        <v>672810</v>
       </c>
       <c r="R32" t="n">
-        <v>7057975</v>
+        <v>7058105</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3909,59 +3923,45 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>126889377</v>
+        <v>126891328</v>
       </c>
       <c r="B33" t="n">
-        <v>98471</v>
+        <v>79011</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>221952</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Kravattensliden, Ång</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>672810</v>
+        <v>672972</v>
       </c>
       <c r="R33" t="n">
-        <v>7058105</v>
+        <v>7058246</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4008,12 +4008,12 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon, Miriam Schenk, Elke Blöhbaum, Mattias Dalkvist, Emil Lindgren, Alva Danielsson, Fredrik Wilde, Liam Sebestyén, Cajsa Björkén, Philipp Weiss</t>
+          <t>Alva Danielsson, Emil Lindgren, Elke Blöhbaum, Fredrik Wilde, Miriam Schenk, Mattias Dalkvist, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr">
@@ -4024,45 +4024,52 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>126889834</v>
+        <v>126893692</v>
       </c>
       <c r="B34" t="n">
-        <v>91297</v>
+        <v>91319</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Kravattensliden, Ång</t>
+          <t>Kravattensliden , Ång</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>672819</v>
+        <v>672811</v>
       </c>
       <c r="R34" t="n">
-        <v>7058089</v>
+        <v>7058091</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4103,18 +4110,19 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
+      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Emil Lindgren</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Philipp Weiss, Miriam Schenk, Cajsa Björkén, Fredrik Wilde, Alva Danielsson, Elke Blöhbaum, Vilhelm Kroon, Mattias Dalkvist</t>
+          <t>Emil Lindgren</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr">
@@ -4125,52 +4133,45 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>126893692</v>
+        <v>126889834</v>
       </c>
       <c r="B35" t="n">
-        <v>91332</v>
+        <v>91284</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr"/>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Kravattensliden , Ång</t>
+          <t>Kravattensliden, Ång</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>672811</v>
+        <v>672819</v>
       </c>
       <c r="R35" t="n">
-        <v>7058091</v>
+        <v>7058089</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4211,19 +4212,18 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
-      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Emil Lindgren</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Emil Lindgren</t>
+          <t>Liam Sebestyén, Philipp Weiss, Miriam Schenk, Cajsa Björkén, Fredrik Wilde, Alva Danielsson, Elke Blöhbaum, Vilhelm Kroon, Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr">
@@ -4237,7 +4237,7 @@
         <v>126891134</v>
       </c>
       <c r="B36" t="n">
-        <v>80152</v>
+        <v>80143</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4338,7 +4338,7 @@
         <v>126892814</v>
       </c>
       <c r="B37" t="n">
-        <v>79052</v>
+        <v>79043</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4449,7 +4449,7 @@
         <v>126892813</v>
       </c>
       <c r="B38" t="n">
-        <v>79020</v>
+        <v>79011</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4560,7 +4560,7 @@
         <v>126890308</v>
       </c>
       <c r="B39" t="n">
-        <v>79020</v>
+        <v>79011</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4647,7 +4647,7 @@
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon, Cajsa Björkén, Fredrik Wilde, Mattias Dalkvist, Philipp Weiss, Miriam Schenk, Liam Sebestyén, Alva Danielsson, Emil Lindgren</t>
+          <t>Liam Sebestyén, Miriam Schenk, Philipp Weiss, Mattias Dalkvist, Fredrik Wilde, Cajsa Björkén, Vilhelm Kroon, Alva Danielsson, Emil Lindgren</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr">
@@ -4661,7 +4661,7 @@
         <v>126891320</v>
       </c>
       <c r="B40" t="n">
-        <v>80123</v>
+        <v>80114</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4748,7 +4748,7 @@
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Liam Sebestyén, Mattias Dalkvist, Miriam Schenk, Fredrik Wilde, Elke Blöhbaum, Emil Lindgren</t>
+          <t>Alva Danielsson, Emil Lindgren, Elke Blöhbaum, Fredrik Wilde, Miriam Schenk, Mattias Dalkvist, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr">
@@ -4762,7 +4762,7 @@
         <v>126893847</v>
       </c>
       <c r="B41" t="n">
-        <v>80123</v>
+        <v>80114</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4867,7 +4867,7 @@
         <v>126880507</v>
       </c>
       <c r="B42" t="n">
-        <v>82861</v>
+        <v>82852</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4965,55 +4965,48 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>126893671</v>
+        <v>126892804</v>
       </c>
       <c r="B43" t="n">
-        <v>91297</v>
+        <v>79011</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="J43" t="inlineStr"/>
-      <c r="K43" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Kravattensliden , Ång</t>
+          <t>Kravattensliden, Ång</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>672808</v>
+        <v>673003</v>
       </c>
       <c r="R43" t="n">
-        <v>7058090</v>
+        <v>7058280</v>
       </c>
       <c r="S43" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5040,30 +5033,39 @@
           <t>2025-07-24</t>
         </is>
       </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>10:49</t>
+        </is>
+      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-07-24</t>
         </is>
       </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>10:49</t>
+        </is>
+      </c>
       <c r="AD43" t="b">
         <v>0</v>
       </c>
       <c r="AE43" t="b">
         <v>0</v>
       </c>
-      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Emil Lindgren</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Emil Lindgren</t>
+          <t>Mattias Dalkvist, Fredrik Wilde, Liam Sebestyén, Alva Danielsson, Elke Blöhbaum, Vilhelm Kroon, Miriam Schenk, Cajsa Björkén, Philipp Weiss, Emil Lindgren</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr">
@@ -5074,10 +5076,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>126892804</v>
+        <v>126889506</v>
       </c>
       <c r="B44" t="n">
-        <v>79020</v>
+        <v>79011</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5109,13 +5111,13 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>673003</v>
+        <v>672889</v>
       </c>
       <c r="R44" t="n">
-        <v>7058280</v>
+        <v>7058145</v>
       </c>
       <c r="S44" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5142,19 +5144,9 @@
           <t>2025-07-24</t>
         </is>
       </c>
-      <c r="Z44" t="inlineStr">
-        <is>
-          <t>10:49</t>
-        </is>
-      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-07-24</t>
-        </is>
-      </c>
-      <c r="AB44" t="inlineStr">
-        <is>
-          <t>10:49</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5169,12 +5161,12 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist, Fredrik Wilde, Liam Sebestyén, Alva Danielsson, Elke Blöhbaum, Vilhelm Kroon, Miriam Schenk, Cajsa Björkén, Philipp Weiss, Emil Lindgren</t>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Fredrik Wilde, Alva Danielsson, Emil Lindgren, Mattias Dalkvist, Elke Blöhbaum, Miriam Schenk, Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr">
@@ -5185,45 +5177,52 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>126889506</v>
+        <v>126893671</v>
       </c>
       <c r="B45" t="n">
-        <v>79020</v>
+        <v>91284</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="J45" t="inlineStr"/>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Kravattensliden, Ång</t>
+          <t>Kravattensliden , Ång</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>672889</v>
+        <v>672808</v>
       </c>
       <c r="R45" t="n">
-        <v>7058145</v>
+        <v>7058090</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5264,18 +5263,19 @@
       <c r="AE45" t="b">
         <v>0</v>
       </c>
+      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Emil Lindgren</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Fredrik Wilde, Alva Danielsson, Emil Lindgren, Mattias Dalkvist, Elke Blöhbaum, Miriam Schenk, Vilhelm Kroon</t>
+          <t>Emil Lindgren</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr">
@@ -5289,7 +5289,7 @@
         <v>126891321</v>
       </c>
       <c r="B46" t="n">
-        <v>80123</v>
+        <v>80114</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5376,7 +5376,7 @@
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Liam Sebestyén, Mattias Dalkvist, Miriam Schenk, Fredrik Wilde, Elke Blöhbaum, Emil Lindgren</t>
+          <t>Alva Danielsson, Emil Lindgren, Elke Blöhbaum, Fredrik Wilde, Miriam Schenk, Mattias Dalkvist, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr">
@@ -5387,10 +5387,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>126890311</v>
+        <v>126890305</v>
       </c>
       <c r="B47" t="n">
-        <v>88735</v>
+        <v>79011</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5398,21 +5398,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>510</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5422,10 +5422,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>673023</v>
+        <v>672724</v>
       </c>
       <c r="R47" t="n">
-        <v>7058218</v>
+        <v>7058075</v>
       </c>
       <c r="S47" t="n">
         <v>15</v>
@@ -5477,7 +5477,7 @@
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon, Cajsa Björkén, Fredrik Wilde, Mattias Dalkvist, Philipp Weiss, Miriam Schenk, Liam Sebestyén, Alva Danielsson, Emil Lindgren</t>
+          <t>Liam Sebestyén, Miriam Schenk, Philipp Weiss, Mattias Dalkvist, Fredrik Wilde, Cajsa Björkén, Vilhelm Kroon, Alva Danielsson, Emil Lindgren</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr">
@@ -5488,10 +5488,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>126890305</v>
+        <v>126890311</v>
       </c>
       <c r="B48" t="n">
-        <v>79020</v>
+        <v>88722</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5499,21 +5499,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>510</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5523,10 +5523,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>672724</v>
+        <v>673023</v>
       </c>
       <c r="R48" t="n">
-        <v>7058075</v>
+        <v>7058218</v>
       </c>
       <c r="S48" t="n">
         <v>15</v>
@@ -5578,7 +5578,7 @@
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon, Cajsa Björkén, Fredrik Wilde, Mattias Dalkvist, Philipp Weiss, Miriam Schenk, Liam Sebestyén, Alva Danielsson, Emil Lindgren</t>
+          <t>Liam Sebestyén, Miriam Schenk, Philipp Weiss, Mattias Dalkvist, Fredrik Wilde, Cajsa Björkén, Vilhelm Kroon, Alva Danielsson, Emil Lindgren</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr">
@@ -5592,7 +5592,7 @@
         <v>126889494</v>
       </c>
       <c r="B49" t="n">
-        <v>79020</v>
+        <v>79011</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5693,7 +5693,7 @@
         <v>126889503</v>
       </c>
       <c r="B50" t="n">
-        <v>79020</v>
+        <v>79011</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5791,10 +5791,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>126879684</v>
+        <v>126889856</v>
       </c>
       <c r="B51" t="n">
-        <v>79020</v>
+        <v>80114</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5802,34 +5802,34 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Kravattensliden, Kravattensliden, Ång</t>
+          <t>Kravattensliden, Ång</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>672895</v>
+        <v>672929</v>
       </c>
       <c r="R51" t="n">
-        <v>7058223</v>
+        <v>7058201</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5876,12 +5876,12 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Fredrik Wilde</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Fredrik Wilde</t>
+          <t>Liam Sebestyén, Philipp Weiss, Miriam Schenk, Cajsa Björkén, Fredrik Wilde, Alva Danielsson, Elke Blöhbaum, Vilhelm Kroon, Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr">
@@ -5892,32 +5892,32 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>126891325</v>
+        <v>126889837</v>
       </c>
       <c r="B52" t="n">
-        <v>79020</v>
+        <v>91284</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5927,10 +5927,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>672660</v>
+        <v>672912</v>
       </c>
       <c r="R52" t="n">
-        <v>7057985</v>
+        <v>7058191</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5977,12 +5977,12 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Liam Sebestyén, Mattias Dalkvist, Miriam Schenk, Fredrik Wilde, Elke Blöhbaum, Emil Lindgren</t>
+          <t>Liam Sebestyén, Philipp Weiss, Miriam Schenk, Cajsa Björkén, Fredrik Wilde, Alva Danielsson, Elke Blöhbaum, Vilhelm Kroon, Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr">
@@ -5993,10 +5993,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>126889856</v>
+        <v>126889862</v>
       </c>
       <c r="B53" t="n">
-        <v>80123</v>
+        <v>91337</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6004,21 +6004,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6028,10 +6028,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>672929</v>
+        <v>672981</v>
       </c>
       <c r="R53" t="n">
-        <v>7058201</v>
+        <v>7058264</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6083,7 +6083,7 @@
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Mattias Dalkvist, Vilhelm Kroon, Elke Blöhbaum, Alva Danielsson, Fredrik Wilde, Cajsa Björkén, Miriam Schenk, Philipp Weiss</t>
+          <t>Liam Sebestyén, Philipp Weiss, Miriam Schenk, Cajsa Björkén, Fredrik Wilde, Alva Danielsson, Elke Blöhbaum, Vilhelm Kroon, Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr">
@@ -6094,45 +6094,45 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>126893733</v>
+        <v>126879684</v>
       </c>
       <c r="B54" t="n">
-        <v>98367</v>
+        <v>79011</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>219790</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Kravattensliden, Ång</t>
+          <t>Kravattensliden, Kravattensliden, Ång</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>672989</v>
+        <v>672895</v>
       </c>
       <c r="R54" t="n">
-        <v>7058233</v>
+        <v>7058223</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6179,12 +6179,12 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Fredrik Wilde</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Fredrik Wilde, Emil Lindgren, Mattias Dalkvist, Miriam Schenk, Elke Blöhbaum, Liam Sebestyén</t>
+          <t>Fredrik Wilde</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr">
@@ -6195,32 +6195,32 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>126889837</v>
+        <v>126891325</v>
       </c>
       <c r="B55" t="n">
-        <v>91297</v>
+        <v>79011</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6230,10 +6230,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>672912</v>
+        <v>672660</v>
       </c>
       <c r="R55" t="n">
-        <v>7058191</v>
+        <v>7057985</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6280,12 +6280,12 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Philipp Weiss, Miriam Schenk, Cajsa Björkén, Fredrik Wilde, Alva Danielsson, Elke Blöhbaum, Vilhelm Kroon, Mattias Dalkvist</t>
+          <t>Alva Danielsson, Emil Lindgren, Elke Blöhbaum, Fredrik Wilde, Miriam Schenk, Mattias Dalkvist, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr">
@@ -6296,32 +6296,32 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>126889862</v>
+        <v>126893733</v>
       </c>
       <c r="B56" t="n">
-        <v>91350</v>
+        <v>98353</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>5432</v>
+        <v>219790</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6331,10 +6331,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>672981</v>
+        <v>672989</v>
       </c>
       <c r="R56" t="n">
-        <v>7058264</v>
+        <v>7058233</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6381,12 +6381,12 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Mattias Dalkvist, Vilhelm Kroon, Elke Blöhbaum, Alva Danielsson, Fredrik Wilde, Cajsa Björkén, Miriam Schenk, Philipp Weiss</t>
+          <t>Alva Danielsson, Fredrik Wilde, Liam Sebestyén, Elke Blöhbaum, Miriam Schenk, Mattias Dalkvist, Emil Lindgren</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr">
@@ -6400,7 +6400,7 @@
         <v>126879133</v>
       </c>
       <c r="B57" t="n">
-        <v>79052</v>
+        <v>79043</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6501,7 +6501,7 @@
         <v>126892806</v>
       </c>
       <c r="B58" t="n">
-        <v>79020</v>
+        <v>79011</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6612,7 +6612,7 @@
         <v>126889504</v>
       </c>
       <c r="B59" t="n">
-        <v>79020</v>
+        <v>79011</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6710,32 +6710,32 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>126890296</v>
+        <v>126892812</v>
       </c>
       <c r="B60" t="n">
-        <v>80152</v>
+        <v>79011</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6745,13 +6745,13 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>673025</v>
+        <v>672685</v>
       </c>
       <c r="R60" t="n">
-        <v>7058244</v>
+        <v>7058010</v>
       </c>
       <c r="S60" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -6778,9 +6778,19 @@
           <t>2025-07-24</t>
         </is>
       </c>
+      <c r="Z60" t="inlineStr">
+        <is>
+          <t>11:41</t>
+        </is>
+      </c>
       <c r="AA60" t="inlineStr">
         <is>
           <t>2025-07-24</t>
+        </is>
+      </c>
+      <c r="AB60" t="inlineStr">
+        <is>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6795,12 +6805,12 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon, Cajsa Björkén, Fredrik Wilde, Mattias Dalkvist, Philipp Weiss, Miriam Schenk, Liam Sebestyén, Alva Danielsson, Emil Lindgren</t>
+          <t>Mattias Dalkvist, Fredrik Wilde, Liam Sebestyén, Alva Danielsson, Elke Blöhbaum, Vilhelm Kroon, Miriam Schenk, Cajsa Björkén, Philipp Weiss, Emil Lindgren</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr">
@@ -6811,10 +6821,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>126892812</v>
+        <v>126892809</v>
       </c>
       <c r="B61" t="n">
-        <v>79020</v>
+        <v>79011</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6846,13 +6856,13 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>672685</v>
+        <v>672831</v>
       </c>
       <c r="R61" t="n">
-        <v>7058010</v>
+        <v>7058091</v>
       </c>
       <c r="S61" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -6881,7 +6891,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -6891,7 +6901,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -6922,53 +6932,48 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>126880199</v>
+        <v>126890296</v>
       </c>
       <c r="B62" t="n">
-        <v>79020</v>
+        <v>80143</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
-      <c r="K62" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Kravattensliden, Kravattensliden, Ång</t>
+          <t>Kravattensliden, Ång</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>672894</v>
+        <v>673025</v>
       </c>
       <c r="R62" t="n">
-        <v>7058198</v>
+        <v>7058244</v>
       </c>
       <c r="S62" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7012,12 +7017,12 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Fredrik Wilde</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Fredrik Wilde</t>
+          <t>Vilhelm Kroon, Cajsa Björkén, Fredrik Wilde, Mattias Dalkvist, Philipp Weiss, Miriam Schenk, Liam Sebestyén, Alva Danielsson, Emil Lindgren</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr">
@@ -7028,10 +7033,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>126892809</v>
+        <v>126880199</v>
       </c>
       <c r="B63" t="n">
-        <v>79020</v>
+        <v>79011</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7057,19 +7062,24 @@
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Kravattensliden, Ång</t>
+          <t>Kravattensliden, Kravattensliden, Ång</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>672831</v>
+        <v>672894</v>
       </c>
       <c r="R63" t="n">
-        <v>7058091</v>
+        <v>7058198</v>
       </c>
       <c r="S63" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7096,19 +7106,9 @@
           <t>2025-07-24</t>
         </is>
       </c>
-      <c r="Z63" t="inlineStr">
-        <is>
-          <t>11:32</t>
-        </is>
-      </c>
       <c r="AA63" t="inlineStr">
         <is>
           <t>2025-07-24</t>
-        </is>
-      </c>
-      <c r="AB63" t="inlineStr">
-        <is>
-          <t>11:32</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7123,12 +7123,12 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Fredrik Wilde</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist, Fredrik Wilde, Liam Sebestyén, Alva Danielsson, Elke Blöhbaum, Vilhelm Kroon, Miriam Schenk, Cajsa Björkén, Philipp Weiss, Emil Lindgren</t>
+          <t>Fredrik Wilde</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr">
@@ -7142,7 +7142,7 @@
         <v>126879033</v>
       </c>
       <c r="B64" t="n">
-        <v>79052</v>
+        <v>79043</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7252,7 +7252,7 @@
         <v>126891312</v>
       </c>
       <c r="B65" t="n">
-        <v>91297</v>
+        <v>91284</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7339,7 +7339,7 @@
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Liam Sebestyén, Mattias Dalkvist, Miriam Schenk, Fredrik Wilde, Elke Blöhbaum, Emil Lindgren</t>
+          <t>Alva Danielsson, Emil Lindgren, Elke Blöhbaum, Fredrik Wilde, Miriam Schenk, Mattias Dalkvist, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr">
@@ -7353,7 +7353,7 @@
         <v>126879425</v>
       </c>
       <c r="B66" t="n">
-        <v>79020</v>
+        <v>79011</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7454,7 +7454,7 @@
         <v>126880532</v>
       </c>
       <c r="B67" t="n">
-        <v>80152</v>
+        <v>80143</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7555,7 +7555,7 @@
         <v>126889382</v>
       </c>
       <c r="B68" t="n">
-        <v>57660</v>
+        <v>57654</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7647,7 +7647,7 @@
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon, Miriam Schenk, Elke Blöhbaum, Mattias Dalkvist, Emil Lindgren, Alva Danielsson, Fredrik Wilde, Liam Sebestyén, Cajsa Björkén, Philipp Weiss</t>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Fredrik Wilde, Alva Danielsson, Emil Lindgren, Mattias Dalkvist, Elke Blöhbaum, Miriam Schenk, Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr">
@@ -7658,32 +7658,32 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>126890370</v>
+        <v>126890401</v>
       </c>
       <c r="B69" t="n">
-        <v>80152</v>
+        <v>79011</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7693,10 +7693,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>672554</v>
+        <v>672705</v>
       </c>
       <c r="R69" t="n">
-        <v>7058145</v>
+        <v>7058080</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7759,10 +7759,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>126890401</v>
+        <v>126890408</v>
       </c>
       <c r="B70" t="n">
-        <v>79020</v>
+        <v>79011</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7794,10 +7794,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>672705</v>
+        <v>672874</v>
       </c>
       <c r="R70" t="n">
-        <v>7058080</v>
+        <v>7058313</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7860,32 +7860,32 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>126890408</v>
+        <v>126890370</v>
       </c>
       <c r="B71" t="n">
-        <v>79020</v>
+        <v>80143</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7895,10 +7895,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>672874</v>
+        <v>672554</v>
       </c>
       <c r="R71" t="n">
-        <v>7058313</v>
+        <v>7058145</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7964,7 +7964,7 @@
         <v>126890405</v>
       </c>
       <c r="B72" t="n">
-        <v>79020</v>
+        <v>79011</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8065,7 +8065,7 @@
         <v>126890409</v>
       </c>
       <c r="B73" t="n">
-        <v>79020</v>
+        <v>79011</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8163,10 +8163,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>126890387</v>
+        <v>126890407</v>
       </c>
       <c r="B74" t="n">
-        <v>80123</v>
+        <v>79011</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8174,21 +8174,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8198,10 +8198,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>672556</v>
+        <v>672859</v>
       </c>
       <c r="R74" t="n">
-        <v>7058143</v>
+        <v>7058290</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8264,10 +8264,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>126890407</v>
+        <v>126890387</v>
       </c>
       <c r="B75" t="n">
-        <v>79020</v>
+        <v>80114</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8275,21 +8275,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8299,10 +8299,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>672859</v>
+        <v>672556</v>
       </c>
       <c r="R75" t="n">
-        <v>7058290</v>
+        <v>7058143</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8365,10 +8365,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>126890354</v>
+        <v>126890404</v>
       </c>
       <c r="B76" t="n">
-        <v>79052</v>
+        <v>79011</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8376,21 +8376,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8400,10 +8400,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>672891</v>
+        <v>672805</v>
       </c>
       <c r="R76" t="n">
-        <v>7058285</v>
+        <v>7058312</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8466,10 +8466,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>126890404</v>
+        <v>126890354</v>
       </c>
       <c r="B77" t="n">
-        <v>79020</v>
+        <v>79043</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8477,21 +8477,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8501,10 +8501,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>672805</v>
+        <v>672891</v>
       </c>
       <c r="R77" t="n">
-        <v>7058312</v>
+        <v>7058285</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8570,7 +8570,7 @@
         <v>126890353</v>
       </c>
       <c r="B78" t="n">
-        <v>79052</v>
+        <v>79043</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8671,7 +8671,7 @@
         <v>126890349</v>
       </c>
       <c r="B79" t="n">
-        <v>79052</v>
+        <v>79043</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8772,7 +8772,7 @@
         <v>126890348</v>
       </c>
       <c r="B80" t="n">
-        <v>79052</v>
+        <v>79043</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8873,7 +8873,7 @@
         <v>126890351</v>
       </c>
       <c r="B81" t="n">
-        <v>79052</v>
+        <v>79043</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8974,7 +8974,7 @@
         <v>126890350</v>
       </c>
       <c r="B82" t="n">
-        <v>79052</v>
+        <v>79043</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9075,7 +9075,7 @@
         <v>126890416</v>
       </c>
       <c r="B83" t="n">
-        <v>80158</v>
+        <v>80149</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9173,10 +9173,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>126890352</v>
+        <v>126890403</v>
       </c>
       <c r="B84" t="n">
-        <v>79052</v>
+        <v>79011</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9184,21 +9184,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9208,10 +9208,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>672847</v>
+        <v>672796</v>
       </c>
       <c r="R84" t="n">
-        <v>7058276</v>
+        <v>7058317</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9274,10 +9274,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>126890403</v>
+        <v>126890352</v>
       </c>
       <c r="B85" t="n">
-        <v>79020</v>
+        <v>79043</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9285,21 +9285,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9309,10 +9309,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>672796</v>
+        <v>672847</v>
       </c>
       <c r="R85" t="n">
-        <v>7058317</v>
+        <v>7058276</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>

--- a/artfynd/A 27938-2023 artfynd.xlsx
+++ b/artfynd/A 27938-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126879850</v>
       </c>
       <c r="B2" t="n">
-        <v>88722</v>
+        <v>88735</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>126889312</v>
       </c>
       <c r="B3" t="n">
-        <v>91284</v>
+        <v>91297</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -880,7 +880,7 @@
         <v>126889833</v>
       </c>
       <c r="B4" t="n">
-        <v>91284</v>
+        <v>91297</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -981,7 +981,7 @@
         <v>126889402</v>
       </c>
       <c r="B5" t="n">
-        <v>97314</v>
+        <v>97327</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1079,10 +1079,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126892811</v>
+        <v>126889505</v>
       </c>
       <c r="B6" t="n">
-        <v>79043</v>
+        <v>79020</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1090,21 +1090,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1114,13 +1114,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>672792</v>
+        <v>672864</v>
       </c>
       <c r="R6" t="n">
-        <v>7058076</v>
+        <v>7058181</v>
       </c>
       <c r="S6" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1147,19 +1147,9 @@
           <t>2025-07-24</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>11:35</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-07-24</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>11:35</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1174,12 +1164,12 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist, Fredrik Wilde, Liam Sebestyén, Alva Danielsson, Elke Blöhbaum, Vilhelm Kroon, Miriam Schenk, Cajsa Björkén, Philipp Weiss, Emil Lindgren</t>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Fredrik Wilde, Alva Danielsson, Emil Lindgren, Mattias Dalkvist, Elke Blöhbaum, Miriam Schenk, Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
@@ -1190,10 +1180,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126889505</v>
+        <v>126892811</v>
       </c>
       <c r="B7" t="n">
-        <v>79011</v>
+        <v>79052</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1201,21 +1191,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,13 +1215,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>672864</v>
+        <v>672792</v>
       </c>
       <c r="R7" t="n">
-        <v>7058181</v>
+        <v>7058076</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1258,9 +1248,19 @@
           <t>2025-07-24</t>
         </is>
       </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>11:35</t>
+        </is>
+      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-07-24</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1275,12 +1275,12 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Fredrik Wilde, Alva Danielsson, Emil Lindgren, Mattias Dalkvist, Elke Blöhbaum, Miriam Schenk, Vilhelm Kroon</t>
+          <t>Mattias Dalkvist, Fredrik Wilde, Liam Sebestyén, Alva Danielsson, Elke Blöhbaum, Vilhelm Kroon, Miriam Schenk, Cajsa Björkén, Philipp Weiss, Emil Lindgren</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
@@ -1294,7 +1294,7 @@
         <v>126892805</v>
       </c>
       <c r="B8" t="n">
-        <v>57657</v>
+        <v>57663</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1407,10 +1407,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126889513</v>
+        <v>126891323</v>
       </c>
       <c r="B9" t="n">
-        <v>79011</v>
+        <v>91350</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1418,21 +1418,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1442,10 +1442,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>673038</v>
+        <v>672897</v>
       </c>
       <c r="R9" t="n">
-        <v>7058279</v>
+        <v>7058210</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1492,12 +1492,12 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Fredrik Wilde, Alva Danielsson, Emil Lindgren, Mattias Dalkvist, Elke Blöhbaum, Miriam Schenk, Vilhelm Kroon</t>
+          <t>Alva Danielsson, Liam Sebestyén, Mattias Dalkvist, Miriam Schenk, Fredrik Wilde, Elke Blöhbaum, Emil Lindgren</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
@@ -1508,10 +1508,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126891323</v>
+        <v>126889513</v>
       </c>
       <c r="B10" t="n">
-        <v>91337</v>
+        <v>79020</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1519,21 +1519,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1543,10 +1543,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>672897</v>
+        <v>673038</v>
       </c>
       <c r="R10" t="n">
-        <v>7058210</v>
+        <v>7058279</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1593,12 +1593,12 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Emil Lindgren, Elke Blöhbaum, Fredrik Wilde, Miriam Schenk, Mattias Dalkvist, Liam Sebestyén</t>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Fredrik Wilde, Alva Danielsson, Emil Lindgren, Mattias Dalkvist, Elke Blöhbaum, Miriam Schenk, Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
@@ -1609,10 +1609,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126893729</v>
+        <v>126889493</v>
       </c>
       <c r="B11" t="n">
-        <v>79011</v>
+        <v>79020</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1644,10 +1644,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>672603</v>
+        <v>672651</v>
       </c>
       <c r="R11" t="n">
-        <v>7057959</v>
+        <v>7057972</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1694,12 +1694,12 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Fredrik Wilde, Liam Sebestyén, Elke Blöhbaum, Miriam Schenk, Mattias Dalkvist, Emil Lindgren</t>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Fredrik Wilde, Alva Danielsson, Emil Lindgren, Mattias Dalkvist, Elke Blöhbaum, Miriam Schenk, Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
@@ -1710,10 +1710,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126889493</v>
+        <v>126893729</v>
       </c>
       <c r="B12" t="n">
-        <v>79011</v>
+        <v>79020</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1745,10 +1745,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>672651</v>
+        <v>672603</v>
       </c>
       <c r="R12" t="n">
-        <v>7057972</v>
+        <v>7057959</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1795,12 +1795,12 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Fredrik Wilde, Alva Danielsson, Emil Lindgren, Mattias Dalkvist, Elke Blöhbaum, Miriam Schenk, Vilhelm Kroon</t>
+          <t>Alva Danielsson, Fredrik Wilde, Liam Sebestyén, Elke Blöhbaum, Miriam Schenk, Mattias Dalkvist, Emil Lindgren</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
@@ -1814,7 +1814,7 @@
         <v>126892815</v>
       </c>
       <c r="B13" t="n">
-        <v>79011</v>
+        <v>79020</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1925,7 +1925,7 @@
         <v>126889387</v>
       </c>
       <c r="B14" t="n">
-        <v>57654</v>
+        <v>57660</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2017,7 +2017,7 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Fredrik Wilde, Alva Danielsson, Emil Lindgren, Mattias Dalkvist, Elke Blöhbaum, Miriam Schenk, Vilhelm Kroon</t>
+          <t>Vilhelm Kroon, Miriam Schenk, Elke Blöhbaum, Mattias Dalkvist, Emil Lindgren, Alva Danielsson, Fredrik Wilde, Liam Sebestyén, Cajsa Björkén, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
@@ -2028,32 +2028,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126889492</v>
+        <v>126889835</v>
       </c>
       <c r="B15" t="n">
-        <v>79011</v>
+        <v>91297</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2063,10 +2063,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>672638</v>
+        <v>672843</v>
       </c>
       <c r="R15" t="n">
-        <v>7057953</v>
+        <v>7058124</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2113,12 +2113,12 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Fredrik Wilde, Alva Danielsson, Emil Lindgren, Mattias Dalkvist, Elke Blöhbaum, Miriam Schenk, Vilhelm Kroon</t>
+          <t>Liam Sebestyén, Philipp Weiss, Miriam Schenk, Cajsa Björkén, Fredrik Wilde, Alva Danielsson, Elke Blöhbaum, Vilhelm Kroon, Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
@@ -2129,32 +2129,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>126889835</v>
+        <v>126889492</v>
       </c>
       <c r="B16" t="n">
-        <v>91284</v>
+        <v>79020</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2164,10 +2164,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>672843</v>
+        <v>672638</v>
       </c>
       <c r="R16" t="n">
-        <v>7058124</v>
+        <v>7057953</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2214,12 +2214,12 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Philipp Weiss, Miriam Schenk, Cajsa Björkén, Fredrik Wilde, Alva Danielsson, Elke Blöhbaum, Vilhelm Kroon, Mattias Dalkvist</t>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Fredrik Wilde, Alva Danielsson, Emil Lindgren, Mattias Dalkvist, Elke Blöhbaum, Miriam Schenk, Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
@@ -2233,7 +2233,7 @@
         <v>126891315</v>
       </c>
       <c r="B17" t="n">
-        <v>98457</v>
+        <v>98471</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2320,7 +2320,7 @@
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Emil Lindgren, Elke Blöhbaum, Fredrik Wilde, Miriam Schenk, Mattias Dalkvist, Liam Sebestyén</t>
+          <t>Alva Danielsson, Liam Sebestyén, Mattias Dalkvist, Miriam Schenk, Fredrik Wilde, Elke Blöhbaum, Emil Lindgren</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
@@ -2331,32 +2331,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>126892810</v>
+        <v>126891131</v>
       </c>
       <c r="B18" t="n">
-        <v>91284</v>
+        <v>79052</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5447</v>
+        <v>185</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2366,13 +2366,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>672801</v>
+        <v>672898</v>
       </c>
       <c r="R18" t="n">
-        <v>7058081</v>
+        <v>7058209</v>
       </c>
       <c r="S18" t="n">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2399,39 +2399,30 @@
           <t>2025-07-24</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>11:35</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-07-24</t>
         </is>
       </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>11:35</t>
-        </is>
-      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Miriam Schenk</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist, Fredrik Wilde, Liam Sebestyén, Alva Danielsson, Elke Blöhbaum, Vilhelm Kroon, Miriam Schenk, Cajsa Björkén, Philipp Weiss, Emil Lindgren</t>
+          <t>Miriam Schenk, Cajsa Björkén, Fredrik Wilde, Philipp Weiss, Mattias Dalkvist, Vilhelm Kroon, Liam Sebestyén, Emil Lindgren, Alva Danielsson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
@@ -2442,32 +2433,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>126891131</v>
+        <v>126892810</v>
       </c>
       <c r="B19" t="n">
-        <v>79043</v>
+        <v>91297</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>185</v>
+        <v>5447</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2477,13 +2468,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>672898</v>
+        <v>672801</v>
       </c>
       <c r="R19" t="n">
-        <v>7058209</v>
+        <v>7058081</v>
       </c>
       <c r="S19" t="n">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2510,30 +2501,39 @@
           <t>2025-07-24</t>
         </is>
       </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>11:35</t>
+        </is>
+      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-07-24</t>
         </is>
       </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>11:35</t>
+        </is>
+      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Miriam Schenk</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Miriam Schenk, Cajsa Björkén, Fredrik Wilde, Philipp Weiss, Mattias Dalkvist, Vilhelm Kroon, Liam Sebestyén, Emil Lindgren, Alva Danielsson</t>
+          <t>Mattias Dalkvist, Fredrik Wilde, Liam Sebestyén, Alva Danielsson, Elke Blöhbaum, Vilhelm Kroon, Miriam Schenk, Cajsa Björkén, Philipp Weiss, Emil Lindgren</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
@@ -2547,7 +2547,7 @@
         <v>126892808</v>
       </c>
       <c r="B20" t="n">
-        <v>79011</v>
+        <v>79020</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2655,10 +2655,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>126889374</v>
+        <v>126889370</v>
       </c>
       <c r="B21" t="n">
-        <v>98457</v>
+        <v>4773</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2666,36 +2666,27 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>221952</v>
+        <v>100299</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>överblommad</t>
+          <t>(Kraatz, 1881)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -2704,10 +2695,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>672898</v>
+        <v>672839</v>
       </c>
       <c r="R21" t="n">
-        <v>7058146</v>
+        <v>7058141</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2759,7 +2750,7 @@
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Fredrik Wilde, Alva Danielsson, Emil Lindgren, Mattias Dalkvist, Elke Blöhbaum, Miriam Schenk, Vilhelm Kroon</t>
+          <t>Vilhelm Kroon, Miriam Schenk, Elke Blöhbaum, Mattias Dalkvist, Emil Lindgren, Alva Danielsson, Fredrik Wilde, Liam Sebestyén, Cajsa Björkén, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
@@ -2773,7 +2764,7 @@
         <v>126889869</v>
       </c>
       <c r="B22" t="n">
-        <v>98353</v>
+        <v>98367</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2860,7 +2851,7 @@
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Philipp Weiss, Miriam Schenk, Cajsa Björkén, Fredrik Wilde, Alva Danielsson, Elke Blöhbaum, Vilhelm Kroon, Mattias Dalkvist</t>
+          <t>Liam Sebestyén, Mattias Dalkvist, Vilhelm Kroon, Elke Blöhbaum, Alva Danielsson, Fredrik Wilde, Cajsa Björkén, Miriam Schenk, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
@@ -2871,10 +2862,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>126889311</v>
+        <v>126889374</v>
       </c>
       <c r="B23" t="n">
-        <v>91284</v>
+        <v>98471</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2882,34 +2873,48 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5447</v>
+        <v>221952</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Kravattensliden, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>672799</v>
+        <v>672898</v>
       </c>
       <c r="R23" t="n">
-        <v>7058086</v>
+        <v>7058146</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2961,7 +2966,7 @@
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Fredrik Wilde, Alva Danielsson, Emil Lindgren, Mattias Dalkvist, Elke Blöhbaum, Miriam Schenk, Vilhelm Kroon</t>
+          <t>Vilhelm Kroon, Miriam Schenk, Elke Blöhbaum, Mattias Dalkvist, Emil Lindgren, Alva Danielsson, Fredrik Wilde, Liam Sebestyén, Cajsa Björkén, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">
@@ -2972,10 +2977,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>126891314</v>
+        <v>126889311</v>
       </c>
       <c r="B24" t="n">
-        <v>80143</v>
+        <v>91297</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2983,21 +2988,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6462</v>
+        <v>5447</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3007,10 +3012,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>672999</v>
+        <v>672799</v>
       </c>
       <c r="R24" t="n">
-        <v>7058211</v>
+        <v>7058086</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3057,12 +3062,12 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Emil Lindgren, Elke Blöhbaum, Fredrik Wilde, Miriam Schenk, Mattias Dalkvist, Liam Sebestyén</t>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Fredrik Wilde, Alva Danielsson, Emil Lindgren, Mattias Dalkvist, Elke Blöhbaum, Miriam Schenk, Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr">
@@ -3073,10 +3078,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>126889370</v>
+        <v>126891314</v>
       </c>
       <c r="B25" t="n">
-        <v>4772</v>
+        <v>80152</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3084,39 +3089,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100299</v>
+        <v>6462</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Kravattensliden, Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>672839</v>
+        <v>672999</v>
       </c>
       <c r="R25" t="n">
-        <v>7058141</v>
+        <v>7058211</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3163,12 +3163,12 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon, Miriam Schenk, Elke Blöhbaum, Mattias Dalkvist, Emil Lindgren, Alva Danielsson, Fredrik Wilde, Liam Sebestyén, Cajsa Björkén, Philipp Weiss</t>
+          <t>Alva Danielsson, Liam Sebestyén, Mattias Dalkvist, Miriam Schenk, Fredrik Wilde, Elke Blöhbaum, Emil Lindgren</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr">
@@ -3179,10 +3179,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>126889502</v>
+        <v>126893730</v>
       </c>
       <c r="B26" t="n">
-        <v>79011</v>
+        <v>79020</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3214,10 +3214,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>672801</v>
+        <v>672929</v>
       </c>
       <c r="R26" t="n">
-        <v>7058095</v>
+        <v>7058213</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3264,12 +3264,12 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Fredrik Wilde, Alva Danielsson, Emil Lindgren, Mattias Dalkvist, Elke Blöhbaum, Miriam Schenk, Vilhelm Kroon</t>
+          <t>Alva Danielsson, Fredrik Wilde, Liam Sebestyén, Elke Blöhbaum, Miriam Schenk, Mattias Dalkvist, Emil Lindgren</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr">
@@ -3280,32 +3280,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>126891313</v>
+        <v>126892816</v>
       </c>
       <c r="B27" t="n">
-        <v>80143</v>
+        <v>79020</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3315,13 +3315,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>672933</v>
+        <v>672627</v>
       </c>
       <c r="R27" t="n">
-        <v>7058201</v>
+        <v>7058024</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3348,9 +3348,19 @@
           <t>2025-07-24</t>
         </is>
       </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>11:52</t>
+        </is>
+      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-07-24</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3365,12 +3375,12 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Emil Lindgren, Elke Blöhbaum, Fredrik Wilde, Miriam Schenk, Mattias Dalkvist, Liam Sebestyén</t>
+          <t>Mattias Dalkvist, Fredrik Wilde, Liam Sebestyén, Alva Danielsson, Elke Blöhbaum, Vilhelm Kroon, Miriam Schenk, Cajsa Björkén, Philipp Weiss, Emil Lindgren</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr">
@@ -3381,10 +3391,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>126889847</v>
+        <v>126889502</v>
       </c>
       <c r="B28" t="n">
-        <v>57654</v>
+        <v>79020</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3392,42 +3402,34 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Kravattensliden, Ång</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>672981</v>
+        <v>672801</v>
       </c>
       <c r="R28" t="n">
-        <v>7058264</v>
+        <v>7058095</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3474,12 +3476,12 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Philipp Weiss, Miriam Schenk, Cajsa Björkén, Fredrik Wilde, Alva Danielsson, Elke Blöhbaum, Vilhelm Kroon, Mattias Dalkvist</t>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Fredrik Wilde, Alva Danielsson, Emil Lindgren, Mattias Dalkvist, Elke Blöhbaum, Miriam Schenk, Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr">
@@ -3490,32 +3492,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>126892816</v>
+        <v>126891313</v>
       </c>
       <c r="B29" t="n">
-        <v>79011</v>
+        <v>80152</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3525,13 +3527,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>672627</v>
+        <v>672933</v>
       </c>
       <c r="R29" t="n">
-        <v>7058024</v>
+        <v>7058201</v>
       </c>
       <c r="S29" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3558,19 +3560,9 @@
           <t>2025-07-24</t>
         </is>
       </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>11:52</t>
-        </is>
-      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-07-24</t>
-        </is>
-      </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>11:52</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3585,12 +3577,12 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist, Fredrik Wilde, Liam Sebestyén, Alva Danielsson, Elke Blöhbaum, Vilhelm Kroon, Miriam Schenk, Cajsa Björkén, Philipp Weiss, Emil Lindgren</t>
+          <t>Alva Danielsson, Liam Sebestyén, Mattias Dalkvist, Miriam Schenk, Fredrik Wilde, Elke Blöhbaum, Emil Lindgren</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr">
@@ -3601,10 +3593,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>126893730</v>
+        <v>126889847</v>
       </c>
       <c r="B30" t="n">
-        <v>79011</v>
+        <v>57660</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3612,34 +3604,42 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Kravattensliden, Ång</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>672929</v>
+        <v>672981</v>
       </c>
       <c r="R30" t="n">
-        <v>7058213</v>
+        <v>7058264</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3686,12 +3686,12 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Fredrik Wilde, Liam Sebestyén, Elke Blöhbaum, Miriam Schenk, Mattias Dalkvist, Emil Lindgren</t>
+          <t>Liam Sebestyén, Mattias Dalkvist, Vilhelm Kroon, Elke Blöhbaum, Alva Danielsson, Fredrik Wilde, Cajsa Björkén, Miriam Schenk, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr">
@@ -3702,50 +3702,45 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>126889536</v>
+        <v>126891328</v>
       </c>
       <c r="B31" t="n">
-        <v>5176</v>
+        <v>79020</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100526</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Kravattensliden, Ång</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>672659</v>
+        <v>672972</v>
       </c>
       <c r="R31" t="n">
-        <v>7057975</v>
+        <v>7058246</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3792,12 +3787,12 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Fredrik Wilde, Alva Danielsson, Emil Lindgren, Mattias Dalkvist, Elke Blöhbaum, Miriam Schenk, Vilhelm Kroon</t>
+          <t>Alva Danielsson, Liam Sebestyén, Mattias Dalkvist, Miriam Schenk, Fredrik Wilde, Elke Blöhbaum, Emil Lindgren</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr">
@@ -3808,10 +3803,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>126889377</v>
+        <v>126889536</v>
       </c>
       <c r="B32" t="n">
-        <v>98457</v>
+        <v>5177</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3819,36 +3814,27 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>221952</v>
+        <v>100526</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K32" t="inlineStr">
-        <is>
-          <t>överblommad</t>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
@@ -3857,10 +3843,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>672810</v>
+        <v>672659</v>
       </c>
       <c r="R32" t="n">
-        <v>7058105</v>
+        <v>7057975</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3923,45 +3909,59 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>126891328</v>
+        <v>126889377</v>
       </c>
       <c r="B33" t="n">
-        <v>79011</v>
+        <v>98471</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>221952</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Kravattensliden, Ång</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>672972</v>
+        <v>672810</v>
       </c>
       <c r="R33" t="n">
-        <v>7058246</v>
+        <v>7058105</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4008,12 +4008,12 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Emil Lindgren, Elke Blöhbaum, Fredrik Wilde, Miriam Schenk, Mattias Dalkvist, Liam Sebestyén</t>
+          <t>Vilhelm Kroon, Miriam Schenk, Elke Blöhbaum, Mattias Dalkvist, Emil Lindgren, Alva Danielsson, Fredrik Wilde, Liam Sebestyén, Cajsa Björkén, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr">
@@ -4024,52 +4024,45 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>126893692</v>
+        <v>126889834</v>
       </c>
       <c r="B34" t="n">
-        <v>91319</v>
+        <v>91297</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Kravattensliden , Ång</t>
+          <t>Kravattensliden, Ång</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>672811</v>
+        <v>672819</v>
       </c>
       <c r="R34" t="n">
-        <v>7058091</v>
+        <v>7058089</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4110,19 +4103,18 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
-      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Emil Lindgren</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Emil Lindgren</t>
+          <t>Liam Sebestyén, Philipp Weiss, Miriam Schenk, Cajsa Björkén, Fredrik Wilde, Alva Danielsson, Elke Blöhbaum, Vilhelm Kroon, Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr">
@@ -4133,45 +4125,52 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>126889834</v>
+        <v>126893692</v>
       </c>
       <c r="B35" t="n">
-        <v>91284</v>
+        <v>91332</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Kravattensliden, Ång</t>
+          <t>Kravattensliden , Ång</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>672819</v>
+        <v>672811</v>
       </c>
       <c r="R35" t="n">
-        <v>7058089</v>
+        <v>7058091</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4212,18 +4211,19 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
+      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Emil Lindgren</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Philipp Weiss, Miriam Schenk, Cajsa Björkén, Fredrik Wilde, Alva Danielsson, Elke Blöhbaum, Vilhelm Kroon, Mattias Dalkvist</t>
+          <t>Emil Lindgren</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr">
@@ -4237,7 +4237,7 @@
         <v>126891134</v>
       </c>
       <c r="B36" t="n">
-        <v>80143</v>
+        <v>80152</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4338,7 +4338,7 @@
         <v>126892814</v>
       </c>
       <c r="B37" t="n">
-        <v>79043</v>
+        <v>79052</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4449,7 +4449,7 @@
         <v>126892813</v>
       </c>
       <c r="B38" t="n">
-        <v>79011</v>
+        <v>79020</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4560,7 +4560,7 @@
         <v>126890308</v>
       </c>
       <c r="B39" t="n">
-        <v>79011</v>
+        <v>79020</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4647,7 +4647,7 @@
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Miriam Schenk, Philipp Weiss, Mattias Dalkvist, Fredrik Wilde, Cajsa Björkén, Vilhelm Kroon, Alva Danielsson, Emil Lindgren</t>
+          <t>Vilhelm Kroon, Cajsa Björkén, Fredrik Wilde, Mattias Dalkvist, Philipp Weiss, Miriam Schenk, Liam Sebestyén, Alva Danielsson, Emil Lindgren</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr">
@@ -4661,7 +4661,7 @@
         <v>126891320</v>
       </c>
       <c r="B40" t="n">
-        <v>80114</v>
+        <v>80123</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4748,7 +4748,7 @@
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Emil Lindgren, Elke Blöhbaum, Fredrik Wilde, Miriam Schenk, Mattias Dalkvist, Liam Sebestyén</t>
+          <t>Alva Danielsson, Liam Sebestyén, Mattias Dalkvist, Miriam Schenk, Fredrik Wilde, Elke Blöhbaum, Emil Lindgren</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr">
@@ -4762,7 +4762,7 @@
         <v>126893847</v>
       </c>
       <c r="B41" t="n">
-        <v>80114</v>
+        <v>80123</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4867,7 +4867,7 @@
         <v>126880507</v>
       </c>
       <c r="B42" t="n">
-        <v>82852</v>
+        <v>82861</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4965,48 +4965,55 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>126892804</v>
+        <v>126893671</v>
       </c>
       <c r="B43" t="n">
-        <v>79011</v>
+        <v>91297</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr"/>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Kravattensliden, Ång</t>
+          <t>Kravattensliden , Ång</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>673003</v>
+        <v>672808</v>
       </c>
       <c r="R43" t="n">
-        <v>7058280</v>
+        <v>7058090</v>
       </c>
       <c r="S43" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5033,39 +5040,30 @@
           <t>2025-07-24</t>
         </is>
       </c>
-      <c r="Z43" t="inlineStr">
-        <is>
-          <t>10:49</t>
-        </is>
-      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-07-24</t>
         </is>
       </c>
-      <c r="AB43" t="inlineStr">
-        <is>
-          <t>10:49</t>
-        </is>
-      </c>
       <c r="AD43" t="b">
         <v>0</v>
       </c>
       <c r="AE43" t="b">
         <v>0</v>
       </c>
+      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Emil Lindgren</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist, Fredrik Wilde, Liam Sebestyén, Alva Danielsson, Elke Blöhbaum, Vilhelm Kroon, Miriam Schenk, Cajsa Björkén, Philipp Weiss, Emil Lindgren</t>
+          <t>Emil Lindgren</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr">
@@ -5076,10 +5074,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>126889506</v>
+        <v>126892804</v>
       </c>
       <c r="B44" t="n">
-        <v>79011</v>
+        <v>79020</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5111,13 +5109,13 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>672889</v>
+        <v>673003</v>
       </c>
       <c r="R44" t="n">
-        <v>7058145</v>
+        <v>7058280</v>
       </c>
       <c r="S44" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5144,9 +5142,19 @@
           <t>2025-07-24</t>
         </is>
       </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>10:49</t>
+        </is>
+      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-07-24</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5161,12 +5169,12 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Fredrik Wilde, Alva Danielsson, Emil Lindgren, Mattias Dalkvist, Elke Blöhbaum, Miriam Schenk, Vilhelm Kroon</t>
+          <t>Mattias Dalkvist, Fredrik Wilde, Liam Sebestyén, Alva Danielsson, Elke Blöhbaum, Vilhelm Kroon, Miriam Schenk, Cajsa Björkén, Philipp Weiss, Emil Lindgren</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr">
@@ -5177,52 +5185,45 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>126893671</v>
+        <v>126889506</v>
       </c>
       <c r="B45" t="n">
-        <v>91284</v>
+        <v>79020</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="J45" t="inlineStr"/>
-      <c r="K45" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Kravattensliden , Ång</t>
+          <t>Kravattensliden, Ång</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>672808</v>
+        <v>672889</v>
       </c>
       <c r="R45" t="n">
-        <v>7058090</v>
+        <v>7058145</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5263,19 +5264,18 @@
       <c r="AE45" t="b">
         <v>0</v>
       </c>
-      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Emil Lindgren</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Emil Lindgren</t>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Fredrik Wilde, Alva Danielsson, Emil Lindgren, Mattias Dalkvist, Elke Blöhbaum, Miriam Schenk, Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr">
@@ -5289,7 +5289,7 @@
         <v>126891321</v>
       </c>
       <c r="B46" t="n">
-        <v>80114</v>
+        <v>80123</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5376,7 +5376,7 @@
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Emil Lindgren, Elke Blöhbaum, Fredrik Wilde, Miriam Schenk, Mattias Dalkvist, Liam Sebestyén</t>
+          <t>Alva Danielsson, Liam Sebestyén, Mattias Dalkvist, Miriam Schenk, Fredrik Wilde, Elke Blöhbaum, Emil Lindgren</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr">
@@ -5387,10 +5387,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>126890305</v>
+        <v>126890311</v>
       </c>
       <c r="B47" t="n">
-        <v>79011</v>
+        <v>88735</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5398,21 +5398,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>510</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5422,10 +5422,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>672724</v>
+        <v>673023</v>
       </c>
       <c r="R47" t="n">
-        <v>7058075</v>
+        <v>7058218</v>
       </c>
       <c r="S47" t="n">
         <v>15</v>
@@ -5477,7 +5477,7 @@
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Miriam Schenk, Philipp Weiss, Mattias Dalkvist, Fredrik Wilde, Cajsa Björkén, Vilhelm Kroon, Alva Danielsson, Emil Lindgren</t>
+          <t>Vilhelm Kroon, Cajsa Björkén, Fredrik Wilde, Mattias Dalkvist, Philipp Weiss, Miriam Schenk, Liam Sebestyén, Alva Danielsson, Emil Lindgren</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr">
@@ -5488,10 +5488,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>126890311</v>
+        <v>126890305</v>
       </c>
       <c r="B48" t="n">
-        <v>88722</v>
+        <v>79020</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5499,21 +5499,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>510</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5523,10 +5523,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>673023</v>
+        <v>672724</v>
       </c>
       <c r="R48" t="n">
-        <v>7058218</v>
+        <v>7058075</v>
       </c>
       <c r="S48" t="n">
         <v>15</v>
@@ -5578,7 +5578,7 @@
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Miriam Schenk, Philipp Weiss, Mattias Dalkvist, Fredrik Wilde, Cajsa Björkén, Vilhelm Kroon, Alva Danielsson, Emil Lindgren</t>
+          <t>Vilhelm Kroon, Cajsa Björkén, Fredrik Wilde, Mattias Dalkvist, Philipp Weiss, Miriam Schenk, Liam Sebestyén, Alva Danielsson, Emil Lindgren</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr">
@@ -5592,7 +5592,7 @@
         <v>126889494</v>
       </c>
       <c r="B49" t="n">
-        <v>79011</v>
+        <v>79020</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5693,7 +5693,7 @@
         <v>126889503</v>
       </c>
       <c r="B50" t="n">
-        <v>79011</v>
+        <v>79020</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5791,10 +5791,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>126889856</v>
+        <v>126879684</v>
       </c>
       <c r="B51" t="n">
-        <v>80114</v>
+        <v>79020</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5802,34 +5802,34 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Kravattensliden, Ång</t>
+          <t>Kravattensliden, Kravattensliden, Ång</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>672929</v>
+        <v>672895</v>
       </c>
       <c r="R51" t="n">
-        <v>7058201</v>
+        <v>7058223</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5876,12 +5876,12 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Fredrik Wilde</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Philipp Weiss, Miriam Schenk, Cajsa Björkén, Fredrik Wilde, Alva Danielsson, Elke Blöhbaum, Vilhelm Kroon, Mattias Dalkvist</t>
+          <t>Fredrik Wilde</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr">
@@ -5892,32 +5892,32 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>126889837</v>
+        <v>126891325</v>
       </c>
       <c r="B52" t="n">
-        <v>91284</v>
+        <v>79020</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5927,10 +5927,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>672912</v>
+        <v>672660</v>
       </c>
       <c r="R52" t="n">
-        <v>7058191</v>
+        <v>7057985</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5977,12 +5977,12 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Philipp Weiss, Miriam Schenk, Cajsa Björkén, Fredrik Wilde, Alva Danielsson, Elke Blöhbaum, Vilhelm Kroon, Mattias Dalkvist</t>
+          <t>Alva Danielsson, Liam Sebestyén, Mattias Dalkvist, Miriam Schenk, Fredrik Wilde, Elke Blöhbaum, Emil Lindgren</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr">
@@ -5993,10 +5993,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>126889862</v>
+        <v>126889856</v>
       </c>
       <c r="B53" t="n">
-        <v>91337</v>
+        <v>80123</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6004,21 +6004,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6028,10 +6028,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>672981</v>
+        <v>672929</v>
       </c>
       <c r="R53" t="n">
-        <v>7058264</v>
+        <v>7058201</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6083,7 +6083,7 @@
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Philipp Weiss, Miriam Schenk, Cajsa Björkén, Fredrik Wilde, Alva Danielsson, Elke Blöhbaum, Vilhelm Kroon, Mattias Dalkvist</t>
+          <t>Liam Sebestyén, Mattias Dalkvist, Vilhelm Kroon, Elke Blöhbaum, Alva Danielsson, Fredrik Wilde, Cajsa Björkén, Miriam Schenk, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr">
@@ -6094,45 +6094,45 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>126879684</v>
+        <v>126893733</v>
       </c>
       <c r="B54" t="n">
-        <v>79011</v>
+        <v>98367</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>219790</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Kravattensliden, Kravattensliden, Ång</t>
+          <t>Kravattensliden, Ång</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>672895</v>
+        <v>672989</v>
       </c>
       <c r="R54" t="n">
-        <v>7058223</v>
+        <v>7058233</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6179,12 +6179,12 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Fredrik Wilde</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Fredrik Wilde</t>
+          <t>Alva Danielsson, Fredrik Wilde, Emil Lindgren, Mattias Dalkvist, Miriam Schenk, Elke Blöhbaum, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr">
@@ -6195,32 +6195,32 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>126891325</v>
+        <v>126889837</v>
       </c>
       <c r="B55" t="n">
-        <v>79011</v>
+        <v>91297</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6230,10 +6230,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>672660</v>
+        <v>672912</v>
       </c>
       <c r="R55" t="n">
-        <v>7057985</v>
+        <v>7058191</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6280,12 +6280,12 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Emil Lindgren, Elke Blöhbaum, Fredrik Wilde, Miriam Schenk, Mattias Dalkvist, Liam Sebestyén</t>
+          <t>Liam Sebestyén, Philipp Weiss, Miriam Schenk, Cajsa Björkén, Fredrik Wilde, Alva Danielsson, Elke Blöhbaum, Vilhelm Kroon, Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr">
@@ -6296,32 +6296,32 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>126893733</v>
+        <v>126889862</v>
       </c>
       <c r="B56" t="n">
-        <v>98353</v>
+        <v>91350</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>219790</v>
+        <v>5432</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6331,10 +6331,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>672989</v>
+        <v>672981</v>
       </c>
       <c r="R56" t="n">
-        <v>7058233</v>
+        <v>7058264</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6381,12 +6381,12 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Fredrik Wilde, Liam Sebestyén, Elke Blöhbaum, Miriam Schenk, Mattias Dalkvist, Emil Lindgren</t>
+          <t>Liam Sebestyén, Mattias Dalkvist, Vilhelm Kroon, Elke Blöhbaum, Alva Danielsson, Fredrik Wilde, Cajsa Björkén, Miriam Schenk, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr">
@@ -6400,7 +6400,7 @@
         <v>126879133</v>
       </c>
       <c r="B57" t="n">
-        <v>79043</v>
+        <v>79052</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6501,7 +6501,7 @@
         <v>126892806</v>
       </c>
       <c r="B58" t="n">
-        <v>79011</v>
+        <v>79020</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6612,7 +6612,7 @@
         <v>126889504</v>
       </c>
       <c r="B59" t="n">
-        <v>79011</v>
+        <v>79020</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6710,32 +6710,32 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>126892812</v>
+        <v>126890296</v>
       </c>
       <c r="B60" t="n">
-        <v>79011</v>
+        <v>80152</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6745,13 +6745,13 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>672685</v>
+        <v>673025</v>
       </c>
       <c r="R60" t="n">
-        <v>7058010</v>
+        <v>7058244</v>
       </c>
       <c r="S60" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -6778,19 +6778,9 @@
           <t>2025-07-24</t>
         </is>
       </c>
-      <c r="Z60" t="inlineStr">
-        <is>
-          <t>11:41</t>
-        </is>
-      </c>
       <c r="AA60" t="inlineStr">
         <is>
           <t>2025-07-24</t>
-        </is>
-      </c>
-      <c r="AB60" t="inlineStr">
-        <is>
-          <t>11:41</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6805,12 +6795,12 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist, Fredrik Wilde, Liam Sebestyén, Alva Danielsson, Elke Blöhbaum, Vilhelm Kroon, Miriam Schenk, Cajsa Björkén, Philipp Weiss, Emil Lindgren</t>
+          <t>Vilhelm Kroon, Cajsa Björkén, Fredrik Wilde, Mattias Dalkvist, Philipp Weiss, Miriam Schenk, Liam Sebestyén, Alva Danielsson, Emil Lindgren</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr">
@@ -6821,10 +6811,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>126892809</v>
+        <v>126892812</v>
       </c>
       <c r="B61" t="n">
-        <v>79011</v>
+        <v>79020</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6856,13 +6846,13 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>672831</v>
+        <v>672685</v>
       </c>
       <c r="R61" t="n">
-        <v>7058091</v>
+        <v>7058010</v>
       </c>
       <c r="S61" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -6891,7 +6881,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -6901,7 +6891,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -6932,48 +6922,53 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>126890296</v>
+        <v>126880199</v>
       </c>
       <c r="B62" t="n">
-        <v>80143</v>
+        <v>79020</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Kravattensliden, Ång</t>
+          <t>Kravattensliden, Kravattensliden, Ång</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>673025</v>
+        <v>672894</v>
       </c>
       <c r="R62" t="n">
-        <v>7058244</v>
+        <v>7058198</v>
       </c>
       <c r="S62" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7017,12 +7012,12 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Fredrik Wilde</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon, Cajsa Björkén, Fredrik Wilde, Mattias Dalkvist, Philipp Weiss, Miriam Schenk, Liam Sebestyén, Alva Danielsson, Emil Lindgren</t>
+          <t>Fredrik Wilde</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr">
@@ -7033,10 +7028,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>126880199</v>
+        <v>126892809</v>
       </c>
       <c r="B63" t="n">
-        <v>79011</v>
+        <v>79020</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7062,24 +7057,19 @@
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
-      <c r="K63" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Kravattensliden, Kravattensliden, Ång</t>
+          <t>Kravattensliden, Ång</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>672894</v>
+        <v>672831</v>
       </c>
       <c r="R63" t="n">
-        <v>7058198</v>
+        <v>7058091</v>
       </c>
       <c r="S63" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7106,9 +7096,19 @@
           <t>2025-07-24</t>
         </is>
       </c>
+      <c r="Z63" t="inlineStr">
+        <is>
+          <t>11:32</t>
+        </is>
+      </c>
       <c r="AA63" t="inlineStr">
         <is>
           <t>2025-07-24</t>
+        </is>
+      </c>
+      <c r="AB63" t="inlineStr">
+        <is>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7123,12 +7123,12 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Fredrik Wilde</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Fredrik Wilde</t>
+          <t>Mattias Dalkvist, Fredrik Wilde, Liam Sebestyén, Alva Danielsson, Elke Blöhbaum, Vilhelm Kroon, Miriam Schenk, Cajsa Björkén, Philipp Weiss, Emil Lindgren</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr">
@@ -7142,7 +7142,7 @@
         <v>126879033</v>
       </c>
       <c r="B64" t="n">
-        <v>79043</v>
+        <v>79052</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7252,7 +7252,7 @@
         <v>126891312</v>
       </c>
       <c r="B65" t="n">
-        <v>91284</v>
+        <v>91297</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7339,7 +7339,7 @@
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Emil Lindgren, Elke Blöhbaum, Fredrik Wilde, Miriam Schenk, Mattias Dalkvist, Liam Sebestyén</t>
+          <t>Alva Danielsson, Liam Sebestyén, Mattias Dalkvist, Miriam Schenk, Fredrik Wilde, Elke Blöhbaum, Emil Lindgren</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr">
@@ -7353,7 +7353,7 @@
         <v>126879425</v>
       </c>
       <c r="B66" t="n">
-        <v>79011</v>
+        <v>79020</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7454,7 +7454,7 @@
         <v>126880532</v>
       </c>
       <c r="B67" t="n">
-        <v>80143</v>
+        <v>80152</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7555,7 +7555,7 @@
         <v>126889382</v>
       </c>
       <c r="B68" t="n">
-        <v>57654</v>
+        <v>57660</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7647,7 +7647,7 @@
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Fredrik Wilde, Alva Danielsson, Emil Lindgren, Mattias Dalkvist, Elke Blöhbaum, Miriam Schenk, Vilhelm Kroon</t>
+          <t>Vilhelm Kroon, Miriam Schenk, Elke Blöhbaum, Mattias Dalkvist, Emil Lindgren, Alva Danielsson, Fredrik Wilde, Liam Sebestyén, Cajsa Björkén, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr">
@@ -7658,32 +7658,32 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>126890401</v>
+        <v>126890370</v>
       </c>
       <c r="B69" t="n">
-        <v>79011</v>
+        <v>80152</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7693,10 +7693,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>672705</v>
+        <v>672554</v>
       </c>
       <c r="R69" t="n">
-        <v>7058080</v>
+        <v>7058145</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7759,10 +7759,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>126890408</v>
+        <v>126890401</v>
       </c>
       <c r="B70" t="n">
-        <v>79011</v>
+        <v>79020</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7794,10 +7794,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>672874</v>
+        <v>672705</v>
       </c>
       <c r="R70" t="n">
-        <v>7058313</v>
+        <v>7058080</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7860,32 +7860,32 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>126890370</v>
+        <v>126890408</v>
       </c>
       <c r="B71" t="n">
-        <v>80143</v>
+        <v>79020</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7895,10 +7895,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>672554</v>
+        <v>672874</v>
       </c>
       <c r="R71" t="n">
-        <v>7058145</v>
+        <v>7058313</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7964,7 +7964,7 @@
         <v>126890405</v>
       </c>
       <c r="B72" t="n">
-        <v>79011</v>
+        <v>79020</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8065,7 +8065,7 @@
         <v>126890409</v>
       </c>
       <c r="B73" t="n">
-        <v>79011</v>
+        <v>79020</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8163,10 +8163,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>126890407</v>
+        <v>126890387</v>
       </c>
       <c r="B74" t="n">
-        <v>79011</v>
+        <v>80123</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8174,21 +8174,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8198,10 +8198,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>672859</v>
+        <v>672556</v>
       </c>
       <c r="R74" t="n">
-        <v>7058290</v>
+        <v>7058143</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8264,10 +8264,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>126890387</v>
+        <v>126890407</v>
       </c>
       <c r="B75" t="n">
-        <v>80114</v>
+        <v>79020</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8275,21 +8275,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8299,10 +8299,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>672556</v>
+        <v>672859</v>
       </c>
       <c r="R75" t="n">
-        <v>7058143</v>
+        <v>7058290</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8365,10 +8365,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>126890404</v>
+        <v>126890354</v>
       </c>
       <c r="B76" t="n">
-        <v>79011</v>
+        <v>79052</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8376,21 +8376,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8400,10 +8400,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>672805</v>
+        <v>672891</v>
       </c>
       <c r="R76" t="n">
-        <v>7058312</v>
+        <v>7058285</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8466,10 +8466,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>126890354</v>
+        <v>126890404</v>
       </c>
       <c r="B77" t="n">
-        <v>79043</v>
+        <v>79020</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8477,21 +8477,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8501,10 +8501,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>672891</v>
+        <v>672805</v>
       </c>
       <c r="R77" t="n">
-        <v>7058285</v>
+        <v>7058312</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8570,7 +8570,7 @@
         <v>126890353</v>
       </c>
       <c r="B78" t="n">
-        <v>79043</v>
+        <v>79052</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8671,7 +8671,7 @@
         <v>126890349</v>
       </c>
       <c r="B79" t="n">
-        <v>79043</v>
+        <v>79052</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8772,7 +8772,7 @@
         <v>126890348</v>
       </c>
       <c r="B80" t="n">
-        <v>79043</v>
+        <v>79052</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8873,7 +8873,7 @@
         <v>126890351</v>
       </c>
       <c r="B81" t="n">
-        <v>79043</v>
+        <v>79052</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8974,7 +8974,7 @@
         <v>126890350</v>
       </c>
       <c r="B82" t="n">
-        <v>79043</v>
+        <v>79052</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9075,7 +9075,7 @@
         <v>126890416</v>
       </c>
       <c r="B83" t="n">
-        <v>80149</v>
+        <v>80158</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9173,10 +9173,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>126890403</v>
+        <v>126890352</v>
       </c>
       <c r="B84" t="n">
-        <v>79011</v>
+        <v>79052</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9184,21 +9184,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9208,10 +9208,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>672796</v>
+        <v>672847</v>
       </c>
       <c r="R84" t="n">
-        <v>7058317</v>
+        <v>7058276</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9274,10 +9274,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>126890352</v>
+        <v>126890403</v>
       </c>
       <c r="B85" t="n">
-        <v>79043</v>
+        <v>79020</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9285,21 +9285,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9309,10 +9309,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>672847</v>
+        <v>672796</v>
       </c>
       <c r="R85" t="n">
-        <v>7058276</v>
+        <v>7058317</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
